--- a/docs/Chiraath-Summary-Jun26.xlsx
+++ b/docs/Chiraath-Summary-Jun26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C3C544-097E-9847-9546-7C8070CBA08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D71F876-72BD-6A4B-B550-68B68D9082B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">INVENTORY!$A$1:$T$188</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Purchases!$A$1:$D$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$209</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2352" uniqueCount="943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2387" uniqueCount="956">
   <si>
     <t>Notes:</t>
   </si>
@@ -1190,9 +1190,6 @@
   </si>
   <si>
     <t>Silpa Kannur</t>
-  </si>
-  <si>
-    <t>Matka Green/Yellow &amp; Bengal Cotton (Adv:100)</t>
   </si>
   <si>
     <t>Aji Roy(Trichue)</t>
@@ -2853,15 +2850,6 @@
     <t>Chanderi Silk Saree (Rani Pink- CHR-119)</t>
   </si>
   <si>
-    <t>First Set: Aruna - violet, Resmi - navy blue, Malini - Rani Pink
-Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-New batch: Blue (2), mustard yellow (1), navy blue (3), Green (2), Rani pink (2), Maroon (2), off white (2), Orange (1)
-New batch2: Black(6), White(5)</t>
-  </si>
-  <si>
     <t>Rose</t>
   </si>
   <si>
@@ -2897,6 +2885,56 @@
   </si>
   <si>
     <t>Matka (royal blue/rani pink-CHR-179), Soft Silk Saree (Navy Blue-CHR-175)</t>
+  </si>
+  <si>
+    <t>Bindu Krishnaraj</t>
+  </si>
+  <si>
+    <t>Kavitha</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree (off white - CHR-119)</t>
+  </si>
+  <si>
+    <t>Jisa Suresh (Anita)</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree (Rani Pink(2)- CHR-119)</t>
+  </si>
+  <si>
+    <t>Sudharma</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree (Navy Blue- CHR-119)</t>
+  </si>
+  <si>
+    <t>P K Sopitha (Sindrella)</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree (Maroon - CHR-119)</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Matka Green/Yellow &amp; Bengal Cotton (Adv:1100)</t>
+  </si>
+  <si>
+    <t>Simi Sudhir</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree (Navy Blue- CHR-119) &amp; Kerala Saree Temple Design</t>
+  </si>
+  <si>
+    <t>Revathi, Simi Sudhir</t>
+  </si>
+  <si>
+    <t>First Set: Aruna - violet, Resmi - navy blue, Malini - Rani Pink
+Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black, Bindu Krisharaj - Black, Kavitha - off white, Jisha Suresh - Rani Pink(2), Sudharma - Navy Blue, SIndrella - Maroon, Unknown - Navy blue, Simi Sudhir - Navy Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Blue (2), mustard yellow (1), Green (2), Maroon (1), off white (1), Orange (1), Black(5), White(5)</t>
   </si>
 </sst>
 </file>
@@ -3809,7 +3847,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>195</c:v>
+                  <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>86</c:v>
@@ -3912,7 +3950,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>77</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>59</c:v>
@@ -4245,7 +4283,7 @@
                   <c:v>61609</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>49408.796666666662</c:v>
+                  <c:v>45010.17</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1357</c:v>
@@ -4735,7 +4773,7 @@
                   <c:v>53524</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>7046</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5175,7 +5213,7 @@
                   <c:v>49075</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>7046</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5642,10 +5680,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>284</c:v>
+                  <c:v>293</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>140</c:v>
+                  <c:v>131</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6832,7 +6870,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>334418</v>
+        <v>341464</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -6849,7 +6887,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>356272</v>
+        <v>363318</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -6866,7 +6904,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-20324</v>
+        <v>-13278</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -7078,15 +7116,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>276319</v>
+        <v>283365</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>111494.96119999999</v>
+        <v>113844.09759999999</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>164824.03880000001</v>
+        <v>169520.90240000002</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -7094,11 +7132,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>27514.012799999997</v>
+        <v>32210.876400000008</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹27,514</v>
+        <v>Pay ₹32,211</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -7112,11 +7150,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>111428.0776</v>
+        <v>113775.8048</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-65859.077600000004</v>
+        <v>-68206.804799999998</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -7124,11 +7162,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>5727.9643999999971</v>
+        <v>3380.2372000000032</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹5,728</v>
+        <v>Pay ₹3,380</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -7142,11 +7180,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>111494.96119999999</v>
+        <v>113844.09759999999</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-98964.961199999991</v>
+        <v>-101314.09759999999</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -7154,11 +7192,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-33241.977199999979</v>
+        <v>-35591.113599999982</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹33,242</v>
+        <v>Receive ₹35,591</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -7270,7 +7308,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46176</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -7286,7 +7324,7 @@
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>334418</v>
+        <v>341464</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7295,14 +7333,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-20324</v>
+        <v>-13278</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>103070.99666666664</v>
+        <v>98672.37</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -7354,7 +7392,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>284</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7378,7 +7416,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>140</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7442,11 +7480,11 @@
       </c>
       <c r="C15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>0</v>
+        <v>7046</v>
       </c>
       <c r="D15" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7046</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
@@ -7574,11 +7612,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -7605,7 +7643,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>49408.796666666662</v>
+        <v>45010.17</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -14640,7 +14678,7 @@
       <c r="F149" s="49"/>
       <c r="G149" s="49"/>
       <c r="H149" s="51" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="I149" s="49" t="s">
         <v>142</v>
@@ -14913,7 +14951,7 @@
       <c r="F160" s="56"/>
       <c r="G160" s="56"/>
       <c r="H160" s="57" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="I160" s="53" t="s">
         <v>341</v>
@@ -15105,7 +15143,7 @@
       <c r="F168" s="49"/>
       <c r="G168" s="49"/>
       <c r="H168" s="51" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="I168" s="49" t="s">
         <v>341</v>
@@ -15401,7 +15439,7 @@
       <c r="F180" s="49"/>
       <c r="G180" s="49"/>
       <c r="H180" s="51" t="s">
-        <v>381</v>
+        <v>950</v>
       </c>
       <c r="I180" s="49" t="s">
         <v>341</v>
@@ -15412,7 +15450,7 @@
         <v>46141</v>
       </c>
       <c r="B181" s="53" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C181" s="54">
         <v>1380</v>
@@ -15426,7 +15464,7 @@
       <c r="F181" s="56"/>
       <c r="G181" s="56"/>
       <c r="H181" s="57" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I181" s="53" t="s">
         <v>142</v>
@@ -15437,7 +15475,7 @@
         <v>46141</v>
       </c>
       <c r="B182" s="49" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C182" s="50">
         <v>690</v>
@@ -15462,7 +15500,7 @@
         <v>46142</v>
       </c>
       <c r="B183" s="53" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C183" s="54">
         <v>690</v>
@@ -15476,7 +15514,7 @@
       <c r="F183" s="56"/>
       <c r="G183" s="56"/>
       <c r="H183" s="57" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I183" s="53" t="s">
         <v>142</v>
@@ -15487,7 +15525,7 @@
         <v>46142</v>
       </c>
       <c r="B184" s="49" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C184" s="50">
         <v>690</v>
@@ -15512,7 +15550,7 @@
         <v>46142</v>
       </c>
       <c r="B185" s="53" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C185" s="54">
         <v>609</v>
@@ -15526,7 +15564,7 @@
       <c r="F185" s="56"/>
       <c r="G185" s="56"/>
       <c r="H185" s="57" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I185" s="53" t="s">
         <v>142</v>
@@ -15537,7 +15575,7 @@
         <v>46144</v>
       </c>
       <c r="B186" s="53" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C186" s="54">
         <v>699</v>
@@ -15551,7 +15589,7 @@
       <c r="F186" s="56"/>
       <c r="G186" s="56"/>
       <c r="H186" s="57" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I186" s="53" t="s">
         <v>142</v>
@@ -15562,7 +15600,7 @@
         <v>46144</v>
       </c>
       <c r="B187" s="49" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C187" s="50">
         <v>690</v>
@@ -15576,7 +15614,7 @@
       <c r="F187" s="49"/>
       <c r="G187" s="49"/>
       <c r="H187" s="51" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I187" s="49" t="s">
         <v>142</v>
@@ -15587,7 +15625,7 @@
         <v>46145</v>
       </c>
       <c r="B188" s="53" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C188" s="54">
         <v>1200</v>
@@ -15601,7 +15639,7 @@
       <c r="F188" s="56"/>
       <c r="G188" s="56"/>
       <c r="H188" s="57" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I188" s="53" t="s">
         <v>142</v>
@@ -15612,7 +15650,7 @@
         <v>46145</v>
       </c>
       <c r="B189" s="49" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C189" s="50">
         <v>1200</v>
@@ -15626,7 +15664,7 @@
       <c r="F189" s="49"/>
       <c r="G189" s="49"/>
       <c r="H189" s="51" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I189" s="49" t="s">
         <v>142</v>
@@ -15651,7 +15689,7 @@
       <c r="F190" s="56"/>
       <c r="G190" s="56"/>
       <c r="H190" s="57" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I190" s="53" t="s">
         <v>142</v>
@@ -15662,7 +15700,7 @@
         <v>46151</v>
       </c>
       <c r="B191" s="49" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C191" s="50">
         <v>5600</v>
@@ -15676,7 +15714,7 @@
       <c r="F191" s="49"/>
       <c r="G191" s="49"/>
       <c r="H191" s="51" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I191" s="49" t="s">
         <v>142</v>
@@ -15687,7 +15725,7 @@
         <v>46152</v>
       </c>
       <c r="B192" s="53" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C192" s="54">
         <v>5600</v>
@@ -15701,7 +15739,7 @@
       <c r="F192" s="56"/>
       <c r="G192" s="56"/>
       <c r="H192" s="57" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I192" s="53" t="s">
         <v>142</v>
@@ -15712,7 +15750,7 @@
         <v>46152</v>
       </c>
       <c r="B193" s="49" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C193" s="50">
         <v>5600</v>
@@ -15726,7 +15764,7 @@
       <c r="F193" s="49"/>
       <c r="G193" s="49"/>
       <c r="H193" s="51" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I193" s="49" t="s">
         <v>142</v>
@@ -15737,7 +15775,7 @@
         <v>46151</v>
       </c>
       <c r="B194" s="53" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C194" s="54">
         <v>3000</v>
@@ -15747,7 +15785,7 @@
       <c r="F194" s="56"/>
       <c r="G194" s="56"/>
       <c r="H194" s="57" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I194" s="53" t="s">
         <v>341</v>
@@ -15758,7 +15796,7 @@
         <v>46155</v>
       </c>
       <c r="B195" s="49" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C195" s="50">
         <v>5400</v>
@@ -15772,7 +15810,7 @@
       <c r="F195" s="49"/>
       <c r="G195" s="49"/>
       <c r="H195" s="51" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I195" s="49" t="s">
         <v>142</v>
@@ -15783,7 +15821,7 @@
         <v>46155</v>
       </c>
       <c r="B196" s="53" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C196" s="54">
         <v>5750</v>
@@ -15797,7 +15835,7 @@
       <c r="F196" s="56"/>
       <c r="G196" s="56"/>
       <c r="H196" s="57" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I196" s="53" t="s">
         <v>142</v>
@@ -15822,7 +15860,7 @@
       <c r="F197" s="49"/>
       <c r="G197" s="49"/>
       <c r="H197" s="51" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I197" s="49" t="s">
         <v>142</v>
@@ -15833,7 +15871,7 @@
         <v>46168</v>
       </c>
       <c r="B198" s="53" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C198" s="54">
         <v>5200</v>
@@ -15847,7 +15885,7 @@
       <c r="F198" s="56"/>
       <c r="G198" s="56"/>
       <c r="H198" s="57" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="I198" s="53" t="s">
         <v>142</v>
@@ -15858,7 +15896,7 @@
         <v>46172</v>
       </c>
       <c r="B199" s="49" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C199" s="50">
         <v>1425</v>
@@ -15872,7 +15910,7 @@
       <c r="F199" s="49"/>
       <c r="G199" s="49"/>
       <c r="H199" s="51" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I199" s="49" t="s">
         <v>341</v>
@@ -15883,7 +15921,7 @@
         <v>46173</v>
       </c>
       <c r="B200" s="53" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="C200" s="54">
         <v>2850</v>
@@ -15897,7 +15935,7 @@
       <c r="F200" s="56"/>
       <c r="G200" s="56"/>
       <c r="H200" s="57" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="I200" s="53" t="s">
         <v>341</v>
@@ -15908,7 +15946,7 @@
         <v>46173</v>
       </c>
       <c r="B201" s="49" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="C201" s="50">
         <v>2850</v>
@@ -15922,7 +15960,7 @@
       <c r="F201" s="49"/>
       <c r="G201" s="49"/>
       <c r="H201" s="51" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="I201" s="49" t="s">
         <v>341</v>
@@ -15933,7 +15971,7 @@
         <v>46173</v>
       </c>
       <c r="B202" s="53" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C202" s="54">
         <v>930</v>
@@ -15947,7 +15985,7 @@
       <c r="F202" s="56"/>
       <c r="G202" s="56"/>
       <c r="H202" s="57" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I202" s="53" t="s">
         <v>341</v>
@@ -15958,7 +15996,7 @@
         <v>46173</v>
       </c>
       <c r="B203" s="49" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="C203" s="50">
         <v>930</v>
@@ -15972,88 +16010,186 @@
       <c r="F203" s="49"/>
       <c r="G203" s="49"/>
       <c r="H203" s="51" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="I203" s="49" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="204" spans="1:9">
-      <c r="A204" s="52"/>
-      <c r="B204" s="53"/>
-      <c r="C204" s="54"/>
-      <c r="D204" s="53"/>
-      <c r="E204" s="53"/>
+    <row r="204" spans="1:9" ht="14">
+      <c r="A204" s="52">
+        <v>46175</v>
+      </c>
+      <c r="B204" s="53" t="s">
+        <v>940</v>
+      </c>
+      <c r="C204" s="54">
+        <v>699</v>
+      </c>
+      <c r="D204" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E204" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F204" s="56"/>
       <c r="G204" s="56"/>
-      <c r="H204" s="57"/>
-      <c r="I204" s="53"/>
-    </row>
-    <row r="205" spans="1:9">
-      <c r="A205" s="48"/>
-      <c r="B205" s="49"/>
-      <c r="C205" s="50"/>
-      <c r="D205" s="49"/>
-      <c r="E205" s="49"/>
+      <c r="H204" s="57" t="s">
+        <v>930</v>
+      </c>
+      <c r="I204" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" ht="14">
+      <c r="A205" s="48">
+        <v>46175</v>
+      </c>
+      <c r="B205" s="49" t="s">
+        <v>941</v>
+      </c>
+      <c r="C205" s="50">
+        <v>700</v>
+      </c>
+      <c r="D205" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E205" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F205" s="49"/>
       <c r="G205" s="49"/>
-      <c r="H205" s="51"/>
-      <c r="I205" s="49"/>
-    </row>
-    <row r="206" spans="1:9">
-      <c r="A206" s="52"/>
-      <c r="B206" s="53"/>
-      <c r="C206" s="54"/>
-      <c r="D206" s="53"/>
-      <c r="E206" s="53"/>
+      <c r="H205" s="51" t="s">
+        <v>942</v>
+      </c>
+      <c r="I205" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" ht="14">
+      <c r="A206" s="52">
+        <v>46175</v>
+      </c>
+      <c r="B206" s="53" t="s">
+        <v>943</v>
+      </c>
+      <c r="C206" s="54">
+        <v>1350</v>
+      </c>
+      <c r="D206" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E206" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F206" s="56"/>
       <c r="G206" s="56"/>
-      <c r="H206" s="57"/>
-      <c r="I206" s="53"/>
-    </row>
-    <row r="207" spans="1:9">
-      <c r="A207" s="48"/>
-      <c r="B207" s="49"/>
-      <c r="C207" s="50"/>
-      <c r="D207" s="49"/>
-      <c r="E207" s="49"/>
+      <c r="H206" s="51" t="s">
+        <v>944</v>
+      </c>
+      <c r="I206" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" ht="14">
+      <c r="A207" s="48">
+        <v>46175</v>
+      </c>
+      <c r="B207" s="49" t="s">
+        <v>945</v>
+      </c>
+      <c r="C207" s="50">
+        <v>699</v>
+      </c>
+      <c r="D207" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E207" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F207" s="49"/>
       <c r="G207" s="49"/>
-      <c r="H207" s="51"/>
-      <c r="I207" s="49"/>
-    </row>
-    <row r="208" spans="1:9">
-      <c r="A208" s="52"/>
-      <c r="B208" s="53"/>
-      <c r="C208" s="54"/>
-      <c r="D208" s="53"/>
-      <c r="E208" s="53"/>
+      <c r="H207" s="51" t="s">
+        <v>946</v>
+      </c>
+      <c r="I207" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" ht="14">
+      <c r="A208" s="52">
+        <v>46175</v>
+      </c>
+      <c r="B208" s="53" t="s">
+        <v>947</v>
+      </c>
+      <c r="C208" s="54">
+        <v>699</v>
+      </c>
+      <c r="D208" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E208" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F208" s="56"/>
       <c r="G208" s="56"/>
-      <c r="H208" s="57"/>
-      <c r="I208" s="53"/>
-    </row>
-    <row r="209" spans="1:9">
-      <c r="A209" s="48"/>
-      <c r="B209" s="49"/>
-      <c r="C209" s="50"/>
-      <c r="D209" s="49"/>
-      <c r="E209" s="49"/>
+      <c r="H208" s="57" t="s">
+        <v>948</v>
+      </c>
+      <c r="I208" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" ht="14">
+      <c r="A209" s="48">
+        <v>46176</v>
+      </c>
+      <c r="B209" s="49" t="s">
+        <v>949</v>
+      </c>
+      <c r="C209" s="50">
+        <v>699</v>
+      </c>
+      <c r="D209" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E209" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F209" s="49"/>
       <c r="G209" s="49"/>
-      <c r="H209" s="51"/>
-      <c r="I209" s="49"/>
-    </row>
-    <row r="210" spans="1:9">
-      <c r="A210" s="52"/>
-      <c r="B210" s="53"/>
-      <c r="C210" s="54"/>
-      <c r="D210" s="53"/>
-      <c r="E210" s="53"/>
+      <c r="H209" s="51" t="s">
+        <v>946</v>
+      </c>
+      <c r="I209" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" ht="28">
+      <c r="A210" s="52">
+        <v>46176</v>
+      </c>
+      <c r="B210" s="53" t="s">
+        <v>951</v>
+      </c>
+      <c r="C210" s="54">
+        <v>2200</v>
+      </c>
+      <c r="D210" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E210" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F210" s="56"/>
       <c r="G210" s="56"/>
-      <c r="H210" s="57"/>
-      <c r="I210" s="53"/>
+      <c r="H210" s="57" t="s">
+        <v>952</v>
+      </c>
+      <c r="I210" s="53" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="211" spans="1:9">
       <c r="A211" s="48"/>
@@ -16603,7 +16739,7 @@
       <c r="I260" s="59"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I197" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:I209" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1260" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Ordered,Pending,Completed,Cancelled"</formula1>
@@ -16645,19 +16781,19 @@
   <sheetData>
     <row r="1" spans="1:246" s="65" customFormat="1" ht="33.75" customHeight="1">
       <c r="A1" s="63" t="s">
+        <v>411</v>
+      </c>
+      <c r="B1" s="63" t="s">
         <v>412</v>
-      </c>
-      <c r="B1" s="63" t="s">
-        <v>413</v>
       </c>
       <c r="C1" s="63" t="s">
         <v>93</v>
       </c>
       <c r="D1" s="63" t="s">
+        <v>413</v>
+      </c>
+      <c r="E1" s="63" t="s">
         <v>414</v>
-      </c>
-      <c r="E1" s="63" t="s">
-        <v>415</v>
       </c>
       <c r="F1" s="63" t="s">
         <v>80</v>
@@ -16666,19 +16802,19 @@
         <v>82</v>
       </c>
       <c r="H1" s="63" t="s">
+        <v>415</v>
+      </c>
+      <c r="I1" s="63" t="s">
         <v>416</v>
       </c>
-      <c r="I1" s="63" t="s">
+      <c r="J1" s="63" t="s">
         <v>417</v>
       </c>
-      <c r="J1" s="63" t="s">
+      <c r="K1" s="63" t="s">
         <v>418</v>
       </c>
-      <c r="K1" s="63" t="s">
+      <c r="L1" s="63" t="s">
         <v>419</v>
-      </c>
-      <c r="L1" s="63" t="s">
-        <v>420</v>
       </c>
       <c r="M1" s="63" t="s">
         <v>135</v>
@@ -16696,13 +16832,13 @@
         <v>138</v>
       </c>
       <c r="R1" s="63" t="s">
+        <v>420</v>
+      </c>
+      <c r="S1" s="63" t="s">
         <v>421</v>
       </c>
-      <c r="S1" s="63" t="s">
+      <c r="T1" s="63" t="s">
         <v>422</v>
-      </c>
-      <c r="T1" s="63" t="s">
-        <v>423</v>
       </c>
       <c r="U1" s="64"/>
       <c r="V1" s="64"/>
@@ -16933,10 +17069,10 @@
     </row>
     <row r="2" spans="1:246" s="68" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="66" t="s">
+        <v>423</v>
+      </c>
+      <c r="B2" s="66" t="s">
         <v>424</v>
-      </c>
-      <c r="B2" s="66" t="s">
-        <v>425</v>
       </c>
       <c r="C2" s="66" t="s">
         <v>95</v>
@@ -16976,7 +17112,7 @@
         <v>49</v>
       </c>
       <c r="N2" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O2" s="66"/>
       <c r="P2" s="66"/>
@@ -17213,10 +17349,10 @@
     </row>
     <row r="3" spans="1:246" ht="15" customHeight="1">
       <c r="A3" s="69" t="s">
+        <v>426</v>
+      </c>
+      <c r="B3" s="69" t="s">
         <v>427</v>
-      </c>
-      <c r="B3" s="69" t="s">
-        <v>428</v>
       </c>
       <c r="C3" s="69" t="s">
         <v>95</v>
@@ -17256,7 +17392,7 @@
         <v>49</v>
       </c>
       <c r="N3" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O3" s="69"/>
       <c r="P3" s="69"/>
@@ -17267,10 +17403,10 @@
     </row>
     <row r="4" spans="1:246" ht="15" customHeight="1">
       <c r="A4" s="66" t="s">
+        <v>428</v>
+      </c>
+      <c r="B4" s="66" t="s">
         <v>429</v>
-      </c>
-      <c r="B4" s="66" t="s">
-        <v>430</v>
       </c>
       <c r="C4" s="66" t="s">
         <v>95</v>
@@ -17310,7 +17446,7 @@
         <v>49</v>
       </c>
       <c r="N4" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O4" s="66"/>
       <c r="P4" s="66"/>
@@ -17321,10 +17457,10 @@
     </row>
     <row r="5" spans="1:246" ht="15" customHeight="1">
       <c r="A5" s="69" t="s">
+        <v>430</v>
+      </c>
+      <c r="B5" s="69" t="s">
         <v>431</v>
-      </c>
-      <c r="B5" s="69" t="s">
-        <v>432</v>
       </c>
       <c r="C5" s="69" t="s">
         <v>95</v>
@@ -17364,7 +17500,7 @@
         <v>49</v>
       </c>
       <c r="N5" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O5" s="69"/>
       <c r="P5" s="69"/>
@@ -17375,10 +17511,10 @@
     </row>
     <row r="6" spans="1:246" ht="15" customHeight="1">
       <c r="A6" s="66" t="s">
+        <v>432</v>
+      </c>
+      <c r="B6" s="66" t="s">
         <v>433</v>
-      </c>
-      <c r="B6" s="66" t="s">
-        <v>434</v>
       </c>
       <c r="C6" s="66" t="s">
         <v>95</v>
@@ -17412,13 +17548,13 @@
         <v>0</v>
       </c>
       <c r="L6" s="66" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M6" s="66" t="s">
         <v>49</v>
       </c>
       <c r="N6" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O6" s="66"/>
       <c r="P6" s="66"/>
@@ -17429,10 +17565,10 @@
     </row>
     <row r="7" spans="1:246" ht="15" customHeight="1">
       <c r="A7" s="69" t="s">
+        <v>435</v>
+      </c>
+      <c r="B7" s="69" t="s">
         <v>436</v>
-      </c>
-      <c r="B7" s="69" t="s">
-        <v>437</v>
       </c>
       <c r="C7" s="69" t="s">
         <v>95</v>
@@ -17472,7 +17608,7 @@
         <v>49</v>
       </c>
       <c r="N7" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O7" s="69"/>
       <c r="P7" s="69"/>
@@ -17483,10 +17619,10 @@
     </row>
     <row r="8" spans="1:246" ht="15" customHeight="1">
       <c r="A8" s="66" t="s">
+        <v>437</v>
+      </c>
+      <c r="B8" s="66" t="s">
         <v>438</v>
-      </c>
-      <c r="B8" s="66" t="s">
-        <v>439</v>
       </c>
       <c r="C8" s="66" t="s">
         <v>95</v>
@@ -17526,7 +17662,7 @@
         <v>49</v>
       </c>
       <c r="N8" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O8" s="66"/>
       <c r="P8" s="66"/>
@@ -17537,10 +17673,10 @@
     </row>
     <row r="9" spans="1:246" ht="15" customHeight="1">
       <c r="A9" s="69" t="s">
+        <v>439</v>
+      </c>
+      <c r="B9" s="69" t="s">
         <v>440</v>
-      </c>
-      <c r="B9" s="69" t="s">
-        <v>441</v>
       </c>
       <c r="C9" s="69" t="s">
         <v>96</v>
@@ -17580,7 +17716,7 @@
         <v>49</v>
       </c>
       <c r="N9" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O9" s="69"/>
       <c r="P9" s="69"/>
@@ -17591,10 +17727,10 @@
     </row>
     <row r="10" spans="1:246" ht="15" customHeight="1">
       <c r="A10" s="66" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C10" s="66" t="s">
         <v>95</v>
@@ -17634,7 +17770,7 @@
         <v>49</v>
       </c>
       <c r="N10" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O10" s="66"/>
       <c r="P10" s="66"/>
@@ -17645,10 +17781,10 @@
     </row>
     <row r="11" spans="1:246" ht="15" customHeight="1">
       <c r="A11" s="69" t="s">
+        <v>442</v>
+      </c>
+      <c r="B11" s="69" t="s">
         <v>443</v>
-      </c>
-      <c r="B11" s="69" t="s">
-        <v>444</v>
       </c>
       <c r="C11" s="69" t="s">
         <v>95</v>
@@ -17682,13 +17818,13 @@
         <v>0</v>
       </c>
       <c r="L11" s="69" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M11" s="69" t="s">
         <v>49</v>
       </c>
       <c r="N11" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O11" s="69"/>
       <c r="P11" s="69"/>
@@ -17699,10 +17835,10 @@
     </row>
     <row r="12" spans="1:246" ht="15" customHeight="1">
       <c r="A12" s="66" t="s">
+        <v>445</v>
+      </c>
+      <c r="B12" s="66" t="s">
         <v>446</v>
-      </c>
-      <c r="B12" s="66" t="s">
-        <v>447</v>
       </c>
       <c r="C12" s="66" t="s">
         <v>96</v>
@@ -17742,7 +17878,7 @@
         <v>49</v>
       </c>
       <c r="N12" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O12" s="66"/>
       <c r="P12" s="66"/>
@@ -17753,10 +17889,10 @@
     </row>
     <row r="13" spans="1:246" ht="15" customHeight="1">
       <c r="A13" s="69" t="s">
+        <v>447</v>
+      </c>
+      <c r="B13" s="69" t="s">
         <v>448</v>
-      </c>
-      <c r="B13" s="69" t="s">
-        <v>449</v>
       </c>
       <c r="C13" s="69" t="s">
         <v>96</v>
@@ -17796,7 +17932,7 @@
         <v>49</v>
       </c>
       <c r="N13" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O13" s="69"/>
       <c r="P13" s="69"/>
@@ -17807,10 +17943,10 @@
     </row>
     <row r="14" spans="1:246" ht="15" customHeight="1">
       <c r="A14" s="66" t="s">
+        <v>449</v>
+      </c>
+      <c r="B14" s="66" t="s">
         <v>450</v>
-      </c>
-      <c r="B14" s="66" t="s">
-        <v>451</v>
       </c>
       <c r="C14" s="66" t="s">
         <v>96</v>
@@ -17850,7 +17986,7 @@
         <v>49</v>
       </c>
       <c r="N14" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O14" s="66"/>
       <c r="P14" s="66"/>
@@ -17861,10 +17997,10 @@
     </row>
     <row r="15" spans="1:246" ht="15" customHeight="1">
       <c r="A15" s="69" t="s">
+        <v>451</v>
+      </c>
+      <c r="B15" s="69" t="s">
         <v>452</v>
-      </c>
-      <c r="B15" s="69" t="s">
-        <v>453</v>
       </c>
       <c r="C15" s="69" t="s">
         <v>96</v>
@@ -17904,7 +18040,7 @@
         <v>49</v>
       </c>
       <c r="N15" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O15" s="69"/>
       <c r="P15" s="69"/>
@@ -17915,10 +18051,10 @@
     </row>
     <row r="16" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="66" t="s">
+        <v>453</v>
+      </c>
+      <c r="B16" s="66" t="s">
         <v>454</v>
-      </c>
-      <c r="B16" s="66" t="s">
-        <v>455</v>
       </c>
       <c r="C16" s="66" t="s">
         <v>96</v>
@@ -17958,7 +18094,7 @@
         <v>49</v>
       </c>
       <c r="N16" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O16" s="66"/>
       <c r="P16" s="66"/>
@@ -18195,10 +18331,10 @@
     </row>
     <row r="17" spans="1:246" ht="15" customHeight="1">
       <c r="A17" s="69" t="s">
+        <v>455</v>
+      </c>
+      <c r="B17" s="69" t="s">
         <v>456</v>
-      </c>
-      <c r="B17" s="69" t="s">
-        <v>457</v>
       </c>
       <c r="C17" s="69" t="s">
         <v>95</v>
@@ -18238,7 +18374,7 @@
         <v>49</v>
       </c>
       <c r="N17" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O17" s="69"/>
       <c r="P17" s="69"/>
@@ -18249,10 +18385,10 @@
     </row>
     <row r="18" spans="1:246" ht="15" customHeight="1">
       <c r="A18" s="66" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B18" s="66" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C18" s="66" t="s">
         <v>95</v>
@@ -18292,7 +18428,7 @@
         <v>49</v>
       </c>
       <c r="N18" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O18" s="66"/>
       <c r="P18" s="66"/>
@@ -18303,10 +18439,10 @@
     </row>
     <row r="19" spans="1:246" ht="15" customHeight="1">
       <c r="A19" s="69" t="s">
+        <v>458</v>
+      </c>
+      <c r="B19" s="69" t="s">
         <v>459</v>
-      </c>
-      <c r="B19" s="69" t="s">
-        <v>460</v>
       </c>
       <c r="C19" s="69" t="s">
         <v>96</v>
@@ -18346,7 +18482,7 @@
         <v>49</v>
       </c>
       <c r="N19" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O19" s="69"/>
       <c r="P19" s="69"/>
@@ -18357,10 +18493,10 @@
     </row>
     <row r="20" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="66" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B20" s="66" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C20" s="66" t="s">
         <v>96</v>
@@ -18400,7 +18536,7 @@
         <v>49</v>
       </c>
       <c r="N20" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O20" s="66"/>
       <c r="P20" s="66"/>
@@ -18637,10 +18773,10 @@
     </row>
     <row r="21" spans="1:246" ht="15" customHeight="1">
       <c r="A21" s="69" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B21" s="69" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C21" s="69" t="s">
         <v>96</v>
@@ -18680,7 +18816,7 @@
         <v>49</v>
       </c>
       <c r="N21" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O21" s="69"/>
       <c r="P21" s="69"/>
@@ -18691,10 +18827,10 @@
     </row>
     <row r="22" spans="1:246" ht="15" customHeight="1">
       <c r="A22" s="66" t="s">
+        <v>462</v>
+      </c>
+      <c r="B22" s="66" t="s">
         <v>463</v>
-      </c>
-      <c r="B22" s="66" t="s">
-        <v>464</v>
       </c>
       <c r="C22" s="66" t="s">
         <v>95</v>
@@ -18734,7 +18870,7 @@
         <v>49</v>
       </c>
       <c r="N22" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O22" s="66"/>
       <c r="P22" s="66"/>
@@ -18745,7 +18881,7 @@
     </row>
     <row r="23" spans="1:246" ht="15" customHeight="1">
       <c r="A23" s="69" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B23" s="69" t="s">
         <v>109</v>
@@ -18782,13 +18918,13 @@
         <v>0</v>
       </c>
       <c r="L23" s="69" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="M23" s="69" t="s">
         <v>49</v>
       </c>
       <c r="N23" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O23" s="69"/>
       <c r="P23" s="69"/>
@@ -18799,10 +18935,10 @@
     </row>
     <row r="24" spans="1:246" ht="15" customHeight="1">
       <c r="A24" s="66" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B24" s="66" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C24" s="66" t="s">
         <v>95</v>
@@ -18842,7 +18978,7 @@
         <v>49</v>
       </c>
       <c r="N24" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O24" s="66"/>
       <c r="P24" s="66"/>
@@ -18853,10 +18989,10 @@
     </row>
     <row r="25" spans="1:246" ht="15" customHeight="1">
       <c r="A25" s="69" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B25" s="69" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C25" s="69" t="s">
         <v>95</v>
@@ -18896,7 +19032,7 @@
         <v>49</v>
       </c>
       <c r="N25" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O25" s="69"/>
       <c r="P25" s="69"/>
@@ -18907,10 +19043,10 @@
     </row>
     <row r="26" spans="1:246" ht="15" customHeight="1">
       <c r="A26" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="B26" s="66" t="s">
         <v>469</v>
-      </c>
-      <c r="B26" s="66" t="s">
-        <v>470</v>
       </c>
       <c r="C26" s="66" t="s">
         <v>95</v>
@@ -18950,7 +19086,7 @@
         <v>49</v>
       </c>
       <c r="N26" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O26" s="66"/>
       <c r="P26" s="66"/>
@@ -18961,10 +19097,10 @@
     </row>
     <row r="27" spans="1:246" ht="15" customHeight="1">
       <c r="A27" s="69" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B27" s="69" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C27" s="69" t="s">
         <v>95</v>
@@ -19004,7 +19140,7 @@
         <v>49</v>
       </c>
       <c r="N27" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O27" s="69"/>
       <c r="P27" s="69"/>
@@ -19015,10 +19151,10 @@
     </row>
     <row r="28" spans="1:246" ht="15" customHeight="1">
       <c r="A28" s="66" t="s">
+        <v>471</v>
+      </c>
+      <c r="B28" s="66" t="s">
         <v>472</v>
-      </c>
-      <c r="B28" s="66" t="s">
-        <v>473</v>
       </c>
       <c r="C28" s="66" t="s">
         <v>95</v>
@@ -19058,7 +19194,7 @@
         <v>49</v>
       </c>
       <c r="N28" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O28" s="66"/>
       <c r="P28" s="66"/>
@@ -19069,10 +19205,10 @@
     </row>
     <row r="29" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="69" t="s">
+        <v>473</v>
+      </c>
+      <c r="B29" s="69" t="s">
         <v>474</v>
-      </c>
-      <c r="B29" s="69" t="s">
-        <v>475</v>
       </c>
       <c r="C29" s="69" t="s">
         <v>96</v>
@@ -19112,7 +19248,7 @@
         <v>49</v>
       </c>
       <c r="N29" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O29" s="69"/>
       <c r="P29" s="69"/>
@@ -19349,10 +19485,10 @@
     </row>
     <row r="30" spans="1:246" ht="15" customHeight="1">
       <c r="A30" s="66" t="s">
+        <v>475</v>
+      </c>
+      <c r="B30" s="66" t="s">
         <v>476</v>
-      </c>
-      <c r="B30" s="66" t="s">
-        <v>477</v>
       </c>
       <c r="C30" s="66" t="s">
         <v>95</v>
@@ -19392,7 +19528,7 @@
         <v>49</v>
       </c>
       <c r="N30" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O30" s="66"/>
       <c r="P30" s="66"/>
@@ -19403,10 +19539,10 @@
     </row>
     <row r="31" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="69" t="s">
+        <v>477</v>
+      </c>
+      <c r="B31" s="69" t="s">
         <v>478</v>
-      </c>
-      <c r="B31" s="69" t="s">
-        <v>479</v>
       </c>
       <c r="C31" s="69" t="s">
         <v>96</v>
@@ -19446,7 +19582,7 @@
         <v>49</v>
       </c>
       <c r="N31" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O31" s="69"/>
       <c r="P31" s="69"/>
@@ -19683,10 +19819,10 @@
     </row>
     <row r="32" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="66" t="s">
+        <v>479</v>
+      </c>
+      <c r="B32" s="66" t="s">
         <v>480</v>
-      </c>
-      <c r="B32" s="66" t="s">
-        <v>481</v>
       </c>
       <c r="C32" s="66" t="s">
         <v>96</v>
@@ -19726,7 +19862,7 @@
         <v>49</v>
       </c>
       <c r="N32" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O32" s="66"/>
       <c r="P32" s="66"/>
@@ -19963,10 +20099,10 @@
     </row>
     <row r="33" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="69" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B33" s="69" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C33" s="69" t="s">
         <v>96</v>
@@ -20006,7 +20142,7 @@
         <v>49</v>
       </c>
       <c r="N33" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O33" s="69"/>
       <c r="P33" s="69"/>
@@ -20243,10 +20379,10 @@
     </row>
     <row r="34" spans="1:246" ht="15" customHeight="1">
       <c r="A34" s="66" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B34" s="66" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C34" s="66" t="s">
         <v>95</v>
@@ -20286,7 +20422,7 @@
         <v>49</v>
       </c>
       <c r="N34" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O34" s="66"/>
       <c r="P34" s="66"/>
@@ -20297,10 +20433,10 @@
     </row>
     <row r="35" spans="1:246" ht="15" customHeight="1">
       <c r="A35" s="69" t="s">
+        <v>483</v>
+      </c>
+      <c r="B35" s="69" t="s">
         <v>484</v>
-      </c>
-      <c r="B35" s="69" t="s">
-        <v>485</v>
       </c>
       <c r="C35" s="69" t="s">
         <v>95</v>
@@ -20340,7 +20476,7 @@
         <v>49</v>
       </c>
       <c r="N35" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O35" s="69"/>
       <c r="P35" s="69"/>
@@ -20351,10 +20487,10 @@
     </row>
     <row r="36" spans="1:246" ht="15" customHeight="1">
       <c r="A36" s="66" t="s">
+        <v>485</v>
+      </c>
+      <c r="B36" s="66" t="s">
         <v>486</v>
-      </c>
-      <c r="B36" s="66" t="s">
-        <v>487</v>
       </c>
       <c r="C36" s="66" t="s">
         <v>95</v>
@@ -20394,7 +20530,7 @@
         <v>49</v>
       </c>
       <c r="N36" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O36" s="66"/>
       <c r="P36" s="66"/>
@@ -20405,10 +20541,10 @@
     </row>
     <row r="37" spans="1:246" ht="15" customHeight="1">
       <c r="A37" s="69" t="s">
+        <v>487</v>
+      </c>
+      <c r="B37" s="69" t="s">
         <v>488</v>
-      </c>
-      <c r="B37" s="69" t="s">
-        <v>489</v>
       </c>
       <c r="C37" s="69" t="s">
         <v>96</v>
@@ -20448,7 +20584,7 @@
         <v>49</v>
       </c>
       <c r="N37" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O37" s="69"/>
       <c r="P37" s="69"/>
@@ -20459,10 +20595,10 @@
     </row>
     <row r="38" spans="1:246" ht="15" customHeight="1">
       <c r="A38" s="66" t="s">
+        <v>489</v>
+      </c>
+      <c r="B38" s="66" t="s">
         <v>490</v>
-      </c>
-      <c r="B38" s="66" t="s">
-        <v>491</v>
       </c>
       <c r="C38" s="66" t="s">
         <v>95</v>
@@ -20502,7 +20638,7 @@
         <v>49</v>
       </c>
       <c r="N38" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O38" s="66"/>
       <c r="P38" s="66"/>
@@ -20513,10 +20649,10 @@
     </row>
     <row r="39" spans="1:246" ht="15" customHeight="1">
       <c r="A39" s="69" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B39" s="69" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C39" s="69" t="s">
         <v>96</v>
@@ -20556,7 +20692,7 @@
         <v>49</v>
       </c>
       <c r="N39" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O39" s="69"/>
       <c r="P39" s="69"/>
@@ -20567,10 +20703,10 @@
     </row>
     <row r="40" spans="1:246" ht="15" customHeight="1">
       <c r="A40" s="66" t="s">
+        <v>492</v>
+      </c>
+      <c r="B40" s="66" t="s">
         <v>493</v>
-      </c>
-      <c r="B40" s="66" t="s">
-        <v>494</v>
       </c>
       <c r="C40" s="66" t="s">
         <v>96</v>
@@ -20610,7 +20746,7 @@
         <v>49</v>
       </c>
       <c r="N40" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O40" s="66"/>
       <c r="P40" s="66"/>
@@ -20621,10 +20757,10 @@
     </row>
     <row r="41" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A41" s="69" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B41" s="69" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C41" s="69" t="s">
         <v>95</v>
@@ -20664,7 +20800,7 @@
         <v>49</v>
       </c>
       <c r="N41" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O41" s="69"/>
       <c r="P41" s="69"/>
@@ -20901,10 +21037,10 @@
     </row>
     <row r="42" spans="1:246" ht="15" customHeight="1">
       <c r="A42" s="66" t="s">
+        <v>495</v>
+      </c>
+      <c r="B42" s="66" t="s">
         <v>496</v>
-      </c>
-      <c r="B42" s="66" t="s">
-        <v>497</v>
       </c>
       <c r="C42" s="66" t="s">
         <v>96</v>
@@ -20944,7 +21080,7 @@
         <v>49</v>
       </c>
       <c r="N42" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O42" s="66"/>
       <c r="P42" s="66"/>
@@ -20955,10 +21091,10 @@
     </row>
     <row r="43" spans="1:246" ht="15" customHeight="1">
       <c r="A43" s="69" t="s">
+        <v>497</v>
+      </c>
+      <c r="B43" s="69" t="s">
         <v>498</v>
-      </c>
-      <c r="B43" s="69" t="s">
-        <v>499</v>
       </c>
       <c r="C43" s="69" t="s">
         <v>96</v>
@@ -20998,7 +21134,7 @@
         <v>49</v>
       </c>
       <c r="N43" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O43" s="69"/>
       <c r="P43" s="69"/>
@@ -21009,10 +21145,10 @@
     </row>
     <row r="44" spans="1:246" ht="15" customHeight="1">
       <c r="A44" s="66" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B44" s="66" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C44" s="66" t="s">
         <v>96</v>
@@ -21046,20 +21182,20 @@
         <v>0</v>
       </c>
       <c r="L44" s="66" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="M44" s="66" t="s">
         <v>49</v>
       </c>
       <c r="N44" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O44" s="66" t="s">
         <v>210</v>
       </c>
       <c r="P44" s="66"/>
       <c r="Q44" s="66" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="R44" s="66"/>
       <c r="S44" s="66"/>
@@ -21067,10 +21203,10 @@
     </row>
     <row r="45" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A45" s="69" t="s">
+        <v>502</v>
+      </c>
+      <c r="B45" s="69" t="s">
         <v>503</v>
-      </c>
-      <c r="B45" s="69" t="s">
-        <v>504</v>
       </c>
       <c r="C45" s="69" t="s">
         <v>95</v>
@@ -21110,7 +21246,7 @@
         <v>49</v>
       </c>
       <c r="N45" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O45" s="69"/>
       <c r="P45" s="69"/>
@@ -21347,10 +21483,10 @@
     </row>
     <row r="46" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A46" s="66" t="s">
+        <v>504</v>
+      </c>
+      <c r="B46" s="66" t="s">
         <v>505</v>
-      </c>
-      <c r="B46" s="66" t="s">
-        <v>506</v>
       </c>
       <c r="C46" s="66" t="s">
         <v>95</v>
@@ -21390,7 +21526,7 @@
         <v>49</v>
       </c>
       <c r="N46" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O46" s="66"/>
       <c r="P46" s="66"/>
@@ -21627,10 +21763,10 @@
     </row>
     <row r="47" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A47" s="69" t="s">
+        <v>506</v>
+      </c>
+      <c r="B47" s="69" t="s">
         <v>507</v>
-      </c>
-      <c r="B47" s="69" t="s">
-        <v>508</v>
       </c>
       <c r="C47" s="69" t="s">
         <v>95</v>
@@ -21664,13 +21800,13 @@
         <v>1094</v>
       </c>
       <c r="L47" s="69" t="s">
+        <v>508</v>
+      </c>
+      <c r="M47" s="69" t="s">
         <v>509</v>
       </c>
-      <c r="M47" s="69" t="s">
+      <c r="N47" s="69" t="s">
         <v>510</v>
-      </c>
-      <c r="N47" s="69" t="s">
-        <v>511</v>
       </c>
       <c r="O47" s="69"/>
       <c r="P47" s="69"/>
@@ -21907,10 +22043,10 @@
     </row>
     <row r="48" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A48" s="66" t="s">
+        <v>511</v>
+      </c>
+      <c r="B48" s="66" t="s">
         <v>512</v>
-      </c>
-      <c r="B48" s="66" t="s">
-        <v>513</v>
       </c>
       <c r="C48" s="66" t="s">
         <v>95</v>
@@ -21950,7 +22086,7 @@
         <v>49</v>
       </c>
       <c r="N48" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O48" s="66"/>
       <c r="P48" s="66"/>
@@ -22187,10 +22323,10 @@
     </row>
     <row r="49" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A49" s="69" t="s">
+        <v>513</v>
+      </c>
+      <c r="B49" s="69" t="s">
         <v>514</v>
-      </c>
-      <c r="B49" s="69" t="s">
-        <v>515</v>
       </c>
       <c r="C49" s="69" t="s">
         <v>95</v>
@@ -22230,11 +22366,11 @@
         <v>49</v>
       </c>
       <c r="N49" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O49" s="69"/>
       <c r="P49" s="69" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="Q49" s="69"/>
       <c r="R49" s="69"/>
@@ -22469,10 +22605,10 @@
     </row>
     <row r="50" spans="1:246" ht="15" customHeight="1">
       <c r="A50" s="66" t="s">
+        <v>516</v>
+      </c>
+      <c r="B50" s="66" t="s">
         <v>517</v>
-      </c>
-      <c r="B50" s="66" t="s">
-        <v>518</v>
       </c>
       <c r="C50" s="66" t="s">
         <v>96</v>
@@ -22512,7 +22648,7 @@
         <v>49</v>
       </c>
       <c r="N50" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O50" s="66"/>
       <c r="P50" s="66"/>
@@ -22523,10 +22659,10 @@
     </row>
     <row r="51" spans="1:246" ht="15" customHeight="1">
       <c r="A51" s="69" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B51" s="69" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C51" s="69" t="s">
         <v>96</v>
@@ -22566,7 +22702,7 @@
         <v>49</v>
       </c>
       <c r="N51" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O51" s="69"/>
       <c r="P51" s="69"/>
@@ -22577,7 +22713,7 @@
     </row>
     <row r="52" spans="1:246" ht="15" customHeight="1">
       <c r="A52" s="66" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B52" s="66" t="s">
         <v>292</v>
@@ -22614,17 +22750,17 @@
         <v>2400</v>
       </c>
       <c r="L52" s="66" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="M52" s="66"/>
       <c r="N52" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O52" s="66" t="s">
+        <v>521</v>
+      </c>
+      <c r="P52" s="66" t="s">
         <v>522</v>
-      </c>
-      <c r="P52" s="66" t="s">
-        <v>523</v>
       </c>
       <c r="Q52" s="66"/>
       <c r="R52" s="66"/>
@@ -22633,7 +22769,7 @@
     </row>
     <row r="53" spans="1:246" ht="15" customHeight="1">
       <c r="A53" s="69" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B53" s="69" t="s">
         <v>290</v>
@@ -22670,7 +22806,7 @@
         <v>1941</v>
       </c>
       <c r="L53" s="69" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="M53" s="69"/>
       <c r="N53" s="69" t="s">
@@ -22680,7 +22816,7 @@
         <v>223</v>
       </c>
       <c r="P53" s="69" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="Q53" s="69"/>
       <c r="R53" s="69"/>
@@ -22689,10 +22825,10 @@
     </row>
     <row r="54" spans="1:246" s="76" customFormat="1" ht="15" customHeight="1">
       <c r="A54" s="66" t="s">
+        <v>526</v>
+      </c>
+      <c r="B54" s="73" t="s">
         <v>527</v>
-      </c>
-      <c r="B54" s="73" t="s">
-        <v>528</v>
       </c>
       <c r="C54" s="73" t="s">
         <v>96</v>
@@ -22734,10 +22870,10 @@
         <v>201</v>
       </c>
       <c r="P54" s="73" t="s">
+        <v>528</v>
+      </c>
+      <c r="Q54" s="66" t="s">
         <v>529</v>
-      </c>
-      <c r="Q54" s="66" t="s">
-        <v>530</v>
       </c>
       <c r="R54" s="73"/>
       <c r="S54" s="73"/>
@@ -22971,10 +23107,10 @@
     </row>
     <row r="55" spans="1:246" ht="15" customHeight="1">
       <c r="A55" s="69" t="s">
+        <v>530</v>
+      </c>
+      <c r="B55" s="69" t="s">
         <v>531</v>
-      </c>
-      <c r="B55" s="69" t="s">
-        <v>532</v>
       </c>
       <c r="C55" s="69" t="s">
         <v>96</v>
@@ -23008,13 +23144,13 @@
         <v>995</v>
       </c>
       <c r="L55" s="69" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="M55" s="69" t="s">
         <v>49</v>
       </c>
       <c r="N55" s="69" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O55" s="69" t="s">
         <v>201</v>
@@ -23027,10 +23163,10 @@
     </row>
     <row r="56" spans="1:246" ht="15" customHeight="1">
       <c r="A56" s="66" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B56" s="66" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C56" s="66" t="s">
         <v>96</v>
@@ -23070,10 +23206,10 @@
         <v>49</v>
       </c>
       <c r="N56" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O56" s="66" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="P56" s="66"/>
       <c r="Q56" s="66"/>
@@ -23083,10 +23219,10 @@
     </row>
     <row r="57" spans="1:246" ht="15" customHeight="1">
       <c r="A57" s="69" t="s">
+        <v>535</v>
+      </c>
+      <c r="B57" s="69" t="s">
         <v>536</v>
-      </c>
-      <c r="B57" s="69" t="s">
-        <v>537</v>
       </c>
       <c r="C57" s="69" t="s">
         <v>96</v>
@@ -23125,7 +23261,7 @@
         <v>341</v>
       </c>
       <c r="O57" s="69" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="P57" s="69"/>
       <c r="Q57" s="69"/>
@@ -23135,10 +23271,10 @@
     </row>
     <row r="58" spans="1:246" ht="15" customHeight="1">
       <c r="A58" s="66" t="s">
+        <v>538</v>
+      </c>
+      <c r="B58" s="66" t="s">
         <v>539</v>
-      </c>
-      <c r="B58" s="66" t="s">
-        <v>540</v>
       </c>
       <c r="C58" s="66" t="s">
         <v>96</v>
@@ -23177,7 +23313,7 @@
         <v>341</v>
       </c>
       <c r="O58" s="66" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="P58" s="66"/>
       <c r="Q58" s="66"/>
@@ -23187,10 +23323,10 @@
     </row>
     <row r="59" spans="1:246" ht="15" customHeight="1">
       <c r="A59" s="69" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B59" s="69" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C59" s="69" t="s">
         <v>96</v>
@@ -23224,17 +23360,17 @@
         <v>2290</v>
       </c>
       <c r="L59" s="69" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M59" s="69"/>
       <c r="N59" s="69" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O59" s="69" t="s">
+        <v>543</v>
+      </c>
+      <c r="P59" s="69" t="s">
         <v>544</v>
-      </c>
-      <c r="P59" s="69" t="s">
-        <v>545</v>
       </c>
       <c r="Q59" s="69"/>
       <c r="R59" s="69"/>
@@ -23243,10 +23379,10 @@
     </row>
     <row r="60" spans="1:246" ht="15" customHeight="1">
       <c r="A60" s="66" t="s">
+        <v>545</v>
+      </c>
+      <c r="B60" s="66" t="s">
         <v>546</v>
-      </c>
-      <c r="B60" s="66" t="s">
-        <v>547</v>
       </c>
       <c r="C60" s="66" t="s">
         <v>96</v>
@@ -23280,17 +23416,17 @@
         <v>1080</v>
       </c>
       <c r="L60" s="66" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="M60" s="66" t="s">
         <v>49</v>
       </c>
       <c r="N60" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O60" s="66"/>
       <c r="P60" s="66" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q60" s="66"/>
       <c r="R60" s="66"/>
@@ -23299,10 +23435,10 @@
     </row>
     <row r="61" spans="1:246" ht="45" customHeight="1">
       <c r="A61" s="69" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B61" s="69" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C61" s="69" t="s">
         <v>96</v>
@@ -23336,20 +23472,20 @@
         <v>4384</v>
       </c>
       <c r="L61" s="69" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M61" s="69"/>
       <c r="N61" s="69" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O61" s="69" t="s">
+        <v>551</v>
+      </c>
+      <c r="P61" s="69" t="s">
         <v>552</v>
       </c>
-      <c r="P61" s="69" t="s">
+      <c r="Q61" s="69" t="s">
         <v>553</v>
-      </c>
-      <c r="Q61" s="69" t="s">
-        <v>554</v>
       </c>
       <c r="R61" s="69"/>
       <c r="S61" s="69"/>
@@ -23357,7 +23493,7 @@
     </row>
     <row r="62" spans="1:246" ht="15" customHeight="1">
       <c r="A62" s="66" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B62" s="66" t="s">
         <v>109</v>
@@ -23394,11 +23530,11 @@
         <v>0</v>
       </c>
       <c r="L62" s="66" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="M62" s="66"/>
       <c r="N62" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O62" s="66"/>
       <c r="P62" s="66"/>
@@ -23409,10 +23545,10 @@
     </row>
     <row r="63" spans="1:246" ht="15" customHeight="1">
       <c r="A63" s="69" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B63" s="69" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C63" s="69" t="s">
         <v>95</v>
@@ -23450,7 +23586,7 @@
       </c>
       <c r="M63" s="69"/>
       <c r="N63" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O63" s="69"/>
       <c r="P63" s="69"/>
@@ -23461,10 +23597,10 @@
     </row>
     <row r="64" spans="1:246" ht="15" customHeight="1">
       <c r="A64" s="66" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B64" s="66" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C64" s="66" t="s">
         <v>95</v>
@@ -23502,7 +23638,7 @@
       </c>
       <c r="M64" s="66"/>
       <c r="N64" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O64" s="66"/>
       <c r="P64" s="66"/>
@@ -23513,10 +23649,10 @@
     </row>
     <row r="65" spans="1:20" ht="15" customHeight="1">
       <c r="A65" s="69" t="s">
+        <v>557</v>
+      </c>
+      <c r="B65" s="69" t="s">
         <v>558</v>
-      </c>
-      <c r="B65" s="69" t="s">
-        <v>559</v>
       </c>
       <c r="C65" s="69" t="s">
         <v>95</v>
@@ -23550,11 +23686,11 @@
         <v>0</v>
       </c>
       <c r="L65" s="69" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="M65" s="69"/>
       <c r="N65" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O65" s="69"/>
       <c r="P65" s="69"/>
@@ -23565,10 +23701,10 @@
     </row>
     <row r="66" spans="1:20" ht="15" customHeight="1">
       <c r="A66" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="B66" s="66" t="s">
         <v>561</v>
-      </c>
-      <c r="B66" s="66" t="s">
-        <v>562</v>
       </c>
       <c r="C66" s="66" t="s">
         <v>95</v>
@@ -23602,11 +23738,11 @@
         <v>1558</v>
       </c>
       <c r="L66" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M66" s="66"/>
       <c r="N66" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O66" s="66"/>
       <c r="P66" s="66"/>
@@ -23617,10 +23753,10 @@
     </row>
     <row r="67" spans="1:20" ht="15" customHeight="1">
       <c r="A67" s="69" t="s">
+        <v>563</v>
+      </c>
+      <c r="B67" s="69" t="s">
         <v>564</v>
-      </c>
-      <c r="B67" s="69" t="s">
-        <v>565</v>
       </c>
       <c r="C67" s="69" t="s">
         <v>95</v>
@@ -23656,7 +23792,7 @@
       <c r="L67" s="69"/>
       <c r="M67" s="69"/>
       <c r="N67" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O67" s="69"/>
       <c r="P67" s="69"/>
@@ -23667,10 +23803,10 @@
     </row>
     <row r="68" spans="1:20" ht="15" customHeight="1">
       <c r="A68" s="66" t="s">
+        <v>565</v>
+      </c>
+      <c r="B68" s="66" t="s">
         <v>566</v>
-      </c>
-      <c r="B68" s="66" t="s">
-        <v>567</v>
       </c>
       <c r="C68" s="66" t="s">
         <v>95</v>
@@ -23704,15 +23840,15 @@
         <v>685</v>
       </c>
       <c r="L68" s="66" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="M68" s="66"/>
       <c r="N68" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O68" s="66"/>
       <c r="P68" s="66" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="Q68" s="66"/>
       <c r="R68" s="66"/>
@@ -23721,10 +23857,10 @@
     </row>
     <row r="69" spans="1:20" ht="15" customHeight="1">
       <c r="A69" s="69" t="s">
+        <v>569</v>
+      </c>
+      <c r="B69" s="69" t="s">
         <v>570</v>
-      </c>
-      <c r="B69" s="69" t="s">
-        <v>571</v>
       </c>
       <c r="C69" s="69" t="s">
         <v>96</v>
@@ -23763,7 +23899,7 @@
         <v>341</v>
       </c>
       <c r="O69" s="69" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="P69" s="69"/>
       <c r="Q69" s="69"/>
@@ -23773,10 +23909,10 @@
     </row>
     <row r="70" spans="1:20" ht="15" customHeight="1">
       <c r="A70" s="66" t="s">
+        <v>572</v>
+      </c>
+      <c r="B70" s="66" t="s">
         <v>573</v>
-      </c>
-      <c r="B70" s="66" t="s">
-        <v>574</v>
       </c>
       <c r="C70" s="66" t="s">
         <v>95</v>
@@ -23810,11 +23946,11 @@
         <v>0</v>
       </c>
       <c r="L70" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="M70" s="66"/>
       <c r="N70" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O70" s="66"/>
       <c r="P70" s="66"/>
@@ -23825,10 +23961,10 @@
     </row>
     <row r="71" spans="1:20" ht="15" customHeight="1">
       <c r="A71" s="69" t="s">
+        <v>575</v>
+      </c>
+      <c r="B71" s="69" t="s">
         <v>576</v>
-      </c>
-      <c r="B71" s="69" t="s">
-        <v>577</v>
       </c>
       <c r="C71" s="69" t="s">
         <v>95</v>
@@ -23862,17 +23998,17 @@
         <v>0</v>
       </c>
       <c r="L71" s="69" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="M71" s="69" t="s">
         <v>49</v>
       </c>
       <c r="N71" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O71" s="69"/>
       <c r="P71" s="69" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="Q71" s="69"/>
       <c r="R71" s="69"/>
@@ -23881,10 +24017,10 @@
     </row>
     <row r="72" spans="1:20" ht="15" customHeight="1">
       <c r="A72" s="66" t="s">
+        <v>579</v>
+      </c>
+      <c r="B72" s="66" t="s">
         <v>580</v>
-      </c>
-      <c r="B72" s="66" t="s">
-        <v>581</v>
       </c>
       <c r="C72" s="66" t="s">
         <v>95</v>
@@ -23922,7 +24058,7 @@
       </c>
       <c r="M72" s="66"/>
       <c r="N72" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O72" s="66"/>
       <c r="P72" s="66"/>
@@ -23933,10 +24069,10 @@
     </row>
     <row r="73" spans="1:20" ht="15" customHeight="1">
       <c r="A73" s="69" t="s">
+        <v>581</v>
+      </c>
+      <c r="B73" s="69" t="s">
         <v>582</v>
-      </c>
-      <c r="B73" s="69" t="s">
-        <v>583</v>
       </c>
       <c r="C73" s="69" t="s">
         <v>96</v>
@@ -23974,7 +24110,7 @@
       </c>
       <c r="M73" s="69"/>
       <c r="N73" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O73" s="69"/>
       <c r="P73" s="69"/>
@@ -23985,10 +24121,10 @@
     </row>
     <row r="74" spans="1:20" ht="15" customHeight="1">
       <c r="A74" s="66" t="s">
+        <v>583</v>
+      </c>
+      <c r="B74" s="66" t="s">
         <v>584</v>
-      </c>
-      <c r="B74" s="66" t="s">
-        <v>585</v>
       </c>
       <c r="C74" s="66" t="s">
         <v>95</v>
@@ -24028,7 +24164,7 @@
         <v>49</v>
       </c>
       <c r="N74" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O74" s="66"/>
       <c r="P74" s="66"/>
@@ -24039,10 +24175,10 @@
     </row>
     <row r="75" spans="1:20" ht="15" customHeight="1">
       <c r="A75" s="69" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B75" s="69" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C75" s="69" t="s">
         <v>96</v>
@@ -24082,7 +24218,7 @@
         <v>49</v>
       </c>
       <c r="N75" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O75" s="69"/>
       <c r="P75" s="69"/>
@@ -24093,10 +24229,10 @@
     </row>
     <row r="76" spans="1:20" ht="15" customHeight="1">
       <c r="A76" s="66" t="s">
+        <v>586</v>
+      </c>
+      <c r="B76" s="66" t="s">
         <v>587</v>
-      </c>
-      <c r="B76" s="66" t="s">
-        <v>588</v>
       </c>
       <c r="C76" s="66" t="s">
         <v>95</v>
@@ -24136,7 +24272,7 @@
         <v>49</v>
       </c>
       <c r="N76" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O76" s="66"/>
       <c r="P76" s="66"/>
@@ -24147,10 +24283,10 @@
     </row>
     <row r="77" spans="1:20" ht="15" customHeight="1">
       <c r="A77" s="69" t="s">
+        <v>588</v>
+      </c>
+      <c r="B77" s="69" t="s">
         <v>589</v>
-      </c>
-      <c r="B77" s="69" t="s">
-        <v>590</v>
       </c>
       <c r="C77" s="69" t="s">
         <v>96</v>
@@ -24184,14 +24320,14 @@
         <v>1990</v>
       </c>
       <c r="L77" s="69" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="M77" s="69"/>
       <c r="N77" s="69" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O77" s="69" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="P77" s="69"/>
       <c r="Q77" s="69"/>
@@ -24201,10 +24337,10 @@
     </row>
     <row r="78" spans="1:20" ht="15" customHeight="1">
       <c r="A78" s="66" t="s">
+        <v>592</v>
+      </c>
+      <c r="B78" s="66" t="s">
         <v>593</v>
-      </c>
-      <c r="B78" s="66" t="s">
-        <v>594</v>
       </c>
       <c r="C78" s="66" t="s">
         <v>96</v>
@@ -24238,14 +24374,14 @@
         <v>2150</v>
       </c>
       <c r="L78" s="66" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="M78" s="66"/>
       <c r="N78" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O78" s="66" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="P78" s="66"/>
       <c r="Q78" s="66"/>
@@ -24255,10 +24391,10 @@
     </row>
     <row r="79" spans="1:20" ht="15" customHeight="1">
       <c r="A79" s="69" t="s">
+        <v>596</v>
+      </c>
+      <c r="B79" s="69" t="s">
         <v>597</v>
-      </c>
-      <c r="B79" s="69" t="s">
-        <v>598</v>
       </c>
       <c r="C79" s="69" t="s">
         <v>96</v>
@@ -24292,14 +24428,14 @@
         <v>0</v>
       </c>
       <c r="L79" s="69" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="M79" s="69"/>
       <c r="N79" s="69" t="s">
+        <v>599</v>
+      </c>
+      <c r="O79" s="69" t="s">
         <v>600</v>
-      </c>
-      <c r="O79" s="69" t="s">
-        <v>601</v>
       </c>
       <c r="P79" s="69"/>
       <c r="Q79" s="69"/>
@@ -24309,10 +24445,10 @@
     </row>
     <row r="80" spans="1:20" ht="15" customHeight="1">
       <c r="A80" s="66" t="s">
+        <v>601</v>
+      </c>
+      <c r="B80" s="66" t="s">
         <v>602</v>
-      </c>
-      <c r="B80" s="66" t="s">
-        <v>603</v>
       </c>
       <c r="C80" s="66" t="s">
         <v>96</v>
@@ -24346,14 +24482,14 @@
         <v>1230</v>
       </c>
       <c r="L80" s="66" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="M80" s="66"/>
       <c r="N80" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O80" s="66" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="P80" s="66"/>
       <c r="Q80" s="66"/>
@@ -24363,10 +24499,10 @@
     </row>
     <row r="81" spans="1:20" ht="30" customHeight="1">
       <c r="A81" s="69" t="s">
+        <v>605</v>
+      </c>
+      <c r="B81" s="69" t="s">
         <v>606</v>
-      </c>
-      <c r="B81" s="69" t="s">
-        <v>607</v>
       </c>
       <c r="C81" s="69" t="s">
         <v>96</v>
@@ -24400,11 +24536,11 @@
         <v>0</v>
       </c>
       <c r="L81" s="69" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="M81" s="69"/>
       <c r="N81" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O81" s="69"/>
       <c r="P81" s="69"/>
@@ -24415,10 +24551,10 @@
     </row>
     <row r="82" spans="1:20" ht="15" customHeight="1">
       <c r="A82" s="66" t="s">
+        <v>608</v>
+      </c>
+      <c r="B82" s="66" t="s">
         <v>609</v>
-      </c>
-      <c r="B82" s="66" t="s">
-        <v>610</v>
       </c>
       <c r="C82" s="66" t="s">
         <v>96</v>
@@ -24452,11 +24588,11 @@
         <v>0</v>
       </c>
       <c r="L82" s="66" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="M82" s="66"/>
       <c r="N82" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O82" s="66"/>
       <c r="P82" s="66"/>
@@ -24467,10 +24603,10 @@
     </row>
     <row r="83" spans="1:20" ht="30" customHeight="1">
       <c r="A83" s="69" t="s">
+        <v>611</v>
+      </c>
+      <c r="B83" s="69" t="s">
         <v>612</v>
-      </c>
-      <c r="B83" s="69" t="s">
-        <v>613</v>
       </c>
       <c r="C83" s="69" t="s">
         <v>96</v>
@@ -24504,14 +24640,14 @@
         <v>0</v>
       </c>
       <c r="L83" s="69" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="M83" s="69"/>
       <c r="N83" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O83" s="69" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="P83" s="69"/>
       <c r="Q83" s="69"/>
@@ -24521,10 +24657,10 @@
     </row>
     <row r="84" spans="1:20" ht="15" customHeight="1">
       <c r="A84" s="66" t="s">
+        <v>615</v>
+      </c>
+      <c r="B84" s="66" t="s">
         <v>616</v>
-      </c>
-      <c r="B84" s="66" t="s">
-        <v>617</v>
       </c>
       <c r="C84" s="66" t="s">
         <v>96</v>
@@ -24558,14 +24694,14 @@
         <v>900</v>
       </c>
       <c r="L84" s="66" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="M84" s="66"/>
       <c r="N84" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O84" s="66" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="P84" s="66"/>
       <c r="Q84" s="66"/>
@@ -24575,10 +24711,10 @@
     </row>
     <row r="85" spans="1:20" ht="15" customHeight="1">
       <c r="A85" s="69" t="s">
+        <v>619</v>
+      </c>
+      <c r="B85" s="69" t="s">
         <v>620</v>
-      </c>
-      <c r="B85" s="69" t="s">
-        <v>621</v>
       </c>
       <c r="C85" s="69" t="s">
         <v>96</v>
@@ -24612,11 +24748,11 @@
         <v>895</v>
       </c>
       <c r="L85" s="69" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="M85" s="69"/>
       <c r="N85" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O85" s="69"/>
       <c r="P85" s="69"/>
@@ -24627,10 +24763,10 @@
     </row>
     <row r="86" spans="1:20" ht="15" customHeight="1">
       <c r="A86" s="66" t="s">
+        <v>622</v>
+      </c>
+      <c r="B86" s="66" t="s">
         <v>623</v>
-      </c>
-      <c r="B86" s="66" t="s">
-        <v>624</v>
       </c>
       <c r="C86" s="66" t="s">
         <v>96</v>
@@ -24664,14 +24800,14 @@
         <v>2090</v>
       </c>
       <c r="L86" s="66" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="M86" s="66"/>
       <c r="N86" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O86" s="66" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="P86" s="66"/>
       <c r="Q86" s="66"/>
@@ -24681,10 +24817,10 @@
     </row>
     <row r="87" spans="1:20" ht="15" customHeight="1">
       <c r="A87" s="69" t="s">
+        <v>625</v>
+      </c>
+      <c r="B87" s="69" t="s">
         <v>626</v>
-      </c>
-      <c r="B87" s="69" t="s">
-        <v>627</v>
       </c>
       <c r="C87" s="69" t="s">
         <v>96</v>
@@ -24720,10 +24856,10 @@
       <c r="L87" s="69"/>
       <c r="M87" s="69"/>
       <c r="N87" s="69" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O87" s="69" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="P87" s="69"/>
       <c r="Q87" s="69"/>
@@ -24733,10 +24869,10 @@
     </row>
     <row r="88" spans="1:20" ht="30" customHeight="1">
       <c r="A88" s="66" t="s">
+        <v>628</v>
+      </c>
+      <c r="B88" s="66" t="s">
         <v>629</v>
-      </c>
-      <c r="B88" s="66" t="s">
-        <v>630</v>
       </c>
       <c r="C88" s="66" t="s">
         <v>96</v>
@@ -24770,14 +24906,14 @@
         <v>795</v>
       </c>
       <c r="L88" s="66" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="M88" s="66"/>
       <c r="N88" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O88" s="66" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="P88" s="66"/>
       <c r="Q88" s="66"/>
@@ -24787,10 +24923,10 @@
     </row>
     <row r="89" spans="1:20" ht="15" customHeight="1">
       <c r="A89" s="69" t="s">
+        <v>632</v>
+      </c>
+      <c r="B89" s="69" t="s">
         <v>633</v>
-      </c>
-      <c r="B89" s="69" t="s">
-        <v>634</v>
       </c>
       <c r="C89" s="69" t="s">
         <v>95</v>
@@ -24824,11 +24960,11 @@
         <v>0</v>
       </c>
       <c r="L89" s="69" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="M89" s="69"/>
       <c r="N89" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O89" s="69"/>
       <c r="P89" s="69"/>
@@ -24839,10 +24975,10 @@
     </row>
     <row r="90" spans="1:20" ht="15" customHeight="1">
       <c r="A90" s="66" t="s">
+        <v>635</v>
+      </c>
+      <c r="B90" s="66" t="s">
         <v>636</v>
-      </c>
-      <c r="B90" s="66" t="s">
-        <v>637</v>
       </c>
       <c r="C90" s="66" t="s">
         <v>95</v>
@@ -24880,7 +25016,7 @@
       </c>
       <c r="M90" s="66"/>
       <c r="N90" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O90" s="66"/>
       <c r="P90" s="66"/>
@@ -24891,13 +25027,13 @@
     </row>
     <row r="91" spans="1:20" ht="15" customHeight="1">
       <c r="A91" s="69" t="s">
+        <v>637</v>
+      </c>
+      <c r="B91" s="69" t="s">
         <v>638</v>
       </c>
-      <c r="B91" s="69" t="s">
+      <c r="C91" s="69" t="s">
         <v>639</v>
-      </c>
-      <c r="C91" s="69" t="s">
-        <v>640</v>
       </c>
       <c r="D91" s="70">
         <v>389</v>
@@ -24928,11 +25064,11 @@
         <v>0</v>
       </c>
       <c r="L91" s="69" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="M91" s="69"/>
       <c r="N91" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O91" s="69"/>
       <c r="P91" s="69"/>
@@ -24943,13 +25079,13 @@
     </row>
     <row r="92" spans="1:20" ht="15" customHeight="1">
       <c r="A92" s="66" t="s">
+        <v>641</v>
+      </c>
+      <c r="B92" s="66" t="s">
         <v>642</v>
       </c>
-      <c r="B92" s="66" t="s">
-        <v>643</v>
-      </c>
       <c r="C92" s="66" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D92" s="67">
         <v>489</v>
@@ -24980,11 +25116,11 @@
         <v>0</v>
       </c>
       <c r="L92" s="66" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="M92" s="66"/>
       <c r="N92" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O92" s="66"/>
       <c r="P92" s="66"/>
@@ -24995,10 +25131,10 @@
     </row>
     <row r="93" spans="1:20" ht="15" customHeight="1">
       <c r="A93" s="69" t="s">
+        <v>644</v>
+      </c>
+      <c r="B93" s="69" t="s">
         <v>645</v>
-      </c>
-      <c r="B93" s="69" t="s">
-        <v>646</v>
       </c>
       <c r="C93" s="69" t="s">
         <v>97</v>
@@ -25032,14 +25168,14 @@
         <v>472</v>
       </c>
       <c r="L93" s="69" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="M93" s="69"/>
       <c r="N93" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O93" s="69" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="P93" s="69"/>
       <c r="Q93" s="69"/>
@@ -25049,10 +25185,10 @@
     </row>
     <row r="94" spans="1:20" ht="15" customHeight="1">
       <c r="A94" s="66" t="s">
+        <v>648</v>
+      </c>
+      <c r="B94" s="66" t="s">
         <v>649</v>
-      </c>
-      <c r="B94" s="66" t="s">
-        <v>650</v>
       </c>
       <c r="C94" s="66" t="s">
         <v>95</v>
@@ -25090,7 +25226,7 @@
       </c>
       <c r="M94" s="66"/>
       <c r="N94" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O94" s="66"/>
       <c r="P94" s="66"/>
@@ -25101,10 +25237,10 @@
     </row>
     <row r="95" spans="1:20" ht="15" customHeight="1">
       <c r="A95" s="69" t="s">
+        <v>650</v>
+      </c>
+      <c r="B95" s="69" t="s">
         <v>651</v>
-      </c>
-      <c r="B95" s="69" t="s">
-        <v>652</v>
       </c>
       <c r="C95" s="69" t="s">
         <v>95</v>
@@ -25138,11 +25274,11 @@
         <v>0</v>
       </c>
       <c r="L95" s="69" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="M95" s="69"/>
       <c r="N95" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O95" s="69"/>
       <c r="P95" s="69"/>
@@ -25153,10 +25289,10 @@
     </row>
     <row r="96" spans="1:20" ht="15" customHeight="1">
       <c r="A96" s="66" t="s">
+        <v>653</v>
+      </c>
+      <c r="B96" s="66" t="s">
         <v>654</v>
-      </c>
-      <c r="B96" s="66" t="s">
-        <v>655</v>
       </c>
       <c r="C96" s="66" t="s">
         <v>95</v>
@@ -25192,7 +25328,7 @@
       <c r="L96" s="66"/>
       <c r="M96" s="66"/>
       <c r="N96" s="66" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O96" s="66"/>
       <c r="P96" s="66"/>
@@ -25203,10 +25339,10 @@
     </row>
     <row r="97" spans="1:20" ht="15" customHeight="1">
       <c r="A97" s="69" t="s">
+        <v>655</v>
+      </c>
+      <c r="B97" s="69" t="s">
         <v>656</v>
-      </c>
-      <c r="B97" s="69" t="s">
-        <v>657</v>
       </c>
       <c r="C97" s="69" t="s">
         <v>95</v>
@@ -25244,7 +25380,7 @@
       </c>
       <c r="M97" s="69"/>
       <c r="N97" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O97" s="69"/>
       <c r="P97" s="69"/>
@@ -25255,10 +25391,10 @@
     </row>
     <row r="98" spans="1:20" ht="15" customHeight="1">
       <c r="A98" s="66" t="s">
+        <v>657</v>
+      </c>
+      <c r="B98" s="66" t="s">
         <v>658</v>
-      </c>
-      <c r="B98" s="66" t="s">
-        <v>659</v>
       </c>
       <c r="C98" s="66" t="s">
         <v>96</v>
@@ -25296,7 +25432,7 @@
       </c>
       <c r="M98" s="66"/>
       <c r="N98" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O98" s="66" t="s">
         <v>201</v>
@@ -25309,10 +25445,10 @@
     </row>
     <row r="99" spans="1:20" ht="15" customHeight="1">
       <c r="A99" s="69" t="s">
+        <v>659</v>
+      </c>
+      <c r="B99" s="69" t="s">
         <v>660</v>
-      </c>
-      <c r="B99" s="69" t="s">
-        <v>661</v>
       </c>
       <c r="C99" s="69" t="s">
         <v>96</v>
@@ -25350,7 +25486,7 @@
       </c>
       <c r="M99" s="69"/>
       <c r="N99" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O99" s="69" t="s">
         <v>201</v>
@@ -25363,10 +25499,10 @@
     </row>
     <row r="100" spans="1:20" ht="15" customHeight="1">
       <c r="A100" s="66" t="s">
+        <v>661</v>
+      </c>
+      <c r="B100" s="66" t="s">
         <v>662</v>
-      </c>
-      <c r="B100" s="66" t="s">
-        <v>663</v>
       </c>
       <c r="C100" s="66" t="s">
         <v>96</v>
@@ -25404,7 +25540,7 @@
       </c>
       <c r="M100" s="66"/>
       <c r="N100" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O100" s="66" t="s">
         <v>201</v>
@@ -25417,10 +25553,10 @@
     </row>
     <row r="101" spans="1:20" ht="15" customHeight="1">
       <c r="A101" s="69" t="s">
+        <v>663</v>
+      </c>
+      <c r="B101" s="69" t="s">
         <v>664</v>
-      </c>
-      <c r="B101" s="69" t="s">
-        <v>665</v>
       </c>
       <c r="C101" s="69" t="s">
         <v>96</v>
@@ -25458,7 +25594,7 @@
       </c>
       <c r="M101" s="69"/>
       <c r="N101" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O101" s="69" t="s">
         <v>201</v>
@@ -25471,10 +25607,10 @@
     </row>
     <row r="102" spans="1:20" ht="15" customHeight="1">
       <c r="A102" s="66" t="s">
+        <v>665</v>
+      </c>
+      <c r="B102" s="66" t="s">
         <v>666</v>
-      </c>
-      <c r="B102" s="66" t="s">
-        <v>667</v>
       </c>
       <c r="C102" s="66" t="s">
         <v>96</v>
@@ -25512,7 +25648,7 @@
       </c>
       <c r="M102" s="66"/>
       <c r="N102" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O102" s="66" t="s">
         <v>201</v>
@@ -25525,10 +25661,10 @@
     </row>
     <row r="103" spans="1:20" ht="15" customHeight="1">
       <c r="A103" s="69" t="s">
+        <v>667</v>
+      </c>
+      <c r="B103" s="69" t="s">
         <v>668</v>
-      </c>
-      <c r="B103" s="69" t="s">
-        <v>669</v>
       </c>
       <c r="C103" s="69" t="s">
         <v>96</v>
@@ -25566,7 +25702,7 @@
       </c>
       <c r="M103" s="69"/>
       <c r="N103" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O103" s="69" t="s">
         <v>201</v>
@@ -25579,10 +25715,10 @@
     </row>
     <row r="104" spans="1:20" ht="15" customHeight="1">
       <c r="A104" s="66" t="s">
+        <v>669</v>
+      </c>
+      <c r="B104" s="66" t="s">
         <v>670</v>
-      </c>
-      <c r="B104" s="66" t="s">
-        <v>671</v>
       </c>
       <c r="C104" s="66" t="s">
         <v>96</v>
@@ -25620,7 +25756,7 @@
       </c>
       <c r="M104" s="66"/>
       <c r="N104" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O104" s="66" t="s">
         <v>201</v>
@@ -25633,10 +25769,10 @@
     </row>
     <row r="105" spans="1:20" ht="15" customHeight="1">
       <c r="A105" s="69" t="s">
+        <v>671</v>
+      </c>
+      <c r="B105" s="69" t="s">
         <v>672</v>
-      </c>
-      <c r="B105" s="69" t="s">
-        <v>673</v>
       </c>
       <c r="C105" s="69" t="s">
         <v>96</v>
@@ -25674,7 +25810,7 @@
       </c>
       <c r="M105" s="69"/>
       <c r="N105" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O105" s="69" t="s">
         <v>201</v>
@@ -25687,10 +25823,10 @@
     </row>
     <row r="106" spans="1:20" ht="15" customHeight="1">
       <c r="A106" s="66" t="s">
+        <v>673</v>
+      </c>
+      <c r="B106" s="66" t="s">
         <v>674</v>
-      </c>
-      <c r="B106" s="66" t="s">
-        <v>675</v>
       </c>
       <c r="C106" s="66" t="s">
         <v>96</v>
@@ -25724,11 +25860,11 @@
         <v>0</v>
       </c>
       <c r="L106" s="66" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="M106" s="66"/>
       <c r="N106" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O106" s="66" t="s">
         <v>201</v>
@@ -25741,10 +25877,10 @@
     </row>
     <row r="107" spans="1:20" ht="15" customHeight="1">
       <c r="A107" s="69" t="s">
+        <v>675</v>
+      </c>
+      <c r="B107" s="69" t="s">
         <v>676</v>
-      </c>
-      <c r="B107" s="69" t="s">
-        <v>677</v>
       </c>
       <c r="C107" s="69" t="s">
         <v>96</v>
@@ -25782,7 +25918,7 @@
       </c>
       <c r="M107" s="69"/>
       <c r="N107" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O107" s="69" t="s">
         <v>201</v>
@@ -25795,10 +25931,10 @@
     </row>
     <row r="108" spans="1:20" ht="15" customHeight="1">
       <c r="A108" s="66" t="s">
+        <v>677</v>
+      </c>
+      <c r="B108" s="66" t="s">
         <v>678</v>
-      </c>
-      <c r="B108" s="66" t="s">
-        <v>679</v>
       </c>
       <c r="C108" s="66" t="s">
         <v>96</v>
@@ -25836,7 +25972,7 @@
       </c>
       <c r="M108" s="66"/>
       <c r="N108" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O108" s="66" t="s">
         <v>201</v>
@@ -25849,10 +25985,10 @@
     </row>
     <row r="109" spans="1:20" ht="15" customHeight="1">
       <c r="A109" s="69" t="s">
+        <v>679</v>
+      </c>
+      <c r="B109" s="69" t="s">
         <v>680</v>
-      </c>
-      <c r="B109" s="69" t="s">
-        <v>681</v>
       </c>
       <c r="C109" s="69" t="s">
         <v>96</v>
@@ -25890,7 +26026,7 @@
       </c>
       <c r="M109" s="69"/>
       <c r="N109" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O109" s="69" t="s">
         <v>201</v>
@@ -25903,10 +26039,10 @@
     </row>
     <row r="110" spans="1:20" ht="15" customHeight="1">
       <c r="A110" s="66" t="s">
+        <v>681</v>
+      </c>
+      <c r="B110" s="66" t="s">
         <v>682</v>
-      </c>
-      <c r="B110" s="66" t="s">
-        <v>683</v>
       </c>
       <c r="C110" s="66" t="s">
         <v>96</v>
@@ -25944,7 +26080,7 @@
       </c>
       <c r="M110" s="66"/>
       <c r="N110" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O110" s="66" t="s">
         <v>201</v>
@@ -25957,10 +26093,10 @@
     </row>
     <row r="111" spans="1:20" ht="15" customHeight="1">
       <c r="A111" s="69" t="s">
+        <v>683</v>
+      </c>
+      <c r="B111" s="69" t="s">
         <v>684</v>
-      </c>
-      <c r="B111" s="69" t="s">
-        <v>685</v>
       </c>
       <c r="C111" s="69" t="s">
         <v>96</v>
@@ -25998,7 +26134,7 @@
       </c>
       <c r="M111" s="69"/>
       <c r="N111" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O111" s="69" t="s">
         <v>201</v>
@@ -26011,10 +26147,10 @@
     </row>
     <row r="112" spans="1:20" ht="15" customHeight="1">
       <c r="A112" s="66" t="s">
+        <v>685</v>
+      </c>
+      <c r="B112" s="66" t="s">
         <v>686</v>
-      </c>
-      <c r="B112" s="66" t="s">
-        <v>687</v>
       </c>
       <c r="C112" s="66" t="s">
         <v>96</v>
@@ -26050,7 +26186,7 @@
       <c r="L112" s="66"/>
       <c r="M112" s="66"/>
       <c r="N112" s="66" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O112" s="66" t="s">
         <v>201</v>
@@ -26063,10 +26199,10 @@
     </row>
     <row r="113" spans="1:246" ht="15" customHeight="1">
       <c r="A113" s="69" t="s">
+        <v>687</v>
+      </c>
+      <c r="B113" s="69" t="s">
         <v>688</v>
-      </c>
-      <c r="B113" s="69" t="s">
-        <v>689</v>
       </c>
       <c r="C113" s="69" t="s">
         <v>96</v>
@@ -26104,7 +26240,7 @@
       </c>
       <c r="M113" s="69"/>
       <c r="N113" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O113" s="69" t="s">
         <v>201</v>
@@ -26117,10 +26253,10 @@
     </row>
     <row r="114" spans="1:246" ht="15" customHeight="1">
       <c r="A114" s="66" t="s">
+        <v>689</v>
+      </c>
+      <c r="B114" s="66" t="s">
         <v>690</v>
-      </c>
-      <c r="B114" s="66" t="s">
-        <v>691</v>
       </c>
       <c r="C114" s="66" t="s">
         <v>95</v>
@@ -26158,7 +26294,7 @@
       </c>
       <c r="M114" s="66"/>
       <c r="N114" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O114" s="66"/>
       <c r="P114" s="66"/>
@@ -26169,10 +26305,10 @@
     </row>
     <row r="115" spans="1:246" ht="30" customHeight="1">
       <c r="A115" s="69" t="s">
+        <v>691</v>
+      </c>
+      <c r="B115" s="69" t="s">
         <v>692</v>
-      </c>
-      <c r="B115" s="69" t="s">
-        <v>693</v>
       </c>
       <c r="C115" s="69" t="s">
         <v>95</v>
@@ -26206,11 +26342,11 @@
         <v>0</v>
       </c>
       <c r="L115" s="69" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="M115" s="69"/>
       <c r="N115" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O115" s="69"/>
       <c r="P115" s="77"/>
@@ -26221,10 +26357,10 @@
     </row>
     <row r="116" spans="1:246" ht="150" customHeight="1">
       <c r="A116" s="66" t="s">
+        <v>694</v>
+      </c>
+      <c r="B116" s="66" t="s">
         <v>695</v>
-      </c>
-      <c r="B116" s="66" t="s">
-        <v>696</v>
       </c>
       <c r="C116" s="66" t="s">
         <v>95</v>
@@ -26258,11 +26394,11 @@
         <v>0</v>
       </c>
       <c r="L116" s="66" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="M116" s="66"/>
       <c r="N116" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O116" s="66"/>
       <c r="P116" s="66"/>
@@ -26273,10 +26409,10 @@
     </row>
     <row r="117" spans="1:246" ht="15" customHeight="1">
       <c r="A117" s="69" t="s">
+        <v>697</v>
+      </c>
+      <c r="B117" s="69" t="s">
         <v>698</v>
-      </c>
-      <c r="B117" s="69" t="s">
-        <v>699</v>
       </c>
       <c r="C117" s="69" t="s">
         <v>95</v>
@@ -26314,7 +26450,7 @@
       </c>
       <c r="M117" s="69"/>
       <c r="N117" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O117" s="69"/>
       <c r="P117" s="69"/>
@@ -26325,10 +26461,10 @@
     </row>
     <row r="118" spans="1:246" ht="15" customHeight="1">
       <c r="A118" s="66" t="s">
+        <v>699</v>
+      </c>
+      <c r="B118" s="66" t="s">
         <v>700</v>
-      </c>
-      <c r="B118" s="66" t="s">
-        <v>701</v>
       </c>
       <c r="C118" s="66" t="s">
         <v>95</v>
@@ -26362,15 +26498,15 @@
         <v>2095.8000000000002</v>
       </c>
       <c r="L118" s="66" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M118" s="66"/>
       <c r="N118" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O118" s="66"/>
       <c r="P118" s="66" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="Q118" s="66"/>
       <c r="R118" s="66"/>
@@ -26379,10 +26515,10 @@
     </row>
     <row r="119" spans="1:246" ht="15" customHeight="1">
       <c r="A119" s="69" t="s">
+        <v>703</v>
+      </c>
+      <c r="B119" s="69" t="s">
         <v>704</v>
-      </c>
-      <c r="B119" s="69" t="s">
-        <v>705</v>
       </c>
       <c r="C119" s="69" t="s">
         <v>95</v>
@@ -26420,7 +26556,7 @@
       </c>
       <c r="M119" s="69"/>
       <c r="N119" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O119" s="69"/>
       <c r="P119" s="69"/>
@@ -26431,10 +26567,10 @@
     </row>
     <row r="120" spans="1:246" ht="158" customHeight="1">
       <c r="A120" s="66" t="s">
+        <v>705</v>
+      </c>
+      <c r="B120" s="66" t="s">
         <v>706</v>
-      </c>
-      <c r="B120" s="66" t="s">
-        <v>707</v>
       </c>
       <c r="C120" s="66" t="s">
         <v>95</v>
@@ -26446,10 +26582,10 @@
         <v>699</v>
       </c>
       <c r="F120" s="67">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G120" s="67">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H120" s="66">
         <f t="shared" si="9"/>
@@ -26461,24 +26597,24 @@
       </c>
       <c r="J120" s="66">
         <f t="shared" si="10"/>
-        <v>9635.926666666659</v>
+        <v>12987.553333333322</v>
       </c>
       <c r="K120" s="66">
         <f t="shared" si="11"/>
-        <v>10892.786666666658</v>
+        <v>7541.1599999999935</v>
       </c>
       <c r="L120" s="66" t="s">
-        <v>930</v>
+        <v>954</v>
       </c>
       <c r="M120" s="66" t="s">
         <v>49</v>
       </c>
       <c r="N120" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O120" s="66"/>
       <c r="P120" s="66" t="s">
-        <v>931</v>
+        <v>955</v>
       </c>
       <c r="Q120" s="66"/>
       <c r="R120" s="66"/>
@@ -26487,10 +26623,10 @@
     </row>
     <row r="121" spans="1:246" ht="15" customHeight="1">
       <c r="A121" s="69" t="s">
+        <v>707</v>
+      </c>
+      <c r="B121" s="69" t="s">
         <v>708</v>
-      </c>
-      <c r="B121" s="69" t="s">
-        <v>709</v>
       </c>
       <c r="C121" s="69" t="s">
         <v>95</v>
@@ -26524,15 +26660,15 @@
         <v>0</v>
       </c>
       <c r="L121" s="69" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="M121" s="69"/>
       <c r="N121" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O121" s="69"/>
       <c r="P121" s="69" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="Q121" s="69"/>
       <c r="R121" s="69"/>
@@ -26541,10 +26677,10 @@
     </row>
     <row r="122" spans="1:246" ht="15" customHeight="1">
       <c r="A122" s="66" t="s">
+        <v>711</v>
+      </c>
+      <c r="B122" s="66" t="s">
         <v>712</v>
-      </c>
-      <c r="B122" s="66" t="s">
-        <v>713</v>
       </c>
       <c r="C122" s="66" t="s">
         <v>96</v>
@@ -26578,11 +26714,11 @@
         <v>4700</v>
       </c>
       <c r="L122" s="66" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="M122" s="66"/>
       <c r="N122" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O122" s="66"/>
       <c r="P122" s="66"/>
@@ -26593,10 +26729,10 @@
     </row>
     <row r="123" spans="1:246" s="72" customFormat="1" ht="75" customHeight="1">
       <c r="A123" s="78" t="s">
+        <v>714</v>
+      </c>
+      <c r="B123" s="78" t="s">
         <v>715</v>
-      </c>
-      <c r="B123" s="78" t="s">
-        <v>716</v>
       </c>
       <c r="C123" s="78" t="s">
         <v>95</v>
@@ -26630,11 +26766,11 @@
         <v>891.44</v>
       </c>
       <c r="L123" s="78" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="M123" s="78"/>
       <c r="N123" s="78" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O123" s="78"/>
       <c r="P123" s="78"/>
@@ -26871,10 +27007,10 @@
     </row>
     <row r="124" spans="1:246" s="83" customFormat="1" ht="30" customHeight="1">
       <c r="A124" s="80" t="s">
+        <v>717</v>
+      </c>
+      <c r="B124" s="80" t="s">
         <v>718</v>
-      </c>
-      <c r="B124" s="80" t="s">
-        <v>719</v>
       </c>
       <c r="C124" s="80" t="s">
         <v>95</v>
@@ -26908,15 +27044,15 @@
         <v>0</v>
       </c>
       <c r="L124" s="80" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="M124" s="80"/>
       <c r="N124" s="80" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O124" s="80"/>
       <c r="P124" s="80" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="Q124" s="80"/>
       <c r="R124" s="80"/>
@@ -27151,10 +27287,10 @@
     </row>
     <row r="125" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A125" s="78" t="s">
+        <v>720</v>
+      </c>
+      <c r="B125" s="78" t="s">
         <v>721</v>
-      </c>
-      <c r="B125" s="78" t="s">
-        <v>722</v>
       </c>
       <c r="C125" s="78" t="s">
         <v>95</v>
@@ -27188,15 +27324,15 @@
         <v>0</v>
       </c>
       <c r="L125" s="78" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="M125" s="78"/>
       <c r="N125" s="78" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O125" s="78"/>
       <c r="P125" s="78" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="Q125" s="78"/>
       <c r="R125" s="78"/>
@@ -27431,10 +27567,10 @@
     </row>
     <row r="126" spans="1:246" ht="15" customHeight="1">
       <c r="A126" s="80" t="s">
+        <v>724</v>
+      </c>
+      <c r="B126" s="66" t="s">
         <v>725</v>
-      </c>
-      <c r="B126" s="66" t="s">
-        <v>726</v>
       </c>
       <c r="C126" s="66" t="s">
         <v>96</v>
@@ -27468,14 +27604,14 @@
         <v>0</v>
       </c>
       <c r="L126" s="66" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="M126" s="66"/>
       <c r="N126" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O126" s="66" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="P126" s="66"/>
       <c r="Q126" s="66"/>
@@ -27485,10 +27621,10 @@
     </row>
     <row r="127" spans="1:246" ht="15" customHeight="1">
       <c r="A127" s="78" t="s">
+        <v>728</v>
+      </c>
+      <c r="B127" s="69" t="s">
         <v>729</v>
-      </c>
-      <c r="B127" s="69" t="s">
-        <v>730</v>
       </c>
       <c r="C127" s="69" t="s">
         <v>96</v>
@@ -27526,7 +27662,7 @@
       </c>
       <c r="M127" s="69"/>
       <c r="N127" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O127" s="69" t="s">
         <v>201</v>
@@ -27539,10 +27675,10 @@
     </row>
     <row r="128" spans="1:246" ht="15" customHeight="1">
       <c r="A128" s="80" t="s">
+        <v>730</v>
+      </c>
+      <c r="B128" s="66" t="s">
         <v>731</v>
-      </c>
-      <c r="B128" s="66" t="s">
-        <v>732</v>
       </c>
       <c r="C128" s="66" t="s">
         <v>95</v>
@@ -27578,7 +27714,7 @@
       <c r="L128" s="66"/>
       <c r="M128" s="66"/>
       <c r="N128" s="66" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O128" s="66"/>
       <c r="P128" s="66"/>
@@ -27589,10 +27725,10 @@
     </row>
     <row r="129" spans="1:20" ht="15" customHeight="1">
       <c r="A129" s="78" t="s">
+        <v>732</v>
+      </c>
+      <c r="B129" s="69" t="s">
         <v>733</v>
-      </c>
-      <c r="B129" s="69" t="s">
-        <v>734</v>
       </c>
       <c r="C129" s="69" t="s">
         <v>95</v>
@@ -27626,11 +27762,11 @@
         <v>0</v>
       </c>
       <c r="L129" s="69" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="M129" s="69"/>
       <c r="N129" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O129" s="69"/>
       <c r="P129" s="69"/>
@@ -27641,10 +27777,10 @@
     </row>
     <row r="130" spans="1:20" ht="15" customHeight="1">
       <c r="A130" s="80" t="s">
+        <v>735</v>
+      </c>
+      <c r="B130" s="66" t="s">
         <v>736</v>
-      </c>
-      <c r="B130" s="66" t="s">
-        <v>737</v>
       </c>
       <c r="C130" s="66" t="s">
         <v>95</v>
@@ -27678,11 +27814,11 @@
         <v>0</v>
       </c>
       <c r="L130" s="66" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="M130" s="66"/>
       <c r="N130" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O130" s="66"/>
       <c r="P130" s="66"/>
@@ -27693,10 +27829,10 @@
     </row>
     <row r="131" spans="1:20" ht="15" customHeight="1">
       <c r="A131" s="78" t="s">
+        <v>738</v>
+      </c>
+      <c r="B131" s="69" t="s">
         <v>739</v>
-      </c>
-      <c r="B131" s="69" t="s">
-        <v>740</v>
       </c>
       <c r="C131" s="69" t="s">
         <v>95</v>
@@ -27732,7 +27868,7 @@
       <c r="L131" s="69"/>
       <c r="M131" s="69"/>
       <c r="N131" s="69" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O131" s="69"/>
       <c r="P131" s="69"/>
@@ -27743,10 +27879,10 @@
     </row>
     <row r="132" spans="1:20" ht="15" customHeight="1">
       <c r="A132" s="80" t="s">
+        <v>740</v>
+      </c>
+      <c r="B132" s="66" t="s">
         <v>741</v>
-      </c>
-      <c r="B132" s="66" t="s">
-        <v>742</v>
       </c>
       <c r="C132" s="66" t="s">
         <v>95</v>
@@ -27780,11 +27916,11 @@
         <v>0</v>
       </c>
       <c r="L132" s="66" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="M132" s="66"/>
       <c r="N132" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O132" s="66"/>
       <c r="P132" s="66"/>
@@ -27795,10 +27931,10 @@
     </row>
     <row r="133" spans="1:20" ht="15" customHeight="1">
       <c r="A133" s="78" t="s">
+        <v>743</v>
+      </c>
+      <c r="B133" s="69" t="s">
         <v>744</v>
-      </c>
-      <c r="B133" s="69" t="s">
-        <v>745</v>
       </c>
       <c r="C133" s="69" t="s">
         <v>95</v>
@@ -27834,7 +27970,7 @@
       <c r="L133" s="69"/>
       <c r="M133" s="69"/>
       <c r="N133" s="69" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O133" s="69"/>
       <c r="P133" s="69"/>
@@ -27845,10 +27981,10 @@
     </row>
     <row r="134" spans="1:20" ht="15" customHeight="1">
       <c r="A134" s="80" t="s">
+        <v>745</v>
+      </c>
+      <c r="B134" s="66" t="s">
         <v>746</v>
-      </c>
-      <c r="B134" s="66" t="s">
-        <v>747</v>
       </c>
       <c r="C134" s="66" t="s">
         <v>95</v>
@@ -27884,7 +28020,7 @@
       <c r="L134" s="66"/>
       <c r="M134" s="66"/>
       <c r="N134" s="66" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O134" s="66"/>
       <c r="P134" s="66"/>
@@ -27895,10 +28031,10 @@
     </row>
     <row r="135" spans="1:20" ht="15" customHeight="1">
       <c r="A135" s="78" t="s">
+        <v>747</v>
+      </c>
+      <c r="B135" s="69" t="s">
         <v>748</v>
-      </c>
-      <c r="B135" s="69" t="s">
-        <v>749</v>
       </c>
       <c r="C135" s="69" t="s">
         <v>95</v>
@@ -27932,11 +28068,11 @@
         <v>0</v>
       </c>
       <c r="L135" s="69" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="M135" s="69"/>
       <c r="N135" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O135" s="69"/>
       <c r="P135" s="69"/>
@@ -27947,10 +28083,10 @@
     </row>
     <row r="136" spans="1:20" ht="15" customHeight="1">
       <c r="A136" s="80" t="s">
+        <v>750</v>
+      </c>
+      <c r="B136" s="66" t="s">
         <v>751</v>
-      </c>
-      <c r="B136" s="66" t="s">
-        <v>752</v>
       </c>
       <c r="C136" s="66" t="s">
         <v>95</v>
@@ -27984,15 +28120,15 @@
         <v>0</v>
       </c>
       <c r="L136" s="66" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="M136" s="66"/>
       <c r="N136" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O136" s="66"/>
       <c r="P136" s="66" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="Q136" s="66"/>
       <c r="R136" s="66"/>
@@ -28001,10 +28137,10 @@
     </row>
     <row r="137" spans="1:20" ht="15" customHeight="1">
       <c r="A137" s="78" t="s">
+        <v>754</v>
+      </c>
+      <c r="B137" s="69" t="s">
         <v>755</v>
-      </c>
-      <c r="B137" s="69" t="s">
-        <v>756</v>
       </c>
       <c r="C137" s="69" t="s">
         <v>95</v>
@@ -28042,7 +28178,7 @@
       </c>
       <c r="M137" s="69"/>
       <c r="N137" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O137" s="69"/>
       <c r="P137" s="69"/>
@@ -28053,10 +28189,10 @@
     </row>
     <row r="138" spans="1:20" ht="15" customHeight="1">
       <c r="A138" s="80" t="s">
+        <v>756</v>
+      </c>
+      <c r="B138" s="66" t="s">
         <v>757</v>
-      </c>
-      <c r="B138" s="66" t="s">
-        <v>758</v>
       </c>
       <c r="C138" s="66" t="s">
         <v>95</v>
@@ -28090,11 +28226,11 @@
         <v>0</v>
       </c>
       <c r="L138" s="66" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="M138" s="66"/>
       <c r="N138" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O138" s="66"/>
       <c r="P138" s="66"/>
@@ -28105,10 +28241,10 @@
     </row>
     <row r="139" spans="1:20" ht="15" customHeight="1">
       <c r="A139" s="78" t="s">
+        <v>759</v>
+      </c>
+      <c r="B139" s="69" t="s">
         <v>760</v>
-      </c>
-      <c r="B139" s="69" t="s">
-        <v>761</v>
       </c>
       <c r="C139" s="69" t="s">
         <v>95</v>
@@ -28146,7 +28282,7 @@
       </c>
       <c r="M139" s="69"/>
       <c r="N139" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O139" s="69"/>
       <c r="P139" s="69"/>
@@ -28157,10 +28293,10 @@
     </row>
     <row r="140" spans="1:20" ht="15" customHeight="1">
       <c r="A140" s="80" t="s">
+        <v>761</v>
+      </c>
+      <c r="B140" s="66" t="s">
         <v>762</v>
-      </c>
-      <c r="B140" s="66" t="s">
-        <v>763</v>
       </c>
       <c r="C140" s="66" t="s">
         <v>95</v>
@@ -28194,11 +28330,11 @@
         <v>699</v>
       </c>
       <c r="L140" s="66" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="M140" s="66"/>
       <c r="N140" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O140" s="66"/>
       <c r="P140" s="66"/>
@@ -28209,10 +28345,10 @@
     </row>
     <row r="141" spans="1:20" ht="15" customHeight="1">
       <c r="A141" s="78" t="s">
+        <v>764</v>
+      </c>
+      <c r="B141" s="69" t="s">
         <v>765</v>
-      </c>
-      <c r="B141" s="69" t="s">
-        <v>766</v>
       </c>
       <c r="C141" s="69" t="s">
         <v>95</v>
@@ -28248,7 +28384,7 @@
       <c r="L141" s="69"/>
       <c r="M141" s="69"/>
       <c r="N141" s="69" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O141" s="69"/>
       <c r="P141" s="69"/>
@@ -28259,10 +28395,10 @@
     </row>
     <row r="142" spans="1:20" ht="15" customHeight="1">
       <c r="A142" s="66" t="s">
+        <v>766</v>
+      </c>
+      <c r="B142" s="66" t="s">
         <v>767</v>
-      </c>
-      <c r="B142" s="66" t="s">
-        <v>768</v>
       </c>
       <c r="C142" s="66" t="s">
         <v>95</v>
@@ -28296,15 +28432,15 @@
         <v>600</v>
       </c>
       <c r="L142" s="66" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="M142" s="66"/>
       <c r="N142" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O142" s="66"/>
       <c r="P142" s="66" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="Q142" s="66"/>
       <c r="R142" s="66"/>
@@ -28313,10 +28449,10 @@
     </row>
     <row r="143" spans="1:20" ht="15" customHeight="1">
       <c r="A143" s="69" t="s">
+        <v>769</v>
+      </c>
+      <c r="B143" s="69" t="s">
         <v>770</v>
-      </c>
-      <c r="B143" s="69" t="s">
-        <v>771</v>
       </c>
       <c r="C143" s="69" t="s">
         <v>95</v>
@@ -28352,7 +28488,7 @@
       <c r="L143" s="69"/>
       <c r="M143" s="69"/>
       <c r="N143" s="69" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O143" s="69"/>
       <c r="P143" s="69"/>
@@ -28363,10 +28499,10 @@
     </row>
     <row r="144" spans="1:20" ht="15" customHeight="1">
       <c r="A144" s="66" t="s">
+        <v>771</v>
+      </c>
+      <c r="B144" s="66" t="s">
         <v>772</v>
-      </c>
-      <c r="B144" s="66" t="s">
-        <v>773</v>
       </c>
       <c r="C144" s="66" t="s">
         <v>95</v>
@@ -28402,7 +28538,7 @@
       <c r="L144" s="66"/>
       <c r="M144" s="66"/>
       <c r="N144" s="66" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O144" s="66"/>
       <c r="P144" s="66"/>
@@ -28413,7 +28549,7 @@
     </row>
     <row r="145" spans="1:20" ht="15" customHeight="1">
       <c r="A145" s="69" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B145" s="69" t="s">
         <v>296</v>
@@ -28454,7 +28590,7 @@
       </c>
       <c r="M145" s="69"/>
       <c r="N145" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O145" s="69"/>
       <c r="P145" s="69"/>
@@ -28465,10 +28601,10 @@
     </row>
     <row r="146" spans="1:20" ht="15" customHeight="1">
       <c r="A146" s="66" t="s">
+        <v>774</v>
+      </c>
+      <c r="B146" s="66" t="s">
         <v>775</v>
-      </c>
-      <c r="B146" s="66" t="s">
-        <v>776</v>
       </c>
       <c r="C146" s="66" t="s">
         <v>95</v>
@@ -28502,15 +28638,15 @@
         <v>761</v>
       </c>
       <c r="L146" s="66" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="M146" s="66"/>
       <c r="N146" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O146" s="66"/>
       <c r="P146" s="66" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="Q146" s="66"/>
       <c r="R146" s="66"/>
@@ -28519,10 +28655,10 @@
     </row>
     <row r="147" spans="1:20" ht="63.75" customHeight="1">
       <c r="A147" s="69" t="s">
+        <v>778</v>
+      </c>
+      <c r="B147" s="69" t="s">
         <v>779</v>
-      </c>
-      <c r="B147" s="69" t="s">
-        <v>780</v>
       </c>
       <c r="C147" s="69" t="s">
         <v>95</v>
@@ -28556,15 +28692,15 @@
         <v>2876</v>
       </c>
       <c r="L147" s="69" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="M147" s="69"/>
       <c r="N147" s="69" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O147" s="69"/>
       <c r="P147" s="69" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="Q147" s="69"/>
       <c r="R147" s="69"/>
@@ -28573,10 +28709,10 @@
     </row>
     <row r="148" spans="1:20" ht="15" customHeight="1">
       <c r="A148" s="66" t="s">
+        <v>782</v>
+      </c>
+      <c r="B148" s="66" t="s">
         <v>783</v>
-      </c>
-      <c r="B148" s="66" t="s">
-        <v>784</v>
       </c>
       <c r="C148" s="66" t="s">
         <v>95</v>
@@ -28610,11 +28746,11 @@
         <v>502</v>
       </c>
       <c r="L148" s="66" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="M148" s="66"/>
       <c r="N148" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O148" s="66"/>
       <c r="P148" s="66"/>
@@ -28625,10 +28761,10 @@
     </row>
     <row r="149" spans="1:20" ht="15" customHeight="1">
       <c r="A149" s="69" t="s">
+        <v>785</v>
+      </c>
+      <c r="B149" s="69" t="s">
         <v>786</v>
-      </c>
-      <c r="B149" s="69" t="s">
-        <v>787</v>
       </c>
       <c r="C149" s="69" t="s">
         <v>95</v>
@@ -28662,11 +28798,11 @@
         <v>1024</v>
       </c>
       <c r="L149" s="69" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="M149" s="69"/>
       <c r="N149" s="69" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O149" s="69"/>
       <c r="P149" s="69"/>
@@ -28677,10 +28813,10 @@
     </row>
     <row r="150" spans="1:20" ht="15" customHeight="1">
       <c r="A150" s="66" t="s">
+        <v>788</v>
+      </c>
+      <c r="B150" s="66" t="s">
         <v>789</v>
-      </c>
-      <c r="B150" s="66" t="s">
-        <v>790</v>
       </c>
       <c r="C150" s="66" t="s">
         <v>95</v>
@@ -28716,7 +28852,7 @@
       <c r="L150" s="66"/>
       <c r="M150" s="66"/>
       <c r="N150" s="66" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O150" s="66"/>
       <c r="P150" s="66"/>
@@ -28727,10 +28863,10 @@
     </row>
     <row r="151" spans="1:20" ht="15" customHeight="1">
       <c r="A151" s="69" t="s">
+        <v>790</v>
+      </c>
+      <c r="B151" s="69" t="s">
         <v>791</v>
-      </c>
-      <c r="B151" s="69" t="s">
-        <v>792</v>
       </c>
       <c r="C151" s="69" t="s">
         <v>96</v>
@@ -28764,17 +28900,17 @@
         <v>645</v>
       </c>
       <c r="L151" s="69" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="M151" s="69"/>
       <c r="N151" s="69" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O151" s="69" t="s">
         <v>210</v>
       </c>
       <c r="P151" s="69" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="Q151" s="69"/>
       <c r="R151" s="69"/>
@@ -28783,10 +28919,10 @@
     </row>
     <row r="152" spans="1:20" ht="15" customHeight="1">
       <c r="A152" s="66" t="s">
+        <v>794</v>
+      </c>
+      <c r="B152" s="66" t="s">
         <v>795</v>
-      </c>
-      <c r="B152" s="66" t="s">
-        <v>796</v>
       </c>
       <c r="C152" s="66" t="s">
         <v>97</v>
@@ -28820,17 +28956,17 @@
         <v>885</v>
       </c>
       <c r="L152" s="66" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="M152" s="66"/>
       <c r="N152" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O152" s="66" t="s">
+        <v>797</v>
+      </c>
+      <c r="P152" s="66" t="s">
         <v>798</v>
-      </c>
-      <c r="P152" s="66" t="s">
-        <v>799</v>
       </c>
       <c r="Q152" s="66"/>
       <c r="R152" s="66"/>
@@ -28839,10 +28975,10 @@
     </row>
     <row r="153" spans="1:20" ht="15" customHeight="1">
       <c r="A153" s="69" t="s">
+        <v>799</v>
+      </c>
+      <c r="B153" s="69" t="s">
         <v>800</v>
-      </c>
-      <c r="B153" s="69" t="s">
-        <v>801</v>
       </c>
       <c r="C153" s="69" t="s">
         <v>95</v>
@@ -28876,15 +29012,15 @@
         <v>891.5</v>
       </c>
       <c r="L153" s="69" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="M153" s="69"/>
       <c r="N153" s="69" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O153" s="69"/>
       <c r="P153" s="69" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="Q153" s="69"/>
       <c r="R153" s="69"/>
@@ -28893,10 +29029,10 @@
     </row>
     <row r="154" spans="1:20" ht="15" customHeight="1">
       <c r="A154" s="66" t="s">
+        <v>803</v>
+      </c>
+      <c r="B154" s="66" t="s">
         <v>804</v>
-      </c>
-      <c r="B154" s="66" t="s">
-        <v>805</v>
       </c>
       <c r="C154" s="66" t="s">
         <v>96</v>
@@ -28930,14 +29066,14 @@
         <v>1898</v>
       </c>
       <c r="L154" s="66" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="M154" s="66"/>
       <c r="N154" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O154" s="66" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="P154" s="66"/>
       <c r="Q154" s="66"/>
@@ -28947,10 +29083,10 @@
     </row>
     <row r="155" spans="1:20" ht="15" customHeight="1">
       <c r="A155" s="69" t="s">
+        <v>807</v>
+      </c>
+      <c r="B155" s="69" t="s">
         <v>808</v>
-      </c>
-      <c r="B155" s="69" t="s">
-        <v>809</v>
       </c>
       <c r="C155" s="69" t="s">
         <v>96</v>
@@ -28986,10 +29122,10 @@
       <c r="L155" s="69"/>
       <c r="M155" s="69"/>
       <c r="N155" s="69" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O155" s="69" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="P155" s="69"/>
       <c r="Q155" s="69"/>
@@ -28999,10 +29135,10 @@
     </row>
     <row r="156" spans="1:20" ht="15" customHeight="1">
       <c r="A156" s="66" t="s">
+        <v>810</v>
+      </c>
+      <c r="B156" s="66" t="s">
         <v>811</v>
-      </c>
-      <c r="B156" s="66" t="s">
-        <v>812</v>
       </c>
       <c r="C156" s="66" t="s">
         <v>96</v>
@@ -29036,14 +29172,14 @@
         <v>2850</v>
       </c>
       <c r="L156" s="66" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="M156" s="66"/>
       <c r="N156" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O156" s="66" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="P156" s="66"/>
       <c r="Q156" s="66"/>
@@ -29053,10 +29189,10 @@
     </row>
     <row r="157" spans="1:20" ht="15" customHeight="1">
       <c r="A157" s="69" t="s">
+        <v>813</v>
+      </c>
+      <c r="B157" s="69" t="s">
         <v>814</v>
-      </c>
-      <c r="B157" s="69" t="s">
-        <v>815</v>
       </c>
       <c r="C157" s="69" t="s">
         <v>96</v>
@@ -29090,14 +29226,14 @@
         <v>1575</v>
       </c>
       <c r="L157" s="69" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="M157" s="69"/>
       <c r="N157" s="69" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O157" s="69" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="P157" s="69"/>
       <c r="Q157" s="69"/>
@@ -29107,10 +29243,10 @@
     </row>
     <row r="158" spans="1:20" ht="15" customHeight="1">
       <c r="A158" s="66" t="s">
+        <v>817</v>
+      </c>
+      <c r="B158" s="66" t="s">
         <v>818</v>
-      </c>
-      <c r="B158" s="66" t="s">
-        <v>819</v>
       </c>
       <c r="C158" s="66" t="s">
         <v>96</v>
@@ -29144,14 +29280,14 @@
         <v>3356</v>
       </c>
       <c r="L158" s="66" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="M158" s="66"/>
       <c r="N158" s="66" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O158" s="66" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="P158" s="66"/>
       <c r="Q158" s="66"/>
@@ -29161,10 +29297,10 @@
     </row>
     <row r="159" spans="1:20" ht="15" customHeight="1">
       <c r="A159" s="69" t="s">
+        <v>821</v>
+      </c>
+      <c r="B159" s="69" t="s">
         <v>822</v>
-      </c>
-      <c r="B159" s="69" t="s">
-        <v>823</v>
       </c>
       <c r="C159" s="69" t="s">
         <v>96</v>
@@ -29198,14 +29334,14 @@
         <v>2517</v>
       </c>
       <c r="L159" s="69" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="M159" s="69"/>
       <c r="N159" s="69" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O159" s="69" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="P159" s="69"/>
       <c r="Q159" s="69"/>
@@ -29215,10 +29351,10 @@
     </row>
     <row r="160" spans="1:20" ht="15" customHeight="1">
       <c r="A160" s="66" t="s">
+        <v>825</v>
+      </c>
+      <c r="B160" s="66" t="s">
         <v>826</v>
-      </c>
-      <c r="B160" s="66" t="s">
-        <v>827</v>
       </c>
       <c r="C160" s="66" t="s">
         <v>95</v>
@@ -29256,7 +29392,7 @@
       </c>
       <c r="M160" s="66"/>
       <c r="N160" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O160" s="66"/>
       <c r="P160" s="66"/>
@@ -29267,10 +29403,10 @@
     </row>
     <row r="161" spans="1:20" ht="15" customHeight="1">
       <c r="A161" s="69" t="s">
+        <v>827</v>
+      </c>
+      <c r="B161" s="69" t="s">
         <v>828</v>
-      </c>
-      <c r="B161" s="69" t="s">
-        <v>829</v>
       </c>
       <c r="C161" s="69" t="s">
         <v>95</v>
@@ -29308,7 +29444,7 @@
       </c>
       <c r="M161" s="69"/>
       <c r="N161" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O161" s="69"/>
       <c r="P161" s="69"/>
@@ -29319,10 +29455,10 @@
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1">
       <c r="A162" s="66" t="s">
+        <v>829</v>
+      </c>
+      <c r="B162" s="66" t="s">
         <v>830</v>
-      </c>
-      <c r="B162" s="66" t="s">
-        <v>831</v>
       </c>
       <c r="C162" s="66" t="s">
         <v>95</v>
@@ -29360,7 +29496,7 @@
       </c>
       <c r="M162" s="66"/>
       <c r="N162" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O162" s="66"/>
       <c r="P162" s="66"/>
@@ -29371,10 +29507,10 @@
     </row>
     <row r="163" spans="1:20" ht="15" customHeight="1">
       <c r="A163" s="69" t="s">
+        <v>831</v>
+      </c>
+      <c r="B163" s="69" t="s">
         <v>832</v>
-      </c>
-      <c r="B163" s="69" t="s">
-        <v>833</v>
       </c>
       <c r="C163" s="69" t="s">
         <v>95</v>
@@ -29410,7 +29546,7 @@
       <c r="L163" s="69"/>
       <c r="M163" s="69"/>
       <c r="N163" s="69" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O163" s="69"/>
       <c r="P163" s="69"/>
@@ -29421,10 +29557,10 @@
     </row>
     <row r="164" spans="1:20" ht="60" customHeight="1">
       <c r="A164" s="66" t="s">
+        <v>833</v>
+      </c>
+      <c r="B164" s="66" t="s">
         <v>834</v>
-      </c>
-      <c r="B164" s="66" t="s">
-        <v>835</v>
       </c>
       <c r="C164" s="66" t="s">
         <v>95</v>
@@ -29458,15 +29594,15 @@
         <v>1013</v>
       </c>
       <c r="L164" s="66" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="M164" s="66"/>
       <c r="N164" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O164" s="66"/>
       <c r="P164" s="66" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="Q164" s="66"/>
       <c r="R164" s="66"/>
@@ -29475,10 +29611,10 @@
     </row>
     <row r="165" spans="1:20" ht="15" customHeight="1">
       <c r="A165" s="69" t="s">
+        <v>835</v>
+      </c>
+      <c r="B165" s="69" t="s">
         <v>836</v>
-      </c>
-      <c r="B165" s="69" t="s">
-        <v>837</v>
       </c>
       <c r="C165" s="69" t="s">
         <v>95</v>
@@ -29516,11 +29652,11 @@
       </c>
       <c r="M165" s="69"/>
       <c r="N165" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O165" s="69"/>
       <c r="P165" s="69" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="Q165" s="69"/>
       <c r="R165" s="69"/>
@@ -29529,10 +29665,10 @@
     </row>
     <row r="166" spans="1:20" ht="15" customHeight="1">
       <c r="A166" s="66" t="s">
+        <v>838</v>
+      </c>
+      <c r="B166" s="66" t="s">
         <v>839</v>
-      </c>
-      <c r="B166" s="66" t="s">
-        <v>840</v>
       </c>
       <c r="C166" s="66" t="s">
         <v>95</v>
@@ -29568,11 +29704,11 @@
       <c r="L166" s="66"/>
       <c r="M166" s="66"/>
       <c r="N166" s="66" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O166" s="66"/>
       <c r="P166" s="66" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="Q166" s="66"/>
       <c r="R166" s="66"/>
@@ -29581,10 +29717,10 @@
     </row>
     <row r="167" spans="1:20" ht="15" customHeight="1">
       <c r="A167" s="69" t="s">
+        <v>841</v>
+      </c>
+      <c r="B167" s="69" t="s">
         <v>842</v>
-      </c>
-      <c r="B167" s="69" t="s">
-        <v>843</v>
       </c>
       <c r="C167" s="69" t="s">
         <v>95</v>
@@ -29618,15 +29754,15 @@
         <v>2220</v>
       </c>
       <c r="L167" s="69" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="M167" s="69"/>
       <c r="N167" s="69" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O167" s="69"/>
       <c r="P167" s="69" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="Q167" s="69"/>
       <c r="R167" s="69"/>
@@ -29635,10 +29771,10 @@
     </row>
     <row r="168" spans="1:20" ht="15" customHeight="1">
       <c r="A168" s="66" t="s">
+        <v>845</v>
+      </c>
+      <c r="B168" s="66" t="s">
         <v>846</v>
-      </c>
-      <c r="B168" s="66" t="s">
-        <v>847</v>
       </c>
       <c r="C168" s="66" t="s">
         <v>95</v>
@@ -29672,15 +29808,15 @@
         <v>1216</v>
       </c>
       <c r="L168" s="66" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="M168" s="66"/>
       <c r="N168" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O168" s="66"/>
       <c r="P168" s="66" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="Q168" s="66"/>
       <c r="R168" s="66"/>
@@ -29689,10 +29825,10 @@
     </row>
     <row r="169" spans="1:20" ht="15" customHeight="1">
       <c r="A169" s="69" t="s">
+        <v>849</v>
+      </c>
+      <c r="B169" s="69" t="s">
         <v>850</v>
-      </c>
-      <c r="B169" s="69" t="s">
-        <v>851</v>
       </c>
       <c r="C169" s="69" t="s">
         <v>95</v>
@@ -29728,11 +29864,11 @@
       <c r="L169" s="69"/>
       <c r="M169" s="69"/>
       <c r="N169" s="69" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O169" s="69"/>
       <c r="P169" s="69" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="Q169" s="69"/>
       <c r="R169" s="69"/>
@@ -29741,10 +29877,10 @@
     </row>
     <row r="170" spans="1:20" ht="30" customHeight="1">
       <c r="A170" s="66" t="s">
+        <v>852</v>
+      </c>
+      <c r="B170" s="66" t="s">
         <v>853</v>
-      </c>
-      <c r="B170" s="66" t="s">
-        <v>854</v>
       </c>
       <c r="C170" s="66" t="s">
         <v>95</v>
@@ -29778,15 +29914,15 @@
         <v>0</v>
       </c>
       <c r="L170" s="66" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="M170" s="66"/>
       <c r="N170" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O170" s="66"/>
       <c r="P170" s="66" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="Q170" s="66"/>
       <c r="R170" s="66"/>
@@ -29795,10 +29931,10 @@
     </row>
     <row r="171" spans="1:20" ht="31.5" customHeight="1">
       <c r="A171" s="69" t="s">
+        <v>856</v>
+      </c>
+      <c r="B171" s="66" t="s">
         <v>857</v>
-      </c>
-      <c r="B171" s="66" t="s">
-        <v>858</v>
       </c>
       <c r="C171" s="69" t="s">
         <v>95</v>
@@ -29832,11 +29968,11 @@
         <v>0</v>
       </c>
       <c r="L171" s="69" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="M171" s="69"/>
       <c r="N171" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O171" s="69"/>
       <c r="P171" s="69"/>
@@ -29847,10 +29983,10 @@
     </row>
     <row r="172" spans="1:20" ht="15" customHeight="1">
       <c r="A172" s="66" t="s">
+        <v>859</v>
+      </c>
+      <c r="B172" s="66" t="s">
         <v>860</v>
-      </c>
-      <c r="B172" s="66" t="s">
-        <v>861</v>
       </c>
       <c r="C172" s="66" t="s">
         <v>95</v>
@@ -29862,10 +29998,10 @@
         <v>1550</v>
       </c>
       <c r="F172" s="81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G172" s="81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H172" s="80">
         <f t="shared" si="15"/>
@@ -29877,18 +30013,18 @@
       </c>
       <c r="J172" s="80">
         <f t="shared" si="16"/>
-        <v>1047</v>
+        <v>2094</v>
       </c>
       <c r="K172" s="80">
         <f t="shared" si="17"/>
-        <v>3141</v>
+        <v>2094</v>
       </c>
       <c r="L172" s="66" t="s">
-        <v>920</v>
+        <v>953</v>
       </c>
       <c r="M172" s="66"/>
       <c r="N172" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O172" s="66"/>
       <c r="P172" s="66"/>
@@ -29899,10 +30035,10 @@
     </row>
     <row r="173" spans="1:20" ht="15" customHeight="1">
       <c r="A173" s="69" t="s">
+        <v>861</v>
+      </c>
+      <c r="B173" s="69" t="s">
         <v>862</v>
-      </c>
-      <c r="B173" s="69" t="s">
-        <v>863</v>
       </c>
       <c r="C173" s="69" t="s">
         <v>95</v>
@@ -29936,11 +30072,11 @@
         <v>803.26</v>
       </c>
       <c r="L173" s="69" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="M173" s="69"/>
       <c r="N173" s="69" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O173" s="69"/>
       <c r="P173" s="69"/>
@@ -29951,10 +30087,10 @@
     </row>
     <row r="174" spans="1:20" ht="15" customHeight="1">
       <c r="A174" s="66" t="s">
+        <v>863</v>
+      </c>
+      <c r="B174" s="66" t="s">
         <v>864</v>
-      </c>
-      <c r="B174" s="66" t="s">
-        <v>865</v>
       </c>
       <c r="C174" s="66" t="s">
         <v>95</v>
@@ -29988,11 +30124,11 @@
         <v>0</v>
       </c>
       <c r="L174" s="66" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="M174" s="66"/>
       <c r="N174" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O174" s="66"/>
       <c r="P174" s="66"/>
@@ -30003,10 +30139,10 @@
     </row>
     <row r="175" spans="1:20" ht="90" customHeight="1">
       <c r="A175" s="69" t="s">
+        <v>866</v>
+      </c>
+      <c r="B175" s="69" t="s">
         <v>867</v>
-      </c>
-      <c r="B175" s="69" t="s">
-        <v>868</v>
       </c>
       <c r="C175" s="69" t="s">
         <v>95</v>
@@ -30040,15 +30176,15 @@
         <v>4887.75</v>
       </c>
       <c r="L175" s="69" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="M175" s="69"/>
       <c r="N175" s="69" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O175" s="69"/>
       <c r="P175" s="69" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="Q175" s="69"/>
       <c r="R175" s="69"/>
@@ -30057,10 +30193,10 @@
     </row>
     <row r="176" spans="1:20" ht="24" customHeight="1">
       <c r="A176" s="66" t="s">
+        <v>868</v>
+      </c>
+      <c r="B176" s="66" t="s">
         <v>869</v>
-      </c>
-      <c r="B176" s="66" t="s">
-        <v>870</v>
       </c>
       <c r="C176" s="66" t="s">
         <v>95</v>
@@ -30094,11 +30230,11 @@
         <v>0</v>
       </c>
       <c r="L176" s="66" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="M176" s="66"/>
       <c r="N176" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O176" s="66"/>
       <c r="P176" s="66"/>
@@ -30109,10 +30245,10 @@
     </row>
     <row r="177" spans="1:20" ht="34" customHeight="1">
       <c r="A177" s="69" t="s">
+        <v>870</v>
+      </c>
+      <c r="B177" s="69" t="s">
         <v>871</v>
-      </c>
-      <c r="B177" s="69" t="s">
-        <v>872</v>
       </c>
       <c r="C177" s="69" t="s">
         <v>95</v>
@@ -30146,15 +30282,15 @@
         <v>0</v>
       </c>
       <c r="L177" s="69" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="M177" s="69"/>
       <c r="N177" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O177" s="69"/>
       <c r="P177" s="69" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="Q177" s="69"/>
       <c r="R177" s="69"/>
@@ -30163,10 +30299,10 @@
     </row>
     <row r="178" spans="1:20" ht="15" customHeight="1">
       <c r="A178" s="66" t="s">
+        <v>873</v>
+      </c>
+      <c r="B178" s="66" t="s">
         <v>874</v>
-      </c>
-      <c r="B178" s="66" t="s">
-        <v>875</v>
       </c>
       <c r="C178" s="66" t="s">
         <v>95</v>
@@ -30200,15 +30336,15 @@
         <v>0</v>
       </c>
       <c r="L178" s="66" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="M178" s="66"/>
       <c r="N178" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O178" s="66"/>
       <c r="P178" s="66" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="Q178" s="66"/>
       <c r="R178" s="66"/>
@@ -30217,10 +30353,10 @@
     </row>
     <row r="179" spans="1:20" ht="30" customHeight="1">
       <c r="A179" s="69" t="s">
+        <v>876</v>
+      </c>
+      <c r="B179" s="69" t="s">
         <v>877</v>
-      </c>
-      <c r="B179" s="69" t="s">
-        <v>878</v>
       </c>
       <c r="C179" s="69" t="s">
         <v>95</v>
@@ -30254,15 +30390,15 @@
         <v>0</v>
       </c>
       <c r="L179" s="69" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="M179" s="69"/>
       <c r="N179" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O179" s="69"/>
       <c r="P179" s="69" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="Q179" s="69"/>
       <c r="R179" s="69"/>
@@ -30271,10 +30407,10 @@
     </row>
     <row r="180" spans="1:20" ht="34" customHeight="1">
       <c r="A180" s="66" t="s">
+        <v>880</v>
+      </c>
+      <c r="B180" s="66" t="s">
         <v>881</v>
-      </c>
-      <c r="B180" s="66" t="s">
-        <v>882</v>
       </c>
       <c r="C180" s="66" t="s">
         <v>95</v>
@@ -30308,11 +30444,11 @@
         <v>0</v>
       </c>
       <c r="L180" s="66" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="M180" s="66"/>
       <c r="N180" s="66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O180" s="66"/>
       <c r="P180" s="66"/>
@@ -30323,7 +30459,7 @@
     </row>
     <row r="181" spans="1:20" ht="15" customHeight="1">
       <c r="A181" s="69" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B181" s="69"/>
       <c r="C181" s="69"/>
@@ -30347,7 +30483,7 @@
     </row>
     <row r="182" spans="1:20" ht="15" customHeight="1">
       <c r="A182" s="66" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B182" s="66"/>
       <c r="C182" s="66"/>
@@ -30371,7 +30507,7 @@
     </row>
     <row r="183" spans="1:20" ht="15" customHeight="1">
       <c r="A183" s="69" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B183" s="69"/>
       <c r="C183" s="69"/>
@@ -30395,7 +30531,7 @@
     </row>
     <row r="184" spans="1:20" ht="15" customHeight="1">
       <c r="A184" s="66" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B184" s="66"/>
       <c r="C184" s="66"/>
@@ -30419,7 +30555,7 @@
     </row>
     <row r="185" spans="1:20" ht="15" customHeight="1">
       <c r="A185" s="69" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B185" s="69"/>
       <c r="C185" s="69"/>
@@ -30443,7 +30579,7 @@
     </row>
     <row r="186" spans="1:20" ht="15" customHeight="1">
       <c r="A186" s="66" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B186" s="66"/>
       <c r="C186" s="66"/>
@@ -30467,7 +30603,7 @@
     </row>
     <row r="187" spans="1:20" ht="15" customHeight="1">
       <c r="A187" s="69" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B187" s="69"/>
       <c r="C187" s="69"/>
@@ -30491,7 +30627,7 @@
     </row>
     <row r="188" spans="1:20" ht="15" customHeight="1">
       <c r="A188" s="66" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B188" s="66"/>
       <c r="C188" s="66"/>
@@ -34566,7 +34702,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1">
       <c r="A1" s="95" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B1" s="95"/>
     </row>
@@ -34575,7 +34711,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1">
@@ -34607,25 +34743,25 @@
         <v>42</v>
       </c>
       <c r="B7" s="86" t="s">
+        <v>892</v>
+      </c>
+      <c r="C7" s="86" t="s">
         <v>893</v>
       </c>
-      <c r="C7" s="86" t="s">
+      <c r="D7" s="86" t="s">
         <v>894</v>
       </c>
-      <c r="D7" s="86" t="s">
+      <c r="E7" s="86" t="s">
         <v>895</v>
       </c>
-      <c r="E7" s="86" t="s">
+      <c r="F7" s="86" t="s">
         <v>896</v>
       </c>
-      <c r="F7" s="86" t="s">
+      <c r="G7" s="86" t="s">
         <v>897</v>
       </c>
-      <c r="G7" s="86" t="s">
+      <c r="H7" s="86" t="s">
         <v>898</v>
-      </c>
-      <c r="H7" s="86" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1">
@@ -34729,7 +34865,7 @@
     </row>
     <row r="12" spans="1:8" s="90" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="96" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B12" s="96"/>
       <c r="C12" s="96"/>
@@ -34742,13 +34878,13 @@
         <v>98</v>
       </c>
       <c r="B13" s="86" t="s">
+        <v>900</v>
+      </c>
+      <c r="C13" s="86" t="s">
         <v>901</v>
       </c>
-      <c r="C13" s="86" t="s">
+      <c r="D13" s="86" t="s">
         <v>902</v>
-      </c>
-      <c r="D13" s="86" t="s">
-        <v>903</v>
       </c>
       <c r="E13" s="86" t="s">
         <v>99</v>
@@ -34762,7 +34898,7 @@
         <v>45952</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>51</v>
@@ -34780,7 +34916,7 @@
         <v>45952</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>51</v>
@@ -34834,7 +34970,7 @@
         <v>45970</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>50</v>
@@ -34852,7 +34988,7 @@
         <v>45970</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>50</v>
@@ -34870,7 +35006,7 @@
         <v>45973</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>50</v>
@@ -34888,7 +35024,7 @@
         <v>45973</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>49</v>
@@ -34906,7 +35042,7 @@
         <v>46058</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>51</v>
@@ -34942,7 +35078,7 @@
         <v>46059</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>49</v>
@@ -34978,7 +35114,7 @@
         <v>46093</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>50</v>
@@ -34996,7 +35132,7 @@
         <v>46093</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>51</v>
@@ -35079,7 +35215,7 @@
     </row>
     <row r="58" spans="2:2" ht="13.5" customHeight="1">
       <c r="B58" s="6" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -35109,7 +35245,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13.5" customHeight="1">
       <c r="A1" s="93" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="87" customFormat="1" ht="13.5" customHeight="1">
@@ -35117,22 +35253,22 @@
         <v>42</v>
       </c>
       <c r="B3" s="86" t="s">
+        <v>906</v>
+      </c>
+      <c r="C3" s="86" t="s">
+        <v>891</v>
+      </c>
+      <c r="D3" s="86" t="s">
         <v>907</v>
       </c>
-      <c r="C3" s="86" t="s">
-        <v>892</v>
-      </c>
-      <c r="D3" s="86" t="s">
+      <c r="E3" s="86" t="s">
         <v>908</v>
       </c>
-      <c r="E3" s="86" t="s">
+      <c r="F3" s="86" t="s">
         <v>909</v>
       </c>
-      <c r="F3" s="86" t="s">
+      <c r="G3" s="86" t="s">
         <v>910</v>
-      </c>
-      <c r="G3" s="86" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1">
@@ -35141,7 +35277,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>276319</v>
+        <v>283365</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -35149,11 +35285,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>111494.96119999999</v>
+        <v>113844.09759999999</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>164824.03880000001</v>
+        <v>169520.90240000002</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35161,7 +35297,7 @@
       </c>
       <c r="G4" s="88">
         <f>E4+F4</f>
-        <v>27514.012799999997</v>
+        <v>32210.876400000008</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -35178,11 +35314,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>111428.0776</v>
+        <v>113775.8048</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-65859.077600000004</v>
+        <v>-68206.804799999998</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35190,7 +35326,7 @@
       </c>
       <c r="G5" s="89">
         <f>E5+F5</f>
-        <v>5727.9643999999971</v>
+        <v>3380.2372000000032</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -35207,11 +35343,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>111494.96119999999</v>
+        <v>113844.09759999999</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-98964.961199999991</v>
+        <v>-101314.09759999999</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35219,7 +35355,7 @@
       </c>
       <c r="G6" s="88">
         <f>E6+F6</f>
-        <v>-33241.977199999979</v>
+        <v>-35591.113599999982</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">
@@ -35229,27 +35365,27 @@
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Chiraath-Summary-Jun26.xlsx
+++ b/docs/Chiraath-Summary-Jun26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D71F876-72BD-6A4B-B550-68B68D9082B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BEC430-30A1-8749-9F7B-35009014FB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">INVENTORY!$A$1:$T$188</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Purchases!$A$1:$D$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$212</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2387" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="960">
   <si>
     <t>Notes:</t>
   </si>
@@ -2405,10 +2405,6 @@
     <t>Blue/bottle green - Saranya Hyd, Blue/red - Jothika, Mustard - Vineetha, Bottle Green/Golden Yellow - Swapna (Thrissur)-1200, Black/Golden yellow - Kavya(Kasargod) - 1200, Back/Yellow - Subha - 1200</t>
   </si>
   <si>
-    <t>Bottle Green/Golden Yellow - 2 
-Navy Blue/Bottle Green - 2</t>
-  </si>
-  <si>
     <t>CHR-147</t>
   </si>
   <si>
@@ -2914,12 +2910,6 @@
     <t>Chanderi Silk Saree (Maroon - CHR-119)</t>
   </si>
   <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>Matka Green/Yellow &amp; Bengal Cotton (Adv:1100)</t>
-  </si>
-  <si>
     <t>Simi Sudhir</t>
   </si>
   <si>
@@ -2929,12 +2919,34 @@
     <t>Revathi, Simi Sudhir</t>
   </si>
   <si>
+    <t>Shaino Benny</t>
+  </si>
+  <si>
+    <t>Supriya</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree (Green- CHR-119)</t>
+  </si>
+  <si>
+    <t>Mercy Reji</t>
+  </si>
+  <si>
+    <t>Matka Green/Yellow</t>
+  </si>
+  <si>
+    <t>Bottle Green/Golden Yellow - 1
+Navy Blue/Bottle Green - 2</t>
+  </si>
+  <si>
+    <t>Kalaisari (Dharmapuri)</t>
+  </si>
+  <si>
     <t>First Set: Aruna - violet, Resmi - navy blue, Malini - Rani Pink
-Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black, Bindu Krisharaj - Black, Kavitha - off white, Jisha Suresh - Rani Pink(2), Sudharma - Navy Blue, SIndrella - Maroon, Unknown - Navy blue, Simi Sudhir - Navy Blue</t>
+Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black, Bindu Krisharaj - Black, Kavitha - off white, Jisha Suresh - Rani Pink(2), Sudharma - Navy Blue, SIndrella - Maroon, Shaino Benny - Navy blue, Simi Sudhir - Navy Blue, Supriya - Green, Mercy - Black, Kalisari - Green</t>
   </si>
   <si>
     <t xml:space="preserve">
-Blue (2), mustard yellow (1), Green (2), Maroon (1), off white (1), Orange (1), Black(5), White(5)</t>
+Blue (2), mustard yellow (1), Maroon (1), off white (1), Orange (1), Black(4), White(5)</t>
   </si>
 </sst>
 </file>
@@ -3847,7 +3859,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>204</c:v>
+                  <c:v>208</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>86</c:v>
@@ -3950,7 +3962,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>68</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>59</c:v>
@@ -4283,7 +4295,7 @@
                   <c:v>61609</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>45010.17</c:v>
+                  <c:v>43034.31</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1357</c:v>
@@ -4767,13 +4779,13 @@
                   <c:v>16248</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>55936</c:v>
+                  <c:v>55237</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>53524</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7046</c:v>
+                  <c:v>9144</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5207,13 +5219,13 @@
                   <c:v>-5924</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-15066</c:v>
+                  <c:v>-15765</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>49075</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7046</c:v>
+                  <c:v>9144</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5680,10 +5692,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>293</c:v>
+                  <c:v>297</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>131</c:v>
+                  <c:v>127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6870,7 +6882,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>341464</v>
+        <v>344762</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -6887,7 +6899,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>363318</v>
+        <v>364717</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -6904,7 +6916,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-13278</v>
+        <v>-9980</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -7116,15 +7128,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>283365</v>
+        <v>286663</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>113844.09759999999</v>
+        <v>114943.65079999999</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>169520.90240000002</v>
+        <v>171719.3492</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -7132,11 +7144,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>32210.876400000008</v>
+        <v>34409.323199999984</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹32,211</v>
+        <v>Pay ₹34,409</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -7150,11 +7162,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>113775.8048</v>
+        <v>114874.69839999999</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-68206.804799999998</v>
+        <v>-69305.698399999994</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -7162,11 +7174,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>3380.2372000000032</v>
+        <v>2281.3436000000074</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹3,380</v>
+        <v>Pay ₹2,281</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -7180,11 +7192,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>113844.09759999999</v>
+        <v>114943.65079999999</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-101314.09759999999</v>
+        <v>-102413.65079999999</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -7192,11 +7204,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-35591.113599999982</v>
+        <v>-36690.666799999977</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹35,591</v>
+        <v>Receive ₹36,691</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -7324,7 +7336,7 @@
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>341464</v>
+        <v>344762</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7333,14 +7345,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-13278</v>
+        <v>-9980</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>98672.37</v>
+        <v>96696.50999999998</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -7392,7 +7404,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7416,7 +7428,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7446,11 +7458,11 @@
       </c>
       <c r="C13" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A13)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>55936</v>
+        <v>55237</v>
       </c>
       <c r="D13" s="27">
         <f t="shared" si="0"/>
-        <v>-15066</v>
+        <v>-15765</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
@@ -7480,11 +7492,11 @@
       </c>
       <c r="C15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>7046</v>
+        <v>9144</v>
       </c>
       <c r="D15" s="27">
         <f t="shared" si="0"/>
-        <v>7046</v>
+        <v>9144</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
@@ -7612,11 +7624,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -7643,7 +7655,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>45010.17</v>
+        <v>43034.31</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -14678,7 +14690,7 @@
       <c r="F149" s="49"/>
       <c r="G149" s="49"/>
       <c r="H149" s="51" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="I149" s="49" t="s">
         <v>142</v>
@@ -14951,7 +14963,7 @@
       <c r="F160" s="56"/>
       <c r="G160" s="56"/>
       <c r="H160" s="57" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="I160" s="53" t="s">
         <v>341</v>
@@ -15143,7 +15155,7 @@
       <c r="F168" s="49"/>
       <c r="G168" s="49"/>
       <c r="H168" s="51" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="I168" s="49" t="s">
         <v>341</v>
@@ -15428,7 +15440,7 @@
         <v>380</v>
       </c>
       <c r="C180" s="50">
-        <v>1899</v>
+        <v>1200</v>
       </c>
       <c r="D180" s="49" t="s">
         <v>156</v>
@@ -15439,10 +15451,10 @@
       <c r="F180" s="49"/>
       <c r="G180" s="49"/>
       <c r="H180" s="51" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="I180" s="49" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="13.5" customHeight="1">
@@ -15871,7 +15883,7 @@
         <v>46168</v>
       </c>
       <c r="B198" s="53" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C198" s="54">
         <v>5200</v>
@@ -15885,7 +15897,7 @@
       <c r="F198" s="56"/>
       <c r="G198" s="56"/>
       <c r="H198" s="57" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="I198" s="53" t="s">
         <v>142</v>
@@ -15896,7 +15908,7 @@
         <v>46172</v>
       </c>
       <c r="B199" s="49" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C199" s="50">
         <v>1425</v>
@@ -15910,7 +15922,7 @@
       <c r="F199" s="49"/>
       <c r="G199" s="49"/>
       <c r="H199" s="51" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="I199" s="49" t="s">
         <v>341</v>
@@ -15921,7 +15933,7 @@
         <v>46173</v>
       </c>
       <c r="B200" s="53" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C200" s="54">
         <v>2850</v>
@@ -15935,7 +15947,7 @@
       <c r="F200" s="56"/>
       <c r="G200" s="56"/>
       <c r="H200" s="57" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="I200" s="53" t="s">
         <v>341</v>
@@ -15946,7 +15958,7 @@
         <v>46173</v>
       </c>
       <c r="B201" s="49" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C201" s="50">
         <v>2850</v>
@@ -15960,7 +15972,7 @@
       <c r="F201" s="49"/>
       <c r="G201" s="49"/>
       <c r="H201" s="51" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="I201" s="49" t="s">
         <v>341</v>
@@ -15971,7 +15983,7 @@
         <v>46173</v>
       </c>
       <c r="B202" s="53" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="C202" s="54">
         <v>930</v>
@@ -15985,7 +15997,7 @@
       <c r="F202" s="56"/>
       <c r="G202" s="56"/>
       <c r="H202" s="57" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I202" s="53" t="s">
         <v>341</v>
@@ -15996,7 +16008,7 @@
         <v>46173</v>
       </c>
       <c r="B203" s="49" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C203" s="50">
         <v>930</v>
@@ -16010,7 +16022,7 @@
       <c r="F203" s="49"/>
       <c r="G203" s="49"/>
       <c r="H203" s="51" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I203" s="49" t="s">
         <v>341</v>
@@ -16021,7 +16033,7 @@
         <v>46175</v>
       </c>
       <c r="B204" s="53" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C204" s="54">
         <v>699</v>
@@ -16035,7 +16047,7 @@
       <c r="F204" s="56"/>
       <c r="G204" s="56"/>
       <c r="H204" s="57" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I204" s="53" t="s">
         <v>142</v>
@@ -16046,7 +16058,7 @@
         <v>46175</v>
       </c>
       <c r="B205" s="49" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C205" s="50">
         <v>700</v>
@@ -16060,7 +16072,7 @@
       <c r="F205" s="49"/>
       <c r="G205" s="49"/>
       <c r="H205" s="51" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="I205" s="49" t="s">
         <v>142</v>
@@ -16071,7 +16083,7 @@
         <v>46175</v>
       </c>
       <c r="B206" s="53" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C206" s="54">
         <v>1350</v>
@@ -16085,7 +16097,7 @@
       <c r="F206" s="56"/>
       <c r="G206" s="56"/>
       <c r="H206" s="51" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="I206" s="53" t="s">
         <v>142</v>
@@ -16096,7 +16108,7 @@
         <v>46175</v>
       </c>
       <c r="B207" s="49" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C207" s="50">
         <v>699</v>
@@ -16110,7 +16122,7 @@
       <c r="F207" s="49"/>
       <c r="G207" s="49"/>
       <c r="H207" s="51" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="I207" s="49" t="s">
         <v>142</v>
@@ -16121,7 +16133,7 @@
         <v>46175</v>
       </c>
       <c r="B208" s="53" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C208" s="54">
         <v>699</v>
@@ -16135,7 +16147,7 @@
       <c r="F208" s="56"/>
       <c r="G208" s="56"/>
       <c r="H208" s="57" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="I208" s="53" t="s">
         <v>142</v>
@@ -16146,7 +16158,7 @@
         <v>46176</v>
       </c>
       <c r="B209" s="49" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C209" s="50">
         <v>699</v>
@@ -16160,7 +16172,7 @@
       <c r="F209" s="49"/>
       <c r="G209" s="49"/>
       <c r="H209" s="51" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="I209" s="49" t="s">
         <v>142</v>
@@ -16171,7 +16183,7 @@
         <v>46176</v>
       </c>
       <c r="B210" s="53" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="C210" s="54">
         <v>2200</v>
@@ -16185,44 +16197,86 @@
       <c r="F210" s="56"/>
       <c r="G210" s="56"/>
       <c r="H210" s="57" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="I210" s="53" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="211" spans="1:9">
-      <c r="A211" s="48"/>
-      <c r="B211" s="49"/>
-      <c r="C211" s="50"/>
-      <c r="D211" s="49"/>
-      <c r="E211" s="49"/>
+    <row r="211" spans="1:9" ht="14">
+      <c r="A211" s="48">
+        <v>46176</v>
+      </c>
+      <c r="B211" s="49" t="s">
+        <v>952</v>
+      </c>
+      <c r="C211" s="50">
+        <v>699</v>
+      </c>
+      <c r="D211" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E211" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F211" s="49"/>
       <c r="G211" s="49"/>
-      <c r="H211" s="51"/>
-      <c r="I211" s="49"/>
+      <c r="H211" s="51" t="s">
+        <v>953</v>
+      </c>
+      <c r="I211" s="49" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="212" spans="1:9">
-      <c r="A212" s="52"/>
-      <c r="B212" s="53"/>
-      <c r="C212" s="54"/>
-      <c r="D212" s="53"/>
-      <c r="E212" s="53"/>
+      <c r="A212" s="52">
+        <v>46176</v>
+      </c>
+      <c r="B212" s="53" t="s">
+        <v>954</v>
+      </c>
+      <c r="C212" s="54">
+        <v>699</v>
+      </c>
+      <c r="D212" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E212" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F212" s="56"/>
       <c r="G212" s="56"/>
-      <c r="H212" s="57"/>
-      <c r="I212" s="53"/>
-    </row>
-    <row r="213" spans="1:9">
-      <c r="A213" s="48"/>
-      <c r="B213" s="49"/>
-      <c r="C213" s="50"/>
-      <c r="D213" s="49"/>
-      <c r="E213" s="49"/>
+      <c r="H212" s="56" t="s">
+        <v>929</v>
+      </c>
+      <c r="I212" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" ht="14">
+      <c r="A213" s="48">
+        <v>46176</v>
+      </c>
+      <c r="B213" s="49" t="s">
+        <v>957</v>
+      </c>
+      <c r="C213" s="50">
+        <v>700</v>
+      </c>
+      <c r="D213" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E213" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F213" s="49"/>
       <c r="G213" s="49"/>
-      <c r="H213" s="51"/>
-      <c r="I213" s="49"/>
+      <c r="H213" s="51" t="s">
+        <v>953</v>
+      </c>
+      <c r="I213" s="49" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="214" spans="1:9">
       <c r="A214" s="52"/>
@@ -16739,7 +16793,7 @@
       <c r="I260" s="59"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I209" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:I212" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1260" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Ordered,Pending,Completed,Cancelled"</formula1>
@@ -23530,7 +23584,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="66" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="M62" s="66"/>
       <c r="N62" s="66" t="s">
@@ -26582,10 +26636,10 @@
         <v>699</v>
       </c>
       <c r="F120" s="67">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G120" s="67">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H120" s="66">
         <f t="shared" si="9"/>
@@ -26597,14 +26651,14 @@
       </c>
       <c r="J120" s="66">
         <f t="shared" si="10"/>
-        <v>12987.553333333322</v>
+        <v>14244.413333333321</v>
       </c>
       <c r="K120" s="66">
         <f t="shared" si="11"/>
-        <v>7541.1599999999935</v>
+        <v>6284.2999999999947</v>
       </c>
       <c r="L120" s="66" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="M120" s="66" t="s">
         <v>49</v>
@@ -26614,7 +26668,7 @@
       </c>
       <c r="O120" s="66"/>
       <c r="P120" s="66" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="Q120" s="66"/>
       <c r="R120" s="66"/>
@@ -28670,10 +28724,10 @@
         <v>1200</v>
       </c>
       <c r="F147" s="79">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G147" s="79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H147" s="78">
         <f t="shared" si="12"/>
@@ -28685,11 +28739,11 @@
       </c>
       <c r="J147" s="78">
         <f t="shared" si="13"/>
-        <v>4314</v>
+        <v>5033</v>
       </c>
       <c r="K147" s="78">
         <f t="shared" si="14"/>
-        <v>2876</v>
+        <v>2157</v>
       </c>
       <c r="L147" s="69" t="s">
         <v>780</v>
@@ -28700,7 +28754,7 @@
       </c>
       <c r="O147" s="69"/>
       <c r="P147" s="69" t="s">
-        <v>781</v>
+        <v>956</v>
       </c>
       <c r="Q147" s="69"/>
       <c r="R147" s="69"/>
@@ -28709,10 +28763,10 @@
     </row>
     <row r="148" spans="1:20" ht="15" customHeight="1">
       <c r="A148" s="66" t="s">
+        <v>781</v>
+      </c>
+      <c r="B148" s="66" t="s">
         <v>782</v>
-      </c>
-      <c r="B148" s="66" t="s">
-        <v>783</v>
       </c>
       <c r="C148" s="66" t="s">
         <v>95</v>
@@ -28746,7 +28800,7 @@
         <v>502</v>
       </c>
       <c r="L148" s="66" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="M148" s="66"/>
       <c r="N148" s="66" t="s">
@@ -28761,10 +28815,10 @@
     </row>
     <row r="149" spans="1:20" ht="15" customHeight="1">
       <c r="A149" s="69" t="s">
+        <v>784</v>
+      </c>
+      <c r="B149" s="69" t="s">
         <v>785</v>
-      </c>
-      <c r="B149" s="69" t="s">
-        <v>786</v>
       </c>
       <c r="C149" s="69" t="s">
         <v>95</v>
@@ -28798,7 +28852,7 @@
         <v>1024</v>
       </c>
       <c r="L149" s="69" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="M149" s="69"/>
       <c r="N149" s="69" t="s">
@@ -28813,10 +28867,10 @@
     </row>
     <row r="150" spans="1:20" ht="15" customHeight="1">
       <c r="A150" s="66" t="s">
+        <v>787</v>
+      </c>
+      <c r="B150" s="66" t="s">
         <v>788</v>
-      </c>
-      <c r="B150" s="66" t="s">
-        <v>789</v>
       </c>
       <c r="C150" s="66" t="s">
         <v>95</v>
@@ -28863,10 +28917,10 @@
     </row>
     <row r="151" spans="1:20" ht="15" customHeight="1">
       <c r="A151" s="69" t="s">
+        <v>789</v>
+      </c>
+      <c r="B151" s="69" t="s">
         <v>790</v>
-      </c>
-      <c r="B151" s="69" t="s">
-        <v>791</v>
       </c>
       <c r="C151" s="69" t="s">
         <v>96</v>
@@ -28900,7 +28954,7 @@
         <v>645</v>
       </c>
       <c r="L151" s="69" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="M151" s="69"/>
       <c r="N151" s="69" t="s">
@@ -28910,7 +28964,7 @@
         <v>210</v>
       </c>
       <c r="P151" s="69" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="Q151" s="69"/>
       <c r="R151" s="69"/>
@@ -28919,10 +28973,10 @@
     </row>
     <row r="152" spans="1:20" ht="15" customHeight="1">
       <c r="A152" s="66" t="s">
+        <v>793</v>
+      </c>
+      <c r="B152" s="66" t="s">
         <v>794</v>
-      </c>
-      <c r="B152" s="66" t="s">
-        <v>795</v>
       </c>
       <c r="C152" s="66" t="s">
         <v>97</v>
@@ -28956,17 +29010,17 @@
         <v>885</v>
       </c>
       <c r="L152" s="66" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="M152" s="66"/>
       <c r="N152" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O152" s="66" t="s">
+        <v>796</v>
+      </c>
+      <c r="P152" s="66" t="s">
         <v>797</v>
-      </c>
-      <c r="P152" s="66" t="s">
-        <v>798</v>
       </c>
       <c r="Q152" s="66"/>
       <c r="R152" s="66"/>
@@ -28975,10 +29029,10 @@
     </row>
     <row r="153" spans="1:20" ht="15" customHeight="1">
       <c r="A153" s="69" t="s">
+        <v>798</v>
+      </c>
+      <c r="B153" s="69" t="s">
         <v>799</v>
-      </c>
-      <c r="B153" s="69" t="s">
-        <v>800</v>
       </c>
       <c r="C153" s="69" t="s">
         <v>95</v>
@@ -29012,7 +29066,7 @@
         <v>891.5</v>
       </c>
       <c r="L153" s="69" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="M153" s="69"/>
       <c r="N153" s="69" t="s">
@@ -29020,7 +29074,7 @@
       </c>
       <c r="O153" s="69"/>
       <c r="P153" s="69" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="Q153" s="69"/>
       <c r="R153" s="69"/>
@@ -29029,10 +29083,10 @@
     </row>
     <row r="154" spans="1:20" ht="15" customHeight="1">
       <c r="A154" s="66" t="s">
+        <v>802</v>
+      </c>
+      <c r="B154" s="66" t="s">
         <v>803</v>
-      </c>
-      <c r="B154" s="66" t="s">
-        <v>804</v>
       </c>
       <c r="C154" s="66" t="s">
         <v>96</v>
@@ -29066,14 +29120,14 @@
         <v>1898</v>
       </c>
       <c r="L154" s="66" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="M154" s="66"/>
       <c r="N154" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O154" s="66" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="P154" s="66"/>
       <c r="Q154" s="66"/>
@@ -29083,10 +29137,10 @@
     </row>
     <row r="155" spans="1:20" ht="15" customHeight="1">
       <c r="A155" s="69" t="s">
+        <v>806</v>
+      </c>
+      <c r="B155" s="69" t="s">
         <v>807</v>
-      </c>
-      <c r="B155" s="69" t="s">
-        <v>808</v>
       </c>
       <c r="C155" s="69" t="s">
         <v>96</v>
@@ -29125,7 +29179,7 @@
         <v>599</v>
       </c>
       <c r="O155" s="69" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="P155" s="69"/>
       <c r="Q155" s="69"/>
@@ -29135,10 +29189,10 @@
     </row>
     <row r="156" spans="1:20" ht="15" customHeight="1">
       <c r="A156" s="66" t="s">
+        <v>809</v>
+      </c>
+      <c r="B156" s="66" t="s">
         <v>810</v>
-      </c>
-      <c r="B156" s="66" t="s">
-        <v>811</v>
       </c>
       <c r="C156" s="66" t="s">
         <v>96</v>
@@ -29172,14 +29226,14 @@
         <v>2850</v>
       </c>
       <c r="L156" s="66" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="M156" s="66"/>
       <c r="N156" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O156" s="66" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="P156" s="66"/>
       <c r="Q156" s="66"/>
@@ -29189,10 +29243,10 @@
     </row>
     <row r="157" spans="1:20" ht="15" customHeight="1">
       <c r="A157" s="69" t="s">
+        <v>812</v>
+      </c>
+      <c r="B157" s="69" t="s">
         <v>813</v>
-      </c>
-      <c r="B157" s="69" t="s">
-        <v>814</v>
       </c>
       <c r="C157" s="69" t="s">
         <v>96</v>
@@ -29226,14 +29280,14 @@
         <v>1575</v>
       </c>
       <c r="L157" s="69" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="M157" s="69"/>
       <c r="N157" s="69" t="s">
         <v>510</v>
       </c>
       <c r="O157" s="69" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="P157" s="69"/>
       <c r="Q157" s="69"/>
@@ -29243,10 +29297,10 @@
     </row>
     <row r="158" spans="1:20" ht="15" customHeight="1">
       <c r="A158" s="66" t="s">
+        <v>816</v>
+      </c>
+      <c r="B158" s="66" t="s">
         <v>817</v>
-      </c>
-      <c r="B158" s="66" t="s">
-        <v>818</v>
       </c>
       <c r="C158" s="66" t="s">
         <v>96</v>
@@ -29280,14 +29334,14 @@
         <v>3356</v>
       </c>
       <c r="L158" s="66" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="M158" s="66"/>
       <c r="N158" s="66" t="s">
         <v>599</v>
       </c>
       <c r="O158" s="66" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="P158" s="66"/>
       <c r="Q158" s="66"/>
@@ -29297,10 +29351,10 @@
     </row>
     <row r="159" spans="1:20" ht="15" customHeight="1">
       <c r="A159" s="69" t="s">
+        <v>820</v>
+      </c>
+      <c r="B159" s="69" t="s">
         <v>821</v>
-      </c>
-      <c r="B159" s="69" t="s">
-        <v>822</v>
       </c>
       <c r="C159" s="69" t="s">
         <v>96</v>
@@ -29334,14 +29388,14 @@
         <v>2517</v>
       </c>
       <c r="L159" s="69" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="M159" s="69"/>
       <c r="N159" s="69" t="s">
         <v>510</v>
       </c>
       <c r="O159" s="69" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="P159" s="69"/>
       <c r="Q159" s="69"/>
@@ -29351,10 +29405,10 @@
     </row>
     <row r="160" spans="1:20" ht="15" customHeight="1">
       <c r="A160" s="66" t="s">
+        <v>824</v>
+      </c>
+      <c r="B160" s="66" t="s">
         <v>825</v>
-      </c>
-      <c r="B160" s="66" t="s">
-        <v>826</v>
       </c>
       <c r="C160" s="66" t="s">
         <v>95</v>
@@ -29403,10 +29457,10 @@
     </row>
     <row r="161" spans="1:20" ht="15" customHeight="1">
       <c r="A161" s="69" t="s">
+        <v>826</v>
+      </c>
+      <c r="B161" s="69" t="s">
         <v>827</v>
-      </c>
-      <c r="B161" s="69" t="s">
-        <v>828</v>
       </c>
       <c r="C161" s="69" t="s">
         <v>95</v>
@@ -29455,10 +29509,10 @@
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1">
       <c r="A162" s="66" t="s">
+        <v>828</v>
+      </c>
+      <c r="B162" s="66" t="s">
         <v>829</v>
-      </c>
-      <c r="B162" s="66" t="s">
-        <v>830</v>
       </c>
       <c r="C162" s="66" t="s">
         <v>95</v>
@@ -29507,10 +29561,10 @@
     </row>
     <row r="163" spans="1:20" ht="15" customHeight="1">
       <c r="A163" s="69" t="s">
+        <v>830</v>
+      </c>
+      <c r="B163" s="69" t="s">
         <v>831</v>
-      </c>
-      <c r="B163" s="69" t="s">
-        <v>832</v>
       </c>
       <c r="C163" s="69" t="s">
         <v>95</v>
@@ -29557,10 +29611,10 @@
     </row>
     <row r="164" spans="1:20" ht="60" customHeight="1">
       <c r="A164" s="66" t="s">
+        <v>832</v>
+      </c>
+      <c r="B164" s="66" t="s">
         <v>833</v>
-      </c>
-      <c r="B164" s="66" t="s">
-        <v>834</v>
       </c>
       <c r="C164" s="66" t="s">
         <v>95</v>
@@ -29594,7 +29648,7 @@
         <v>1013</v>
       </c>
       <c r="L164" s="66" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="M164" s="66"/>
       <c r="N164" s="66" t="s">
@@ -29602,7 +29656,7 @@
       </c>
       <c r="O164" s="66"/>
       <c r="P164" s="66" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="Q164" s="66"/>
       <c r="R164" s="66"/>
@@ -29611,10 +29665,10 @@
     </row>
     <row r="165" spans="1:20" ht="15" customHeight="1">
       <c r="A165" s="69" t="s">
+        <v>834</v>
+      </c>
+      <c r="B165" s="69" t="s">
         <v>835</v>
-      </c>
-      <c r="B165" s="69" t="s">
-        <v>836</v>
       </c>
       <c r="C165" s="69" t="s">
         <v>95</v>
@@ -29656,7 +29710,7 @@
       </c>
       <c r="O165" s="69"/>
       <c r="P165" s="69" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="Q165" s="69"/>
       <c r="R165" s="69"/>
@@ -29665,10 +29719,10 @@
     </row>
     <row r="166" spans="1:20" ht="15" customHeight="1">
       <c r="A166" s="66" t="s">
+        <v>837</v>
+      </c>
+      <c r="B166" s="66" t="s">
         <v>838</v>
-      </c>
-      <c r="B166" s="66" t="s">
-        <v>839</v>
       </c>
       <c r="C166" s="66" t="s">
         <v>95</v>
@@ -29708,7 +29762,7 @@
       </c>
       <c r="O166" s="66"/>
       <c r="P166" s="66" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q166" s="66"/>
       <c r="R166" s="66"/>
@@ -29717,10 +29771,10 @@
     </row>
     <row r="167" spans="1:20" ht="15" customHeight="1">
       <c r="A167" s="69" t="s">
+        <v>840</v>
+      </c>
+      <c r="B167" s="69" t="s">
         <v>841</v>
-      </c>
-      <c r="B167" s="69" t="s">
-        <v>842</v>
       </c>
       <c r="C167" s="69" t="s">
         <v>95</v>
@@ -29754,7 +29808,7 @@
         <v>2220</v>
       </c>
       <c r="L167" s="69" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="M167" s="69"/>
       <c r="N167" s="69" t="s">
@@ -29762,7 +29816,7 @@
       </c>
       <c r="O167" s="69"/>
       <c r="P167" s="69" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="Q167" s="69"/>
       <c r="R167" s="69"/>
@@ -29771,10 +29825,10 @@
     </row>
     <row r="168" spans="1:20" ht="15" customHeight="1">
       <c r="A168" s="66" t="s">
+        <v>844</v>
+      </c>
+      <c r="B168" s="66" t="s">
         <v>845</v>
-      </c>
-      <c r="B168" s="66" t="s">
-        <v>846</v>
       </c>
       <c r="C168" s="66" t="s">
         <v>95</v>
@@ -29808,7 +29862,7 @@
         <v>1216</v>
       </c>
       <c r="L168" s="66" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="M168" s="66"/>
       <c r="N168" s="66" t="s">
@@ -29816,7 +29870,7 @@
       </c>
       <c r="O168" s="66"/>
       <c r="P168" s="66" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="Q168" s="66"/>
       <c r="R168" s="66"/>
@@ -29825,10 +29879,10 @@
     </row>
     <row r="169" spans="1:20" ht="15" customHeight="1">
       <c r="A169" s="69" t="s">
+        <v>848</v>
+      </c>
+      <c r="B169" s="69" t="s">
         <v>849</v>
-      </c>
-      <c r="B169" s="69" t="s">
-        <v>850</v>
       </c>
       <c r="C169" s="69" t="s">
         <v>95</v>
@@ -29868,7 +29922,7 @@
       </c>
       <c r="O169" s="69"/>
       <c r="P169" s="69" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="Q169" s="69"/>
       <c r="R169" s="69"/>
@@ -29877,10 +29931,10 @@
     </row>
     <row r="170" spans="1:20" ht="30" customHeight="1">
       <c r="A170" s="66" t="s">
+        <v>851</v>
+      </c>
+      <c r="B170" s="66" t="s">
         <v>852</v>
-      </c>
-      <c r="B170" s="66" t="s">
-        <v>853</v>
       </c>
       <c r="C170" s="66" t="s">
         <v>95</v>
@@ -29914,7 +29968,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="66" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="M170" s="66"/>
       <c r="N170" s="66" t="s">
@@ -29922,7 +29976,7 @@
       </c>
       <c r="O170" s="66"/>
       <c r="P170" s="66" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="Q170" s="66"/>
       <c r="R170" s="66"/>
@@ -29931,10 +29985,10 @@
     </row>
     <row r="171" spans="1:20" ht="31.5" customHeight="1">
       <c r="A171" s="69" t="s">
+        <v>855</v>
+      </c>
+      <c r="B171" s="66" t="s">
         <v>856</v>
-      </c>
-      <c r="B171" s="66" t="s">
-        <v>857</v>
       </c>
       <c r="C171" s="69" t="s">
         <v>95</v>
@@ -29968,7 +30022,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="69" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="M171" s="69"/>
       <c r="N171" s="69" t="s">
@@ -29983,10 +30037,10 @@
     </row>
     <row r="172" spans="1:20" ht="15" customHeight="1">
       <c r="A172" s="66" t="s">
+        <v>858</v>
+      </c>
+      <c r="B172" s="66" t="s">
         <v>859</v>
-      </c>
-      <c r="B172" s="66" t="s">
-        <v>860</v>
       </c>
       <c r="C172" s="66" t="s">
         <v>95</v>
@@ -30020,7 +30074,7 @@
         <v>2094</v>
       </c>
       <c r="L172" s="66" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="M172" s="66"/>
       <c r="N172" s="66" t="s">
@@ -30035,10 +30089,10 @@
     </row>
     <row r="173" spans="1:20" ht="15" customHeight="1">
       <c r="A173" s="69" t="s">
+        <v>860</v>
+      </c>
+      <c r="B173" s="69" t="s">
         <v>861</v>
-      </c>
-      <c r="B173" s="69" t="s">
-        <v>862</v>
       </c>
       <c r="C173" s="69" t="s">
         <v>95</v>
@@ -30087,10 +30141,10 @@
     </row>
     <row r="174" spans="1:20" ht="15" customHeight="1">
       <c r="A174" s="66" t="s">
+        <v>862</v>
+      </c>
+      <c r="B174" s="66" t="s">
         <v>863</v>
-      </c>
-      <c r="B174" s="66" t="s">
-        <v>864</v>
       </c>
       <c r="C174" s="66" t="s">
         <v>95</v>
@@ -30124,7 +30178,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="66" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="M174" s="66"/>
       <c r="N174" s="66" t="s">
@@ -30139,10 +30193,10 @@
     </row>
     <row r="175" spans="1:20" ht="90" customHeight="1">
       <c r="A175" s="69" t="s">
+        <v>865</v>
+      </c>
+      <c r="B175" s="69" t="s">
         <v>866</v>
-      </c>
-      <c r="B175" s="69" t="s">
-        <v>867</v>
       </c>
       <c r="C175" s="69" t="s">
         <v>95</v>
@@ -30176,7 +30230,7 @@
         <v>4887.75</v>
       </c>
       <c r="L175" s="69" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="M175" s="69"/>
       <c r="N175" s="69" t="s">
@@ -30184,7 +30238,7 @@
       </c>
       <c r="O175" s="69"/>
       <c r="P175" s="69" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="Q175" s="69"/>
       <c r="R175" s="69"/>
@@ -30193,10 +30247,10 @@
     </row>
     <row r="176" spans="1:20" ht="24" customHeight="1">
       <c r="A176" s="66" t="s">
+        <v>867</v>
+      </c>
+      <c r="B176" s="66" t="s">
         <v>868</v>
-      </c>
-      <c r="B176" s="66" t="s">
-        <v>869</v>
       </c>
       <c r="C176" s="66" t="s">
         <v>95</v>
@@ -30230,7 +30284,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="66" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="M176" s="66"/>
       <c r="N176" s="66" t="s">
@@ -30245,10 +30299,10 @@
     </row>
     <row r="177" spans="1:20" ht="34" customHeight="1">
       <c r="A177" s="69" t="s">
+        <v>869</v>
+      </c>
+      <c r="B177" s="69" t="s">
         <v>870</v>
-      </c>
-      <c r="B177" s="69" t="s">
-        <v>871</v>
       </c>
       <c r="C177" s="69" t="s">
         <v>95</v>
@@ -30282,7 +30336,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="69" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="M177" s="69"/>
       <c r="N177" s="69" t="s">
@@ -30290,7 +30344,7 @@
       </c>
       <c r="O177" s="69"/>
       <c r="P177" s="69" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="Q177" s="69"/>
       <c r="R177" s="69"/>
@@ -30299,10 +30353,10 @@
     </row>
     <row r="178" spans="1:20" ht="15" customHeight="1">
       <c r="A178" s="66" t="s">
+        <v>872</v>
+      </c>
+      <c r="B178" s="66" t="s">
         <v>873</v>
-      </c>
-      <c r="B178" s="66" t="s">
-        <v>874</v>
       </c>
       <c r="C178" s="66" t="s">
         <v>95</v>
@@ -30336,7 +30390,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="66" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="M178" s="66"/>
       <c r="N178" s="66" t="s">
@@ -30344,7 +30398,7 @@
       </c>
       <c r="O178" s="66"/>
       <c r="P178" s="66" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="Q178" s="66"/>
       <c r="R178" s="66"/>
@@ -30353,10 +30407,10 @@
     </row>
     <row r="179" spans="1:20" ht="30" customHeight="1">
       <c r="A179" s="69" t="s">
+        <v>875</v>
+      </c>
+      <c r="B179" s="69" t="s">
         <v>876</v>
-      </c>
-      <c r="B179" s="69" t="s">
-        <v>877</v>
       </c>
       <c r="C179" s="69" t="s">
         <v>95</v>
@@ -30390,7 +30444,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="69" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="M179" s="69"/>
       <c r="N179" s="69" t="s">
@@ -30398,7 +30452,7 @@
       </c>
       <c r="O179" s="69"/>
       <c r="P179" s="69" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="Q179" s="69"/>
       <c r="R179" s="69"/>
@@ -30407,10 +30461,10 @@
     </row>
     <row r="180" spans="1:20" ht="34" customHeight="1">
       <c r="A180" s="66" t="s">
+        <v>879</v>
+      </c>
+      <c r="B180" s="66" t="s">
         <v>880</v>
-      </c>
-      <c r="B180" s="66" t="s">
-        <v>881</v>
       </c>
       <c r="C180" s="66" t="s">
         <v>95</v>
@@ -30444,7 +30498,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="66" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="M180" s="66"/>
       <c r="N180" s="66" t="s">
@@ -30459,7 +30513,7 @@
     </row>
     <row r="181" spans="1:20" ht="15" customHeight="1">
       <c r="A181" s="69" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B181" s="69"/>
       <c r="C181" s="69"/>
@@ -30483,7 +30537,7 @@
     </row>
     <row r="182" spans="1:20" ht="15" customHeight="1">
       <c r="A182" s="66" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B182" s="66"/>
       <c r="C182" s="66"/>
@@ -30507,7 +30561,7 @@
     </row>
     <row r="183" spans="1:20" ht="15" customHeight="1">
       <c r="A183" s="69" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B183" s="69"/>
       <c r="C183" s="69"/>
@@ -30531,7 +30585,7 @@
     </row>
     <row r="184" spans="1:20" ht="15" customHeight="1">
       <c r="A184" s="66" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B184" s="66"/>
       <c r="C184" s="66"/>
@@ -30555,7 +30609,7 @@
     </row>
     <row r="185" spans="1:20" ht="15" customHeight="1">
       <c r="A185" s="69" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B185" s="69"/>
       <c r="C185" s="69"/>
@@ -30579,7 +30633,7 @@
     </row>
     <row r="186" spans="1:20" ht="15" customHeight="1">
       <c r="A186" s="66" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B186" s="66"/>
       <c r="C186" s="66"/>
@@ -30603,7 +30657,7 @@
     </row>
     <row r="187" spans="1:20" ht="15" customHeight="1">
       <c r="A187" s="69" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B187" s="69"/>
       <c r="C187" s="69"/>
@@ -30627,7 +30681,7 @@
     </row>
     <row r="188" spans="1:20" ht="15" customHeight="1">
       <c r="A188" s="66" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B188" s="66"/>
       <c r="C188" s="66"/>
@@ -34702,7 +34756,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1">
       <c r="A1" s="95" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B1" s="95"/>
     </row>
@@ -34711,7 +34765,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1">
@@ -34743,25 +34797,25 @@
         <v>42</v>
       </c>
       <c r="B7" s="86" t="s">
+        <v>891</v>
+      </c>
+      <c r="C7" s="86" t="s">
         <v>892</v>
       </c>
-      <c r="C7" s="86" t="s">
+      <c r="D7" s="86" t="s">
         <v>893</v>
       </c>
-      <c r="D7" s="86" t="s">
+      <c r="E7" s="86" t="s">
         <v>894</v>
       </c>
-      <c r="E7" s="86" t="s">
+      <c r="F7" s="86" t="s">
         <v>895</v>
       </c>
-      <c r="F7" s="86" t="s">
+      <c r="G7" s="86" t="s">
         <v>896</v>
       </c>
-      <c r="G7" s="86" t="s">
+      <c r="H7" s="86" t="s">
         <v>897</v>
-      </c>
-      <c r="H7" s="86" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1">
@@ -34865,7 +34919,7 @@
     </row>
     <row r="12" spans="1:8" s="90" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="96" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B12" s="96"/>
       <c r="C12" s="96"/>
@@ -34878,13 +34932,13 @@
         <v>98</v>
       </c>
       <c r="B13" s="86" t="s">
+        <v>899</v>
+      </c>
+      <c r="C13" s="86" t="s">
         <v>900</v>
       </c>
-      <c r="C13" s="86" t="s">
+      <c r="D13" s="86" t="s">
         <v>901</v>
-      </c>
-      <c r="D13" s="86" t="s">
-        <v>902</v>
       </c>
       <c r="E13" s="86" t="s">
         <v>99</v>
@@ -34898,7 +34952,7 @@
         <v>45952</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>51</v>
@@ -34916,7 +34970,7 @@
         <v>45952</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>51</v>
@@ -34970,7 +35024,7 @@
         <v>45970</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>50</v>
@@ -34988,7 +35042,7 @@
         <v>45970</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>50</v>
@@ -35006,7 +35060,7 @@
         <v>45973</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>50</v>
@@ -35024,7 +35078,7 @@
         <v>45973</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>49</v>
@@ -35042,7 +35096,7 @@
         <v>46058</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>51</v>
@@ -35078,7 +35132,7 @@
         <v>46059</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>49</v>
@@ -35114,7 +35168,7 @@
         <v>46093</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>50</v>
@@ -35132,7 +35186,7 @@
         <v>46093</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>51</v>
@@ -35215,7 +35269,7 @@
     </row>
     <row r="58" spans="2:2" ht="13.5" customHeight="1">
       <c r="B58" s="6" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
   </sheetData>
@@ -35245,7 +35299,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13.5" customHeight="1">
       <c r="A1" s="93" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="87" customFormat="1" ht="13.5" customHeight="1">
@@ -35253,22 +35307,22 @@
         <v>42</v>
       </c>
       <c r="B3" s="86" t="s">
+        <v>905</v>
+      </c>
+      <c r="C3" s="86" t="s">
+        <v>890</v>
+      </c>
+      <c r="D3" s="86" t="s">
         <v>906</v>
       </c>
-      <c r="C3" s="86" t="s">
-        <v>891</v>
-      </c>
-      <c r="D3" s="86" t="s">
+      <c r="E3" s="86" t="s">
         <v>907</v>
       </c>
-      <c r="E3" s="86" t="s">
+      <c r="F3" s="86" t="s">
         <v>908</v>
       </c>
-      <c r="F3" s="86" t="s">
+      <c r="G3" s="86" t="s">
         <v>909</v>
-      </c>
-      <c r="G3" s="86" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1">
@@ -35277,7 +35331,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>283365</v>
+        <v>286663</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -35285,11 +35339,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>113844.09759999999</v>
+        <v>114943.65079999999</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>169520.90240000002</v>
+        <v>171719.3492</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35297,7 +35351,7 @@
       </c>
       <c r="G4" s="88">
         <f>E4+F4</f>
-        <v>32210.876400000008</v>
+        <v>34409.323199999984</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -35314,11 +35368,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>113775.8048</v>
+        <v>114874.69839999999</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-68206.804799999998</v>
+        <v>-69305.698399999994</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35326,7 +35380,7 @@
       </c>
       <c r="G5" s="89">
         <f>E5+F5</f>
-        <v>3380.2372000000032</v>
+        <v>2281.3436000000074</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -35343,11 +35397,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>113844.09759999999</v>
+        <v>114943.65079999999</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-101314.09759999999</v>
+        <v>-102413.65079999999</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35355,7 +35409,7 @@
       </c>
       <c r="G6" s="88">
         <f>E6+F6</f>
-        <v>-35591.113599999982</v>
+        <v>-36690.666799999977</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">
@@ -35365,27 +35419,27 @@
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Chiraath-Summary-Jun26.xlsx
+++ b/docs/Chiraath-Summary-Jun26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BEC430-30A1-8749-9F7B-35009014FB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA0668F-0587-AE42-A516-1D92C0DF7564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">INVENTORY!$A$1:$T$188</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Purchases!$A$1:$D$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$214</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2416" uniqueCount="964">
   <si>
     <t>Notes:</t>
   </si>
@@ -2941,12 +2941,24 @@
     <t>Kalaisari (Dharmapuri)</t>
   </si>
   <si>
+    <t>Latha Suresh (Malappuram)</t>
+  </si>
+  <si>
     <t>First Set: Aruna - violet, Resmi - navy blue, Malini - Rani Pink
-Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black, Bindu Krisharaj - Black, Kavitha - off white, Jisha Suresh - Rani Pink(2), Sudharma - Navy Blue, SIndrella - Maroon, Shaino Benny - Navy blue, Simi Sudhir - Navy Blue, Supriya - Green, Mercy - Black, Kalisari - Green</t>
+Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black, Bindu Krisharaj - Black, Kavitha - off white, Jisha Suresh - Rani Pink(2), Sudharma - Navy Blue, SIndrella - Maroon, Shaino Benny - Navy blue, Simi Sudhir - Navy Blue, Supriya - Green, Mercy - Black, Kalisari - Green, Latha Suresh - Black</t>
   </si>
   <si>
     <t xml:space="preserve">
-Blue (2), mustard yellow (1), Maroon (1), off white (1), Orange (1), Black(4), White(5)</t>
+Blue (2), mustard yellow (1), Maroon (1), off white (1), Orange (1), Black(3), White(5)</t>
+  </si>
+  <si>
+    <t>Boostin charges</t>
+  </si>
+  <si>
+    <t>Kannur Salwar Purchase</t>
+  </si>
+  <si>
+    <t>Courier covers and butter papers</t>
   </si>
 </sst>
 </file>
@@ -3859,7 +3871,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>208</c:v>
+                  <c:v>209</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>86</c:v>
@@ -3962,7 +3974,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>64</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>59</c:v>
@@ -4295,7 +4307,7 @@
                   <c:v>61609</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>43034.31</c:v>
+                  <c:v>42615.356666666667</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1357</c:v>
@@ -4625,7 +4637,7 @@
                   <c:v>4449</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>4440</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -4779,13 +4791,13 @@
                   <c:v>16248</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>55237</c:v>
+                  <c:v>55267</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>53524</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9144</c:v>
+                  <c:v>9843</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5219,13 +5231,13 @@
                   <c:v>-5924</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-15765</c:v>
+                  <c:v>-15735</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>49075</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9144</c:v>
+                  <c:v>5403</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5692,10 +5704,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>297</c:v>
+                  <c:v>298</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>127</c:v>
+                  <c:v>126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6867,7 +6879,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>354742</v>
+        <v>359182</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -6882,7 +6894,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>344762</v>
+        <v>346141</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -6899,7 +6911,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>364717</v>
+        <v>365446</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -6916,7 +6928,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-9980</v>
+        <v>-13041</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -6951,7 +6963,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>18214.326666666671</v>
+        <v>20214.326666666671</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -6961,7 +6973,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>7490.3366666666698</v>
+        <v>6970.3366666666698</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -6971,7 +6983,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-25704.66333333333</v>
+        <v>-27184.66333333333</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -7010,15 +7022,15 @@
       </c>
       <c r="B18" s="10">
         <f>PartnerShares!B8</f>
-        <v>154765</v>
+        <v>158245</v>
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>118247.33333333333</v>
+        <v>119727.33333333333</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>36517.666666666672</v>
+        <v>38517.666666666672</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7026,11 +7038,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>18214.326666666671</v>
+        <v>20214.326666666671</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹18,214</v>
+        <v>Receive ₹20,214</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -7040,15 +7052,15 @@
       </c>
       <c r="B19" s="12">
         <f>PartnerShares!B9</f>
-        <v>167377</v>
+        <v>168337</v>
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>118247.33333333333</v>
+        <v>119727.33333333333</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>49129.666666666672</v>
+        <v>48609.666666666672</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7056,11 +7068,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>7490.3366666666698</v>
+        <v>6970.3366666666698</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹7,490</v>
+        <v>Receive ₹6,970</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -7074,11 +7086,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>118247.33333333333</v>
+        <v>119727.33333333333</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-85647.333333333328</v>
+        <v>-87127.333333333328</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7086,11 +7098,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-25704.66333333333</v>
+        <v>-27184.66333333333</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹25,705</v>
+        <v>Pay ₹27,185</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -7128,15 +7140,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>286663</v>
+        <v>288042</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>114943.65079999999</v>
+        <v>115403.40939999999</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>171719.3492</v>
+        <v>172638.5906</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -7144,11 +7156,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>34409.323199999984</v>
+        <v>35328.564599999983</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹34,409</v>
+        <v>Pay ₹35,329</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -7162,11 +7174,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>114874.69839999999</v>
+        <v>115334.18119999999</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-69305.698399999994</v>
+        <v>-69765.181199999992</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -7174,11 +7186,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>2281.3436000000074</v>
+        <v>1821.8608000000095</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹2,281</v>
+        <v>Pay ₹1,822</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -7192,11 +7204,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>114943.65079999999</v>
+        <v>115403.40939999999</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-102413.65079999999</v>
+        <v>-102873.40939999999</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -7204,11 +7216,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-36690.666799999977</v>
+        <v>-37150.425399999978</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹36,691</v>
+        <v>Receive ₹37,150</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -7320,7 +7332,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46176</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -7329,14 +7341,14 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>354742</v>
+        <v>359182</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>344762</v>
+        <v>346141</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7345,14 +7357,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-9980</v>
+        <v>-13041</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>96696.50999999998</v>
+        <v>96277.556666666656</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -7404,7 +7416,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7428,7 +7440,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7458,11 +7470,11 @@
       </c>
       <c r="C13" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A13)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>55237</v>
+        <v>55267</v>
       </c>
       <c r="D13" s="27">
         <f t="shared" si="0"/>
-        <v>-15765</v>
+        <v>-15735</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
@@ -7488,15 +7500,15 @@
       </c>
       <c r="B15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A15)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>0</v>
+        <v>4440</v>
       </c>
       <c r="C15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>9144</v>
+        <v>9843</v>
       </c>
       <c r="D15" s="27">
         <f t="shared" si="0"/>
-        <v>9144</v>
+        <v>5403</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
@@ -7624,11 +7636,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -7655,7 +7667,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>43034.31</v>
+        <v>42615.356666666667</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -8780,28 +8792,60 @@
       </c>
     </row>
     <row r="74" spans="1:4" ht="15" customHeight="1">
-      <c r="A74" s="35"/>
-      <c r="B74" s="36"/>
-      <c r="C74" s="37"/>
-      <c r="D74" s="36"/>
+      <c r="A74" s="35">
+        <v>46176</v>
+      </c>
+      <c r="B74" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C74" s="37">
+        <v>960</v>
+      </c>
+      <c r="D74" s="36" t="s">
+        <v>961</v>
+      </c>
     </row>
     <row r="75" spans="1:4" ht="15" customHeight="1">
-      <c r="A75" s="38"/>
-      <c r="B75" s="39"/>
-      <c r="C75" s="40"/>
-      <c r="D75" s="39"/>
+      <c r="A75" s="38">
+        <v>46176</v>
+      </c>
+      <c r="B75" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C75" s="40">
+        <v>400</v>
+      </c>
+      <c r="D75" s="39" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="76" spans="1:4" ht="15" customHeight="1">
-      <c r="A76" s="35"/>
-      <c r="B76" s="36"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="36"/>
+      <c r="A76" s="35">
+        <v>46177</v>
+      </c>
+      <c r="B76" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C76" s="37">
+        <v>2900</v>
+      </c>
+      <c r="D76" s="36" t="s">
+        <v>962</v>
+      </c>
     </row>
     <row r="77" spans="1:4" ht="15" customHeight="1">
-      <c r="A77" s="38"/>
-      <c r="B77" s="39"/>
-      <c r="C77" s="40"/>
-      <c r="D77" s="39"/>
+      <c r="A77" s="38">
+        <v>46177</v>
+      </c>
+      <c r="B77" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C77" s="40">
+        <v>180</v>
+      </c>
+      <c r="D77" s="39" t="s">
+        <v>963</v>
+      </c>
     </row>
     <row r="78" spans="1:4" ht="15" customHeight="1">
       <c r="A78" s="35"/>
@@ -15217,9 +15261,11 @@
         <v>208</v>
       </c>
       <c r="C171" s="54">
-        <v>650</v>
-      </c>
-      <c r="D171" s="53"/>
+        <v>680</v>
+      </c>
+      <c r="D171" s="53" t="s">
+        <v>156</v>
+      </c>
       <c r="E171" s="53" t="s">
         <v>49</v>
       </c>
@@ -15229,7 +15275,7 @@
         <v>363</v>
       </c>
       <c r="I171" s="53" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="13.5" customHeight="1">
@@ -16279,15 +16325,29 @@
       </c>
     </row>
     <row r="214" spans="1:9">
-      <c r="A214" s="52"/>
-      <c r="B214" s="53"/>
-      <c r="C214" s="54"/>
-      <c r="D214" s="53"/>
-      <c r="E214" s="53"/>
+      <c r="A214" s="52">
+        <v>46177</v>
+      </c>
+      <c r="B214" s="53" t="s">
+        <v>958</v>
+      </c>
+      <c r="C214" s="54">
+        <v>699</v>
+      </c>
+      <c r="D214" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E214" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F214" s="56"/>
       <c r="G214" s="56"/>
-      <c r="H214" s="57"/>
-      <c r="I214" s="53"/>
+      <c r="H214" s="56" t="s">
+        <v>929</v>
+      </c>
+      <c r="I214" s="53" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="215" spans="1:9">
       <c r="A215" s="48"/>
@@ -16793,7 +16853,7 @@
       <c r="I260" s="59"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I212" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:I214" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1260" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Ordered,Pending,Completed,Cancelled"</formula1>
@@ -26636,10 +26696,10 @@
         <v>699</v>
       </c>
       <c r="F120" s="67">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G120" s="67">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H120" s="66">
         <f t="shared" si="9"/>
@@ -26651,14 +26711,14 @@
       </c>
       <c r="J120" s="66">
         <f t="shared" si="10"/>
-        <v>14244.413333333321</v>
+        <v>14663.366666666654</v>
       </c>
       <c r="K120" s="66">
         <f t="shared" si="11"/>
-        <v>6284.2999999999947</v>
+        <v>5865.3466666666618</v>
       </c>
       <c r="L120" s="66" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="M120" s="66" t="s">
         <v>49</v>
@@ -26668,7 +26728,7 @@
       </c>
       <c r="O120" s="66"/>
       <c r="P120" s="66" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="Q120" s="66"/>
       <c r="R120" s="66"/>
@@ -34824,15 +34884,15 @@
       </c>
       <c r="B8" s="9">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A8,Purchases!$C:$C),0)</f>
-        <v>154765</v>
+        <v>158245</v>
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>118247.33333333333</v>
+        <v>119727.33333333333</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>36517.666666666672</v>
+        <v>38517.666666666672</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -34840,7 +34900,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>36517.666666666672</v>
+        <v>38517.666666666672</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -34848,7 +34908,7 @@
       </c>
       <c r="H8" s="88">
         <f>F8-G8</f>
-        <v>18214.326666666671</v>
+        <v>20214.326666666671</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -34857,15 +34917,15 @@
       </c>
       <c r="B9" s="11">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A9,Purchases!$C:$C),0)</f>
-        <v>167377</v>
+        <v>168337</v>
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>118247.33333333333</v>
+        <v>119727.33333333333</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>49129.666666666672</v>
+        <v>48609.666666666672</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -34873,7 +34933,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>49129.666666666672</v>
+        <v>48609.666666666672</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -34881,7 +34941,7 @@
       </c>
       <c r="H9" s="89">
         <f>F9-G9</f>
-        <v>7490.3366666666698</v>
+        <v>6970.3366666666698</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -34894,11 +34954,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>118247.33333333333</v>
+        <v>119727.33333333333</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-85647.333333333328</v>
+        <v>-87127.333333333328</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -34906,7 +34966,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-85647.333333333328</v>
+        <v>-87127.333333333328</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -34914,7 +34974,7 @@
       </c>
       <c r="H10" s="88">
         <f>F10-G10</f>
-        <v>-25704.66333333333</v>
+        <v>-27184.66333333333</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="90" customFormat="1" ht="15.75" customHeight="1">
@@ -35331,7 +35391,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>286663</v>
+        <v>288042</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -35339,11 +35399,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>114943.65079999999</v>
+        <v>115403.40939999999</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>171719.3492</v>
+        <v>172638.5906</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35351,7 +35411,7 @@
       </c>
       <c r="G4" s="88">
         <f>E4+F4</f>
-        <v>34409.323199999984</v>
+        <v>35328.564599999983</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -35368,11 +35428,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>114874.69839999999</v>
+        <v>115334.18119999999</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-69305.698399999994</v>
+        <v>-69765.181199999992</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35380,7 +35440,7 @@
       </c>
       <c r="G5" s="89">
         <f>E5+F5</f>
-        <v>2281.3436000000074</v>
+        <v>1821.8608000000095</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -35397,11 +35457,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>114943.65079999999</v>
+        <v>115403.40939999999</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-102413.65079999999</v>
+        <v>-102873.40939999999</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35409,7 +35469,7 @@
       </c>
       <c r="G6" s="88">
         <f>E6+F6</f>
-        <v>-36690.666799999977</v>
+        <v>-37150.425399999978</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">

--- a/docs/Chiraath-Summary-Jun26.xlsx
+++ b/docs/Chiraath-Summary-Jun26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA0668F-0587-AE42-A516-1D92C0DF7564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C4AA3B-FDC8-314D-8B5B-49CF0365A1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2416" uniqueCount="964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2423" uniqueCount="965">
   <si>
     <t>Notes:</t>
   </si>
@@ -2807,13 +2807,7 @@
     <t>5. Cash Position After Settlements = Over/(Under) + Net Cash Settlements.</t>
   </si>
   <si>
-    <t>Banarasi Green Old design (1000 advance)</t>
-  </si>
-  <si>
     <t>Sungudi (Alice Christy inspired)</t>
-  </si>
-  <si>
-    <t>Salwar maroon single piece M (CHR-78) - 500 advance, 300 pending</t>
   </si>
   <si>
     <t>Revathi</t>
@@ -2959,6 +2953,15 @@
   </si>
   <si>
     <t>Courier covers and butter papers</t>
+  </si>
+  <si>
+    <t>Salwar maroon single piece M (CHR-78)</t>
+  </si>
+  <si>
+    <t>Banarasi Green Old design</t>
+  </si>
+  <si>
+    <t>Postal parcel charges</t>
   </si>
 </sst>
 </file>
@@ -3977,7 +3980,7 @@
                   <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>59</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>4</c:v>
@@ -4304,7 +4307,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>61609</c:v>
+                  <c:v>60714</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>42615.356666666667</c:v>
@@ -4637,7 +4640,7 @@
                   <c:v>4449</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4440</c:v>
+                  <c:v>4524</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -4791,7 +4794,7 @@
                   <c:v>16248</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>55267</c:v>
+                  <c:v>54177</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>53524</c:v>
@@ -5231,13 +5234,13 @@
                   <c:v>-5924</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-15735</c:v>
+                  <c:v>-16825</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>49075</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5403</c:v>
+                  <c:v>5319</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5707,7 +5710,7 @@
                   <c:v>298</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>126</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6879,7 +6882,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>359182</v>
+        <v>359266</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -6894,7 +6897,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>346141</v>
+        <v>351391</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -6911,7 +6914,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>365446</v>
+        <v>364356</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -6928,7 +6931,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-13041</v>
+        <v>-7875</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -6963,7 +6966,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>20214.326666666671</v>
+        <v>20270.326666666671</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -6973,7 +6976,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>6970.3366666666698</v>
+        <v>6942.3366666666698</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -6983,7 +6986,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-27184.66333333333</v>
+        <v>-27212.66333333333</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -7022,15 +7025,15 @@
       </c>
       <c r="B18" s="10">
         <f>PartnerShares!B8</f>
-        <v>158245</v>
+        <v>158329</v>
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>119727.33333333333</v>
+        <v>119755.33333333333</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>38517.666666666672</v>
+        <v>38573.666666666672</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7038,11 +7041,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>20214.326666666671</v>
+        <v>20270.326666666671</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹20,214</v>
+        <v>Receive ₹20,270</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -7056,11 +7059,11 @@
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>119727.33333333333</v>
+        <v>119755.33333333333</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>48609.666666666672</v>
+        <v>48581.666666666672</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7068,11 +7071,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>6970.3366666666698</v>
+        <v>6942.3366666666698</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹6,970</v>
+        <v>Receive ₹6,942</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -7086,11 +7089,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>119727.33333333333</v>
+        <v>119755.33333333333</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-87127.333333333328</v>
+        <v>-87155.333333333328</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7098,11 +7101,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-27184.66333333333</v>
+        <v>-27212.66333333333</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹27,185</v>
+        <v>Pay ₹27,213</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -7140,15 +7143,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>288042</v>
+        <v>293292</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>115403.40939999999</v>
+        <v>117153.7594</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>172638.5906</v>
+        <v>176138.24060000002</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -7156,11 +7159,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>35328.564599999983</v>
+        <v>38828.214600000007</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹35,329</v>
+        <v>Pay ₹38,828</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -7174,11 +7177,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>115334.18119999999</v>
+        <v>117083.48119999999</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-69765.181199999992</v>
+        <v>-71514.481199999995</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -7186,11 +7189,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>1821.8608000000095</v>
+        <v>72.560800000006566</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹1,822</v>
+        <v>Pay ₹73</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -7204,11 +7207,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>115403.40939999999</v>
+        <v>117153.7594</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-102873.40939999999</v>
+        <v>-104623.7594</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -7216,11 +7219,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-37150.425399999978</v>
+        <v>-38900.775399999984</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹37,150</v>
+        <v>Receive ₹38,901</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -7332,7 +7335,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -7341,14 +7344,14 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>359182</v>
+        <v>359266</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>346141</v>
+        <v>351391</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7357,7 +7360,7 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-13041</v>
+        <v>-7875</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
@@ -7440,7 +7443,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7470,11 +7473,11 @@
       </c>
       <c r="C13" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A13)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>55267</v>
+        <v>54177</v>
       </c>
       <c r="D13" s="27">
         <f t="shared" si="0"/>
-        <v>-15735</v>
+        <v>-16825</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
@@ -7500,7 +7503,7 @@
       </c>
       <c r="B15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A15)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>4440</v>
+        <v>4524</v>
       </c>
       <c r="C15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
@@ -7508,7 +7511,7 @@
       </c>
       <c r="D15" s="27">
         <f t="shared" si="0"/>
-        <v>5403</v>
+        <v>5319</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
@@ -7647,7 +7650,7 @@
       </c>
       <c r="K47" s="31">
         <f t="array" ref="K47">SUMPRODUCT((INVENTORY!$C$2:$C$477=J47)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>61609</v>
+        <v>60714</v>
       </c>
     </row>
     <row r="48" spans="6:11" ht="15" customHeight="1">
@@ -7660,7 +7663,7 @@
       </c>
       <c r="H48" s="30">
         <f>SUMIF(INVENTORY!C:C, F48, INVENTORY!G:G)</f>
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J48" s="30" t="s">
         <v>95</v>
@@ -8802,7 +8805,7 @@
         <v>960</v>
       </c>
       <c r="D74" s="36" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15" customHeight="1">
@@ -8830,7 +8833,7 @@
         <v>2900</v>
       </c>
       <c r="D76" s="36" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15" customHeight="1">
@@ -8844,14 +8847,22 @@
         <v>180</v>
       </c>
       <c r="D77" s="39" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15" customHeight="1">
-      <c r="A78" s="35"/>
-      <c r="B78" s="36"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="36"/>
+      <c r="A78" s="35">
+        <v>46178</v>
+      </c>
+      <c r="B78" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C78" s="37">
+        <v>84</v>
+      </c>
+      <c r="D78" s="36" t="s">
+        <v>964</v>
+      </c>
     </row>
     <row r="79" spans="1:4" ht="15" customHeight="1">
       <c r="A79" s="38"/>
@@ -14734,7 +14745,7 @@
       <c r="F149" s="49"/>
       <c r="G149" s="49"/>
       <c r="H149" s="51" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="I149" s="49" t="s">
         <v>142</v>
@@ -14996,7 +15007,7 @@
         <v>352</v>
       </c>
       <c r="C160" s="54">
-        <v>1380</v>
+        <v>1000</v>
       </c>
       <c r="D160" s="53" t="s">
         <v>156</v>
@@ -15007,10 +15018,10 @@
       <c r="F160" s="56"/>
       <c r="G160" s="56"/>
       <c r="H160" s="57" t="s">
-        <v>915</v>
+        <v>963</v>
       </c>
       <c r="I160" s="53" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="13.5" customHeight="1">
@@ -15096,9 +15107,11 @@
         <v>209</v>
       </c>
       <c r="C164" s="54">
-        <v>1380</v>
-      </c>
-      <c r="D164" s="53"/>
+        <v>1000</v>
+      </c>
+      <c r="D164" s="53" t="s">
+        <v>156</v>
+      </c>
       <c r="E164" s="53" t="s">
         <v>49</v>
       </c>
@@ -15108,7 +15121,7 @@
         <v>358</v>
       </c>
       <c r="I164" s="53" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="13.5" customHeight="1">
@@ -15119,9 +15132,11 @@
         <v>158</v>
       </c>
       <c r="C165" s="50">
-        <v>1380</v>
-      </c>
-      <c r="D165" s="49"/>
+        <v>1200</v>
+      </c>
+      <c r="D165" s="49" t="s">
+        <v>156</v>
+      </c>
       <c r="E165" s="49" t="s">
         <v>49</v>
       </c>
@@ -15131,7 +15146,7 @@
         <v>359</v>
       </c>
       <c r="I165" s="49" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="13.5" customHeight="1">
@@ -15167,9 +15182,11 @@
         <v>185</v>
       </c>
       <c r="C167" s="50">
-        <v>1250</v>
-      </c>
-      <c r="D167" s="49"/>
+        <v>1100</v>
+      </c>
+      <c r="D167" s="49" t="s">
+        <v>156</v>
+      </c>
       <c r="E167" s="49" t="s">
         <v>49</v>
       </c>
@@ -15179,7 +15196,7 @@
         <v>362</v>
       </c>
       <c r="I167" s="49" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="13.5" customHeight="1">
@@ -15192,17 +15209,19 @@
       <c r="C168" s="50">
         <v>950</v>
       </c>
-      <c r="D168" s="49"/>
+      <c r="D168" s="49" t="s">
+        <v>156</v>
+      </c>
       <c r="E168" s="49" t="s">
         <v>49</v>
       </c>
       <c r="F168" s="49"/>
       <c r="G168" s="49"/>
       <c r="H168" s="51" t="s">
-        <v>917</v>
+        <v>962</v>
       </c>
       <c r="I168" s="49" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="13.5" customHeight="1">
@@ -15215,7 +15234,9 @@
       <c r="C169" s="54">
         <v>650</v>
       </c>
-      <c r="D169" s="53"/>
+      <c r="D169" s="53" t="s">
+        <v>156</v>
+      </c>
       <c r="E169" s="53" t="s">
         <v>49</v>
       </c>
@@ -15497,7 +15518,7 @@
       <c r="F180" s="49"/>
       <c r="G180" s="49"/>
       <c r="H180" s="51" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="I180" s="49" t="s">
         <v>142</v>
@@ -15929,7 +15950,7 @@
         <v>46168</v>
       </c>
       <c r="B198" s="53" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C198" s="54">
         <v>5200</v>
@@ -15943,7 +15964,7 @@
       <c r="F198" s="56"/>
       <c r="G198" s="56"/>
       <c r="H198" s="57" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="I198" s="53" t="s">
         <v>142</v>
@@ -15954,7 +15975,7 @@
         <v>46172</v>
       </c>
       <c r="B199" s="49" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C199" s="50">
         <v>1425</v>
@@ -15968,7 +15989,7 @@
       <c r="F199" s="49"/>
       <c r="G199" s="49"/>
       <c r="H199" s="51" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="I199" s="49" t="s">
         <v>341</v>
@@ -15979,7 +16000,7 @@
         <v>46173</v>
       </c>
       <c r="B200" s="53" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C200" s="54">
         <v>2850</v>
@@ -15993,7 +16014,7 @@
       <c r="F200" s="56"/>
       <c r="G200" s="56"/>
       <c r="H200" s="57" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="I200" s="53" t="s">
         <v>341</v>
@@ -16004,7 +16025,7 @@
         <v>46173</v>
       </c>
       <c r="B201" s="49" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C201" s="50">
         <v>2850</v>
@@ -16018,7 +16039,7 @@
       <c r="F201" s="49"/>
       <c r="G201" s="49"/>
       <c r="H201" s="51" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="I201" s="49" t="s">
         <v>341</v>
@@ -16029,7 +16050,7 @@
         <v>46173</v>
       </c>
       <c r="B202" s="53" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C202" s="54">
         <v>930</v>
@@ -16043,7 +16064,7 @@
       <c r="F202" s="56"/>
       <c r="G202" s="56"/>
       <c r="H202" s="57" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="I202" s="53" t="s">
         <v>341</v>
@@ -16054,7 +16075,7 @@
         <v>46173</v>
       </c>
       <c r="B203" s="49" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C203" s="50">
         <v>930</v>
@@ -16068,7 +16089,7 @@
       <c r="F203" s="49"/>
       <c r="G203" s="49"/>
       <c r="H203" s="51" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="I203" s="49" t="s">
         <v>341</v>
@@ -16079,7 +16100,7 @@
         <v>46175</v>
       </c>
       <c r="B204" s="53" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C204" s="54">
         <v>699</v>
@@ -16093,7 +16114,7 @@
       <c r="F204" s="56"/>
       <c r="G204" s="56"/>
       <c r="H204" s="57" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="I204" s="53" t="s">
         <v>142</v>
@@ -16104,7 +16125,7 @@
         <v>46175</v>
       </c>
       <c r="B205" s="49" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C205" s="50">
         <v>700</v>
@@ -16118,7 +16139,7 @@
       <c r="F205" s="49"/>
       <c r="G205" s="49"/>
       <c r="H205" s="51" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="I205" s="49" t="s">
         <v>142</v>
@@ -16129,7 +16150,7 @@
         <v>46175</v>
       </c>
       <c r="B206" s="53" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C206" s="54">
         <v>1350</v>
@@ -16143,7 +16164,7 @@
       <c r="F206" s="56"/>
       <c r="G206" s="56"/>
       <c r="H206" s="51" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="I206" s="53" t="s">
         <v>142</v>
@@ -16154,7 +16175,7 @@
         <v>46175</v>
       </c>
       <c r="B207" s="49" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C207" s="50">
         <v>699</v>
@@ -16168,7 +16189,7 @@
       <c r="F207" s="49"/>
       <c r="G207" s="49"/>
       <c r="H207" s="51" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="I207" s="49" t="s">
         <v>142</v>
@@ -16179,7 +16200,7 @@
         <v>46175</v>
       </c>
       <c r="B208" s="53" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="C208" s="54">
         <v>699</v>
@@ -16193,7 +16214,7 @@
       <c r="F208" s="56"/>
       <c r="G208" s="56"/>
       <c r="H208" s="57" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="I208" s="53" t="s">
         <v>142</v>
@@ -16204,7 +16225,7 @@
         <v>46176</v>
       </c>
       <c r="B209" s="49" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C209" s="50">
         <v>699</v>
@@ -16218,7 +16239,7 @@
       <c r="F209" s="49"/>
       <c r="G209" s="49"/>
       <c r="H209" s="51" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="I209" s="49" t="s">
         <v>142</v>
@@ -16229,7 +16250,7 @@
         <v>46176</v>
       </c>
       <c r="B210" s="53" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="C210" s="54">
         <v>2200</v>
@@ -16243,7 +16264,7 @@
       <c r="F210" s="56"/>
       <c r="G210" s="56"/>
       <c r="H210" s="57" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="I210" s="53" t="s">
         <v>142</v>
@@ -16254,7 +16275,7 @@
         <v>46176</v>
       </c>
       <c r="B211" s="49" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C211" s="50">
         <v>699</v>
@@ -16268,7 +16289,7 @@
       <c r="F211" s="49"/>
       <c r="G211" s="49"/>
       <c r="H211" s="51" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="I211" s="49" t="s">
         <v>142</v>
@@ -16279,7 +16300,7 @@
         <v>46176</v>
       </c>
       <c r="B212" s="53" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C212" s="54">
         <v>699</v>
@@ -16293,7 +16314,7 @@
       <c r="F212" s="56"/>
       <c r="G212" s="56"/>
       <c r="H212" s="56" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="I212" s="53" t="s">
         <v>142</v>
@@ -16304,7 +16325,7 @@
         <v>46176</v>
       </c>
       <c r="B213" s="49" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C213" s="50">
         <v>700</v>
@@ -16318,7 +16339,7 @@
       <c r="F213" s="49"/>
       <c r="G213" s="49"/>
       <c r="H213" s="51" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="I213" s="49" t="s">
         <v>142</v>
@@ -16329,7 +16350,7 @@
         <v>46177</v>
       </c>
       <c r="B214" s="53" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C214" s="54">
         <v>699</v>
@@ -16343,7 +16364,7 @@
       <c r="F214" s="56"/>
       <c r="G214" s="56"/>
       <c r="H214" s="56" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="I214" s="53" t="s">
         <v>142</v>
@@ -23644,7 +23665,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="66" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="M62" s="66"/>
       <c r="N62" s="66" t="s">
@@ -24843,11 +24864,11 @@
         <v>3</v>
       </c>
       <c r="G85" s="70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" s="69">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I85" s="69">
         <f>IF(D85&lt;&gt;"",D85,IFERROR(E85/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -24859,7 +24880,7 @@
       </c>
       <c r="K85" s="69">
         <f t="shared" si="8"/>
-        <v>895</v>
+        <v>0</v>
       </c>
       <c r="L85" s="69" t="s">
         <v>621</v>
@@ -26718,7 +26739,7 @@
         <v>5865.3466666666618</v>
       </c>
       <c r="L120" s="66" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="M120" s="66" t="s">
         <v>49</v>
@@ -26728,7 +26749,7 @@
       </c>
       <c r="O120" s="66"/>
       <c r="P120" s="66" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="Q120" s="66"/>
       <c r="R120" s="66"/>
@@ -28814,7 +28835,7 @@
       </c>
       <c r="O147" s="69"/>
       <c r="P147" s="69" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="Q147" s="69"/>
       <c r="R147" s="69"/>
@@ -29708,7 +29729,7 @@
         <v>1013</v>
       </c>
       <c r="L164" s="66" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="M164" s="66"/>
       <c r="N164" s="66" t="s">
@@ -29716,7 +29737,7 @@
       </c>
       <c r="O164" s="66"/>
       <c r="P164" s="66" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="Q164" s="66"/>
       <c r="R164" s="66"/>
@@ -30134,7 +30155,7 @@
         <v>2094</v>
       </c>
       <c r="L172" s="66" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="M172" s="66"/>
       <c r="N172" s="66" t="s">
@@ -30290,7 +30311,7 @@
         <v>4887.75</v>
       </c>
       <c r="L175" s="69" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="M175" s="69"/>
       <c r="N175" s="69" t="s">
@@ -30298,7 +30319,7 @@
       </c>
       <c r="O175" s="69"/>
       <c r="P175" s="69" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="Q175" s="69"/>
       <c r="R175" s="69"/>
@@ -30344,7 +30365,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="66" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="M176" s="66"/>
       <c r="N176" s="66" t="s">
@@ -30396,7 +30417,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="69" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="M177" s="69"/>
       <c r="N177" s="69" t="s">
@@ -30450,7 +30471,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="66" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="M178" s="66"/>
       <c r="N178" s="66" t="s">
@@ -30558,7 +30579,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="66" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="M180" s="66"/>
       <c r="N180" s="66" t="s">
@@ -34884,15 +34905,15 @@
       </c>
       <c r="B8" s="9">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A8,Purchases!$C:$C),0)</f>
-        <v>158245</v>
+        <v>158329</v>
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>119727.33333333333</v>
+        <v>119755.33333333333</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>38517.666666666672</v>
+        <v>38573.666666666672</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -34900,7 +34921,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>38517.666666666672</v>
+        <v>38573.666666666672</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -34908,7 +34929,7 @@
       </c>
       <c r="H8" s="88">
         <f>F8-G8</f>
-        <v>20214.326666666671</v>
+        <v>20270.326666666671</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -34921,11 +34942,11 @@
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>119727.33333333333</v>
+        <v>119755.33333333333</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>48609.666666666672</v>
+        <v>48581.666666666672</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -34933,7 +34954,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>48609.666666666672</v>
+        <v>48581.666666666672</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -34941,7 +34962,7 @@
       </c>
       <c r="H9" s="89">
         <f>F9-G9</f>
-        <v>6970.3366666666698</v>
+        <v>6942.3366666666698</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -34954,11 +34975,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>119727.33333333333</v>
+        <v>119755.33333333333</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-87127.333333333328</v>
+        <v>-87155.333333333328</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -34966,7 +34987,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-87127.333333333328</v>
+        <v>-87155.333333333328</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -34974,7 +34995,7 @@
       </c>
       <c r="H10" s="88">
         <f>F10-G10</f>
-        <v>-27184.66333333333</v>
+        <v>-27212.66333333333</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="90" customFormat="1" ht="15.75" customHeight="1">
@@ -35391,7 +35412,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>288042</v>
+        <v>293292</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -35399,11 +35420,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>115403.40939999999</v>
+        <v>117153.7594</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>172638.5906</v>
+        <v>176138.24060000002</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35411,7 +35432,7 @@
       </c>
       <c r="G4" s="88">
         <f>E4+F4</f>
-        <v>35328.564599999983</v>
+        <v>38828.214600000007</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -35428,11 +35449,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>115334.18119999999</v>
+        <v>117083.48119999999</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-69765.181199999992</v>
+        <v>-71514.481199999995</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35440,7 +35461,7 @@
       </c>
       <c r="G5" s="89">
         <f>E5+F5</f>
-        <v>1821.8608000000095</v>
+        <v>72.560800000006566</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -35457,11 +35478,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>115403.40939999999</v>
+        <v>117153.7594</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-102873.40939999999</v>
+        <v>-104623.7594</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35469,7 +35490,7 @@
       </c>
       <c r="G6" s="88">
         <f>E6+F6</f>
-        <v>-37150.425399999978</v>
+        <v>-38900.775399999984</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">

--- a/docs/Chiraath-Summary-Jun26.xlsx
+++ b/docs/Chiraath-Summary-Jun26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C4AA3B-FDC8-314D-8B5B-49CF0365A1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128BE14C-F788-4747-9C4B-4951ACAA3A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>

--- a/docs/Chiraath-Summary-Jun26.xlsx
+++ b/docs/Chiraath-Summary-Jun26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128BE14C-F788-4747-9C4B-4951ACAA3A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C1FD16-9354-0C4D-BD3C-A24F32FA3370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2423" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="966">
   <si>
     <t>Notes:</t>
   </si>
@@ -2864,9 +2864,6 @@
     <t>Grey-Black/Red</t>
   </si>
   <si>
-    <t>Matka (peacock blue/maroon CHR-174), Narayanpett purple/bottle green (CHR-163)</t>
-  </si>
-  <si>
     <t>Peacok Blue/Maroon - 2
 Purple/Green - 1
 Navy Blue/Maroon - 2
@@ -2962,6 +2959,12 @@
   </si>
   <si>
     <t>Postal parcel charges</t>
+  </si>
+  <si>
+    <t>Matka (peacock blue/maroon CHR-174), Narayanpett purple/bottle green (CHR-163), Ganga Jamuna (CHR-140)</t>
+  </si>
+  <si>
+    <t>Jaimy (1000)</t>
   </si>
 </sst>
 </file>
@@ -3874,7 +3877,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>209</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>86</c:v>
@@ -3977,7 +3980,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>63</c:v>
+                  <c:v>62</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>58</c:v>
@@ -4310,7 +4313,7 @@
                   <c:v>60714</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42615.356666666667</c:v>
+                  <c:v>41777.356666666667</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1357</c:v>
@@ -4797,7 +4800,7 @@
                   <c:v>54177</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>53524</c:v>
+                  <c:v>54524</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>9843</c:v>
@@ -5237,7 +5240,7 @@
                   <c:v>-16825</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>49075</c:v>
+                  <c:v>50075</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>5319</c:v>
@@ -5707,10 +5710,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>298</c:v>
+                  <c:v>299</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>124</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6897,7 +6900,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>351391</v>
+        <v>359021</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -6914,7 +6917,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>364356</v>
+        <v>365356</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -6931,7 +6934,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-7875</v>
+        <v>-245</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -7147,11 +7150,11 @@
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>117153.7594</v>
+        <v>119697.60139999999</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>176138.24060000002</v>
+        <v>173594.39860000001</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -7159,11 +7162,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>38828.214600000007</v>
+        <v>36284.372600000002</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹38,828</v>
+        <v>Pay ₹36,284</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -7173,15 +7176,15 @@
       </c>
       <c r="B27" s="12">
         <f>'Cash Pool'!B5</f>
-        <v>45569</v>
+        <v>53199</v>
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>117083.48119999999</v>
+        <v>119625.7972</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-71514.481199999995</v>
+        <v>-66426.797200000001</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -7189,11 +7192,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>72.560800000006566</v>
+        <v>5160.2448000000004</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹73</v>
+        <v>Pay ₹5,160</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -7207,11 +7210,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>117153.7594</v>
+        <v>119697.60139999999</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-104623.7594</v>
+        <v>-107167.60139999999</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -7219,11 +7222,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-38900.775399999984</v>
+        <v>-41444.617399999974</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹38,901</v>
+        <v>Receive ₹41,445</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -7351,7 +7354,7 @@
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>351391</v>
+        <v>359021</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7360,14 +7363,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-7875</v>
+        <v>-245</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>96277.556666666656</v>
+        <v>95439.556666666656</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -7419,7 +7422,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7443,7 +7446,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7490,11 +7493,11 @@
       </c>
       <c r="C14" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A14)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>53524</v>
+        <v>54524</v>
       </c>
       <c r="D14" s="21">
         <f t="shared" si="0"/>
-        <v>49075</v>
+        <v>50075</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
@@ -7639,11 +7642,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -7670,7 +7673,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>42615.356666666667</v>
+        <v>41777.356666666667</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -8805,7 +8808,7 @@
         <v>960</v>
       </c>
       <c r="D74" s="36" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15" customHeight="1">
@@ -8833,7 +8836,7 @@
         <v>2900</v>
       </c>
       <c r="D76" s="36" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15" customHeight="1">
@@ -8847,7 +8850,7 @@
         <v>180</v>
       </c>
       <c r="D77" s="39" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15" customHeight="1">
@@ -8861,7 +8864,7 @@
         <v>84</v>
       </c>
       <c r="D78" s="36" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15" customHeight="1">
@@ -15018,7 +15021,7 @@
       <c r="F160" s="56"/>
       <c r="G160" s="56"/>
       <c r="H160" s="57" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="I160" s="53" t="s">
         <v>142</v>
@@ -15218,7 +15221,7 @@
       <c r="F168" s="49"/>
       <c r="G168" s="49"/>
       <c r="H168" s="51" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="I168" s="49" t="s">
         <v>142</v>
@@ -15518,7 +15521,7 @@
       <c r="F180" s="49"/>
       <c r="G180" s="49"/>
       <c r="H180" s="51" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="I180" s="49" t="s">
         <v>142</v>
@@ -16014,13 +16017,13 @@
       <c r="F200" s="56"/>
       <c r="G200" s="56"/>
       <c r="H200" s="57" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="I200" s="53" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9" ht="28">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="42">
       <c r="A201" s="48">
         <v>46173</v>
       </c>
@@ -16028,7 +16031,7 @@
         <v>930</v>
       </c>
       <c r="C201" s="50">
-        <v>2850</v>
+        <v>3850</v>
       </c>
       <c r="D201" s="49" t="s">
         <v>144</v>
@@ -16039,10 +16042,10 @@
       <c r="F201" s="49"/>
       <c r="G201" s="49"/>
       <c r="H201" s="51" t="s">
-        <v>934</v>
+        <v>964</v>
       </c>
       <c r="I201" s="49" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="14">
@@ -16067,7 +16070,7 @@
         <v>925</v>
       </c>
       <c r="I202" s="53" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
     </row>
     <row r="203" spans="1:9" ht="14">
@@ -16100,7 +16103,7 @@
         <v>46175</v>
       </c>
       <c r="B204" s="53" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C204" s="54">
         <v>699</v>
@@ -16125,7 +16128,7 @@
         <v>46175</v>
       </c>
       <c r="B205" s="49" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C205" s="50">
         <v>700</v>
@@ -16139,7 +16142,7 @@
       <c r="F205" s="49"/>
       <c r="G205" s="49"/>
       <c r="H205" s="51" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="I205" s="49" t="s">
         <v>142</v>
@@ -16150,7 +16153,7 @@
         <v>46175</v>
       </c>
       <c r="B206" s="53" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C206" s="54">
         <v>1350</v>
@@ -16164,7 +16167,7 @@
       <c r="F206" s="56"/>
       <c r="G206" s="56"/>
       <c r="H206" s="51" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="I206" s="53" t="s">
         <v>142</v>
@@ -16175,7 +16178,7 @@
         <v>46175</v>
       </c>
       <c r="B207" s="49" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C207" s="50">
         <v>699</v>
@@ -16189,7 +16192,7 @@
       <c r="F207" s="49"/>
       <c r="G207" s="49"/>
       <c r="H207" s="51" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="I207" s="49" t="s">
         <v>142</v>
@@ -16200,7 +16203,7 @@
         <v>46175</v>
       </c>
       <c r="B208" s="53" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C208" s="54">
         <v>699</v>
@@ -16214,7 +16217,7 @@
       <c r="F208" s="56"/>
       <c r="G208" s="56"/>
       <c r="H208" s="57" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="I208" s="53" t="s">
         <v>142</v>
@@ -16225,7 +16228,7 @@
         <v>46176</v>
       </c>
       <c r="B209" s="49" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C209" s="50">
         <v>699</v>
@@ -16239,7 +16242,7 @@
       <c r="F209" s="49"/>
       <c r="G209" s="49"/>
       <c r="H209" s="51" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="I209" s="49" t="s">
         <v>142</v>
@@ -16250,7 +16253,7 @@
         <v>46176</v>
       </c>
       <c r="B210" s="53" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C210" s="54">
         <v>2200</v>
@@ -16264,7 +16267,7 @@
       <c r="F210" s="56"/>
       <c r="G210" s="56"/>
       <c r="H210" s="57" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="I210" s="53" t="s">
         <v>142</v>
@@ -16275,7 +16278,7 @@
         <v>46176</v>
       </c>
       <c r="B211" s="49" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C211" s="50">
         <v>699</v>
@@ -16289,7 +16292,7 @@
       <c r="F211" s="49"/>
       <c r="G211" s="49"/>
       <c r="H211" s="51" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="I211" s="49" t="s">
         <v>142</v>
@@ -16300,7 +16303,7 @@
         <v>46176</v>
       </c>
       <c r="B212" s="53" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C212" s="54">
         <v>699</v>
@@ -16325,7 +16328,7 @@
         <v>46176</v>
       </c>
       <c r="B213" s="49" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C213" s="50">
         <v>700</v>
@@ -16339,7 +16342,7 @@
       <c r="F213" s="49"/>
       <c r="G213" s="49"/>
       <c r="H213" s="51" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="I213" s="49" t="s">
         <v>142</v>
@@ -16350,7 +16353,7 @@
         <v>46177</v>
       </c>
       <c r="B214" s="53" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C214" s="54">
         <v>699</v>
@@ -26739,7 +26742,7 @@
         <v>5865.3466666666618</v>
       </c>
       <c r="L120" s="66" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="M120" s="66" t="s">
         <v>49</v>
@@ -26749,7 +26752,7 @@
       </c>
       <c r="O120" s="66"/>
       <c r="P120" s="66" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Q120" s="66"/>
       <c r="R120" s="66"/>
@@ -28495,10 +28498,10 @@
         <v>1100</v>
       </c>
       <c r="F141" s="79">
+        <v>1</v>
+      </c>
+      <c r="G141" s="79">
         <v>0</v>
-      </c>
-      <c r="G141" s="79">
-        <v>1</v>
       </c>
       <c r="H141" s="78">
         <f t="shared" si="12"/>
@@ -28510,16 +28513,18 @@
       </c>
       <c r="J141" s="78">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>838</v>
       </c>
       <c r="K141" s="78">
         <f t="shared" si="14"/>
-        <v>838</v>
-      </c>
-      <c r="L141" s="69"/>
+        <v>0</v>
+      </c>
+      <c r="L141" s="69" t="s">
+        <v>965</v>
+      </c>
       <c r="M141" s="69"/>
       <c r="N141" s="69" t="s">
-        <v>599</v>
+        <v>425</v>
       </c>
       <c r="O141" s="69"/>
       <c r="P141" s="69"/>
@@ -28835,7 +28840,7 @@
       </c>
       <c r="O147" s="69"/>
       <c r="P147" s="69" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="Q147" s="69"/>
       <c r="R147" s="69"/>
@@ -30155,7 +30160,7 @@
         <v>2094</v>
       </c>
       <c r="L172" s="66" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="M172" s="66"/>
       <c r="N172" s="66" t="s">
@@ -30319,7 +30324,7 @@
       </c>
       <c r="O175" s="69"/>
       <c r="P175" s="69" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="Q175" s="69"/>
       <c r="R175" s="69"/>
@@ -35420,11 +35425,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>117153.7594</v>
+        <v>119697.60139999999</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>176138.24060000002</v>
+        <v>173594.39860000001</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35432,7 +35437,7 @@
       </c>
       <c r="G4" s="88">
         <f>E4+F4</f>
-        <v>38828.214600000007</v>
+        <v>36284.372600000002</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -35441,7 +35446,7 @@
       </c>
       <c r="B5" s="11">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A5,Sales!$I:$I,"Completed"),0)</f>
-        <v>45569</v>
+        <v>53199</v>
       </c>
       <c r="C5" s="11">
         <f>VLOOKUP($A5,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -35449,11 +35454,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>117083.48119999999</v>
+        <v>119625.7972</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-71514.481199999995</v>
+        <v>-66426.797200000001</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35461,7 +35466,7 @@
       </c>
       <c r="G5" s="89">
         <f>E5+F5</f>
-        <v>72.560800000006566</v>
+        <v>5160.2448000000004</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -35478,11 +35483,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>117153.7594</v>
+        <v>119697.60139999999</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-104623.7594</v>
+        <v>-107167.60139999999</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35490,7 +35495,7 @@
       </c>
       <c r="G6" s="88">
         <f>E6+F6</f>
-        <v>-38900.775399999984</v>
+        <v>-41444.617399999974</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">

--- a/docs/Chiraath-Summary-Jun26.xlsx
+++ b/docs/Chiraath-Summary-Jun26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C1FD16-9354-0C4D-BD3C-A24F32FA3370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D858E6E-A89D-4045-BCA2-565636D81419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2426" uniqueCount="966">
   <si>
     <t>Notes:</t>
   </si>
@@ -4643,7 +4643,7 @@
                   <c:v>4449</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4524</c:v>
+                  <c:v>4732</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5243,7 +5243,7 @@
                   <c:v>50075</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5319</c:v>
+                  <c:v>5111</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>359266</v>
+        <v>359474</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-245</v>
+        <v>-453</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>20270.326666666671</v>
+        <v>20408.993333333328</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>6942.3366666666698</v>
+        <v>6873.0033333333267</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-27212.66333333333</v>
+        <v>-27281.996666666673</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -7028,15 +7028,15 @@
       </c>
       <c r="B18" s="10">
         <f>PartnerShares!B8</f>
-        <v>158329</v>
+        <v>158537</v>
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>119755.33333333333</v>
+        <v>119824.66666666667</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>38573.666666666672</v>
+        <v>38712.333333333328</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7044,11 +7044,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>20270.326666666671</v>
+        <v>20408.993333333328</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹20,270</v>
+        <v>Receive ₹20,409</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -7062,11 +7062,11 @@
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>119755.33333333333</v>
+        <v>119824.66666666667</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>48581.666666666672</v>
+        <v>48512.333333333328</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7074,11 +7074,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>6942.3366666666698</v>
+        <v>6873.0033333333267</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹6,942</v>
+        <v>Receive ₹6,873</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -7092,11 +7092,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>119755.33333333333</v>
+        <v>119824.66666666667</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-87155.333333333328</v>
+        <v>-87224.666666666672</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7104,11 +7104,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-27212.66333333333</v>
+        <v>-27281.996666666673</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹27,213</v>
+        <v>Pay ₹27,282</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46179</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>359266</v>
+        <v>359474</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-245</v>
+        <v>-453</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="B15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A15)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>4524</v>
+        <v>4732</v>
       </c>
       <c r="C15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="D15" s="27">
         <f t="shared" si="0"/>
-        <v>5319</v>
+        <v>5111</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
@@ -8868,10 +8868,18 @@
       </c>
     </row>
     <row r="79" spans="1:4" ht="15" customHeight="1">
-      <c r="A79" s="38"/>
-      <c r="B79" s="39"/>
-      <c r="C79" s="40"/>
-      <c r="D79" s="39"/>
+      <c r="A79" s="38">
+        <v>46179</v>
+      </c>
+      <c r="B79" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C79" s="40">
+        <v>208</v>
+      </c>
+      <c r="D79" s="39" t="s">
+        <v>963</v>
+      </c>
     </row>
     <row r="80" spans="1:4" ht="15" customHeight="1">
       <c r="A80" s="35"/>
@@ -34910,15 +34918,15 @@
       </c>
       <c r="B8" s="9">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A8,Purchases!$C:$C),0)</f>
-        <v>158329</v>
+        <v>158537</v>
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>119755.33333333333</v>
+        <v>119824.66666666667</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>38573.666666666672</v>
+        <v>38712.333333333328</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -34926,7 +34934,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>38573.666666666672</v>
+        <v>38712.333333333328</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -34934,7 +34942,7 @@
       </c>
       <c r="H8" s="88">
         <f>F8-G8</f>
-        <v>20270.326666666671</v>
+        <v>20408.993333333328</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -34947,11 +34955,11 @@
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>119755.33333333333</v>
+        <v>119824.66666666667</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>48581.666666666672</v>
+        <v>48512.333333333328</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -34959,7 +34967,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>48581.666666666672</v>
+        <v>48512.333333333328</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -34967,7 +34975,7 @@
       </c>
       <c r="H9" s="89">
         <f>F9-G9</f>
-        <v>6942.3366666666698</v>
+        <v>6873.0033333333267</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -34980,11 +34988,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>119755.33333333333</v>
+        <v>119824.66666666667</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-87155.333333333328</v>
+        <v>-87224.666666666672</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -34992,7 +35000,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-87155.333333333328</v>
+        <v>-87224.666666666672</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -35000,7 +35008,7 @@
       </c>
       <c r="H10" s="88">
         <f>F10-G10</f>
-        <v>-27212.66333333333</v>
+        <v>-27281.996666666673</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="90" customFormat="1" ht="15.75" customHeight="1">

--- a/docs/Chiraath-Summary-Jun26.xlsx
+++ b/docs/Chiraath-Summary-Jun26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D858E6E-A89D-4045-BCA2-565636D81419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36FCD25-7E2D-7F49-8D55-19C0F313FE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2426" uniqueCount="966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2439" uniqueCount="971">
   <si>
     <t>Notes:</t>
   </si>
@@ -2965,6 +2965,21 @@
   </si>
   <si>
     <t>Jaimy (1000)</t>
+  </si>
+  <si>
+    <t>M, L, XL, XXL</t>
+  </si>
+  <si>
+    <t>Cotton 3 piece salwar set</t>
+  </si>
+  <si>
+    <t>Linen Blend floral embrioidered sarees</t>
+  </si>
+  <si>
+    <t>Sky Blue, Mint Green, Blush Pink</t>
+  </si>
+  <si>
+    <t>Coffee brown with Rust Floral Print</t>
   </si>
 </sst>
 </file>
@@ -3980,10 +3995,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>62</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>58</c:v>
+                  <c:v>62</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>4</c:v>
@@ -4310,10 +4325,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>60714</c:v>
+                  <c:v>64790</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>41777.356666666667</c:v>
+                  <c:v>43967.356666666667</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1357</c:v>
@@ -4643,7 +4658,7 @@
                   <c:v>4449</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4732</c:v>
+                  <c:v>14730</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5243,7 +5258,7 @@
                   <c:v>50075</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5111</c:v>
+                  <c:v>-4887</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5713,7 +5728,7 @@
                   <c:v>299</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>124</c:v>
+                  <c:v>131</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6885,7 +6900,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>359474</v>
+        <v>369472</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -6900,7 +6915,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>359021</v>
+        <v>360446</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -6934,7 +6949,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-453</v>
+        <v>-9026</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -6969,7 +6984,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>20408.993333333328</v>
+        <v>27074.326666666671</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -6979,7 +6994,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>6873.0033333333267</v>
+        <v>3540.3366666666698</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -6989,7 +7004,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-27281.996666666673</v>
+        <v>-30614.66333333333</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -7028,15 +7043,15 @@
       </c>
       <c r="B18" s="10">
         <f>PartnerShares!B8</f>
-        <v>158537</v>
+        <v>168535</v>
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>119824.66666666667</v>
+        <v>123157.33333333333</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>38712.333333333328</v>
+        <v>45377.666666666672</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7044,11 +7059,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>20408.993333333328</v>
+        <v>27074.326666666671</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹20,409</v>
+        <v>Receive ₹27,074</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -7062,11 +7077,11 @@
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>119824.66666666667</v>
+        <v>123157.33333333333</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>48512.333333333328</v>
+        <v>45179.666666666672</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7074,11 +7089,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>6873.0033333333267</v>
+        <v>3540.3366666666698</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹6,873</v>
+        <v>Receive ₹3,540</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -7092,11 +7107,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>119824.66666666667</v>
+        <v>123157.33333333333</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-87224.666666666672</v>
+        <v>-90557.333333333328</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7104,11 +7119,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-27281.996666666673</v>
+        <v>-30614.66333333333</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹27,282</v>
+        <v>Pay ₹30,615</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -7150,11 +7165,11 @@
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>119697.60139999999</v>
+        <v>120172.69639999999</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>173594.39860000001</v>
+        <v>173119.30360000001</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -7162,11 +7177,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>36284.372600000002</v>
+        <v>35809.277600000001</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹36,284</v>
+        <v>Pay ₹35,809</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -7176,15 +7191,15 @@
       </c>
       <c r="B27" s="12">
         <f>'Cash Pool'!B5</f>
-        <v>53199</v>
+        <v>54624</v>
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>119625.7972</v>
+        <v>120100.6072</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-66426.797200000001</v>
+        <v>-65476.607199999999</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -7192,11 +7207,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>5160.2448000000004</v>
+        <v>6110.4348000000027</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹5,160</v>
+        <v>Pay ₹6,110</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -7210,11 +7225,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>119697.60139999999</v>
+        <v>120172.69639999999</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-107167.60139999999</v>
+        <v>-107642.69639999999</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -7222,11 +7237,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-41444.617399999974</v>
+        <v>-41919.712399999975</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹41,445</v>
+        <v>Receive ₹41,920</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -7338,7 +7353,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46179</v>
+        <v>46187</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -7347,14 +7362,14 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>359474</v>
+        <v>369472</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>359021</v>
+        <v>360446</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7363,14 +7378,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-453</v>
+        <v>-9026</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>95439.556666666656</v>
+        <v>101705.55666666666</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -7446,7 +7461,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7506,7 +7521,7 @@
       </c>
       <c r="B15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A15)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>4732</v>
+        <v>14730</v>
       </c>
       <c r="C15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
@@ -7514,7 +7529,7 @@
       </c>
       <c r="D15" s="27">
         <f t="shared" si="0"/>
-        <v>5111</v>
+        <v>-4887</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
@@ -7646,14 +7661,14 @@
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
       </c>
       <c r="K47" s="31">
         <f t="array" ref="K47">SUMPRODUCT((INVENTORY!$C$2:$C$477=J47)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>60714</v>
+        <v>64790</v>
       </c>
     </row>
     <row r="48" spans="6:11" ht="15" customHeight="1">
@@ -7666,14 +7681,14 @@
       </c>
       <c r="H48" s="30">
         <f>SUMIF(INVENTORY!C:C, F48, INVENTORY!G:G)</f>
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J48" s="30" t="s">
         <v>95</v>
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>41777.356666666667</v>
+        <v>43967.356666666667</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -8882,16 +8897,32 @@
       </c>
     </row>
     <row r="80" spans="1:4" ht="15" customHeight="1">
-      <c r="A80" s="35"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="36"/>
+      <c r="A80" s="35">
+        <v>46178</v>
+      </c>
+      <c r="B80" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C80" s="37">
+        <v>2189</v>
+      </c>
+      <c r="D80" s="36" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="81" spans="1:4" ht="15" customHeight="1">
-      <c r="A81" s="38"/>
-      <c r="B81" s="39"/>
-      <c r="C81" s="40"/>
-      <c r="D81" s="39"/>
+      <c r="A81" s="38">
+        <v>46179</v>
+      </c>
+      <c r="B81" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="40">
+        <v>7809</v>
+      </c>
+      <c r="D81" s="39" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="82" spans="1:4" ht="15" customHeight="1">
       <c r="A82" s="35"/>
@@ -11116,6 +11147,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
@@ -11160,7 +11192,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" hidden="1">
       <c r="A2" s="48">
         <v>45900</v>
       </c>
@@ -11183,7 +11215,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" hidden="1">
       <c r="A3" s="52">
         <v>45900</v>
       </c>
@@ -11206,7 +11238,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" hidden="1">
       <c r="A4" s="48">
         <v>45900</v>
       </c>
@@ -11229,7 +11261,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" hidden="1">
       <c r="A5" s="52">
         <v>45900</v>
       </c>
@@ -11252,7 +11284,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" hidden="1">
       <c r="A6" s="48">
         <v>45900</v>
       </c>
@@ -11275,7 +11307,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" hidden="1">
       <c r="A7" s="52">
         <v>45900</v>
       </c>
@@ -11298,7 +11330,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" hidden="1">
       <c r="A8" s="48">
         <v>45900</v>
       </c>
@@ -11321,7 +11353,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" hidden="1">
       <c r="A9" s="52">
         <v>45901</v>
       </c>
@@ -11344,7 +11376,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" hidden="1">
       <c r="A10" s="48">
         <v>45902</v>
       </c>
@@ -11367,7 +11399,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" hidden="1">
       <c r="A11" s="52">
         <v>45903</v>
       </c>
@@ -11390,7 +11422,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" hidden="1">
       <c r="A12" s="48">
         <v>45904</v>
       </c>
@@ -11413,7 +11445,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" hidden="1">
       <c r="A13" s="52">
         <v>45905</v>
       </c>
@@ -11436,7 +11468,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" hidden="1">
       <c r="A14" s="48">
         <v>45906</v>
       </c>
@@ -11459,7 +11491,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" hidden="1">
       <c r="A15" s="52">
         <v>45907</v>
       </c>
@@ -11482,7 +11514,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" hidden="1">
       <c r="A16" s="48">
         <v>45908</v>
       </c>
@@ -11505,7 +11537,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" hidden="1">
       <c r="A17" s="52">
         <v>45909</v>
       </c>
@@ -11528,7 +11560,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" hidden="1">
       <c r="A18" s="48">
         <v>45910</v>
       </c>
@@ -11551,7 +11583,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" hidden="1">
       <c r="A19" s="52">
         <v>45911</v>
       </c>
@@ -11574,7 +11606,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" hidden="1">
       <c r="A20" s="48">
         <v>45912</v>
       </c>
@@ -11597,7 +11629,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" hidden="1">
       <c r="A21" s="52">
         <v>45913</v>
       </c>
@@ -11620,7 +11652,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" hidden="1">
       <c r="A22" s="48">
         <v>45914</v>
       </c>
@@ -11643,7 +11675,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" hidden="1">
       <c r="A23" s="52">
         <v>45915</v>
       </c>
@@ -11666,7 +11698,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" hidden="1">
       <c r="A24" s="48">
         <v>45916</v>
       </c>
@@ -11689,7 +11721,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" hidden="1">
       <c r="A25" s="52">
         <v>45917</v>
       </c>
@@ -11712,7 +11744,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" hidden="1">
       <c r="A26" s="48">
         <v>45917</v>
       </c>
@@ -11735,7 +11767,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" hidden="1">
       <c r="A27" s="52">
         <v>45918</v>
       </c>
@@ -11758,7 +11790,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" hidden="1">
       <c r="A28" s="48">
         <v>45919</v>
       </c>
@@ -11781,7 +11813,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" hidden="1">
       <c r="A29" s="52">
         <v>45920</v>
       </c>
@@ -11804,7 +11836,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" hidden="1">
       <c r="A30" s="48">
         <v>45921</v>
       </c>
@@ -11827,7 +11859,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" hidden="1">
       <c r="A31" s="52">
         <v>45922</v>
       </c>
@@ -11850,7 +11882,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" hidden="1">
       <c r="A32" s="48">
         <v>45924</v>
       </c>
@@ -11873,7 +11905,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" hidden="1">
       <c r="A33" s="52">
         <v>45924</v>
       </c>
@@ -11896,7 +11928,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" hidden="1">
       <c r="A34" s="48">
         <v>45930</v>
       </c>
@@ -11919,7 +11951,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" hidden="1">
       <c r="A35" s="52">
         <v>45933.931944444397</v>
       </c>
@@ -11942,7 +11974,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" hidden="1">
       <c r="A36" s="48">
         <v>45934.931944386597</v>
       </c>
@@ -11965,7 +11997,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" hidden="1">
       <c r="A37" s="52">
         <v>45935.931944386597</v>
       </c>
@@ -11988,7 +12020,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" hidden="1">
       <c r="A38" s="48">
         <v>45939.931944444397</v>
       </c>
@@ -12011,7 +12043,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" hidden="1">
       <c r="A39" s="52">
         <v>45939.931944444397</v>
       </c>
@@ -12034,7 +12066,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" hidden="1">
       <c r="A40" s="48">
         <v>45945</v>
       </c>
@@ -12057,7 +12089,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" hidden="1">
       <c r="A41" s="52">
         <v>45946</v>
       </c>
@@ -12080,7 +12112,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" hidden="1">
       <c r="A42" s="48">
         <v>45946</v>
       </c>
@@ -12103,7 +12135,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" hidden="1">
       <c r="A43" s="52">
         <v>45947</v>
       </c>
@@ -12126,7 +12158,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" hidden="1">
       <c r="A44" s="48">
         <v>45948</v>
       </c>
@@ -12149,7 +12181,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" hidden="1">
       <c r="A45" s="52">
         <v>45949</v>
       </c>
@@ -12172,7 +12204,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" hidden="1">
       <c r="A46" s="48">
         <v>45950</v>
       </c>
@@ -12195,7 +12227,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" hidden="1">
       <c r="A47" s="52">
         <v>45951</v>
       </c>
@@ -12218,7 +12250,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" hidden="1">
       <c r="A48" s="48">
         <v>45964</v>
       </c>
@@ -12241,7 +12273,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" hidden="1">
       <c r="A49" s="52">
         <v>45963</v>
       </c>
@@ -12264,7 +12296,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" hidden="1">
       <c r="A50" s="48">
         <v>45982</v>
       </c>
@@ -12287,7 +12319,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" hidden="1">
       <c r="A51" s="52">
         <v>45983</v>
       </c>
@@ -12310,7 +12342,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" hidden="1">
       <c r="A52" s="48">
         <v>45984</v>
       </c>
@@ -12333,7 +12365,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" hidden="1">
       <c r="A53" s="52">
         <v>45985</v>
       </c>
@@ -12356,7 +12388,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="13.5" customHeight="1">
+    <row r="54" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A54" s="48">
         <v>45986</v>
       </c>
@@ -12381,7 +12413,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" customHeight="1">
+    <row r="55" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A55" s="52">
         <v>45992</v>
       </c>
@@ -12406,7 +12438,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="13.5" customHeight="1">
+    <row r="56" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A56" s="48">
         <v>45992</v>
       </c>
@@ -12431,7 +12463,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.75" customHeight="1">
+    <row r="57" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A57" s="52">
         <v>45996</v>
       </c>
@@ -12456,7 +12488,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="42" customHeight="1">
+    <row r="58" spans="1:9" ht="42" hidden="1" customHeight="1">
       <c r="A58" s="48">
         <v>45996</v>
       </c>
@@ -12481,7 +12513,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" customHeight="1">
+    <row r="59" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A59" s="52">
         <v>45996</v>
       </c>
@@ -12506,7 +12538,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="13.5" customHeight="1">
+    <row r="60" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A60" s="48">
         <v>46007</v>
       </c>
@@ -12531,7 +12563,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" customHeight="1">
+    <row r="61" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A61" s="52">
         <v>46008</v>
       </c>
@@ -12558,7 +12590,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="13.5" customHeight="1">
+    <row r="62" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A62" s="48">
         <v>46008</v>
       </c>
@@ -12583,7 +12615,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.75" customHeight="1">
+    <row r="63" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A63" s="52">
         <v>46008</v>
       </c>
@@ -12608,7 +12640,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.75" customHeight="1">
+    <row r="64" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A64" s="52">
         <v>46008</v>
       </c>
@@ -12633,7 +12665,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="13.5" customHeight="1">
+    <row r="65" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A65" s="48">
         <v>46009</v>
       </c>
@@ -12658,7 +12690,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.75" customHeight="1">
+    <row r="66" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A66" s="52">
         <v>46010</v>
       </c>
@@ -12683,7 +12715,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="13.5" customHeight="1">
+    <row r="67" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A67" s="48">
         <v>46010</v>
       </c>
@@ -12710,7 +12742,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="31.5" customHeight="1">
+    <row r="68" spans="1:9" ht="31.5" hidden="1" customHeight="1">
       <c r="A68" s="52">
         <v>46011</v>
       </c>
@@ -12735,7 +12767,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="13.5" customHeight="1">
+    <row r="69" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A69" s="48">
         <v>46011</v>
       </c>
@@ -12760,7 +12792,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="13.5" customHeight="1">
+    <row r="70" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A70" s="48">
         <v>46011</v>
       </c>
@@ -12785,7 +12817,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.75" customHeight="1">
+    <row r="71" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A71" s="52">
         <v>46011</v>
       </c>
@@ -12810,7 +12842,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="27.75" customHeight="1">
+    <row r="72" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A72" s="48">
         <v>46011</v>
       </c>
@@ -12835,7 +12867,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="31.5" customHeight="1">
+    <row r="73" spans="1:9" ht="31.5" hidden="1" customHeight="1">
       <c r="A73" s="52">
         <v>46011</v>
       </c>
@@ -12860,7 +12892,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="13.5" customHeight="1">
+    <row r="74" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A74" s="48">
         <v>46013</v>
       </c>
@@ -12887,7 +12919,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.75" customHeight="1">
+    <row r="75" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A75" s="52">
         <v>46013</v>
       </c>
@@ -12912,7 +12944,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.75" customHeight="1">
+    <row r="76" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A76" s="52">
         <v>46017</v>
       </c>
@@ -12937,7 +12969,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="13.5" customHeight="1">
+    <row r="77" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A77" s="48">
         <v>46017</v>
       </c>
@@ -12962,7 +12994,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.75" customHeight="1">
+    <row r="78" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A78" s="52">
         <v>46017</v>
       </c>
@@ -12987,7 +13019,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="13.5" customHeight="1">
+    <row r="79" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A79" s="48">
         <v>46017</v>
       </c>
@@ -13012,7 +13044,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.75" customHeight="1">
+    <row r="80" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A80" s="52">
         <v>46020</v>
       </c>
@@ -13037,7 +13069,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="13.5" customHeight="1">
+    <row r="81" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A81" s="48">
         <v>46024</v>
       </c>
@@ -13062,7 +13094,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.75" customHeight="1">
+    <row r="82" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A82" s="52">
         <v>46024</v>
       </c>
@@ -13087,7 +13119,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="13.5" customHeight="1">
+    <row r="83" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A83" s="48">
         <v>46024</v>
       </c>
@@ -13112,7 +13144,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.75" customHeight="1">
+    <row r="84" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A84" s="52">
         <v>46024</v>
       </c>
@@ -13137,7 +13169,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="13.5" customHeight="1">
+    <row r="85" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A85" s="48">
         <v>46027</v>
       </c>
@@ -13162,7 +13194,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="13.5" customHeight="1">
+    <row r="86" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A86" s="48">
         <v>46028</v>
       </c>
@@ -13187,7 +13219,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.75" customHeight="1">
+    <row r="87" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A87" s="52">
         <v>46029</v>
       </c>
@@ -13212,7 +13244,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="13.5" customHeight="1">
+    <row r="88" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A88" s="48">
         <v>46032</v>
       </c>
@@ -13237,7 +13269,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" customHeight="1">
+    <row r="89" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A89" s="52">
         <v>46033</v>
       </c>
@@ -13262,7 +13294,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="13.5" customHeight="1">
+    <row r="90" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A90" s="48">
         <v>46033</v>
       </c>
@@ -13287,7 +13319,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.75" customHeight="1">
+    <row r="91" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A91" s="52">
         <v>46034</v>
       </c>
@@ -13312,7 +13344,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="27.75" customHeight="1">
+    <row r="92" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A92" s="48">
         <v>46034</v>
       </c>
@@ -13337,7 +13369,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" customHeight="1">
+    <row r="93" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A93" s="52">
         <v>46035</v>
       </c>
@@ -13362,7 +13394,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="13.5" customHeight="1">
+    <row r="94" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A94" s="48">
         <v>46036</v>
       </c>
@@ -13387,7 +13419,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.75" customHeight="1">
+    <row r="95" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A95" s="52">
         <v>46038</v>
       </c>
@@ -13412,7 +13444,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="13.5" customHeight="1">
+    <row r="96" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A96" s="48">
         <v>46038</v>
       </c>
@@ -13437,7 +13469,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.75" customHeight="1">
+    <row r="97" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A97" s="52">
         <v>46039</v>
       </c>
@@ -13462,7 +13494,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="13.5" customHeight="1">
+    <row r="98" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A98" s="48">
         <v>46040</v>
       </c>
@@ -13487,7 +13519,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.75" customHeight="1">
+    <row r="99" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A99" s="52">
         <v>46041</v>
       </c>
@@ -13512,7 +13544,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="13.5" customHeight="1">
+    <row r="100" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A100" s="48">
         <v>46042</v>
       </c>
@@ -13537,7 +13569,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.75" customHeight="1">
+    <row r="101" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A101" s="52">
         <v>46043</v>
       </c>
@@ -13562,7 +13594,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="13.5" customHeight="1">
+    <row r="102" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A102" s="48">
         <v>46046</v>
       </c>
@@ -13587,7 +13619,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="13.5" customHeight="1">
+    <row r="103" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A103" s="52">
         <v>46048</v>
       </c>
@@ -13612,7 +13644,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="13.5" customHeight="1">
+    <row r="104" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A104" s="48">
         <v>46048</v>
       </c>
@@ -13637,7 +13669,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15.75" customHeight="1">
+    <row r="105" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A105" s="52">
         <v>46049</v>
       </c>
@@ -13662,7 +13694,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="13.5" customHeight="1">
+    <row r="106" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A106" s="48">
         <v>46049</v>
       </c>
@@ -13687,7 +13719,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15.75" customHeight="1">
+    <row r="107" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A107" s="52">
         <v>46049</v>
       </c>
@@ -13712,7 +13744,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="13.5" customHeight="1">
+    <row r="108" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A108" s="48">
         <v>46050</v>
       </c>
@@ -13737,7 +13769,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15.75" customHeight="1">
+    <row r="109" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A109" s="52">
         <v>46051</v>
       </c>
@@ -13762,7 +13794,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="13.5" customHeight="1">
+    <row r="110" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A110" s="48">
         <v>46051</v>
       </c>
@@ -13787,7 +13819,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15.75" customHeight="1">
+    <row r="111" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A111" s="52">
         <v>46051</v>
       </c>
@@ -13812,7 +13844,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="27.75" customHeight="1">
+    <row r="112" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A112" s="48">
         <v>46054</v>
       </c>
@@ -13837,7 +13869,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15.75" customHeight="1">
+    <row r="113" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A113" s="52">
         <v>46054</v>
       </c>
@@ -13862,7 +13894,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="13.5" customHeight="1">
+    <row r="114" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A114" s="48">
         <v>46055</v>
       </c>
@@ -13887,7 +13919,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15.75" customHeight="1">
+    <row r="115" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A115" s="52">
         <v>46055</v>
       </c>
@@ -13912,7 +13944,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="13.5" customHeight="1">
+    <row r="116" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A116" s="48">
         <v>46060</v>
       </c>
@@ -13937,7 +13969,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="15.75" customHeight="1">
+    <row r="117" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A117" s="52">
         <v>46062</v>
       </c>
@@ -13962,7 +13994,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="13.5" customHeight="1">
+    <row r="118" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A118" s="48">
         <v>46065</v>
       </c>
@@ -13987,7 +14019,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="15.75" customHeight="1">
+    <row r="119" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A119" s="52">
         <v>46055</v>
       </c>
@@ -14012,7 +14044,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="27.75" customHeight="1">
+    <row r="120" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A120" s="48">
         <v>46070</v>
       </c>
@@ -14037,7 +14069,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15.75" customHeight="1">
+    <row r="121" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A121" s="52">
         <v>46073</v>
       </c>
@@ -14062,7 +14094,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="13.5" customHeight="1">
+    <row r="122" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A122" s="48">
         <v>46074</v>
       </c>
@@ -14087,7 +14119,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15.75" customHeight="1">
+    <row r="123" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A123" s="52">
         <v>46075</v>
       </c>
@@ -14112,7 +14144,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="13.5" customHeight="1">
+    <row r="124" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A124" s="48">
         <v>46075</v>
       </c>
@@ -14137,7 +14169,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="31.5" customHeight="1">
+    <row r="125" spans="1:9" ht="31.5" hidden="1" customHeight="1">
       <c r="A125" s="52">
         <v>46079</v>
       </c>
@@ -14162,7 +14194,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="13.5" customHeight="1">
+    <row r="126" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A126" s="48">
         <v>46079</v>
       </c>
@@ -14187,7 +14219,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="13.5" customHeight="1">
+    <row r="127" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A127" s="52">
         <v>46090</v>
       </c>
@@ -14212,7 +14244,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="13.5" customHeight="1">
+    <row r="128" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A128" s="48">
         <v>46090</v>
       </c>
@@ -14237,7 +14269,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="13.5" customHeight="1">
+    <row r="129" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A129" s="48">
         <v>46090</v>
       </c>
@@ -14262,7 +14294,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="15.75" customHeight="1">
+    <row r="130" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A130" s="52">
         <v>46091</v>
       </c>
@@ -14287,7 +14319,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="13.5" customHeight="1">
+    <row r="131" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A131" s="48">
         <v>46092</v>
       </c>
@@ -14312,7 +14344,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="15.75" customHeight="1">
+    <row r="132" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A132" s="52">
         <v>46092</v>
       </c>
@@ -14337,7 +14369,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="27.75" customHeight="1">
+    <row r="133" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A133" s="48">
         <v>46093</v>
       </c>
@@ -14362,7 +14394,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15.75" customHeight="1">
+    <row r="134" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A134" s="52">
         <v>46093</v>
       </c>
@@ -14387,7 +14419,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="13.5" customHeight="1">
+    <row r="135" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A135" s="48">
         <v>46097</v>
       </c>
@@ -14412,7 +14444,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="15.75" customHeight="1">
+    <row r="136" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A136" s="52">
         <v>46097</v>
       </c>
@@ -14437,7 +14469,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="13.5" customHeight="1">
+    <row r="137" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A137" s="48">
         <v>46100</v>
       </c>
@@ -14462,7 +14494,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="15.75" customHeight="1">
+    <row r="138" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A138" s="52">
         <v>46104</v>
       </c>
@@ -14487,7 +14519,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="27.75" customHeight="1">
+    <row r="139" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A139" s="48">
         <v>46105</v>
       </c>
@@ -14512,7 +14544,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="31.5" customHeight="1">
+    <row r="140" spans="1:9" ht="31.5" hidden="1" customHeight="1">
       <c r="A140" s="52">
         <v>46113</v>
       </c>
@@ -14537,7 +14569,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="13.5" customHeight="1">
+    <row r="141" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A141" s="48">
         <v>46118</v>
       </c>
@@ -14562,7 +14594,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="15.75" customHeight="1">
+    <row r="142" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A142" s="52">
         <v>46119</v>
       </c>
@@ -14587,7 +14619,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="13.5" customHeight="1">
+    <row r="143" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A143" s="48">
         <v>46120</v>
       </c>
@@ -14612,7 +14644,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="15.75" customHeight="1">
+    <row r="144" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A144" s="52">
         <v>46120</v>
       </c>
@@ -14637,7 +14669,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="13.5" customHeight="1">
+    <row r="145" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A145" s="48">
         <v>46120</v>
       </c>
@@ -14662,7 +14694,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="31.5" customHeight="1">
+    <row r="146" spans="1:9" ht="31.5" hidden="1" customHeight="1">
       <c r="A146" s="52">
         <v>46122</v>
       </c>
@@ -14687,7 +14719,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="13.5" customHeight="1">
+    <row r="147" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A147" s="48">
         <v>46122</v>
       </c>
@@ -14712,7 +14744,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="15.75" customHeight="1">
+    <row r="148" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A148" s="52">
         <v>46122</v>
       </c>
@@ -14737,7 +14769,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="13.5" customHeight="1">
+    <row r="149" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A149" s="48">
         <v>46122</v>
       </c>
@@ -14762,7 +14794,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="15.75" customHeight="1">
+    <row r="150" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A150" s="52">
         <v>46125</v>
       </c>
@@ -14787,7 +14819,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="13.5" customHeight="1">
+    <row r="151" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A151" s="48">
         <v>46125</v>
       </c>
@@ -14812,7 +14844,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="15.75" customHeight="1">
+    <row r="152" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A152" s="52">
         <v>46125</v>
       </c>
@@ -14837,7 +14869,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="13.5" customHeight="1">
+    <row r="153" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A153" s="48">
         <v>46125</v>
       </c>
@@ -14862,7 +14894,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="15.75" customHeight="1">
+    <row r="154" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A154" s="52">
         <v>46126</v>
       </c>
@@ -14887,7 +14919,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="13.5" customHeight="1">
+    <row r="155" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A155" s="48">
         <v>46127</v>
       </c>
@@ -14912,7 +14944,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="15.75" customHeight="1">
+    <row r="156" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A156" s="52">
         <v>46129</v>
       </c>
@@ -14937,7 +14969,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="13.5" customHeight="1">
+    <row r="157" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A157" s="48">
         <v>46129</v>
       </c>
@@ -14985,7 +15017,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="13.5" customHeight="1">
+    <row r="159" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A159" s="48">
         <v>46130</v>
       </c>
@@ -15010,7 +15042,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="15.75" customHeight="1">
+    <row r="160" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A160" s="52">
         <v>46131</v>
       </c>
@@ -15035,7 +15067,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="13.5" customHeight="1">
+    <row r="161" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A161" s="48">
         <v>46132</v>
       </c>
@@ -15060,7 +15092,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="42" customHeight="1">
+    <row r="162" spans="1:9" ht="42" hidden="1" customHeight="1">
       <c r="A162" s="52">
         <v>46132</v>
       </c>
@@ -15085,7 +15117,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="13.5" customHeight="1">
+    <row r="163" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A163" s="48">
         <v>46133</v>
       </c>
@@ -15110,7 +15142,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="13.5" customHeight="1">
+    <row r="164" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A164" s="52">
         <v>46133</v>
       </c>
@@ -15135,7 +15167,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="13.5" customHeight="1">
+    <row r="165" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A165" s="48">
         <v>46133</v>
       </c>
@@ -15160,7 +15192,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="13.5" customHeight="1">
+    <row r="166" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A166" s="52">
         <v>46134</v>
       </c>
@@ -15185,7 +15217,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="13.5" customHeight="1">
+    <row r="167" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A167" s="48">
         <v>46134</v>
       </c>
@@ -15210,7 +15242,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="13.5" customHeight="1">
+    <row r="168" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A168" s="48">
         <v>46134</v>
       </c>
@@ -15235,7 +15267,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="13.5" customHeight="1">
+    <row r="169" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A169" s="52">
         <v>46134</v>
       </c>
@@ -15260,7 +15292,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="13.5" customHeight="1">
+    <row r="170" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A170" s="48">
         <v>46134</v>
       </c>
@@ -15285,7 +15317,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="13.5" customHeight="1">
+    <row r="171" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A171" s="52">
         <v>46136</v>
       </c>
@@ -15310,7 +15342,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="13.5" customHeight="1">
+    <row r="172" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A172" s="48">
         <v>46138</v>
       </c>
@@ -15335,7 +15367,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="13.5" customHeight="1">
+    <row r="173" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A173" s="52">
         <v>46138</v>
       </c>
@@ -15360,7 +15392,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="13.5" customHeight="1">
+    <row r="174" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A174" s="48">
         <v>46139</v>
       </c>
@@ -15385,7 +15417,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="13.5" customHeight="1">
+    <row r="175" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A175" s="52">
         <v>46139</v>
       </c>
@@ -15410,7 +15442,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="13.5" customHeight="1">
+    <row r="176" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A176" s="48">
         <v>46139</v>
       </c>
@@ -15435,7 +15467,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="13.5" customHeight="1">
+    <row r="177" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A177" s="52">
         <v>46140</v>
       </c>
@@ -15460,7 +15492,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="13.5" customHeight="1">
+    <row r="178" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A178" s="48">
         <v>46140</v>
       </c>
@@ -15485,7 +15517,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="13.5" customHeight="1">
+    <row r="179" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A179" s="52">
         <v>46140</v>
       </c>
@@ -15510,7 +15542,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="13.5" customHeight="1">
+    <row r="180" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A180" s="48">
         <v>46140</v>
       </c>
@@ -15535,7 +15567,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="13.5" customHeight="1">
+    <row r="181" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A181" s="52">
         <v>46141</v>
       </c>
@@ -15560,7 +15592,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="13.5" customHeight="1">
+    <row r="182" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A182" s="48">
         <v>46141</v>
       </c>
@@ -15585,7 +15617,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="13.5" customHeight="1">
+    <row r="183" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A183" s="52">
         <v>46142</v>
       </c>
@@ -15610,7 +15642,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="13.5" customHeight="1">
+    <row r="184" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A184" s="48">
         <v>46142</v>
       </c>
@@ -15635,7 +15667,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="13.5" customHeight="1">
+    <row r="185" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A185" s="52">
         <v>46142</v>
       </c>
@@ -15660,7 +15692,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="13.5" customHeight="1">
+    <row r="186" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A186" s="52">
         <v>46144</v>
       </c>
@@ -15685,7 +15717,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="13.5" customHeight="1">
+    <row r="187" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A187" s="48">
         <v>46144</v>
       </c>
@@ -15710,7 +15742,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="13.5" customHeight="1">
+    <row r="188" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A188" s="52">
         <v>46145</v>
       </c>
@@ -15735,7 +15767,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="13.5" customHeight="1">
+    <row r="189" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A189" s="48">
         <v>46145</v>
       </c>
@@ -15760,7 +15792,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="13.5" customHeight="1">
+    <row r="190" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A190" s="52">
         <v>46145</v>
       </c>
@@ -15785,7 +15817,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="42" customHeight="1">
+    <row r="191" spans="1:9" ht="42" hidden="1" customHeight="1">
       <c r="A191" s="48">
         <v>46151</v>
       </c>
@@ -15810,7 +15842,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="27.75" customHeight="1">
+    <row r="192" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A192" s="52">
         <v>46152</v>
       </c>
@@ -15835,7 +15867,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="42" customHeight="1">
+    <row r="193" spans="1:9" ht="42" hidden="1" customHeight="1">
       <c r="A193" s="48">
         <v>46152</v>
       </c>
@@ -15881,7 +15913,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="42" customHeight="1">
+    <row r="195" spans="1:9" ht="42" hidden="1" customHeight="1">
       <c r="A195" s="48">
         <v>46155</v>
       </c>
@@ -15906,7 +15938,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="42" customHeight="1">
+    <row r="196" spans="1:9" ht="42" hidden="1" customHeight="1">
       <c r="A196" s="52">
         <v>46155</v>
       </c>
@@ -15931,7 +15963,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="42" customHeight="1">
+    <row r="197" spans="1:9" ht="42" hidden="1" customHeight="1">
       <c r="A197" s="48">
         <v>46155</v>
       </c>
@@ -15956,7 +15988,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="42">
+    <row r="198" spans="1:9" ht="42" hidden="1">
       <c r="A198" s="52">
         <v>46168</v>
       </c>
@@ -16003,10 +16035,10 @@
         <v>922</v>
       </c>
       <c r="I199" s="49" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9" ht="28">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="28" hidden="1">
       <c r="A200" s="52">
         <v>46173</v>
       </c>
@@ -16031,7 +16063,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="42">
+    <row r="201" spans="1:9" ht="42" hidden="1">
       <c r="A201" s="48">
         <v>46173</v>
       </c>
@@ -16056,7 +16088,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="14">
+    <row r="202" spans="1:9" ht="14" hidden="1">
       <c r="A202" s="52">
         <v>46173</v>
       </c>
@@ -16106,7 +16138,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="14">
+    <row r="204" spans="1:9" ht="14" hidden="1">
       <c r="A204" s="52">
         <v>46175</v>
       </c>
@@ -16131,7 +16163,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="14">
+    <row r="205" spans="1:9" ht="14" hidden="1">
       <c r="A205" s="48">
         <v>46175</v>
       </c>
@@ -16156,7 +16188,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="14">
+    <row r="206" spans="1:9" ht="14" hidden="1">
       <c r="A206" s="52">
         <v>46175</v>
       </c>
@@ -16181,7 +16213,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="14">
+    <row r="207" spans="1:9" ht="14" hidden="1">
       <c r="A207" s="48">
         <v>46175</v>
       </c>
@@ -16206,7 +16238,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="14">
+    <row r="208" spans="1:9" ht="14" hidden="1">
       <c r="A208" s="52">
         <v>46175</v>
       </c>
@@ -16231,7 +16263,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="14">
+    <row r="209" spans="1:9" ht="14" hidden="1">
       <c r="A209" s="48">
         <v>46176</v>
       </c>
@@ -16256,7 +16288,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="28">
+    <row r="210" spans="1:9" ht="28" hidden="1">
       <c r="A210" s="52">
         <v>46176</v>
       </c>
@@ -16281,7 +16313,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="14">
+    <row r="211" spans="1:9" ht="14" hidden="1">
       <c r="A211" s="48">
         <v>46176</v>
       </c>
@@ -16306,7 +16338,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="212" spans="1:9">
+    <row r="212" spans="1:9" hidden="1">
       <c r="A212" s="52">
         <v>46176</v>
       </c>
@@ -16331,7 +16363,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="14">
+    <row r="213" spans="1:9" ht="14" hidden="1">
       <c r="A213" s="48">
         <v>46176</v>
       </c>
@@ -16356,7 +16388,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="214" spans="1:9">
+    <row r="214" spans="1:9" hidden="1">
       <c r="A214" s="52">
         <v>46177</v>
       </c>
@@ -16885,7 +16917,13 @@
       <c r="I260" s="59"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I214" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:I214" xr:uid="{00000000-0009-0000-0000-000004000000}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="Pending"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1260" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Ordered,Pending,Completed,Cancelled"</formula1>
@@ -30609,21 +30647,51 @@
       <c r="A181" s="69" t="s">
         <v>881</v>
       </c>
-      <c r="B181" s="69"/>
-      <c r="C181" s="69"/>
-      <c r="D181" s="70"/>
-      <c r="E181" s="70"/>
-      <c r="F181" s="79"/>
-      <c r="G181" s="79"/>
-      <c r="H181" s="78"/>
-      <c r="I181" s="78"/>
-      <c r="J181" s="78"/>
-      <c r="K181" s="78"/>
+      <c r="B181" s="69" t="s">
+        <v>967</v>
+      </c>
+      <c r="C181" s="69" t="s">
+        <v>96</v>
+      </c>
+      <c r="D181" s="70">
+        <v>1019</v>
+      </c>
+      <c r="E181" s="70">
+        <v>1499</v>
+      </c>
+      <c r="F181" s="79">
+        <v>0</v>
+      </c>
+      <c r="G181" s="79">
+        <v>4</v>
+      </c>
+      <c r="H181" s="78">
+        <f t="shared" ref="H181:H182" si="18">F181+IF(LEN(G181)=0,0,G181)</f>
+        <v>4</v>
+      </c>
+      <c r="I181" s="78">
+        <f>IF(D181&lt;&gt;"",D181,IFERROR(E181/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>1019</v>
+      </c>
+      <c r="J181" s="78">
+        <f t="shared" ref="J181:J182" si="19">F181*I181</f>
+        <v>0</v>
+      </c>
+      <c r="K181" s="78">
+        <f t="shared" ref="K181:K182" si="20">IF(LEN(G181)=0,0,G181)*I181</f>
+        <v>4076</v>
+      </c>
       <c r="L181" s="69"/>
       <c r="M181" s="69"/>
-      <c r="N181" s="69"/>
-      <c r="O181" s="69"/>
-      <c r="P181" s="69"/>
+      <c r="N181" s="69" t="s">
+        <v>599</v>
+      </c>
+      <c r="O181" s="69" t="s">
+        <v>966</v>
+      </c>
+      <c r="P181" s="69" t="s">
+        <v>970</v>
+      </c>
       <c r="Q181" s="69"/>
       <c r="R181" s="69"/>
       <c r="S181" s="69"/>
@@ -30633,21 +30701,49 @@
       <c r="A182" s="66" t="s">
         <v>882</v>
       </c>
-      <c r="B182" s="66"/>
-      <c r="C182" s="66"/>
-      <c r="D182" s="67"/>
-      <c r="E182" s="67"/>
-      <c r="F182" s="81"/>
-      <c r="G182" s="81"/>
-      <c r="H182" s="80"/>
-      <c r="I182" s="80"/>
-      <c r="J182" s="80"/>
-      <c r="K182" s="80"/>
+      <c r="B182" s="66" t="s">
+        <v>968</v>
+      </c>
+      <c r="C182" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D182" s="67">
+        <v>730</v>
+      </c>
+      <c r="E182" s="67">
+        <v>1100</v>
+      </c>
+      <c r="F182" s="81">
+        <v>0</v>
+      </c>
+      <c r="G182" s="81">
+        <v>3</v>
+      </c>
+      <c r="H182" s="80">
+        <f t="shared" si="18"/>
+        <v>3</v>
+      </c>
+      <c r="I182" s="80">
+        <f>IF(D182&lt;&gt;"",D182,IFERROR(E182/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>730</v>
+      </c>
+      <c r="J182" s="80">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="K182" s="80">
+        <f t="shared" si="20"/>
+        <v>2190</v>
+      </c>
       <c r="L182" s="66"/>
       <c r="M182" s="66"/>
-      <c r="N182" s="66"/>
+      <c r="N182" s="66" t="s">
+        <v>599</v>
+      </c>
       <c r="O182" s="66"/>
-      <c r="P182" s="66"/>
+      <c r="P182" s="66" t="s">
+        <v>969</v>
+      </c>
       <c r="Q182" s="66"/>
       <c r="R182" s="66"/>
       <c r="S182" s="66"/>
@@ -34918,15 +35014,15 @@
       </c>
       <c r="B8" s="9">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A8,Purchases!$C:$C),0)</f>
-        <v>158537</v>
+        <v>168535</v>
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>119824.66666666667</v>
+        <v>123157.33333333333</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>38712.333333333328</v>
+        <v>45377.666666666672</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -34934,7 +35030,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>38712.333333333328</v>
+        <v>45377.666666666672</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -34942,7 +35038,7 @@
       </c>
       <c r="H8" s="88">
         <f>F8-G8</f>
-        <v>20408.993333333328</v>
+        <v>27074.326666666671</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -34955,11 +35051,11 @@
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>119824.66666666667</v>
+        <v>123157.33333333333</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>48512.333333333328</v>
+        <v>45179.666666666672</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -34967,7 +35063,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>48512.333333333328</v>
+        <v>45179.666666666672</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -34975,7 +35071,7 @@
       </c>
       <c r="H9" s="89">
         <f>F9-G9</f>
-        <v>6873.0033333333267</v>
+        <v>3540.3366666666698</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -34988,11 +35084,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>119824.66666666667</v>
+        <v>123157.33333333333</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-87224.666666666672</v>
+        <v>-90557.333333333328</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -35000,7 +35096,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-87224.666666666672</v>
+        <v>-90557.333333333328</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -35008,7 +35104,7 @@
       </c>
       <c r="H10" s="88">
         <f>F10-G10</f>
-        <v>-27281.996666666673</v>
+        <v>-30614.66333333333</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="90" customFormat="1" ht="15.75" customHeight="1">
@@ -35433,11 +35529,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>119697.60139999999</v>
+        <v>120172.69639999999</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>173594.39860000001</v>
+        <v>173119.30360000001</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35445,7 +35541,7 @@
       </c>
       <c r="G4" s="88">
         <f>E4+F4</f>
-        <v>36284.372600000002</v>
+        <v>35809.277600000001</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -35454,7 +35550,7 @@
       </c>
       <c r="B5" s="11">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A5,Sales!$I:$I,"Completed"),0)</f>
-        <v>53199</v>
+        <v>54624</v>
       </c>
       <c r="C5" s="11">
         <f>VLOOKUP($A5,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -35462,11 +35558,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>119625.7972</v>
+        <v>120100.6072</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-66426.797200000001</v>
+        <v>-65476.607199999999</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35474,7 +35570,7 @@
       </c>
       <c r="G5" s="89">
         <f>E5+F5</f>
-        <v>5160.2448000000004</v>
+        <v>6110.4348000000027</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -35491,11 +35587,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>119697.60139999999</v>
+        <v>120172.69639999999</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-107167.60139999999</v>
+        <v>-107642.69639999999</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35503,7 +35599,7 @@
       </c>
       <c r="G6" s="88">
         <f>E6+F6</f>
-        <v>-41444.617399999974</v>
+        <v>-41919.712399999975</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">

--- a/docs/Chiraath-Summary-Jun26.xlsx
+++ b/docs/Chiraath-Summary-Jun26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36FCD25-7E2D-7F49-8D55-19C0F313FE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614187F4-154F-304F-895A-B1C1FB5AEF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">INVENTORY!$A$1:$T$188</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Purchases!$A$1:$D$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$217</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2439" uniqueCount="971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2596" uniqueCount="1042">
   <si>
     <t>Notes:</t>
   </si>
@@ -1829,9 +1829,6 @@
   </si>
   <si>
     <t>Chanderi silk soft dusty rose/pink kurta suit set with delicate floral prints and light embroiderysalwar 3 piece set</t>
-  </si>
-  <si>
-    <t>Saida (1400), Binija (1560)</t>
   </si>
   <si>
     <t>Size: M, L</t>
@@ -1990,9 +1987,6 @@
   </si>
   <si>
     <t>Sourabhya (XL - 580), Lakshmi - L</t>
-  </si>
-  <si>
-    <t>L, XXL</t>
   </si>
   <si>
     <t>CHR-93</t>
@@ -2206,780 +2200,997 @@
     <t>Banarasi Silk (Parrot Green)</t>
   </si>
   <si>
+    <t>CHR-123</t>
+  </si>
+  <si>
+    <t>Kalyani cotton silk (red)</t>
+  </si>
+  <si>
+    <t>Divya (Kollam), Ananya (TVM), Liji (Vadakara), Archana(Devagiri)-Ordered, Anu(Kottayam), Linu(Kottayam)</t>
+  </si>
+  <si>
+    <t>CHR-124</t>
+  </si>
+  <si>
+    <t>Viscose Chokda</t>
+  </si>
+  <si>
+    <t>Neethu(Pkd)-1450, Remya(Pkd)-1250</t>
+  </si>
+  <si>
+    <t>Blue, Green</t>
+  </si>
+  <si>
+    <t>CHR-125</t>
+  </si>
+  <si>
+    <t>Aanchal Maroon Salwar</t>
+  </si>
+  <si>
+    <t>Malu (1800)</t>
+  </si>
+  <si>
+    <t>XXXL</t>
+  </si>
+  <si>
+    <t>CHR-126</t>
+  </si>
+  <si>
+    <t>Aanchal maroon palzo kurta</t>
+  </si>
+  <si>
+    <t>CHR-127</t>
+  </si>
+  <si>
+    <t>⁠Rustic Geo Kota (Stairs) - Net Kota</t>
+  </si>
+  <si>
+    <t>CHR-128</t>
+  </si>
+  <si>
+    <t>⁠Grey Arrow Kota (Arrow) - Net kota</t>
+  </si>
+  <si>
+    <t>Chris (1250)</t>
+  </si>
+  <si>
+    <t>CHR-129</t>
+  </si>
+  <si>
+    <t>Dolla silk Olive Green</t>
+  </si>
+  <si>
+    <t>Ranju(1000)</t>
+  </si>
+  <si>
+    <t>CHR-130</t>
+  </si>
+  <si>
+    <t>Chanderi Cotton (Golden Yellow)</t>
+  </si>
+  <si>
+    <t>CHR-131</t>
+  </si>
+  <si>
+    <t>⁠​Regal Black semi silk Brocade type</t>
+  </si>
+  <si>
+    <t>Saranya Gopalakrishnan(1300)</t>
+  </si>
+  <si>
+    <t>CHR-132</t>
+  </si>
+  <si>
+    <t>Kota Doria (Green with silver floral work)</t>
+  </si>
+  <si>
+    <t>CHR-133</t>
+  </si>
+  <si>
+    <t>Semi Silk (Peach)</t>
+  </si>
+  <si>
+    <t>CHR-134</t>
+  </si>
+  <si>
+    <t>Net kota saree - turquoise blue with floral design and maroon border</t>
+  </si>
+  <si>
+    <t>priya(hosur)</t>
+  </si>
+  <si>
+    <t>CHR-135</t>
+  </si>
+  <si>
+    <t>⁠Viscose Chokda</t>
+  </si>
+  <si>
+    <t>Sreeja -Green:1250, Ranju - rust orange:1000, Aasa - 1250 (Lotus)</t>
+  </si>
+  <si>
+    <t>burned orange (lotus)</t>
+  </si>
+  <si>
+    <t>CHR-136</t>
+  </si>
+  <si>
+    <t>Banarasi silk (lavender)</t>
+  </si>
+  <si>
+    <t>CHR-137</t>
+  </si>
+  <si>
+    <t>⁠​Blue manipuri silk saree</t>
+  </si>
+  <si>
+    <t>Priya (TVM)</t>
+  </si>
+  <si>
+    <t>CHR-138</t>
+  </si>
+  <si>
+    <t>⁠​Linen black saree</t>
+  </si>
+  <si>
+    <t>CHR-139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⁠​Maheswari cotton Silk saree </t>
+  </si>
+  <si>
+    <t>haris(ekm)</t>
+  </si>
+  <si>
+    <t>CHR-140</t>
+  </si>
+  <si>
+    <t>⁠​Ganga Jamuna kalyani Cotton Saree</t>
+  </si>
+  <si>
+    <t>CHR-141</t>
+  </si>
+  <si>
+    <t>Semi Silk</t>
+  </si>
+  <si>
+    <t>Annu (Light Violet Semi Silk), Susmi - Coffee, Navya - mustard</t>
+  </si>
+  <si>
+    <t>CHR-142</t>
+  </si>
+  <si>
+    <t>Semi Silk (Rose Pink)</t>
+  </si>
+  <si>
+    <t>CHR-143</t>
+  </si>
+  <si>
+    <t>Synthetic Net Kota Doria (Soft ivory/off-white - Muted Coral Pink &amp; Olive green floral motifs)</t>
+  </si>
+  <si>
+    <t>CHR-144</t>
+  </si>
+  <si>
+    <t>CHR-145</t>
+  </si>
+  <si>
+    <t>Linen Saree with Check (Maroon with golden checks, Rust Orange with golden checks)</t>
+  </si>
+  <si>
+    <t>Chris (1000 - Green), Chithra - Maroon</t>
+  </si>
+  <si>
+    <t>Rust Orange</t>
+  </si>
+  <si>
+    <t>CHR-146</t>
+  </si>
+  <si>
+    <t>Matka Silk Saree collections - old design</t>
+  </si>
+  <si>
+    <t>Blue/bottle green - Saranya Hyd, Blue/red - Jothika, Mustard - Vineetha, Bottle Green/Golden Yellow - Swapna (Thrissur)-1200, Black/Golden yellow - Kavya(Kasargod) - 1200, Back/Yellow - Subha - 1200</t>
+  </si>
+  <si>
+    <t>CHR-147</t>
+  </si>
+  <si>
+    <t>Soft Cotton Saree (with butterfly design on Pallu)</t>
+  </si>
+  <si>
+    <t>Latha(Yellow), Sari(Peach)</t>
+  </si>
+  <si>
+    <t>CHR-148</t>
+  </si>
+  <si>
+    <t>SAREES 5619 (Tissue Silk Saree Golden Color)</t>
+  </si>
+  <si>
+    <t>Chris (Goldern with flowers), Indu Varrier</t>
+  </si>
+  <si>
+    <t>CHR-149</t>
+  </si>
+  <si>
+    <t>SAREE TISSUE EMB (Lavender (light &amp; dark), Red)</t>
+  </si>
+  <si>
+    <t>CHR-150</t>
+  </si>
+  <si>
+    <t>CHIKKANKARI SALWAR</t>
+  </si>
+  <si>
+    <t>Praneetha (L), Rameez Cousin (M), Indu (XL)</t>
+  </si>
+  <si>
+    <t>Purple</t>
+  </si>
+  <si>
+    <t>CHR-151</t>
+  </si>
+  <si>
+    <t>Short Kurta</t>
+  </si>
+  <si>
+    <t>Light Brown colr</t>
+  </si>
+  <si>
+    <t>CHR-152</t>
+  </si>
+  <si>
+    <t>Banarasi (Yellow/Green)</t>
+  </si>
+  <si>
+    <t>Shinoob (1200)</t>
+  </si>
+  <si>
+    <t>Yellow Green</t>
+  </si>
+  <si>
+    <t>CHR-153</t>
+  </si>
+  <si>
+    <t>Ivory &amp; black printed cotton 3-piece salwar set</t>
+  </si>
+  <si>
+    <t>Indukala - XL</t>
+  </si>
+  <si>
+    <t>XL, XXL</t>
+  </si>
+  <si>
+    <t>CHR-154</t>
+  </si>
+  <si>
+    <t>Dark brown embroidered cotton 3-piece salwar set</t>
+  </si>
+  <si>
+    <t>M, XL, XXL</t>
+  </si>
+  <si>
+    <t>CHR-155</t>
+  </si>
+  <si>
+    <t>Black cotton 3-piece salwar set with printed dupatta</t>
+  </si>
+  <si>
+    <t>Indukala - L</t>
+  </si>
+  <si>
+    <t>CHR-156</t>
+  </si>
+  <si>
+    <t>Off-white cotton 2-piece set with blue floral prints</t>
+  </si>
+  <si>
+    <t>CHR-157</t>
+  </si>
+  <si>
+    <t>Off-white printed 2-piece kurti set with multicolor pattern</t>
+  </si>
+  <si>
+    <t>Indu - M</t>
+  </si>
+  <si>
+    <t>L, XL, XXL, XXXL</t>
+  </si>
+  <si>
+    <t>CHR-158</t>
+  </si>
+  <si>
+    <t>Olive green cotton 2-piece kurti set with floral prints</t>
+  </si>
+  <si>
+    <t>Indu - XXL, Susmi - M</t>
+  </si>
+  <si>
+    <t>L, XL, XXXL</t>
+  </si>
+  <si>
+    <t>CHR-159</t>
+  </si>
+  <si>
+    <t>Khadee Saree - Navy Blue and Olive Green</t>
+  </si>
+  <si>
+    <t>CHR-160</t>
+  </si>
+  <si>
+    <t>Khadee Saree - Brown &amp; Black</t>
+  </si>
+  <si>
+    <t>CHR-161</t>
+  </si>
+  <si>
+    <t>Khadee Saree - Black &amp; Beige Leaf Print Cotton Silk Saree</t>
+  </si>
+  <si>
+    <t>CHR-162</t>
+  </si>
+  <si>
+    <t>Khadee Saree - Teal &amp; Coral Abstract Print Cotton Silk Saree</t>
+  </si>
+  <si>
+    <t>CHR-163</t>
+  </si>
+  <si>
+    <t>Narayanpet sarees</t>
+  </si>
+  <si>
+    <t>CHR-164</t>
+  </si>
+  <si>
+    <t>Sungudi Saree (Alice Christy inspired)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red &amp; Navy Blue </t>
+  </si>
+  <si>
+    <t>CHR-165</t>
+  </si>
+  <si>
+    <t>Jute Silk Checked Saree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violet, Chocolate Brown, Bottle Green  </t>
+  </si>
+  <si>
+    <t>CHR-166</t>
+  </si>
+  <si>
+    <t>Tant Mix (Bank)</t>
+  </si>
+  <si>
+    <t>Rajna - 740, Malini - 980, Baby Khadeeja - 980</t>
+  </si>
+  <si>
+    <t>Peacock blue with rany pink</t>
+  </si>
+  <si>
+    <t>CHR-167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khadi Cotton Saree (Jar Border)  </t>
+  </si>
+  <si>
+    <t>Baby Khadeeja - Violet</t>
+  </si>
+  <si>
+    <t>Yellow, Dark Green</t>
+  </si>
+  <si>
+    <t>CHR-168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bengal Cotton (Light Orange Floral)  </t>
+  </si>
+  <si>
+    <t>Orange floral</t>
+  </si>
+  <si>
+    <t>CHR-169</t>
+  </si>
+  <si>
+    <t>Banarasi Sarees (New Collection)</t>
+  </si>
+  <si>
+    <t>Leena - Chikku Green, Prema - Chikku Maroon, Shini - Green</t>
+  </si>
+  <si>
+    <t>Dark biege with bottle green, Biege Maroon combination, Green</t>
+  </si>
+  <si>
+    <t>CHR-170</t>
+  </si>
+  <si>
+    <t>Banarasi Sarees with Paisley motifs</t>
+  </si>
+  <si>
+    <t>Ponnu - Red (1350), Indu - Maroon, Anju Shinoob - Blue</t>
+  </si>
+  <si>
+    <t>CHR-171</t>
+  </si>
+  <si>
+    <t>Kerala Saree Temple design</t>
+  </si>
+  <si>
+    <t>CHR-172</t>
+  </si>
+  <si>
+    <t>Kerala Saree Kathakali</t>
+  </si>
+  <si>
+    <t>CHR-173</t>
+  </si>
+  <si>
+    <t>Kerala Saree floral embroidery</t>
+  </si>
+  <si>
+    <t>Smita</t>
+  </si>
+  <si>
+    <t>CHR-174</t>
+  </si>
+  <si>
+    <t>Matka Silk Saree collections - new design</t>
+  </si>
+  <si>
+    <t>CHR-175</t>
+  </si>
+  <si>
+    <t>Soft Silk Saree Collection</t>
+  </si>
+  <si>
+    <t>CHR-176</t>
+  </si>
+  <si>
+    <t>Tussar Silk Collection</t>
+  </si>
+  <si>
+    <t>Grey, wine (damaged)</t>
+  </si>
+  <si>
+    <t>CHR-177</t>
+  </si>
+  <si>
+    <t>Tissue Silk Saree Collection</t>
+  </si>
+  <si>
+    <t>Light brown</t>
+  </si>
+  <si>
+    <t>CHR-178</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree Collection</t>
+  </si>
+  <si>
+    <t>Smita - Parrot Green, Lakshmi - Black &amp; Orange, Indukala - Black/Pink</t>
+  </si>
+  <si>
+    <t>black/pink</t>
+  </si>
+  <si>
+    <t>CHR-179</t>
+  </si>
+  <si>
+    <t>Matka Silk Saree Collection</t>
+  </si>
+  <si>
+    <t>CHR-180</t>
+  </si>
+  <si>
+    <t>CHR-181</t>
+  </si>
+  <si>
+    <t>CHR-182</t>
+  </si>
+  <si>
+    <t>CHR-183</t>
+  </si>
+  <si>
+    <t>CHR-184</t>
+  </si>
+  <si>
+    <t>CHR-185</t>
+  </si>
+  <si>
+    <t>CHR-186</t>
+  </si>
+  <si>
+    <t>CHR-187</t>
+  </si>
+  <si>
+    <t>Partner Settings</t>
+  </si>
+  <si>
+    <t>Share %</t>
+  </si>
+  <si>
+    <t>Total Purchases (Contributions)</t>
+  </si>
+  <si>
+    <t>Target Contributions (by %)</t>
+  </si>
+  <si>
+    <t>Contribution Over/(Under)</t>
+  </si>
+  <si>
+    <t>Profit Share (Completed Only)</t>
+  </si>
+  <si>
+    <t>Net Before Settlements</t>
+  </si>
+  <si>
+    <t>Net Settlements (Received - Paid)</t>
+  </si>
+  <si>
+    <t>Net Position After Settlements</t>
+  </si>
+  <si>
+    <t>Global Settlements Log (used for Contributions, Cash Pool &amp; Profit)</t>
+  </si>
+  <si>
+    <t>Type (Contribution/Cash/Profit)</t>
+  </si>
+  <si>
+    <t>From Partner</t>
+  </si>
+  <si>
+    <t>To Partner</t>
+  </si>
+  <si>
+    <t>Contribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Cash Pool Overview (Completed Sales Only)</t>
+  </si>
+  <si>
+    <t>Cash Collected (Completed Sales)</t>
+  </si>
+  <si>
+    <t>Target Cash Based on %</t>
+  </si>
+  <si>
+    <t>Over/(Under) Collection</t>
+  </si>
+  <si>
+    <t>Net Cash Settlements (Received - Paid)</t>
+  </si>
+  <si>
+    <t>Cash Position After Settlements</t>
+  </si>
+  <si>
+    <t>1. Cash Collected only counts sales with Status = "Completed".</t>
+  </si>
+  <si>
+    <t>2. Target Cash is based on the same partner percentages as profit sharing.</t>
+  </si>
+  <si>
+    <t>3. Over/(Under) is the raw difference before any cash settlements.</t>
+  </si>
+  <si>
+    <t>4. Net Cash Settlements reads Type = "Cash" rows from PartnerShares Settlements Log.</t>
+  </si>
+  <si>
+    <t>5. Cash Position After Settlements = Over/(Under) + Net Cash Settlements.</t>
+  </si>
+  <si>
+    <t>Sungudi (Alice Christy inspired)</t>
+  </si>
+  <si>
+    <t>Revathi</t>
+  </si>
+  <si>
+    <t>Resmi(Tvm) - 500, Revathi</t>
+  </si>
+  <si>
+    <t>Kerala Saree Temple Design, Pink Cottton Saree (CHR-61), Chanderi Silk Saree (Orange &amp; Maroon-CHR-119), Matka Saree (Green/Pink -CHR-179)</t>
+  </si>
+  <si>
+    <t>Siji</t>
+  </si>
+  <si>
+    <t>Anju Sanjeev</t>
+  </si>
+  <si>
+    <t>Saritha</t>
+  </si>
+  <si>
+    <t>Tussar Silk Saree (CHR-177)</t>
+  </si>
+  <si>
+    <t>Lipcy - Green, Siji -Dusty Rose</t>
+  </si>
+  <si>
+    <t>Smitha - Rust orange &amp; Onion Peel, Lipcy - Blue, Grey &amp; Wine - Returned</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree (Rani Pink- CHR-119)</t>
+  </si>
+  <si>
+    <t>Rose</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree (Black - CHR-119)</t>
+  </si>
+  <si>
+    <t>Lipcy - Red/Green, Revathi - Parrot Green/Red, Anju Sanjeev - royal blue/rani pink</t>
+  </si>
+  <si>
+    <t>Soft Silk Black - Chithra, Violet - Susmi, Maroon - Returned, Anju Sanjeev - Navy Blue</t>
+  </si>
+  <si>
+    <t>Jaimy</t>
+  </si>
+  <si>
+    <t>Chithra- peacok blue, Indu Varier - Green, Susmi - Maroon, Jaimy - Purple/Bottle Green</t>
+  </si>
+  <si>
+    <t>Grey-Black/Red</t>
+  </si>
+  <si>
+    <t>Matka (royal blue/rani pink-CHR-179), Soft Silk Saree (Navy Blue-CHR-175)</t>
+  </si>
+  <si>
+    <t>Bindu Krishnaraj</t>
+  </si>
+  <si>
+    <t>Kavitha</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree (off white - CHR-119)</t>
+  </si>
+  <si>
+    <t>Jisa Suresh (Anita)</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree (Rani Pink(2)- CHR-119)</t>
+  </si>
+  <si>
+    <t>Sudharma</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree (Navy Blue- CHR-119)</t>
+  </si>
+  <si>
+    <t>P K Sopitha (Sindrella)</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree (Maroon - CHR-119)</t>
+  </si>
+  <si>
+    <t>Simi Sudhir</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree (Navy Blue- CHR-119) &amp; Kerala Saree Temple Design</t>
+  </si>
+  <si>
+    <t>Revathi, Simi Sudhir</t>
+  </si>
+  <si>
+    <t>Shaino Benny</t>
+  </si>
+  <si>
+    <t>Supriya</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree (Green- CHR-119)</t>
+  </si>
+  <si>
+    <t>Mercy Reji</t>
+  </si>
+  <si>
+    <t>Matka Green/Yellow</t>
+  </si>
+  <si>
+    <t>Bottle Green/Golden Yellow - 1
+Navy Blue/Bottle Green - 2</t>
+  </si>
+  <si>
+    <t>Kalaisari (Dharmapuri)</t>
+  </si>
+  <si>
+    <t>Latha Suresh (Malappuram)</t>
+  </si>
+  <si>
+    <t>Boostin charges</t>
+  </si>
+  <si>
+    <t>Kannur Salwar Purchase</t>
+  </si>
+  <si>
+    <t>Courier covers and butter papers</t>
+  </si>
+  <si>
+    <t>Salwar maroon single piece M (CHR-78)</t>
+  </si>
+  <si>
+    <t>Banarasi Green Old design</t>
+  </si>
+  <si>
+    <t>Postal parcel charges</t>
+  </si>
+  <si>
+    <t>Matka (peacock blue/maroon CHR-174), Narayanpett purple/bottle green (CHR-163), Ganga Jamuna (CHR-140)</t>
+  </si>
+  <si>
+    <t>Jaimy (1000)</t>
+  </si>
+  <si>
+    <t>M, L, XL, XXL</t>
+  </si>
+  <si>
+    <t>Cotton 3 piece salwar set</t>
+  </si>
+  <si>
+    <t>Linen Blend floral embrioidered sarees</t>
+  </si>
+  <si>
+    <t>Sky Blue, Mint Green, Blush Pink</t>
+  </si>
+  <si>
+    <t>Coffee brown with Rust Floral Print</t>
+  </si>
+  <si>
     <t>Nisha Nair
 Shiji
 Priya Reji
 Raji
-Nisha Sajitha</t>
-  </si>
-  <si>
-    <t>CHR-123</t>
-  </si>
-  <si>
-    <t>Kalyani cotton silk (red)</t>
-  </si>
-  <si>
-    <t>Divya (Kollam), Ananya (TVM), Liji (Vadakara), Archana(Devagiri)-Ordered, Anu(Kottayam), Linu(Kottayam)</t>
-  </si>
-  <si>
-    <t>CHR-124</t>
-  </si>
-  <si>
-    <t>Viscose Chokda</t>
-  </si>
-  <si>
-    <t>Neethu(Pkd)-1450, Remya(Pkd)-1250</t>
-  </si>
-  <si>
-    <t>Blue, Green</t>
-  </si>
-  <si>
-    <t>CHR-125</t>
-  </si>
-  <si>
-    <t>Aanchal Maroon Salwar</t>
-  </si>
-  <si>
-    <t>Malu (1800)</t>
-  </si>
-  <si>
-    <t>XXXL</t>
-  </si>
-  <si>
-    <t>CHR-126</t>
-  </si>
-  <si>
-    <t>Aanchal maroon palzo kurta</t>
-  </si>
-  <si>
-    <t>CHR-127</t>
-  </si>
-  <si>
-    <t>⁠Rustic Geo Kota (Stairs) - Net Kota</t>
-  </si>
-  <si>
-    <t>CHR-128</t>
-  </si>
-  <si>
-    <t>⁠Grey Arrow Kota (Arrow) - Net kota</t>
-  </si>
-  <si>
-    <t>Chris (1250)</t>
-  </si>
-  <si>
-    <t>CHR-129</t>
-  </si>
-  <si>
-    <t>Dolla silk Olive Green</t>
-  </si>
-  <si>
-    <t>Ranju(1000)</t>
-  </si>
-  <si>
-    <t>CHR-130</t>
-  </si>
-  <si>
-    <t>Chanderi Cotton (Golden Yellow)</t>
-  </si>
-  <si>
-    <t>CHR-131</t>
-  </si>
-  <si>
-    <t>⁠​Regal Black semi silk Brocade type</t>
-  </si>
-  <si>
-    <t>Saranya Gopalakrishnan(1300)</t>
-  </si>
-  <si>
-    <t>CHR-132</t>
-  </si>
-  <si>
-    <t>Kota Doria (Green with silver floral work)</t>
-  </si>
-  <si>
-    <t>CHR-133</t>
-  </si>
-  <si>
-    <t>Semi Silk (Peach)</t>
-  </si>
-  <si>
-    <t>CHR-134</t>
-  </si>
-  <si>
-    <t>Net kota saree - turquoise blue with floral design and maroon border</t>
-  </si>
-  <si>
-    <t>priya(hosur)</t>
-  </si>
-  <si>
-    <t>CHR-135</t>
-  </si>
-  <si>
-    <t>⁠Viscose Chokda</t>
-  </si>
-  <si>
-    <t>Sreeja -Green:1250, Ranju - rust orange:1000, Aasa - 1250 (Lotus)</t>
-  </si>
-  <si>
-    <t>burned orange (lotus)</t>
-  </si>
-  <si>
-    <t>CHR-136</t>
-  </si>
-  <si>
-    <t>Banarasi silk (lavender)</t>
-  </si>
-  <si>
-    <t>CHR-137</t>
-  </si>
-  <si>
-    <t>⁠​Blue manipuri silk saree</t>
-  </si>
-  <si>
-    <t>Priya (TVM)</t>
-  </si>
-  <si>
-    <t>CHR-138</t>
-  </si>
-  <si>
-    <t>⁠​Linen black saree</t>
-  </si>
-  <si>
-    <t>CHR-139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⁠​Maheswari cotton Silk saree </t>
-  </si>
-  <si>
-    <t>haris(ekm)</t>
-  </si>
-  <si>
-    <t>CHR-140</t>
-  </si>
-  <si>
-    <t>⁠​Ganga Jamuna kalyani Cotton Saree</t>
-  </si>
-  <si>
-    <t>CHR-141</t>
-  </si>
-  <si>
-    <t>Semi Silk</t>
-  </si>
-  <si>
-    <t>Annu (Light Violet Semi Silk), Susmi - Coffee, Navya - mustard</t>
-  </si>
-  <si>
-    <t>CHR-142</t>
-  </si>
-  <si>
-    <t>Semi Silk (Rose Pink)</t>
-  </si>
-  <si>
-    <t>CHR-143</t>
-  </si>
-  <si>
-    <t>Synthetic Net Kota Doria (Soft ivory/off-white - Muted Coral Pink &amp; Olive green floral motifs)</t>
-  </si>
-  <si>
-    <t>CHR-144</t>
-  </si>
-  <si>
-    <t>CHR-145</t>
-  </si>
-  <si>
-    <t>Linen Saree with Check (Maroon with golden checks, Rust Orange with golden checks)</t>
-  </si>
-  <si>
-    <t>Chris (1000 - Green), Chithra - Maroon</t>
-  </si>
-  <si>
-    <t>Rust Orange</t>
-  </si>
-  <si>
-    <t>CHR-146</t>
-  </si>
-  <si>
-    <t>Matka Silk Saree collections - old design</t>
-  </si>
-  <si>
-    <t>Blue/bottle green - Saranya Hyd, Blue/red - Jothika, Mustard - Vineetha, Bottle Green/Golden Yellow - Swapna (Thrissur)-1200, Black/Golden yellow - Kavya(Kasargod) - 1200, Back/Yellow - Subha - 1200</t>
-  </si>
-  <si>
-    <t>CHR-147</t>
-  </si>
-  <si>
-    <t>Soft Cotton Saree (with butterfly design on Pallu)</t>
-  </si>
-  <si>
-    <t>Latha(Yellow), Sari(Peach)</t>
-  </si>
-  <si>
-    <t>CHR-148</t>
-  </si>
-  <si>
-    <t>SAREES 5619 (Tissue Silk Saree Golden Color)</t>
-  </si>
-  <si>
-    <t>Chris (Goldern with flowers), Indu Varrier</t>
-  </si>
-  <si>
-    <t>CHR-149</t>
-  </si>
-  <si>
-    <t>SAREE TISSUE EMB (Lavender (light &amp; dark), Red)</t>
-  </si>
-  <si>
-    <t>CHR-150</t>
-  </si>
-  <si>
-    <t>CHIKKANKARI SALWAR</t>
-  </si>
-  <si>
-    <t>Praneetha (L), Rameez Cousin (M), Indu (XL)</t>
-  </si>
-  <si>
-    <t>Purple</t>
-  </si>
-  <si>
-    <t>CHR-151</t>
-  </si>
-  <si>
-    <t>Short Kurta</t>
-  </si>
-  <si>
-    <t>Rinsha(M)</t>
-  </si>
-  <si>
-    <t>L,XL,XXL</t>
-  </si>
-  <si>
-    <t>Light Brown colr</t>
-  </si>
-  <si>
-    <t>CHR-152</t>
-  </si>
-  <si>
-    <t>Banarasi (Yellow/Green)</t>
-  </si>
-  <si>
-    <t>Shinoob (1200)</t>
-  </si>
-  <si>
-    <t>Yellow Green</t>
-  </si>
-  <si>
-    <t>CHR-153</t>
-  </si>
-  <si>
-    <t>Ivory &amp; black printed cotton 3-piece salwar set</t>
-  </si>
-  <si>
-    <t>Indukala - XL</t>
-  </si>
-  <si>
-    <t>XL, XXL</t>
-  </si>
-  <si>
-    <t>CHR-154</t>
-  </si>
-  <si>
-    <t>Dark brown embroidered cotton 3-piece salwar set</t>
-  </si>
-  <si>
-    <t>M, XL, XXL</t>
-  </si>
-  <si>
-    <t>CHR-155</t>
-  </si>
-  <si>
-    <t>Black cotton 3-piece salwar set with printed dupatta</t>
-  </si>
-  <si>
-    <t>Indukala - L</t>
-  </si>
-  <si>
-    <t>CHR-156</t>
-  </si>
-  <si>
-    <t>Off-white cotton 2-piece set with blue floral prints</t>
-  </si>
-  <si>
-    <t>Prema(XXL)- 550</t>
-  </si>
-  <si>
-    <t>M, L, XL</t>
-  </si>
-  <si>
-    <t>CHR-157</t>
-  </si>
-  <si>
-    <t>Off-white printed 2-piece kurti set with multicolor pattern</t>
-  </si>
-  <si>
-    <t>Indu - M</t>
-  </si>
-  <si>
-    <t>L, XL, XXL, XXXL</t>
-  </si>
-  <si>
-    <t>CHR-158</t>
-  </si>
-  <si>
-    <t>Olive green cotton 2-piece kurti set with floral prints</t>
-  </si>
-  <si>
-    <t>Indu - XXL, Susmi - M</t>
-  </si>
-  <si>
-    <t>L, XL, XXXL</t>
-  </si>
-  <si>
-    <t>CHR-159</t>
-  </si>
-  <si>
-    <t>Khadee Saree - Navy Blue and Olive Green</t>
-  </si>
-  <si>
-    <t>CHR-160</t>
-  </si>
-  <si>
-    <t>Khadee Saree - Brown &amp; Black</t>
-  </si>
-  <si>
-    <t>CHR-161</t>
-  </si>
-  <si>
-    <t>Khadee Saree - Black &amp; Beige Leaf Print Cotton Silk Saree</t>
-  </si>
-  <si>
-    <t>CHR-162</t>
-  </si>
-  <si>
-    <t>Khadee Saree - Teal &amp; Coral Abstract Print Cotton Silk Saree</t>
-  </si>
-  <si>
-    <t>CHR-163</t>
-  </si>
-  <si>
-    <t>Narayanpet sarees</t>
-  </si>
-  <si>
-    <t>CHR-164</t>
-  </si>
-  <si>
-    <t>Sungudi Saree (Alice Christy inspired)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red &amp; Navy Blue </t>
-  </si>
-  <si>
-    <t>CHR-165</t>
-  </si>
-  <si>
-    <t>Jute Silk Checked Saree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violet, Chocolate Brown, Bottle Green  </t>
-  </si>
-  <si>
-    <t>CHR-166</t>
-  </si>
-  <si>
-    <t>Tant Mix (Bank)</t>
-  </si>
-  <si>
-    <t>Rajna - 740, Malini - 980, Baby Khadeeja - 980</t>
-  </si>
-  <si>
-    <t>Peacock blue with rany pink</t>
-  </si>
-  <si>
-    <t>CHR-167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khadi Cotton Saree (Jar Border)  </t>
-  </si>
-  <si>
-    <t>Baby Khadeeja - Violet</t>
-  </si>
-  <si>
-    <t>Yellow, Dark Green</t>
-  </si>
-  <si>
-    <t>CHR-168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bengal Cotton (Light Orange Floral)  </t>
-  </si>
-  <si>
-    <t>Orange floral</t>
-  </si>
-  <si>
-    <t>CHR-169</t>
-  </si>
-  <si>
-    <t>Banarasi Sarees (New Collection)</t>
-  </si>
-  <si>
-    <t>Leena - Chikku Green, Prema - Chikku Maroon, Shini - Green</t>
-  </si>
-  <si>
-    <t>Dark biege with bottle green, Biege Maroon combination, Green</t>
-  </si>
-  <si>
-    <t>CHR-170</t>
-  </si>
-  <si>
-    <t>Banarasi Sarees with Paisley motifs</t>
-  </si>
-  <si>
-    <t>Ponnu - Red (1350), Indu - Maroon, Anju Shinoob - Blue</t>
-  </si>
-  <si>
-    <t>CHR-171</t>
-  </si>
-  <si>
-    <t>Kerala Saree Temple design</t>
-  </si>
-  <si>
-    <t>CHR-172</t>
-  </si>
-  <si>
-    <t>Kerala Saree Kathakali</t>
-  </si>
-  <si>
-    <t>CHR-173</t>
-  </si>
-  <si>
-    <t>Kerala Saree floral embroidery</t>
-  </si>
-  <si>
-    <t>Smita</t>
-  </si>
-  <si>
-    <t>CHR-174</t>
-  </si>
-  <si>
-    <t>Matka Silk Saree collections - new design</t>
-  </si>
-  <si>
-    <t>CHR-175</t>
-  </si>
-  <si>
-    <t>Soft Silk Saree Collection</t>
-  </si>
-  <si>
-    <t>CHR-176</t>
-  </si>
-  <si>
-    <t>Tussar Silk Collection</t>
-  </si>
-  <si>
-    <t>Grey, wine (damaged)</t>
-  </si>
-  <si>
-    <t>CHR-177</t>
-  </si>
-  <si>
-    <t>Tissue Silk Saree Collection</t>
-  </si>
-  <si>
-    <t>Light brown</t>
-  </si>
-  <si>
-    <t>CHR-178</t>
-  </si>
-  <si>
-    <t>Chanderi Silk Saree Collection</t>
-  </si>
-  <si>
-    <t>Smita - Parrot Green, Lakshmi - Black &amp; Orange, Indukala - Black/Pink</t>
-  </si>
-  <si>
-    <t>black/pink</t>
-  </si>
-  <si>
-    <t>CHR-179</t>
-  </si>
-  <si>
-    <t>Matka Silk Saree Collection</t>
-  </si>
-  <si>
-    <t>CHR-180</t>
-  </si>
-  <si>
-    <t>CHR-181</t>
-  </si>
-  <si>
-    <t>CHR-182</t>
-  </si>
-  <si>
-    <t>CHR-183</t>
-  </si>
-  <si>
-    <t>CHR-184</t>
-  </si>
-  <si>
-    <t>CHR-185</t>
-  </si>
-  <si>
-    <t>CHR-186</t>
-  </si>
-  <si>
-    <t>CHR-187</t>
-  </si>
-  <si>
-    <t>Partner Settings</t>
-  </si>
-  <si>
-    <t>Share %</t>
-  </si>
-  <si>
-    <t>Total Purchases (Contributions)</t>
-  </si>
-  <si>
-    <t>Target Contributions (by %)</t>
-  </si>
-  <si>
-    <t>Contribution Over/(Under)</t>
-  </si>
-  <si>
-    <t>Profit Share (Completed Only)</t>
-  </si>
-  <si>
-    <t>Net Before Settlements</t>
-  </si>
-  <si>
-    <t>Net Settlements (Received - Paid)</t>
-  </si>
-  <si>
-    <t>Net Position After Settlements</t>
-  </si>
-  <si>
-    <t>Global Settlements Log (used for Contributions, Cash Pool &amp; Profit)</t>
-  </si>
-  <si>
-    <t>Type (Contribution/Cash/Profit)</t>
-  </si>
-  <si>
-    <t>From Partner</t>
-  </si>
-  <si>
-    <t>To Partner</t>
-  </si>
-  <si>
-    <t>Contribution</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Cash Pool Overview (Completed Sales Only)</t>
-  </si>
-  <si>
-    <t>Cash Collected (Completed Sales)</t>
-  </si>
-  <si>
-    <t>Target Cash Based on %</t>
-  </si>
-  <si>
-    <t>Over/(Under) Collection</t>
-  </si>
-  <si>
-    <t>Net Cash Settlements (Received - Paid)</t>
-  </si>
-  <si>
-    <t>Cash Position After Settlements</t>
-  </si>
-  <si>
-    <t>1. Cash Collected only counts sales with Status = "Completed".</t>
-  </si>
-  <si>
-    <t>2. Target Cash is based on the same partner percentages as profit sharing.</t>
-  </si>
-  <si>
-    <t>3. Over/(Under) is the raw difference before any cash settlements.</t>
-  </si>
-  <si>
-    <t>4. Net Cash Settlements reads Type = "Cash" rows from PartnerShares Settlements Log.</t>
-  </si>
-  <si>
-    <t>5. Cash Position After Settlements = Over/(Under) + Net Cash Settlements.</t>
-  </si>
-  <si>
-    <t>Sungudi (Alice Christy inspired)</t>
-  </si>
-  <si>
-    <t>Revathi</t>
-  </si>
-  <si>
-    <t>Resmi(Tvm) - 500, Revathi</t>
-  </si>
-  <si>
-    <t>Kerala Saree Temple Design, Pink Cottton Saree (CHR-61), Chanderi Silk Saree (Orange &amp; Maroon-CHR-119), Matka Saree (Green/Pink -CHR-179)</t>
-  </si>
-  <si>
-    <t>Siji</t>
-  </si>
-  <si>
-    <t>Anju Sanjeev</t>
-  </si>
-  <si>
-    <t>Saritha</t>
-  </si>
-  <si>
-    <t>Tussar Silk Saree (CHR-177)</t>
-  </si>
-  <si>
-    <t>Lipcy - Green, Siji -Dusty Rose</t>
-  </si>
-  <si>
-    <t>Smitha - Rust orange &amp; Onion Peel, Lipcy - Blue, Grey &amp; Wine - Returned</t>
-  </si>
-  <si>
-    <t>Chanderi Silk Saree (Rani Pink- CHR-119)</t>
-  </si>
-  <si>
-    <t>Rose</t>
-  </si>
-  <si>
-    <t>Chanderi Silk Saree (Black - CHR-119)</t>
-  </si>
-  <si>
-    <t>Lipcy - Red/Green, Revathi - Parrot Green/Red, Anju Sanjeev - royal blue/rani pink</t>
-  </si>
-  <si>
-    <t>Soft Silk Black - Chithra, Violet - Susmi, Maroon - Returned, Anju Sanjeev - Navy Blue</t>
-  </si>
-  <si>
-    <t>Jaimy</t>
-  </si>
-  <si>
-    <t>Sherin - Maroon/navy blue(1099), Lakshmi - Navy Blue &amp; Maroon, Jaimy - Peacok Blue/Maroon</t>
-  </si>
-  <si>
-    <t>Chithra- peacok blue, Indu Varier - Green, Susmi - Maroon, Jaimy - Purple/Bottle Green</t>
-  </si>
-  <si>
-    <t>Grey-Black/Red</t>
+Nisha Sajitha, Bhavana Meenakshi</t>
+  </si>
+  <si>
+    <t>Bhavana Meenakshi</t>
+  </si>
+  <si>
+    <t>Shinoob Cousin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sherin - Maroon/navy blue(1099), Lakshmi - Navy Blue &amp; Maroon, Jaimy - Peacok Blue/Maroon, Shinoob Cousin - Lavender/Violet and Purple/Green </t>
   </si>
   <si>
     <t>Peacok Blue/Maroon - 2
-Purple/Green - 1
 Navy Blue/Maroon - 2
-Lavender/Violet - 1
 Grey/Blue - 1</t>
   </si>
   <si>
-    <t>Matka (royal blue/rani pink-CHR-179), Soft Silk Saree (Navy Blue-CHR-175)</t>
-  </si>
-  <si>
-    <t>Bindu Krishnaraj</t>
-  </si>
-  <si>
-    <t>Kavitha</t>
-  </si>
-  <si>
-    <t>Chanderi Silk Saree (off white - CHR-119)</t>
-  </si>
-  <si>
-    <t>Jisa Suresh (Anita)</t>
-  </si>
-  <si>
-    <t>Chanderi Silk Saree (Rani Pink(2)- CHR-119)</t>
-  </si>
-  <si>
-    <t>Sudharma</t>
-  </si>
-  <si>
-    <t>Chanderi Silk Saree (Navy Blue- CHR-119)</t>
-  </si>
-  <si>
-    <t>P K Sopitha (Sindrella)</t>
-  </si>
-  <si>
-    <t>Chanderi Silk Saree (Maroon - CHR-119)</t>
-  </si>
-  <si>
-    <t>Simi Sudhir</t>
-  </si>
-  <si>
-    <t>Chanderi Silk Saree (Navy Blue- CHR-119) &amp; Kerala Saree Temple Design</t>
-  </si>
-  <si>
-    <t>Revathi, Simi Sudhir</t>
-  </si>
-  <si>
-    <t>Shaino Benny</t>
-  </si>
-  <si>
-    <t>Supriya</t>
-  </si>
-  <si>
-    <t>Chanderi Silk Saree (Green- CHR-119)</t>
-  </si>
-  <si>
-    <t>Mercy Reji</t>
-  </si>
-  <si>
-    <t>Matka Green/Yellow</t>
-  </si>
-  <si>
-    <t>Bottle Green/Golden Yellow - 1
-Navy Blue/Bottle Green - 2</t>
-  </si>
-  <si>
-    <t>Kalaisari (Dharmapuri)</t>
-  </si>
-  <si>
-    <t>Latha Suresh (Malappuram)</t>
+    <t>Cotton 2-piece set with blue floral prints-M (CHR-156), Short Kurti(CHR-151)-L, Dusty Rose Salwar(CHR-77)-L, Chanderis Silk Saree(Yellow-CHR-119), Matka - Lavender/Violet &amp; Purple/Green (CHR-174)</t>
+  </si>
+  <si>
+    <t>Saida (1400), Binija (1560), Shinoob Cousin(1000)</t>
+  </si>
+  <si>
+    <t>Rinsha(M), Shinoob Cousin(L)</t>
+  </si>
+  <si>
+    <t>XL,XXL</t>
+  </si>
+  <si>
+    <t>Prema(XXL)- 550, Shinoob cousin(M)-850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Blue (2), Maroon (1), Orange (1), Black(3), White(5)</t>
   </si>
   <si>
     <t>First Set: Aruna - violet, Resmi - navy blue, Malini - Rani Pink
-Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black, Bindu Krisharaj - Black, Kavitha - off white, Jisha Suresh - Rani Pink(2), Sudharma - Navy Blue, SIndrella - Maroon, Shaino Benny - Navy blue, Simi Sudhir - Navy Blue, Supriya - Green, Mercy - Black, Kalisari - Green, Latha Suresh - Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Blue (2), mustard yellow (1), Maroon (1), off white (1), Orange (1), Black(3), White(5)</t>
-  </si>
-  <si>
-    <t>Boostin charges</t>
-  </si>
-  <si>
-    <t>Kannur Salwar Purchase</t>
-  </si>
-  <si>
-    <t>Courier covers and butter papers</t>
-  </si>
-  <si>
-    <t>Salwar maroon single piece M (CHR-78)</t>
-  </si>
-  <si>
-    <t>Banarasi Green Old design</t>
-  </si>
-  <si>
-    <t>Postal parcel charges</t>
-  </si>
-  <si>
-    <t>Matka (peacock blue/maroon CHR-174), Narayanpett purple/bottle green (CHR-163), Ganga Jamuna (CHR-140)</t>
-  </si>
-  <si>
-    <t>Jaimy (1000)</t>
-  </si>
-  <si>
-    <t>M, L, XL, XXL</t>
-  </si>
-  <si>
-    <t>Cotton 3 piece salwar set</t>
-  </si>
-  <si>
-    <t>Linen Blend floral embrioidered sarees</t>
-  </si>
-  <si>
-    <t>Sky Blue, Mint Green, Blush Pink</t>
-  </si>
-  <si>
-    <t>Coffee brown with Rust Floral Print</t>
+Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black, Bindu Krisharaj - Black, Kavitha - off white, Jisha Suresh - Rani Pink(2), Sudharma - Navy Blue, SIndrella - Maroon, Shaino Benny - Navy blue, Simi Sudhir - Navy Blue, Supriya - Green, Mercy - Black, Kalisari - Green, Latha Suresh - Black, Shinoob cousin - mustard yellow, off white returned</t>
+  </si>
+  <si>
+    <t>CHR-188</t>
+  </si>
+  <si>
+    <t>CHR-189</t>
+  </si>
+  <si>
+    <t>CHR-190</t>
+  </si>
+  <si>
+    <t>CHR-191</t>
+  </si>
+  <si>
+    <t>CHR-192</t>
+  </si>
+  <si>
+    <t>CHR-193</t>
+  </si>
+  <si>
+    <t>CHR-194</t>
+  </si>
+  <si>
+    <t>CHR-195</t>
+  </si>
+  <si>
+    <t>CHR-196</t>
+  </si>
+  <si>
+    <t>CHR-197</t>
+  </si>
+  <si>
+    <t>CHR-198</t>
+  </si>
+  <si>
+    <t>CHR-199</t>
+  </si>
+  <si>
+    <t>CHR-200</t>
+  </si>
+  <si>
+    <t>CHR-201</t>
+  </si>
+  <si>
+    <t>CHR-202</t>
+  </si>
+  <si>
+    <t>CHR-203</t>
+  </si>
+  <si>
+    <t>CHR-204</t>
+  </si>
+  <si>
+    <t>CHR-205</t>
+  </si>
+  <si>
+    <t>CHR-206</t>
+  </si>
+  <si>
+    <t>CHR-207</t>
+  </si>
+  <si>
+    <t>CHR-208</t>
+  </si>
+  <si>
+    <t>CHR-209</t>
+  </si>
+  <si>
+    <t>CHR-210</t>
+  </si>
+  <si>
+    <t>CHR-211</t>
+  </si>
+  <si>
+    <t>CHR-212</t>
+  </si>
+  <si>
+    <t>CHR-213</t>
+  </si>
+  <si>
+    <t>CHR-214</t>
+  </si>
+  <si>
+    <t>CHR-215</t>
+  </si>
+  <si>
+    <t>CHR-216</t>
+  </si>
+  <si>
+    <t>CHR-217</t>
+  </si>
+  <si>
+    <t>CHR-218</t>
+  </si>
+  <si>
+    <t>CHR-219</t>
+  </si>
+  <si>
+    <t>CHR-220</t>
+  </si>
+  <si>
+    <t>CHR-221</t>
+  </si>
+  <si>
+    <t>CHR-222</t>
+  </si>
+  <si>
+    <t>CHR-223</t>
+  </si>
+  <si>
+    <t>CHR-224</t>
+  </si>
+  <si>
+    <t>CHR-225</t>
+  </si>
+  <si>
+    <t>Yellow Lotus Saree Line</t>
+  </si>
+  <si>
+    <t>Postal</t>
+  </si>
+  <si>
+    <t>Temple design preordered - Yet to share the item</t>
+  </si>
+  <si>
+    <t>Banarasil Silk (Chikku Maroon)</t>
+  </si>
+  <si>
+    <t>Banarasi Silk (Chikku Green)</t>
+  </si>
+  <si>
+    <t>Banarasi Silk (Golden Yellow Green)</t>
+  </si>
+  <si>
+    <t>Banarasi Silk (Golden Yellow Blue)</t>
+  </si>
+  <si>
+    <t>Banarasi Silk (New Design)</t>
+  </si>
+  <si>
+    <t>Banarasi Silk (Leaf design)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New </t>
+  </si>
+  <si>
+    <t>Light green/dark green, navy/light, violet/green (leaf designs)</t>
+  </si>
+  <si>
+    <t>rust orange/coffee brown, peacock blue/navy, red/green, mustard/blue, chikku maroon, chikku green, golden yellow &amp; green triangle</t>
+  </si>
+  <si>
+    <t>Green/maroon - Rajitha Teacher</t>
+  </si>
+  <si>
+    <t>Jayalakshmi, Preetha, Prasanna, Philomina</t>
+  </si>
+  <si>
+    <t>Sanam, Geetha, Unknown, Jessy Joseph, Soji Thomas, Sheeba George</t>
+  </si>
+  <si>
+    <t>Rajitha Teacher</t>
+  </si>
+  <si>
+    <t>Green/maroon banarasi new design</t>
+  </si>
+  <si>
+    <t>Sheeba George</t>
+  </si>
+  <si>
+    <t>Soji Thomas</t>
+  </si>
+  <si>
+    <t>Jessy Joseph</t>
+  </si>
+  <si>
+    <t>Preetha</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Prasanna</t>
+  </si>
+  <si>
+    <t>Philomina Anto</t>
+  </si>
+  <si>
+    <t>Sanam</t>
+  </si>
+  <si>
+    <t>Geetha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silk Sarees </t>
+  </si>
+  <si>
+    <t>Green/maroon border, maroon peacock blue, light green &amp; bottle green, purple &amp; blue</t>
+  </si>
+  <si>
+    <t>Floral green, floral peach, floral lavender</t>
+  </si>
+  <si>
+    <t>Kerala Sarees with Floral design</t>
+  </si>
+  <si>
+    <t>Kerala Saree with small temple design</t>
+  </si>
+  <si>
+    <t>Small temple design</t>
   </si>
 </sst>
 </file>
@@ -2991,7 +3202,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3207,6 +3418,12 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Trebuchet MS"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -3892,13 +4109,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>210</c:v>
+                  <c:v>225</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>86</c:v>
+                  <c:v>88</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3995,13 +4212,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>65</c:v>
+                  <c:v>106</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>62</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4325,13 +4542,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>64790</c:v>
+                  <c:v>63190</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>43967.356666666667</c:v>
+                  <c:v>76679.463333333319</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1357</c:v>
+                  <c:v>1062</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4658,7 +4875,7 @@
                   <c:v>4449</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14730</c:v>
+                  <c:v>98456</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -4818,7 +5035,7 @@
                   <c:v>54524</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9843</c:v>
+                  <c:v>32953</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5258,7 +5475,7 @@
                   <c:v>50075</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-4887</c:v>
+                  <c:v>-65503</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5725,10 +5942,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>299</c:v>
+                  <c:v>317</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>131</c:v>
+                  <c:v>-656</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6900,7 +7117,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>369472</v>
+        <v>453198</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -6915,7 +7132,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>360446</v>
+        <v>383556</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -6932,7 +7149,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>365356</v>
+        <v>388466</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -6949,7 +7166,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-9026</v>
+        <v>-69642</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -6984,7 +7201,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>27074.326666666671</v>
+        <v>42891.66</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -6994,7 +7211,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>3540.3366666666698</v>
+        <v>15631.669999999998</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -7004,7 +7221,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-30614.66333333333</v>
+        <v>-58523.33</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -7043,15 +7260,15 @@
       </c>
       <c r="B18" s="10">
         <f>PartnerShares!B8</f>
-        <v>168535</v>
+        <v>212261</v>
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>123157.33333333333</v>
+        <v>151066</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>45377.666666666672</v>
+        <v>61195</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7059,11 +7276,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>27074.326666666671</v>
+        <v>42891.66</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹27,074</v>
+        <v>Receive ₹42,892</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -7073,15 +7290,15 @@
       </c>
       <c r="B19" s="12">
         <f>PartnerShares!B9</f>
-        <v>168337</v>
+        <v>208337</v>
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>123157.33333333333</v>
+        <v>151066</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>45179.666666666672</v>
+        <v>57271</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7089,11 +7306,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>3540.3366666666698</v>
+        <v>15631.669999999998</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹3,540</v>
+        <v>Receive ₹15,632</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -7107,11 +7324,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>123157.33333333333</v>
+        <v>151066</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-90557.333333333328</v>
+        <v>-118466</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7119,11 +7336,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-30614.66333333333</v>
+        <v>-58523.33</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹30,615</v>
+        <v>Pay ₹58,523</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -7161,15 +7378,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>293292</v>
+        <v>316402</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>120172.69639999999</v>
+        <v>127877.5704</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>173119.30360000001</v>
+        <v>188524.4296</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -7177,11 +7394,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>35809.277600000001</v>
+        <v>51214.403599999991</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹35,809</v>
+        <v>Pay ₹51,214</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -7195,11 +7412,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>120100.6072</v>
+        <v>127800.85919999999</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-65476.607199999999</v>
+        <v>-73176.859199999992</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -7207,11 +7424,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>6110.4348000000027</v>
+        <v>-1589.8171999999904</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹6,110</v>
+        <v>Receive ₹1,590</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -7225,11 +7442,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>120172.69639999999</v>
+        <v>127877.5704</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-107642.69639999999</v>
+        <v>-115347.5704</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -7237,11 +7454,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-41919.712399999975</v>
+        <v>-49624.586399999986</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹41,920</v>
+        <v>Receive ₹49,625</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -7353,7 +7570,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46187</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -7362,14 +7579,14 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>369472</v>
+        <v>453198</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>360446</v>
+        <v>383556</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7378,14 +7595,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-9026</v>
+        <v>-69642</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>101705.55666666666</v>
+        <v>132522.66333333333</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -7437,7 +7654,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>299</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7461,7 +7678,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>131</v>
+        <v>-656</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7521,15 +7738,15 @@
       </c>
       <c r="B15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A15)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>14730</v>
+        <v>98456</v>
       </c>
       <c r="C15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>9843</v>
+        <v>32953</v>
       </c>
       <c r="D15" s="27">
         <f t="shared" si="0"/>
-        <v>-4887</v>
+        <v>-65503</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
@@ -7657,18 +7874,18 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
       </c>
       <c r="K47" s="31">
         <f t="array" ref="K47">SUMPRODUCT((INVENTORY!$C$2:$C$477=J47)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>64790</v>
+        <v>63190</v>
       </c>
     </row>
     <row r="48" spans="6:11" ht="15" customHeight="1">
@@ -7677,18 +7894,18 @@
       </c>
       <c r="G48" s="30">
         <f>SUMIF(INVENTORY!C:C, F48, INVENTORY!F:F)</f>
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H48" s="30">
         <f>SUMIF(INVENTORY!C:C, F48, INVENTORY!G:G)</f>
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J48" s="30" t="s">
         <v>95</v>
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>43967.356666666667</v>
+        <v>76679.463333333319</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -7697,18 +7914,18 @@
       </c>
       <c r="G49" s="30">
         <f>SUMIF(INVENTORY!C:C, F49, INVENTORY!F:F)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H49" s="30">
         <f>SUMIF(INVENTORY!C:C, F49, INVENTORY!G:G)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J49" s="30" t="s">
         <v>97</v>
       </c>
       <c r="K49" s="31">
         <f t="array" ref="K49">SUMPRODUCT((INVENTORY!$C$2:$C$477=J49)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>1357</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="55" spans="5:12" ht="15" customHeight="1">
@@ -8823,7 +9040,7 @@
         <v>960</v>
       </c>
       <c r="D74" s="36" t="s">
-        <v>958</v>
+        <v>947</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15" customHeight="1">
@@ -8851,7 +9068,7 @@
         <v>2900</v>
       </c>
       <c r="D76" s="36" t="s">
-        <v>959</v>
+        <v>948</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15" customHeight="1">
@@ -8865,7 +9082,7 @@
         <v>180</v>
       </c>
       <c r="D77" s="39" t="s">
-        <v>960</v>
+        <v>949</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15" customHeight="1">
@@ -8879,7 +9096,7 @@
         <v>84</v>
       </c>
       <c r="D78" s="36" t="s">
-        <v>963</v>
+        <v>952</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15" customHeight="1">
@@ -8893,7 +9110,7 @@
         <v>208</v>
       </c>
       <c r="D79" s="39" t="s">
-        <v>963</v>
+        <v>952</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15" customHeight="1">
@@ -8925,28 +9142,60 @@
       </c>
     </row>
     <row r="82" spans="1:4" ht="15" customHeight="1">
-      <c r="A82" s="35"/>
-      <c r="B82" s="36"/>
-      <c r="C82" s="37"/>
-      <c r="D82" s="36"/>
+      <c r="A82" s="35">
+        <v>46186</v>
+      </c>
+      <c r="B82" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C82" s="37">
+        <v>40000</v>
+      </c>
+      <c r="D82" s="36" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="83" spans="1:4" ht="15" customHeight="1">
-      <c r="A83" s="38"/>
-      <c r="B83" s="39"/>
-      <c r="C83" s="40"/>
-      <c r="D83" s="39"/>
+      <c r="A83" s="38">
+        <v>46186</v>
+      </c>
+      <c r="B83" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C83" s="40">
+        <v>24760</v>
+      </c>
+      <c r="D83" s="39" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="84" spans="1:4" ht="15" customHeight="1">
-      <c r="A84" s="35"/>
-      <c r="B84" s="36"/>
-      <c r="C84" s="37"/>
-      <c r="D84" s="36"/>
+      <c r="A84" s="35">
+        <v>46192</v>
+      </c>
+      <c r="B84" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C84" s="37">
+        <v>246</v>
+      </c>
+      <c r="D84" s="36" t="s">
+        <v>1011</v>
+      </c>
     </row>
     <row r="85" spans="1:4" ht="15" customHeight="1">
-      <c r="A85" s="38"/>
-      <c r="B85" s="39"/>
-      <c r="C85" s="40"/>
-      <c r="D85" s="39"/>
+      <c r="A85" s="38">
+        <v>46192</v>
+      </c>
+      <c r="B85" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C85" s="40">
+        <v>18720</v>
+      </c>
+      <c r="D85" s="39" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="86" spans="1:4" ht="15" customHeight="1">
       <c r="A86" s="35"/>
@@ -11147,7 +11396,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
@@ -11158,7 +11406,7 @@
     <col min="5" max="5" width="17.1640625" style="42" customWidth="1"/>
     <col min="6" max="6" width="6.83203125" style="43" customWidth="1"/>
     <col min="7" max="7" width="7.83203125" style="42" customWidth="1"/>
-    <col min="8" max="8" width="38" style="42" customWidth="1"/>
+    <col min="8" max="8" width="49" style="42" customWidth="1"/>
     <col min="9" max="9" width="9.1640625" style="42" customWidth="1"/>
     <col min="10" max="16384" width="8.83203125" style="42"/>
   </cols>
@@ -11192,7 +11440,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1">
+    <row r="2" spans="1:9">
       <c r="A2" s="48">
         <v>45900</v>
       </c>
@@ -11215,7 +11463,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1">
+    <row r="3" spans="1:9">
       <c r="A3" s="52">
         <v>45900</v>
       </c>
@@ -11238,7 +11486,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1">
+    <row r="4" spans="1:9">
       <c r="A4" s="48">
         <v>45900</v>
       </c>
@@ -11261,7 +11509,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1">
+    <row r="5" spans="1:9">
       <c r="A5" s="52">
         <v>45900</v>
       </c>
@@ -11284,7 +11532,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1">
+    <row r="6" spans="1:9">
       <c r="A6" s="48">
         <v>45900</v>
       </c>
@@ -11307,7 +11555,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1">
+    <row r="7" spans="1:9">
       <c r="A7" s="52">
         <v>45900</v>
       </c>
@@ -11330,7 +11578,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1">
+    <row r="8" spans="1:9">
       <c r="A8" s="48">
         <v>45900</v>
       </c>
@@ -11353,7 +11601,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1">
+    <row r="9" spans="1:9">
       <c r="A9" s="52">
         <v>45901</v>
       </c>
@@ -11376,7 +11624,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1">
+    <row r="10" spans="1:9">
       <c r="A10" s="48">
         <v>45902</v>
       </c>
@@ -11399,7 +11647,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1">
+    <row r="11" spans="1:9">
       <c r="A11" s="52">
         <v>45903</v>
       </c>
@@ -11422,7 +11670,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1">
+    <row r="12" spans="1:9">
       <c r="A12" s="48">
         <v>45904</v>
       </c>
@@ -11445,7 +11693,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1">
+    <row r="13" spans="1:9">
       <c r="A13" s="52">
         <v>45905</v>
       </c>
@@ -11468,7 +11716,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1">
+    <row r="14" spans="1:9">
       <c r="A14" s="48">
         <v>45906</v>
       </c>
@@ -11491,7 +11739,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1">
+    <row r="15" spans="1:9">
       <c r="A15" s="52">
         <v>45907</v>
       </c>
@@ -11514,7 +11762,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1">
+    <row r="16" spans="1:9">
       <c r="A16" s="48">
         <v>45908</v>
       </c>
@@ -11537,7 +11785,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1">
+    <row r="17" spans="1:9">
       <c r="A17" s="52">
         <v>45909</v>
       </c>
@@ -11560,7 +11808,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1">
+    <row r="18" spans="1:9">
       <c r="A18" s="48">
         <v>45910</v>
       </c>
@@ -11583,7 +11831,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1">
+    <row r="19" spans="1:9">
       <c r="A19" s="52">
         <v>45911</v>
       </c>
@@ -11606,7 +11854,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1">
+    <row r="20" spans="1:9">
       <c r="A20" s="48">
         <v>45912</v>
       </c>
@@ -11629,7 +11877,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1">
+    <row r="21" spans="1:9">
       <c r="A21" s="52">
         <v>45913</v>
       </c>
@@ -11652,7 +11900,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1">
+    <row r="22" spans="1:9">
       <c r="A22" s="48">
         <v>45914</v>
       </c>
@@ -11675,7 +11923,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1">
+    <row r="23" spans="1:9">
       <c r="A23" s="52">
         <v>45915</v>
       </c>
@@ -11698,7 +11946,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1">
+    <row r="24" spans="1:9">
       <c r="A24" s="48">
         <v>45916</v>
       </c>
@@ -11721,7 +11969,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1">
+    <row r="25" spans="1:9">
       <c r="A25" s="52">
         <v>45917</v>
       </c>
@@ -11744,7 +11992,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1">
+    <row r="26" spans="1:9">
       <c r="A26" s="48">
         <v>45917</v>
       </c>
@@ -11767,7 +12015,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1">
+    <row r="27" spans="1:9">
       <c r="A27" s="52">
         <v>45918</v>
       </c>
@@ -11790,7 +12038,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1">
+    <row r="28" spans="1:9">
       <c r="A28" s="48">
         <v>45919</v>
       </c>
@@ -11813,7 +12061,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1">
+    <row r="29" spans="1:9">
       <c r="A29" s="52">
         <v>45920</v>
       </c>
@@ -11836,7 +12084,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1">
+    <row r="30" spans="1:9">
       <c r="A30" s="48">
         <v>45921</v>
       </c>
@@ -11859,7 +12107,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1">
+    <row r="31" spans="1:9">
       <c r="A31" s="52">
         <v>45922</v>
       </c>
@@ -11882,7 +12130,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1">
+    <row r="32" spans="1:9">
       <c r="A32" s="48">
         <v>45924</v>
       </c>
@@ -11905,7 +12153,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1">
+    <row r="33" spans="1:9">
       <c r="A33" s="52">
         <v>45924</v>
       </c>
@@ -11928,7 +12176,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1">
+    <row r="34" spans="1:9">
       <c r="A34" s="48">
         <v>45930</v>
       </c>
@@ -11951,7 +12199,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1">
+    <row r="35" spans="1:9">
       <c r="A35" s="52">
         <v>45933.931944444397</v>
       </c>
@@ -11974,7 +12222,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1">
+    <row r="36" spans="1:9">
       <c r="A36" s="48">
         <v>45934.931944386597</v>
       </c>
@@ -11997,7 +12245,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1">
+    <row r="37" spans="1:9">
       <c r="A37" s="52">
         <v>45935.931944386597</v>
       </c>
@@ -12020,7 +12268,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1">
+    <row r="38" spans="1:9">
       <c r="A38" s="48">
         <v>45939.931944444397</v>
       </c>
@@ -12043,7 +12291,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1">
+    <row r="39" spans="1:9">
       <c r="A39" s="52">
         <v>45939.931944444397</v>
       </c>
@@ -12066,7 +12314,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1">
+    <row r="40" spans="1:9">
       <c r="A40" s="48">
         <v>45945</v>
       </c>
@@ -12089,7 +12337,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1">
+    <row r="41" spans="1:9">
       <c r="A41" s="52">
         <v>45946</v>
       </c>
@@ -12112,7 +12360,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1">
+    <row r="42" spans="1:9">
       <c r="A42" s="48">
         <v>45946</v>
       </c>
@@ -12135,7 +12383,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1">
+    <row r="43" spans="1:9">
       <c r="A43" s="52">
         <v>45947</v>
       </c>
@@ -12158,7 +12406,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1">
+    <row r="44" spans="1:9">
       <c r="A44" s="48">
         <v>45948</v>
       </c>
@@ -12181,7 +12429,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1">
+    <row r="45" spans="1:9">
       <c r="A45" s="52">
         <v>45949</v>
       </c>
@@ -12204,7 +12452,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1">
+    <row r="46" spans="1:9">
       <c r="A46" s="48">
         <v>45950</v>
       </c>
@@ -12227,7 +12475,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1">
+    <row r="47" spans="1:9">
       <c r="A47" s="52">
         <v>45951</v>
       </c>
@@ -12250,7 +12498,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1">
+    <row r="48" spans="1:9">
       <c r="A48" s="48">
         <v>45964</v>
       </c>
@@ -12273,7 +12521,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1">
+    <row r="49" spans="1:9">
       <c r="A49" s="52">
         <v>45963</v>
       </c>
@@ -12296,7 +12544,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1">
+    <row r="50" spans="1:9">
       <c r="A50" s="48">
         <v>45982</v>
       </c>
@@ -12319,7 +12567,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1">
+    <row r="51" spans="1:9">
       <c r="A51" s="52">
         <v>45983</v>
       </c>
@@ -12342,7 +12590,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1">
+    <row r="52" spans="1:9">
       <c r="A52" s="48">
         <v>45984</v>
       </c>
@@ -12365,7 +12613,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1">
+    <row r="53" spans="1:9">
       <c r="A53" s="52">
         <v>45985</v>
       </c>
@@ -12388,7 +12636,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="54" spans="1:9" ht="13.5" customHeight="1">
       <c r="A54" s="48">
         <v>45986</v>
       </c>
@@ -12413,7 +12661,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="55" spans="1:9" ht="15.75" customHeight="1">
       <c r="A55" s="52">
         <v>45992</v>
       </c>
@@ -12438,7 +12686,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="56" spans="1:9" ht="13.5" customHeight="1">
       <c r="A56" s="48">
         <v>45992</v>
       </c>
@@ -12463,7 +12711,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="57" spans="1:9" ht="15.75" customHeight="1">
       <c r="A57" s="52">
         <v>45996</v>
       </c>
@@ -12488,7 +12736,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="42" hidden="1" customHeight="1">
+    <row r="58" spans="1:9" ht="42" customHeight="1">
       <c r="A58" s="48">
         <v>45996</v>
       </c>
@@ -12513,7 +12761,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="59" spans="1:9" ht="15.75" customHeight="1">
       <c r="A59" s="52">
         <v>45996</v>
       </c>
@@ -12538,7 +12786,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="60" spans="1:9" ht="13.5" customHeight="1">
       <c r="A60" s="48">
         <v>46007</v>
       </c>
@@ -12563,7 +12811,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="61" spans="1:9" ht="15.75" customHeight="1">
       <c r="A61" s="52">
         <v>46008</v>
       </c>
@@ -12590,7 +12838,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="62" spans="1:9" ht="13.5" customHeight="1">
       <c r="A62" s="48">
         <v>46008</v>
       </c>
@@ -12615,7 +12863,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="63" spans="1:9" ht="15.75" customHeight="1">
       <c r="A63" s="52">
         <v>46008</v>
       </c>
@@ -12640,7 +12888,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="64" spans="1:9" ht="15.75" customHeight="1">
       <c r="A64" s="52">
         <v>46008</v>
       </c>
@@ -12665,7 +12913,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="65" spans="1:9" ht="13.5" customHeight="1">
       <c r="A65" s="48">
         <v>46009</v>
       </c>
@@ -12690,7 +12938,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="66" spans="1:9" ht="15.75" customHeight="1">
       <c r="A66" s="52">
         <v>46010</v>
       </c>
@@ -12715,7 +12963,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="67" spans="1:9" ht="13.5" customHeight="1">
       <c r="A67" s="48">
         <v>46010</v>
       </c>
@@ -12742,7 +12990,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="31.5" hidden="1" customHeight="1">
+    <row r="68" spans="1:9" ht="31.5" customHeight="1">
       <c r="A68" s="52">
         <v>46011</v>
       </c>
@@ -12767,7 +13015,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="69" spans="1:9" ht="13.5" customHeight="1">
       <c r="A69" s="48">
         <v>46011</v>
       </c>
@@ -12792,7 +13040,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="70" spans="1:9" ht="13.5" customHeight="1">
       <c r="A70" s="48">
         <v>46011</v>
       </c>
@@ -12817,7 +13065,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="71" spans="1:9" ht="15.75" customHeight="1">
       <c r="A71" s="52">
         <v>46011</v>
       </c>
@@ -12842,7 +13090,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="27.75" hidden="1" customHeight="1">
+    <row r="72" spans="1:9" ht="27.75" customHeight="1">
       <c r="A72" s="48">
         <v>46011</v>
       </c>
@@ -12867,7 +13115,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="31.5" hidden="1" customHeight="1">
+    <row r="73" spans="1:9" ht="31.5" customHeight="1">
       <c r="A73" s="52">
         <v>46011</v>
       </c>
@@ -12892,7 +13140,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="74" spans="1:9" ht="13.5" customHeight="1">
       <c r="A74" s="48">
         <v>46013</v>
       </c>
@@ -12919,7 +13167,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="75" spans="1:9" ht="15.75" customHeight="1">
       <c r="A75" s="52">
         <v>46013</v>
       </c>
@@ -12944,7 +13192,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="76" spans="1:9" ht="15.75" customHeight="1">
       <c r="A76" s="52">
         <v>46017</v>
       </c>
@@ -12969,7 +13217,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="77" spans="1:9" ht="13.5" customHeight="1">
       <c r="A77" s="48">
         <v>46017</v>
       </c>
@@ -12994,7 +13242,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="78" spans="1:9" ht="15.75" customHeight="1">
       <c r="A78" s="52">
         <v>46017</v>
       </c>
@@ -13019,7 +13267,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="79" spans="1:9" ht="13.5" customHeight="1">
       <c r="A79" s="48">
         <v>46017</v>
       </c>
@@ -13044,7 +13292,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="80" spans="1:9" ht="15.75" customHeight="1">
       <c r="A80" s="52">
         <v>46020</v>
       </c>
@@ -13069,7 +13317,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="81" spans="1:9" ht="13.5" customHeight="1">
       <c r="A81" s="48">
         <v>46024</v>
       </c>
@@ -13094,7 +13342,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="82" spans="1:9" ht="15.75" customHeight="1">
       <c r="A82" s="52">
         <v>46024</v>
       </c>
@@ -13119,7 +13367,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="83" spans="1:9" ht="13.5" customHeight="1">
       <c r="A83" s="48">
         <v>46024</v>
       </c>
@@ -13144,7 +13392,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="84" spans="1:9" ht="15.75" customHeight="1">
       <c r="A84" s="52">
         <v>46024</v>
       </c>
@@ -13169,7 +13417,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="85" spans="1:9" ht="13.5" customHeight="1">
       <c r="A85" s="48">
         <v>46027</v>
       </c>
@@ -13194,7 +13442,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="86" spans="1:9" ht="13.5" customHeight="1">
       <c r="A86" s="48">
         <v>46028</v>
       </c>
@@ -13219,7 +13467,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="87" spans="1:9" ht="15.75" customHeight="1">
       <c r="A87" s="52">
         <v>46029</v>
       </c>
@@ -13244,7 +13492,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="88" spans="1:9" ht="13.5" customHeight="1">
       <c r="A88" s="48">
         <v>46032</v>
       </c>
@@ -13269,7 +13517,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="89" spans="1:9" ht="15.75" customHeight="1">
       <c r="A89" s="52">
         <v>46033</v>
       </c>
@@ -13294,7 +13542,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="90" spans="1:9" ht="13.5" customHeight="1">
       <c r="A90" s="48">
         <v>46033</v>
       </c>
@@ -13319,7 +13567,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="91" spans="1:9" ht="15.75" customHeight="1">
       <c r="A91" s="52">
         <v>46034</v>
       </c>
@@ -13344,7 +13592,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="27.75" hidden="1" customHeight="1">
+    <row r="92" spans="1:9" ht="27.75" customHeight="1">
       <c r="A92" s="48">
         <v>46034</v>
       </c>
@@ -13369,7 +13617,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="93" spans="1:9" ht="15.75" customHeight="1">
       <c r="A93" s="52">
         <v>46035</v>
       </c>
@@ -13394,7 +13642,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="94" spans="1:9" ht="13.5" customHeight="1">
       <c r="A94" s="48">
         <v>46036</v>
       </c>
@@ -13419,7 +13667,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="95" spans="1:9" ht="15.75" customHeight="1">
       <c r="A95" s="52">
         <v>46038</v>
       </c>
@@ -13444,7 +13692,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="96" spans="1:9" ht="13.5" customHeight="1">
       <c r="A96" s="48">
         <v>46038</v>
       </c>
@@ -13469,7 +13717,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="97" spans="1:9" ht="15.75" customHeight="1">
       <c r="A97" s="52">
         <v>46039</v>
       </c>
@@ -13494,7 +13742,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="98" spans="1:9" ht="13.5" customHeight="1">
       <c r="A98" s="48">
         <v>46040</v>
       </c>
@@ -13519,7 +13767,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="99" spans="1:9" ht="15.75" customHeight="1">
       <c r="A99" s="52">
         <v>46041</v>
       </c>
@@ -13544,7 +13792,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="100" spans="1:9" ht="13.5" customHeight="1">
       <c r="A100" s="48">
         <v>46042</v>
       </c>
@@ -13569,7 +13817,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="101" spans="1:9" ht="15.75" customHeight="1">
       <c r="A101" s="52">
         <v>46043</v>
       </c>
@@ -13594,7 +13842,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="102" spans="1:9" ht="13.5" customHeight="1">
       <c r="A102" s="48">
         <v>46046</v>
       </c>
@@ -13619,7 +13867,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="103" spans="1:9" ht="13.5" customHeight="1">
       <c r="A103" s="52">
         <v>46048</v>
       </c>
@@ -13644,7 +13892,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="104" spans="1:9" ht="13.5" customHeight="1">
       <c r="A104" s="48">
         <v>46048</v>
       </c>
@@ -13669,7 +13917,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="105" spans="1:9" ht="15.75" customHeight="1">
       <c r="A105" s="52">
         <v>46049</v>
       </c>
@@ -13694,7 +13942,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="106" spans="1:9" ht="13.5" customHeight="1">
       <c r="A106" s="48">
         <v>46049</v>
       </c>
@@ -13719,7 +13967,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="107" spans="1:9" ht="15.75" customHeight="1">
       <c r="A107" s="52">
         <v>46049</v>
       </c>
@@ -13744,7 +13992,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="108" spans="1:9" ht="13.5" customHeight="1">
       <c r="A108" s="48">
         <v>46050</v>
       </c>
@@ -13769,7 +14017,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="109" spans="1:9" ht="15.75" customHeight="1">
       <c r="A109" s="52">
         <v>46051</v>
       </c>
@@ -13794,7 +14042,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="110" spans="1:9" ht="13.5" customHeight="1">
       <c r="A110" s="48">
         <v>46051</v>
       </c>
@@ -13819,7 +14067,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="111" spans="1:9" ht="15.75" customHeight="1">
       <c r="A111" s="52">
         <v>46051</v>
       </c>
@@ -13844,7 +14092,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="27.75" hidden="1" customHeight="1">
+    <row r="112" spans="1:9" ht="27.75" customHeight="1">
       <c r="A112" s="48">
         <v>46054</v>
       </c>
@@ -13869,7 +14117,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="113" spans="1:9" ht="15.75" customHeight="1">
       <c r="A113" s="52">
         <v>46054</v>
       </c>
@@ -13894,7 +14142,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="114" spans="1:9" ht="13.5" customHeight="1">
       <c r="A114" s="48">
         <v>46055</v>
       </c>
@@ -13919,7 +14167,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="115" spans="1:9" ht="15.75" customHeight="1">
       <c r="A115" s="52">
         <v>46055</v>
       </c>
@@ -13944,7 +14192,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="116" spans="1:9" ht="13.5" customHeight="1">
       <c r="A116" s="48">
         <v>46060</v>
       </c>
@@ -13969,7 +14217,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="117" spans="1:9" ht="15.75" customHeight="1">
       <c r="A117" s="52">
         <v>46062</v>
       </c>
@@ -13994,7 +14242,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="118" spans="1:9" ht="13.5" customHeight="1">
       <c r="A118" s="48">
         <v>46065</v>
       </c>
@@ -14019,7 +14267,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="119" spans="1:9" ht="15.75" customHeight="1">
       <c r="A119" s="52">
         <v>46055</v>
       </c>
@@ -14044,7 +14292,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="27.75" hidden="1" customHeight="1">
+    <row r="120" spans="1:9" ht="27.75" customHeight="1">
       <c r="A120" s="48">
         <v>46070</v>
       </c>
@@ -14069,7 +14317,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="121" spans="1:9" ht="15.75" customHeight="1">
       <c r="A121" s="52">
         <v>46073</v>
       </c>
@@ -14094,7 +14342,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="122" spans="1:9" ht="13.5" customHeight="1">
       <c r="A122" s="48">
         <v>46074</v>
       </c>
@@ -14119,7 +14367,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="123" spans="1:9" ht="15.75" customHeight="1">
       <c r="A123" s="52">
         <v>46075</v>
       </c>
@@ -14144,7 +14392,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="124" spans="1:9" ht="13.5" customHeight="1">
       <c r="A124" s="48">
         <v>46075</v>
       </c>
@@ -14169,7 +14417,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="31.5" hidden="1" customHeight="1">
+    <row r="125" spans="1:9" ht="31.5" customHeight="1">
       <c r="A125" s="52">
         <v>46079</v>
       </c>
@@ -14194,7 +14442,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="126" spans="1:9" ht="13.5" customHeight="1">
       <c r="A126" s="48">
         <v>46079</v>
       </c>
@@ -14219,7 +14467,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="127" spans="1:9" ht="13.5" customHeight="1">
       <c r="A127" s="52">
         <v>46090</v>
       </c>
@@ -14244,7 +14492,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="128" spans="1:9" ht="13.5" customHeight="1">
       <c r="A128" s="48">
         <v>46090</v>
       </c>
@@ -14269,7 +14517,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="129" spans="1:9" ht="13.5" customHeight="1">
       <c r="A129" s="48">
         <v>46090</v>
       </c>
@@ -14294,7 +14542,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="130" spans="1:9" ht="15.75" customHeight="1">
       <c r="A130" s="52">
         <v>46091</v>
       </c>
@@ -14319,7 +14567,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="131" spans="1:9" ht="13.5" customHeight="1">
       <c r="A131" s="48">
         <v>46092</v>
       </c>
@@ -14344,7 +14592,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="132" spans="1:9" ht="15.75" customHeight="1">
       <c r="A132" s="52">
         <v>46092</v>
       </c>
@@ -14369,7 +14617,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="27.75" hidden="1" customHeight="1">
+    <row r="133" spans="1:9" ht="27.75" customHeight="1">
       <c r="A133" s="48">
         <v>46093</v>
       </c>
@@ -14394,7 +14642,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="134" spans="1:9" ht="15.75" customHeight="1">
       <c r="A134" s="52">
         <v>46093</v>
       </c>
@@ -14419,7 +14667,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="135" spans="1:9" ht="13.5" customHeight="1">
       <c r="A135" s="48">
         <v>46097</v>
       </c>
@@ -14444,7 +14692,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="136" spans="1:9" ht="15.75" customHeight="1">
       <c r="A136" s="52">
         <v>46097</v>
       </c>
@@ -14469,7 +14717,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="137" spans="1:9" ht="13.5" customHeight="1">
       <c r="A137" s="48">
         <v>46100</v>
       </c>
@@ -14494,7 +14742,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="138" spans="1:9" ht="15.75" customHeight="1">
       <c r="A138" s="52">
         <v>46104</v>
       </c>
@@ -14519,7 +14767,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="27.75" hidden="1" customHeight="1">
+    <row r="139" spans="1:9" ht="27.75" customHeight="1">
       <c r="A139" s="48">
         <v>46105</v>
       </c>
@@ -14544,7 +14792,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="31.5" hidden="1" customHeight="1">
+    <row r="140" spans="1:9" ht="31.5" customHeight="1">
       <c r="A140" s="52">
         <v>46113</v>
       </c>
@@ -14569,7 +14817,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="141" spans="1:9" ht="13.5" customHeight="1">
       <c r="A141" s="48">
         <v>46118</v>
       </c>
@@ -14594,7 +14842,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="142" spans="1:9" ht="15.75" customHeight="1">
       <c r="A142" s="52">
         <v>46119</v>
       </c>
@@ -14619,7 +14867,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="143" spans="1:9" ht="13.5" customHeight="1">
       <c r="A143" s="48">
         <v>46120</v>
       </c>
@@ -14644,7 +14892,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="144" spans="1:9" ht="15.75" customHeight="1">
       <c r="A144" s="52">
         <v>46120</v>
       </c>
@@ -14669,7 +14917,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="145" spans="1:9" ht="13.5" customHeight="1">
       <c r="A145" s="48">
         <v>46120</v>
       </c>
@@ -14694,7 +14942,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="31.5" hidden="1" customHeight="1">
+    <row r="146" spans="1:9" ht="31.5" customHeight="1">
       <c r="A146" s="52">
         <v>46122</v>
       </c>
@@ -14719,7 +14967,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="147" spans="1:9" ht="13.5" customHeight="1">
       <c r="A147" s="48">
         <v>46122</v>
       </c>
@@ -14744,7 +14992,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="148" spans="1:9" ht="15.75" customHeight="1">
       <c r="A148" s="52">
         <v>46122</v>
       </c>
@@ -14769,7 +15017,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="149" spans="1:9" ht="13.5" customHeight="1">
       <c r="A149" s="48">
         <v>46122</v>
       </c>
@@ -14788,13 +15036,13 @@
       <c r="F149" s="49"/>
       <c r="G149" s="49"/>
       <c r="H149" s="51" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="I149" s="49" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="150" spans="1:9" ht="15.75" customHeight="1">
       <c r="A150" s="52">
         <v>46125</v>
       </c>
@@ -14819,7 +15067,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="151" spans="1:9" ht="13.5" customHeight="1">
       <c r="A151" s="48">
         <v>46125</v>
       </c>
@@ -14844,7 +15092,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="152" spans="1:9" ht="15.75" customHeight="1">
       <c r="A152" s="52">
         <v>46125</v>
       </c>
@@ -14869,7 +15117,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="153" spans="1:9" ht="13.5" customHeight="1">
       <c r="A153" s="48">
         <v>46125</v>
       </c>
@@ -14894,7 +15142,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="154" spans="1:9" ht="15.75" customHeight="1">
       <c r="A154" s="52">
         <v>46126</v>
       </c>
@@ -14919,7 +15167,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="155" spans="1:9" ht="13.5" customHeight="1">
       <c r="A155" s="48">
         <v>46127</v>
       </c>
@@ -14944,7 +15192,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="156" spans="1:9" ht="15.75" customHeight="1">
       <c r="A156" s="52">
         <v>46129</v>
       </c>
@@ -14969,7 +15217,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="157" spans="1:9" ht="13.5" customHeight="1">
       <c r="A157" s="48">
         <v>46129</v>
       </c>
@@ -15017,7 +15265,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="159" spans="1:9" ht="13.5" customHeight="1">
       <c r="A159" s="48">
         <v>46130</v>
       </c>
@@ -15042,7 +15290,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="15.75" hidden="1" customHeight="1">
+    <row r="160" spans="1:9" ht="15.75" customHeight="1">
       <c r="A160" s="52">
         <v>46131</v>
       </c>
@@ -15061,13 +15309,13 @@
       <c r="F160" s="56"/>
       <c r="G160" s="56"/>
       <c r="H160" s="57" t="s">
-        <v>962</v>
+        <v>951</v>
       </c>
       <c r="I160" s="53" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="161" spans="1:9" ht="13.5" customHeight="1">
       <c r="A161" s="48">
         <v>46132</v>
       </c>
@@ -15092,7 +15340,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="42" hidden="1" customHeight="1">
+    <row r="162" spans="1:9" ht="42" customHeight="1">
       <c r="A162" s="52">
         <v>46132</v>
       </c>
@@ -15117,7 +15365,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="163" spans="1:9" ht="13.5" customHeight="1">
       <c r="A163" s="48">
         <v>46133</v>
       </c>
@@ -15142,7 +15390,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="164" spans="1:9" ht="13.5" customHeight="1">
       <c r="A164" s="52">
         <v>46133</v>
       </c>
@@ -15167,7 +15415,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="165" spans="1:9" ht="13.5" customHeight="1">
       <c r="A165" s="48">
         <v>46133</v>
       </c>
@@ -15192,7 +15440,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="166" spans="1:9" ht="13.5" customHeight="1">
       <c r="A166" s="52">
         <v>46134</v>
       </c>
@@ -15217,7 +15465,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="167" spans="1:9" ht="13.5" customHeight="1">
       <c r="A167" s="48">
         <v>46134</v>
       </c>
@@ -15242,7 +15490,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="168" spans="1:9" ht="13.5" customHeight="1">
       <c r="A168" s="48">
         <v>46134</v>
       </c>
@@ -15261,13 +15509,13 @@
       <c r="F168" s="49"/>
       <c r="G168" s="49"/>
       <c r="H168" s="51" t="s">
-        <v>961</v>
+        <v>950</v>
       </c>
       <c r="I168" s="49" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="169" spans="1:9" ht="13.5" customHeight="1">
       <c r="A169" s="52">
         <v>46134</v>
       </c>
@@ -15292,7 +15540,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="170" spans="1:9" ht="13.5" customHeight="1">
       <c r="A170" s="48">
         <v>46134</v>
       </c>
@@ -15317,7 +15565,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="171" spans="1:9" ht="13.5" customHeight="1">
       <c r="A171" s="52">
         <v>46136</v>
       </c>
@@ -15342,7 +15590,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="172" spans="1:9" ht="13.5" customHeight="1">
       <c r="A172" s="48">
         <v>46138</v>
       </c>
@@ -15367,7 +15615,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="173" spans="1:9" ht="13.5" customHeight="1">
       <c r="A173" s="52">
         <v>46138</v>
       </c>
@@ -15392,7 +15640,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="174" spans="1:9" ht="13.5" customHeight="1">
       <c r="A174" s="48">
         <v>46139</v>
       </c>
@@ -15417,7 +15665,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="175" spans="1:9" ht="13.5" customHeight="1">
       <c r="A175" s="52">
         <v>46139</v>
       </c>
@@ -15442,7 +15690,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="176" spans="1:9" ht="13.5" customHeight="1">
       <c r="A176" s="48">
         <v>46139</v>
       </c>
@@ -15467,7 +15715,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="177" spans="1:9" ht="13.5" customHeight="1">
       <c r="A177" s="52">
         <v>46140</v>
       </c>
@@ -15492,7 +15740,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="178" spans="1:9" ht="13.5" customHeight="1">
       <c r="A178" s="48">
         <v>46140</v>
       </c>
@@ -15517,7 +15765,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="179" spans="1:9" ht="13.5" customHeight="1">
       <c r="A179" s="52">
         <v>46140</v>
       </c>
@@ -15542,7 +15790,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="180" spans="1:9" ht="13.5" customHeight="1">
       <c r="A180" s="48">
         <v>46140</v>
       </c>
@@ -15561,13 +15809,13 @@
       <c r="F180" s="49"/>
       <c r="G180" s="49"/>
       <c r="H180" s="51" t="s">
-        <v>952</v>
+        <v>943</v>
       </c>
       <c r="I180" s="49" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="181" spans="1:9" ht="13.5" customHeight="1">
       <c r="A181" s="52">
         <v>46141</v>
       </c>
@@ -15592,7 +15840,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="182" spans="1:9" ht="13.5" customHeight="1">
       <c r="A182" s="48">
         <v>46141</v>
       </c>
@@ -15617,7 +15865,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="183" spans="1:9" ht="13.5" customHeight="1">
       <c r="A183" s="52">
         <v>46142</v>
       </c>
@@ -15642,7 +15890,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="184" spans="1:9" ht="13.5" customHeight="1">
       <c r="A184" s="48">
         <v>46142</v>
       </c>
@@ -15667,7 +15915,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="185" spans="1:9" ht="13.5" customHeight="1">
       <c r="A185" s="52">
         <v>46142</v>
       </c>
@@ -15692,7 +15940,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="186" spans="1:9" ht="13.5" customHeight="1">
       <c r="A186" s="52">
         <v>46144</v>
       </c>
@@ -15717,7 +15965,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="187" spans="1:9" ht="13.5" customHeight="1">
       <c r="A187" s="48">
         <v>46144</v>
       </c>
@@ -15742,7 +15990,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="188" spans="1:9" ht="13.5" customHeight="1">
       <c r="A188" s="52">
         <v>46145</v>
       </c>
@@ -15767,7 +16015,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="189" spans="1:9" ht="13.5" customHeight="1">
       <c r="A189" s="48">
         <v>46145</v>
       </c>
@@ -15792,7 +16040,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="13.5" hidden="1" customHeight="1">
+    <row r="190" spans="1:9" ht="13.5" customHeight="1">
       <c r="A190" s="52">
         <v>46145</v>
       </c>
@@ -15817,7 +16065,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="42" hidden="1" customHeight="1">
+    <row r="191" spans="1:9" ht="42" customHeight="1">
       <c r="A191" s="48">
         <v>46151</v>
       </c>
@@ -15842,7 +16090,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="27.75" hidden="1" customHeight="1">
+    <row r="192" spans="1:9" ht="27.75" customHeight="1">
       <c r="A192" s="52">
         <v>46152</v>
       </c>
@@ -15867,7 +16115,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="42" hidden="1" customHeight="1">
+    <row r="193" spans="1:9" ht="42" customHeight="1">
       <c r="A193" s="48">
         <v>46152</v>
       </c>
@@ -15913,7 +16161,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="42" hidden="1" customHeight="1">
+    <row r="195" spans="1:9" ht="42" customHeight="1">
       <c r="A195" s="48">
         <v>46155</v>
       </c>
@@ -15938,7 +16186,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="42" hidden="1" customHeight="1">
+    <row r="196" spans="1:9" ht="42" customHeight="1">
       <c r="A196" s="52">
         <v>46155</v>
       </c>
@@ -15963,7 +16211,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="42" hidden="1" customHeight="1">
+    <row r="197" spans="1:9" ht="42" customHeight="1">
       <c r="A197" s="48">
         <v>46155</v>
       </c>
@@ -15988,12 +16236,12 @@
         <v>142</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="42" hidden="1">
+    <row r="198" spans="1:9" ht="42">
       <c r="A198" s="52">
         <v>46168</v>
       </c>
       <c r="B198" s="53" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="C198" s="54">
         <v>5200</v>
@@ -16007,7 +16255,7 @@
       <c r="F198" s="56"/>
       <c r="G198" s="56"/>
       <c r="H198" s="57" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="I198" s="53" t="s">
         <v>142</v>
@@ -16018,7 +16266,7 @@
         <v>46172</v>
       </c>
       <c r="B199" s="49" t="s">
-        <v>919</v>
+        <v>912</v>
       </c>
       <c r="C199" s="50">
         <v>1425</v>
@@ -16032,18 +16280,18 @@
       <c r="F199" s="49"/>
       <c r="G199" s="49"/>
       <c r="H199" s="51" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="I199" s="49" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="28" hidden="1">
+    <row r="200" spans="1:9" ht="28">
       <c r="A200" s="52">
         <v>46173</v>
       </c>
       <c r="B200" s="53" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
       <c r="C200" s="54">
         <v>2850</v>
@@ -16057,18 +16305,18 @@
       <c r="F200" s="56"/>
       <c r="G200" s="56"/>
       <c r="H200" s="57" t="s">
-        <v>935</v>
+        <v>926</v>
       </c>
       <c r="I200" s="53" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="42" hidden="1">
+    <row r="201" spans="1:9" ht="28">
       <c r="A201" s="48">
         <v>46173</v>
       </c>
       <c r="B201" s="49" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
       <c r="C201" s="50">
         <v>3850</v>
@@ -16082,18 +16330,18 @@
       <c r="F201" s="49"/>
       <c r="G201" s="49"/>
       <c r="H201" s="51" t="s">
-        <v>964</v>
+        <v>953</v>
       </c>
       <c r="I201" s="49" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="14" hidden="1">
+    <row r="202" spans="1:9" ht="14">
       <c r="A202" s="52">
         <v>46173</v>
       </c>
       <c r="B202" s="53" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="C202" s="54">
         <v>930</v>
@@ -16107,7 +16355,7 @@
       <c r="F202" s="56"/>
       <c r="G202" s="56"/>
       <c r="H202" s="57" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="I202" s="53" t="s">
         <v>142</v>
@@ -16118,7 +16366,7 @@
         <v>46173</v>
       </c>
       <c r="B203" s="49" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="C203" s="50">
         <v>930</v>
@@ -16132,18 +16380,18 @@
       <c r="F203" s="49"/>
       <c r="G203" s="49"/>
       <c r="H203" s="51" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="I203" s="49" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="14" hidden="1">
+    <row r="204" spans="1:9" ht="14">
       <c r="A204" s="52">
         <v>46175</v>
       </c>
       <c r="B204" s="53" t="s">
-        <v>936</v>
+        <v>927</v>
       </c>
       <c r="C204" s="54">
         <v>699</v>
@@ -16157,18 +16405,18 @@
       <c r="F204" s="56"/>
       <c r="G204" s="56"/>
       <c r="H204" s="57" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="I204" s="53" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="14" hidden="1">
+    <row r="205" spans="1:9" ht="14">
       <c r="A205" s="48">
         <v>46175</v>
       </c>
       <c r="B205" s="49" t="s">
-        <v>937</v>
+        <v>928</v>
       </c>
       <c r="C205" s="50">
         <v>700</v>
@@ -16182,18 +16430,18 @@
       <c r="F205" s="49"/>
       <c r="G205" s="49"/>
       <c r="H205" s="51" t="s">
-        <v>938</v>
+        <v>929</v>
       </c>
       <c r="I205" s="49" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="14" hidden="1">
+    <row r="206" spans="1:9" ht="14">
       <c r="A206" s="52">
         <v>46175</v>
       </c>
       <c r="B206" s="53" t="s">
-        <v>939</v>
+        <v>930</v>
       </c>
       <c r="C206" s="54">
         <v>1350</v>
@@ -16207,18 +16455,18 @@
       <c r="F206" s="56"/>
       <c r="G206" s="56"/>
       <c r="H206" s="51" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
       <c r="I206" s="53" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="14" hidden="1">
+    <row r="207" spans="1:9" ht="14">
       <c r="A207" s="48">
         <v>46175</v>
       </c>
       <c r="B207" s="49" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
       <c r="C207" s="50">
         <v>699</v>
@@ -16232,18 +16480,18 @@
       <c r="F207" s="49"/>
       <c r="G207" s="49"/>
       <c r="H207" s="51" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="I207" s="49" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="14" hidden="1">
+    <row r="208" spans="1:9" ht="14">
       <c r="A208" s="52">
         <v>46175</v>
       </c>
       <c r="B208" s="53" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
       <c r="C208" s="54">
         <v>699</v>
@@ -16257,18 +16505,18 @@
       <c r="F208" s="56"/>
       <c r="G208" s="56"/>
       <c r="H208" s="57" t="s">
-        <v>944</v>
+        <v>935</v>
       </c>
       <c r="I208" s="53" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="14" hidden="1">
+    <row r="209" spans="1:9" ht="14">
       <c r="A209" s="48">
         <v>46176</v>
       </c>
       <c r="B209" s="49" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="C209" s="50">
         <v>699</v>
@@ -16282,18 +16530,18 @@
       <c r="F209" s="49"/>
       <c r="G209" s="49"/>
       <c r="H209" s="51" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="I209" s="49" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="28" hidden="1">
+    <row r="210" spans="1:9" ht="28">
       <c r="A210" s="52">
         <v>46176</v>
       </c>
       <c r="B210" s="53" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C210" s="54">
         <v>2200</v>
@@ -16307,18 +16555,18 @@
       <c r="F210" s="56"/>
       <c r="G210" s="56"/>
       <c r="H210" s="57" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="I210" s="53" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="14" hidden="1">
+    <row r="211" spans="1:9" ht="14">
       <c r="A211" s="48">
         <v>46176</v>
       </c>
       <c r="B211" s="49" t="s">
-        <v>949</v>
+        <v>940</v>
       </c>
       <c r="C211" s="50">
         <v>699</v>
@@ -16332,18 +16580,18 @@
       <c r="F211" s="49"/>
       <c r="G211" s="49"/>
       <c r="H211" s="51" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
       <c r="I211" s="49" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1">
+    <row r="212" spans="1:9">
       <c r="A212" s="52">
         <v>46176</v>
       </c>
       <c r="B212" s="53" t="s">
-        <v>951</v>
+        <v>942</v>
       </c>
       <c r="C212" s="54">
         <v>699</v>
@@ -16357,18 +16605,18 @@
       <c r="F212" s="56"/>
       <c r="G212" s="56"/>
       <c r="H212" s="56" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="I212" s="53" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="14" hidden="1">
+    <row r="213" spans="1:9" ht="14">
       <c r="A213" s="48">
         <v>46176</v>
       </c>
       <c r="B213" s="49" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="C213" s="50">
         <v>700</v>
@@ -16382,18 +16630,18 @@
       <c r="F213" s="49"/>
       <c r="G213" s="49"/>
       <c r="H213" s="51" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
       <c r="I213" s="49" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1">
+    <row r="214" spans="1:9">
       <c r="A214" s="52">
         <v>46177</v>
       </c>
       <c r="B214" s="53" t="s">
-        <v>955</v>
+        <v>946</v>
       </c>
       <c r="C214" s="54">
         <v>699</v>
@@ -16407,165 +16655,361 @@
       <c r="F214" s="56"/>
       <c r="G214" s="56"/>
       <c r="H214" s="56" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="I214" s="53" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="215" spans="1:9">
-      <c r="A215" s="48"/>
-      <c r="B215" s="49"/>
-      <c r="C215" s="50"/>
-      <c r="D215" s="49"/>
-      <c r="E215" s="49"/>
+    <row r="215" spans="1:9" ht="14">
+      <c r="A215" s="48">
+        <v>46187</v>
+      </c>
+      <c r="B215" s="49" t="s">
+        <v>961</v>
+      </c>
+      <c r="C215" s="50">
+        <v>1380</v>
+      </c>
+      <c r="D215" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E215" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F215" s="49"/>
       <c r="G215" s="49"/>
-      <c r="H215" s="51"/>
-      <c r="I215" s="49"/>
-    </row>
-    <row r="216" spans="1:9">
-      <c r="A216" s="52"/>
-      <c r="B216" s="53"/>
-      <c r="C216" s="54"/>
-      <c r="D216" s="53"/>
-      <c r="E216" s="53"/>
+      <c r="H215" s="51" t="s">
+        <v>229</v>
+      </c>
+      <c r="I215" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" ht="56">
+      <c r="A216" s="52">
+        <v>46188</v>
+      </c>
+      <c r="B216" s="53" t="s">
+        <v>962</v>
+      </c>
+      <c r="C216" s="54">
+        <v>5000</v>
+      </c>
+      <c r="D216" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E216" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F216" s="56"/>
       <c r="G216" s="56"/>
-      <c r="H216" s="57"/>
-      <c r="I216" s="53"/>
-    </row>
-    <row r="217" spans="1:9">
-      <c r="A217" s="48"/>
-      <c r="B217" s="49"/>
-      <c r="C217" s="50"/>
-      <c r="D217" s="49"/>
-      <c r="E217" s="49"/>
+      <c r="H216" s="57" t="s">
+        <v>965</v>
+      </c>
+      <c r="I216" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" ht="14">
+      <c r="A217" s="48">
+        <v>46188</v>
+      </c>
+      <c r="B217" s="49" t="s">
+        <v>301</v>
+      </c>
+      <c r="C217" s="50">
+        <v>1550</v>
+      </c>
+      <c r="D217" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E217" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F217" s="49"/>
       <c r="G217" s="49"/>
-      <c r="H217" s="51"/>
-      <c r="I217" s="49"/>
-    </row>
-    <row r="218" spans="1:9">
-      <c r="A218" s="52"/>
-      <c r="B218" s="53"/>
-      <c r="C218" s="54"/>
-      <c r="D218" s="53"/>
-      <c r="E218" s="53"/>
+      <c r="H217" s="51" t="s">
+        <v>1012</v>
+      </c>
+      <c r="I217" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" ht="14">
+      <c r="A218" s="52">
+        <v>46191</v>
+      </c>
+      <c r="B218" s="53" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C218" s="54">
+        <v>1380</v>
+      </c>
+      <c r="D218" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E218" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F218" s="56"/>
       <c r="G218" s="56"/>
-      <c r="H218" s="57"/>
-      <c r="I218" s="53"/>
-    </row>
-    <row r="219" spans="1:9">
-      <c r="A219" s="48"/>
-      <c r="B219" s="49"/>
-      <c r="C219" s="50"/>
-      <c r="D219" s="49"/>
-      <c r="E219" s="49"/>
+      <c r="H218" s="57" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I218" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" ht="14">
+      <c r="A219" s="48">
+        <v>46191</v>
+      </c>
+      <c r="B219" s="49" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C219" s="50">
+        <v>1380</v>
+      </c>
+      <c r="D219" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E219" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F219" s="49"/>
       <c r="G219" s="49"/>
-      <c r="H219" s="51"/>
-      <c r="I219" s="49"/>
-    </row>
-    <row r="220" spans="1:9">
-      <c r="A220" s="52"/>
-      <c r="B220" s="53"/>
-      <c r="C220" s="54"/>
-      <c r="D220" s="53"/>
-      <c r="E220" s="53"/>
+      <c r="H219" s="51" t="s">
+        <v>358</v>
+      </c>
+      <c r="I219" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" ht="14">
+      <c r="A220" s="52">
+        <v>46191</v>
+      </c>
+      <c r="B220" s="53" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C220" s="54">
+        <v>1380</v>
+      </c>
+      <c r="D220" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E220" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F220" s="56"/>
       <c r="G220" s="56"/>
-      <c r="H220" s="57"/>
-      <c r="I220" s="53"/>
-    </row>
-    <row r="221" spans="1:9">
-      <c r="A221" s="48"/>
-      <c r="B221" s="49"/>
-      <c r="C221" s="50"/>
-      <c r="D221" s="49"/>
-      <c r="E221" s="49"/>
+      <c r="H220" s="57" t="s">
+        <v>358</v>
+      </c>
+      <c r="I220" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" ht="14">
+      <c r="A221" s="48">
+        <v>46191</v>
+      </c>
+      <c r="B221" s="49" t="s">
+        <v>364</v>
+      </c>
+      <c r="C221" s="50">
+        <v>1380</v>
+      </c>
+      <c r="D221" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E221" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F221" s="49"/>
       <c r="G221" s="49"/>
-      <c r="H221" s="51"/>
-      <c r="I221" s="49"/>
-    </row>
-    <row r="222" spans="1:9">
-      <c r="A222" s="52"/>
-      <c r="B222" s="53"/>
-      <c r="C222" s="54"/>
-      <c r="D222" s="53"/>
-      <c r="E222" s="53"/>
+      <c r="H221" s="51" t="s">
+        <v>359</v>
+      </c>
+      <c r="I221" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" ht="14">
+      <c r="A222" s="52">
+        <v>46191</v>
+      </c>
+      <c r="B222" s="53" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C222" s="54">
+        <v>1380</v>
+      </c>
+      <c r="D222" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E222" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F222" s="56"/>
       <c r="G222" s="56"/>
-      <c r="H222" s="57"/>
-      <c r="I222" s="53"/>
-    </row>
-    <row r="223" spans="1:9">
-      <c r="A223" s="48"/>
-      <c r="B223" s="49"/>
-      <c r="C223" s="50"/>
-      <c r="D223" s="49"/>
-      <c r="E223" s="49"/>
+      <c r="H222" s="57" t="s">
+        <v>358</v>
+      </c>
+      <c r="I222" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" ht="14">
+      <c r="A223" s="48">
+        <v>46191</v>
+      </c>
+      <c r="B223" s="49" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C223" s="50">
+        <v>1380</v>
+      </c>
+      <c r="D223" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E223" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F223" s="49"/>
       <c r="G223" s="49"/>
-      <c r="H223" s="51"/>
-      <c r="I223" s="49"/>
-    </row>
-    <row r="224" spans="1:9">
-      <c r="A224" s="52"/>
-      <c r="B224" s="53"/>
-      <c r="C224" s="54"/>
-      <c r="D224" s="53"/>
-      <c r="E224" s="53"/>
+      <c r="H223" s="51" t="s">
+        <v>359</v>
+      </c>
+      <c r="I223" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" ht="14">
+      <c r="A224" s="52">
+        <v>46191</v>
+      </c>
+      <c r="B224" s="53" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C224" s="54">
+        <v>1380</v>
+      </c>
+      <c r="D224" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E224" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F224" s="56"/>
       <c r="G224" s="56"/>
-      <c r="H224" s="57"/>
-      <c r="I224" s="53"/>
-    </row>
-    <row r="225" spans="1:9">
-      <c r="A225" s="48"/>
-      <c r="B225" s="49"/>
-      <c r="C225" s="50"/>
-      <c r="D225" s="49"/>
-      <c r="E225" s="49"/>
+      <c r="H224" s="57" t="s">
+        <v>358</v>
+      </c>
+      <c r="I224" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" ht="14">
+      <c r="A225" s="48">
+        <v>46192</v>
+      </c>
+      <c r="B225" s="49" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C225" s="50">
+        <v>1380</v>
+      </c>
+      <c r="D225" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E225" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F225" s="49"/>
       <c r="G225" s="49"/>
-      <c r="H225" s="51"/>
-      <c r="I225" s="49"/>
-    </row>
-    <row r="226" spans="1:9">
-      <c r="A226" s="52"/>
-      <c r="B226" s="53"/>
-      <c r="C226" s="54"/>
-      <c r="D226" s="53"/>
-      <c r="E226" s="53"/>
+      <c r="H225" s="51" t="s">
+        <v>359</v>
+      </c>
+      <c r="I225" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" ht="14">
+      <c r="A226" s="52">
+        <v>46192</v>
+      </c>
+      <c r="B226" s="53" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C226" s="54">
+        <v>1380</v>
+      </c>
+      <c r="D226" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E226" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F226" s="56"/>
       <c r="G226" s="56"/>
-      <c r="H226" s="57"/>
-      <c r="I226" s="53"/>
-    </row>
-    <row r="227" spans="1:9">
-      <c r="A227" s="48"/>
-      <c r="B227" s="49"/>
-      <c r="C227" s="50"/>
-      <c r="D227" s="49"/>
-      <c r="E227" s="49"/>
+      <c r="H226" s="57" t="s">
+        <v>359</v>
+      </c>
+      <c r="I226" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" ht="14">
+      <c r="A227" s="48">
+        <v>46192</v>
+      </c>
+      <c r="B227" s="49" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C227" s="50">
+        <v>1380</v>
+      </c>
+      <c r="D227" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E227" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F227" s="49"/>
       <c r="G227" s="49"/>
-      <c r="H227" s="51"/>
-      <c r="I227" s="49"/>
-    </row>
-    <row r="228" spans="1:9">
-      <c r="A228" s="52"/>
-      <c r="B228" s="53"/>
-      <c r="C228" s="54"/>
-      <c r="D228" s="53"/>
-      <c r="E228" s="53"/>
+      <c r="H227" s="51" t="s">
+        <v>358</v>
+      </c>
+      <c r="I227" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" ht="14">
+      <c r="A228" s="52">
+        <v>46192</v>
+      </c>
+      <c r="B228" s="53" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C228" s="54">
+        <v>1380</v>
+      </c>
+      <c r="D228" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E228" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F228" s="56"/>
       <c r="G228" s="56"/>
-      <c r="H228" s="57"/>
-      <c r="I228" s="53"/>
+      <c r="H228" s="57" t="s">
+        <v>358</v>
+      </c>
+      <c r="I228" s="53" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" s="48"/>
@@ -16917,13 +17361,7 @@
       <c r="I260" s="59"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I214" xr:uid="{00000000-0009-0000-0000-000004000000}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="Pending"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I217" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1260" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Ordered,Pending,Completed,Cancelled"</formula1>
@@ -23714,7 +24152,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="66" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="M62" s="66"/>
       <c r="N62" s="66" t="s">
@@ -24536,10 +24974,10 @@
         <v>1560</v>
       </c>
       <c r="F78" s="67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G78" s="67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="66">
         <f t="shared" si="6"/>
@@ -24551,21 +24989,21 @@
       </c>
       <c r="J78" s="66">
         <f t="shared" si="7"/>
-        <v>2150</v>
+        <v>3225</v>
       </c>
       <c r="K78" s="66">
         <f t="shared" si="8"/>
-        <v>2150</v>
+        <v>1075</v>
       </c>
       <c r="L78" s="66" t="s">
-        <v>594</v>
+        <v>966</v>
       </c>
       <c r="M78" s="66"/>
       <c r="N78" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O78" s="66" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="P78" s="66"/>
       <c r="Q78" s="66"/>
@@ -24575,10 +25013,10 @@
     </row>
     <row r="79" spans="1:20" ht="15" customHeight="1">
       <c r="A79" s="69" t="s">
+        <v>595</v>
+      </c>
+      <c r="B79" s="69" t="s">
         <v>596</v>
-      </c>
-      <c r="B79" s="69" t="s">
-        <v>597</v>
       </c>
       <c r="C79" s="69" t="s">
         <v>96</v>
@@ -24612,14 +25050,14 @@
         <v>0</v>
       </c>
       <c r="L79" s="69" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="M79" s="69"/>
       <c r="N79" s="69" t="s">
+        <v>598</v>
+      </c>
+      <c r="O79" s="69" t="s">
         <v>599</v>
-      </c>
-      <c r="O79" s="69" t="s">
-        <v>600</v>
       </c>
       <c r="P79" s="69"/>
       <c r="Q79" s="69"/>
@@ -24629,10 +25067,10 @@
     </row>
     <row r="80" spans="1:20" ht="15" customHeight="1">
       <c r="A80" s="66" t="s">
+        <v>600</v>
+      </c>
+      <c r="B80" s="66" t="s">
         <v>601</v>
-      </c>
-      <c r="B80" s="66" t="s">
-        <v>602</v>
       </c>
       <c r="C80" s="66" t="s">
         <v>96</v>
@@ -24666,14 +25104,14 @@
         <v>1230</v>
       </c>
       <c r="L80" s="66" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M80" s="66"/>
       <c r="N80" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O80" s="66" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="P80" s="66"/>
       <c r="Q80" s="66"/>
@@ -24683,10 +25121,10 @@
     </row>
     <row r="81" spans="1:20" ht="30" customHeight="1">
       <c r="A81" s="69" t="s">
+        <v>604</v>
+      </c>
+      <c r="B81" s="69" t="s">
         <v>605</v>
-      </c>
-      <c r="B81" s="69" t="s">
-        <v>606</v>
       </c>
       <c r="C81" s="69" t="s">
         <v>96</v>
@@ -24720,7 +25158,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="69" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="M81" s="69"/>
       <c r="N81" s="69" t="s">
@@ -24735,10 +25173,10 @@
     </row>
     <row r="82" spans="1:20" ht="15" customHeight="1">
       <c r="A82" s="66" t="s">
+        <v>607</v>
+      </c>
+      <c r="B82" s="66" t="s">
         <v>608</v>
-      </c>
-      <c r="B82" s="66" t="s">
-        <v>609</v>
       </c>
       <c r="C82" s="66" t="s">
         <v>96</v>
@@ -24772,7 +25210,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="66" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="M82" s="66"/>
       <c r="N82" s="66" t="s">
@@ -24787,10 +25225,10 @@
     </row>
     <row r="83" spans="1:20" ht="30" customHeight="1">
       <c r="A83" s="69" t="s">
+        <v>610</v>
+      </c>
+      <c r="B83" s="69" t="s">
         <v>611</v>
-      </c>
-      <c r="B83" s="69" t="s">
-        <v>612</v>
       </c>
       <c r="C83" s="69" t="s">
         <v>96</v>
@@ -24824,14 +25262,14 @@
         <v>0</v>
       </c>
       <c r="L83" s="69" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="M83" s="69"/>
       <c r="N83" s="69" t="s">
         <v>425</v>
       </c>
       <c r="O83" s="69" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="P83" s="69"/>
       <c r="Q83" s="69"/>
@@ -24841,10 +25279,10 @@
     </row>
     <row r="84" spans="1:20" ht="15" customHeight="1">
       <c r="A84" s="66" t="s">
+        <v>614</v>
+      </c>
+      <c r="B84" s="66" t="s">
         <v>615</v>
-      </c>
-      <c r="B84" s="66" t="s">
-        <v>616</v>
       </c>
       <c r="C84" s="66" t="s">
         <v>96</v>
@@ -24878,14 +25316,14 @@
         <v>900</v>
       </c>
       <c r="L84" s="66" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M84" s="66"/>
       <c r="N84" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O84" s="66" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="P84" s="66"/>
       <c r="Q84" s="66"/>
@@ -24895,10 +25333,10 @@
     </row>
     <row r="85" spans="1:20" ht="15" customHeight="1">
       <c r="A85" s="69" t="s">
+        <v>618</v>
+      </c>
+      <c r="B85" s="69" t="s">
         <v>619</v>
-      </c>
-      <c r="B85" s="69" t="s">
-        <v>620</v>
       </c>
       <c r="C85" s="69" t="s">
         <v>96</v>
@@ -24932,7 +25370,7 @@
         <v>0</v>
       </c>
       <c r="L85" s="69" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="M85" s="69"/>
       <c r="N85" s="69" t="s">
@@ -24947,10 +25385,10 @@
     </row>
     <row r="86" spans="1:20" ht="15" customHeight="1">
       <c r="A86" s="66" t="s">
+        <v>621</v>
+      </c>
+      <c r="B86" s="66" t="s">
         <v>622</v>
-      </c>
-      <c r="B86" s="66" t="s">
-        <v>623</v>
       </c>
       <c r="C86" s="66" t="s">
         <v>96</v>
@@ -24984,14 +25422,14 @@
         <v>2090</v>
       </c>
       <c r="L86" s="66" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="M86" s="66"/>
       <c r="N86" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O86" s="66" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="P86" s="66"/>
       <c r="Q86" s="66"/>
@@ -25001,10 +25439,10 @@
     </row>
     <row r="87" spans="1:20" ht="15" customHeight="1">
       <c r="A87" s="69" t="s">
+        <v>624</v>
+      </c>
+      <c r="B87" s="69" t="s">
         <v>625</v>
-      </c>
-      <c r="B87" s="69" t="s">
-        <v>626</v>
       </c>
       <c r="C87" s="69" t="s">
         <v>96</v>
@@ -25040,10 +25478,10 @@
       <c r="L87" s="69"/>
       <c r="M87" s="69"/>
       <c r="N87" s="69" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O87" s="69" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="P87" s="69"/>
       <c r="Q87" s="69"/>
@@ -25053,10 +25491,10 @@
     </row>
     <row r="88" spans="1:20" ht="30" customHeight="1">
       <c r="A88" s="66" t="s">
+        <v>627</v>
+      </c>
+      <c r="B88" s="66" t="s">
         <v>628</v>
-      </c>
-      <c r="B88" s="66" t="s">
-        <v>629</v>
       </c>
       <c r="C88" s="66" t="s">
         <v>96</v>
@@ -25090,14 +25528,14 @@
         <v>795</v>
       </c>
       <c r="L88" s="66" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="M88" s="66"/>
       <c r="N88" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O88" s="66" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="P88" s="66"/>
       <c r="Q88" s="66"/>
@@ -25107,10 +25545,10 @@
     </row>
     <row r="89" spans="1:20" ht="15" customHeight="1">
       <c r="A89" s="69" t="s">
+        <v>631</v>
+      </c>
+      <c r="B89" s="69" t="s">
         <v>632</v>
-      </c>
-      <c r="B89" s="69" t="s">
-        <v>633</v>
       </c>
       <c r="C89" s="69" t="s">
         <v>95</v>
@@ -25144,7 +25582,7 @@
         <v>0</v>
       </c>
       <c r="L89" s="69" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="M89" s="69"/>
       <c r="N89" s="69" t="s">
@@ -25159,10 +25597,10 @@
     </row>
     <row r="90" spans="1:20" ht="15" customHeight="1">
       <c r="A90" s="66" t="s">
+        <v>634</v>
+      </c>
+      <c r="B90" s="66" t="s">
         <v>635</v>
-      </c>
-      <c r="B90" s="66" t="s">
-        <v>636</v>
       </c>
       <c r="C90" s="66" t="s">
         <v>95</v>
@@ -25211,13 +25649,13 @@
     </row>
     <row r="91" spans="1:20" ht="15" customHeight="1">
       <c r="A91" s="69" t="s">
+        <v>636</v>
+      </c>
+      <c r="B91" s="69" t="s">
         <v>637</v>
       </c>
-      <c r="B91" s="69" t="s">
+      <c r="C91" s="69" t="s">
         <v>638</v>
-      </c>
-      <c r="C91" s="69" t="s">
-        <v>639</v>
       </c>
       <c r="D91" s="70">
         <v>389</v>
@@ -25248,7 +25686,7 @@
         <v>0</v>
       </c>
       <c r="L91" s="69" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="M91" s="69"/>
       <c r="N91" s="69" t="s">
@@ -25263,13 +25701,13 @@
     </row>
     <row r="92" spans="1:20" ht="15" customHeight="1">
       <c r="A92" s="66" t="s">
+        <v>640</v>
+      </c>
+      <c r="B92" s="66" t="s">
         <v>641</v>
       </c>
-      <c r="B92" s="66" t="s">
-        <v>642</v>
-      </c>
       <c r="C92" s="66" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D92" s="67">
         <v>489</v>
@@ -25300,7 +25738,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="66" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M92" s="66"/>
       <c r="N92" s="66" t="s">
@@ -25315,10 +25753,10 @@
     </row>
     <row r="93" spans="1:20" ht="15" customHeight="1">
       <c r="A93" s="69" t="s">
+        <v>643</v>
+      </c>
+      <c r="B93" s="69" t="s">
         <v>644</v>
-      </c>
-      <c r="B93" s="69" t="s">
-        <v>645</v>
       </c>
       <c r="C93" s="69" t="s">
         <v>97</v>
@@ -25352,14 +25790,14 @@
         <v>472</v>
       </c>
       <c r="L93" s="69" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="M93" s="69"/>
       <c r="N93" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O93" s="69" t="s">
-        <v>647</v>
+        <v>210</v>
       </c>
       <c r="P93" s="69"/>
       <c r="Q93" s="69"/>
@@ -25369,10 +25807,10 @@
     </row>
     <row r="94" spans="1:20" ht="15" customHeight="1">
       <c r="A94" s="66" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B94" s="66" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C94" s="66" t="s">
         <v>95</v>
@@ -25421,10 +25859,10 @@
     </row>
     <row r="95" spans="1:20" ht="15" customHeight="1">
       <c r="A95" s="69" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B95" s="69" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C95" s="69" t="s">
         <v>95</v>
@@ -25458,7 +25896,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="69" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="M95" s="69"/>
       <c r="N95" s="69" t="s">
@@ -25473,10 +25911,10 @@
     </row>
     <row r="96" spans="1:20" ht="15" customHeight="1">
       <c r="A96" s="66" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B96" s="66" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C96" s="66" t="s">
         <v>95</v>
@@ -25512,7 +25950,7 @@
       <c r="L96" s="66"/>
       <c r="M96" s="66"/>
       <c r="N96" s="66" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O96" s="66"/>
       <c r="P96" s="66"/>
@@ -25523,10 +25961,10 @@
     </row>
     <row r="97" spans="1:20" ht="15" customHeight="1">
       <c r="A97" s="69" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B97" s="69" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C97" s="69" t="s">
         <v>95</v>
@@ -25575,10 +26013,10 @@
     </row>
     <row r="98" spans="1:20" ht="15" customHeight="1">
       <c r="A98" s="66" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B98" s="66" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C98" s="66" t="s">
         <v>96</v>
@@ -25629,10 +26067,10 @@
     </row>
     <row r="99" spans="1:20" ht="15" customHeight="1">
       <c r="A99" s="69" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B99" s="69" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C99" s="69" t="s">
         <v>96</v>
@@ -25683,10 +26121,10 @@
     </row>
     <row r="100" spans="1:20" ht="15" customHeight="1">
       <c r="A100" s="66" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B100" s="66" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C100" s="66" t="s">
         <v>96</v>
@@ -25737,10 +26175,10 @@
     </row>
     <row r="101" spans="1:20" ht="15" customHeight="1">
       <c r="A101" s="69" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B101" s="69" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C101" s="69" t="s">
         <v>96</v>
@@ -25791,10 +26229,10 @@
     </row>
     <row r="102" spans="1:20" ht="15" customHeight="1">
       <c r="A102" s="66" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B102" s="66" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C102" s="66" t="s">
         <v>96</v>
@@ -25845,10 +26283,10 @@
     </row>
     <row r="103" spans="1:20" ht="15" customHeight="1">
       <c r="A103" s="69" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B103" s="69" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C103" s="69" t="s">
         <v>96</v>
@@ -25899,10 +26337,10 @@
     </row>
     <row r="104" spans="1:20" ht="15" customHeight="1">
       <c r="A104" s="66" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B104" s="66" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C104" s="66" t="s">
         <v>96</v>
@@ -25953,10 +26391,10 @@
     </row>
     <row r="105" spans="1:20" ht="15" customHeight="1">
       <c r="A105" s="69" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B105" s="69" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C105" s="69" t="s">
         <v>96</v>
@@ -26007,10 +26445,10 @@
     </row>
     <row r="106" spans="1:20" ht="15" customHeight="1">
       <c r="A106" s="66" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B106" s="66" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C106" s="66" t="s">
         <v>96</v>
@@ -26061,10 +26499,10 @@
     </row>
     <row r="107" spans="1:20" ht="15" customHeight="1">
       <c r="A107" s="69" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B107" s="69" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C107" s="69" t="s">
         <v>96</v>
@@ -26115,10 +26553,10 @@
     </row>
     <row r="108" spans="1:20" ht="15" customHeight="1">
       <c r="A108" s="66" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B108" s="66" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C108" s="66" t="s">
         <v>96</v>
@@ -26169,10 +26607,10 @@
     </row>
     <row r="109" spans="1:20" ht="15" customHeight="1">
       <c r="A109" s="69" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B109" s="69" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C109" s="69" t="s">
         <v>96</v>
@@ -26223,10 +26661,10 @@
     </row>
     <row r="110" spans="1:20" ht="15" customHeight="1">
       <c r="A110" s="66" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B110" s="66" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C110" s="66" t="s">
         <v>96</v>
@@ -26277,10 +26715,10 @@
     </row>
     <row r="111" spans="1:20" ht="15" customHeight="1">
       <c r="A111" s="69" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B111" s="69" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C111" s="69" t="s">
         <v>96</v>
@@ -26331,10 +26769,10 @@
     </row>
     <row r="112" spans="1:20" ht="15" customHeight="1">
       <c r="A112" s="66" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B112" s="66" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C112" s="66" t="s">
         <v>96</v>
@@ -26370,7 +26808,7 @@
       <c r="L112" s="66"/>
       <c r="M112" s="66"/>
       <c r="N112" s="66" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O112" s="66" t="s">
         <v>201</v>
@@ -26383,10 +26821,10 @@
     </row>
     <row r="113" spans="1:246" ht="15" customHeight="1">
       <c r="A113" s="69" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B113" s="69" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C113" s="69" t="s">
         <v>96</v>
@@ -26437,10 +26875,10 @@
     </row>
     <row r="114" spans="1:246" ht="15" customHeight="1">
       <c r="A114" s="66" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B114" s="66" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C114" s="66" t="s">
         <v>95</v>
@@ -26489,10 +26927,10 @@
     </row>
     <row r="115" spans="1:246" ht="30" customHeight="1">
       <c r="A115" s="69" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B115" s="69" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C115" s="69" t="s">
         <v>95</v>
@@ -26526,7 +26964,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="69" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="M115" s="69"/>
       <c r="N115" s="69" t="s">
@@ -26541,10 +26979,10 @@
     </row>
     <row r="116" spans="1:246" ht="150" customHeight="1">
       <c r="A116" s="66" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B116" s="66" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C116" s="66" t="s">
         <v>95</v>
@@ -26578,7 +27016,7 @@
         <v>0</v>
       </c>
       <c r="L116" s="66" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="M116" s="66"/>
       <c r="N116" s="66" t="s">
@@ -26593,10 +27031,10 @@
     </row>
     <row r="117" spans="1:246" ht="15" customHeight="1">
       <c r="A117" s="69" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B117" s="69" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C117" s="69" t="s">
         <v>95</v>
@@ -26645,10 +27083,10 @@
     </row>
     <row r="118" spans="1:246" ht="15" customHeight="1">
       <c r="A118" s="66" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B118" s="66" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C118" s="66" t="s">
         <v>95</v>
@@ -26682,7 +27120,7 @@
         <v>2095.8000000000002</v>
       </c>
       <c r="L118" s="66" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="M118" s="66"/>
       <c r="N118" s="66" t="s">
@@ -26690,7 +27128,7 @@
       </c>
       <c r="O118" s="66"/>
       <c r="P118" s="66" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="Q118" s="66"/>
       <c r="R118" s="66"/>
@@ -26699,10 +27137,10 @@
     </row>
     <row r="119" spans="1:246" ht="15" customHeight="1">
       <c r="A119" s="69" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B119" s="69" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C119" s="69" t="s">
         <v>95</v>
@@ -26751,10 +27189,10 @@
     </row>
     <row r="120" spans="1:246" ht="158" customHeight="1">
       <c r="A120" s="66" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B120" s="66" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C120" s="66" t="s">
         <v>95</v>
@@ -26766,10 +27204,10 @@
         <v>699</v>
       </c>
       <c r="F120" s="67">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G120" s="67">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H120" s="66">
         <f t="shared" si="9"/>
@@ -26781,14 +27219,14 @@
       </c>
       <c r="J120" s="66">
         <f t="shared" si="10"/>
-        <v>14663.366666666654</v>
+        <v>15082.319999999987</v>
       </c>
       <c r="K120" s="66">
         <f t="shared" si="11"/>
-        <v>5865.3466666666618</v>
+        <v>5446.3933333333289</v>
       </c>
       <c r="L120" s="66" t="s">
-        <v>956</v>
+        <v>971</v>
       </c>
       <c r="M120" s="66" t="s">
         <v>49</v>
@@ -26798,7 +27236,7 @@
       </c>
       <c r="O120" s="66"/>
       <c r="P120" s="66" t="s">
-        <v>957</v>
+        <v>970</v>
       </c>
       <c r="Q120" s="66"/>
       <c r="R120" s="66"/>
@@ -26807,10 +27245,10 @@
     </row>
     <row r="121" spans="1:246" ht="15" customHeight="1">
       <c r="A121" s="69" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B121" s="69" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C121" s="69" t="s">
         <v>95</v>
@@ -26844,7 +27282,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="69" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="M121" s="69"/>
       <c r="N121" s="69" t="s">
@@ -26852,7 +27290,7 @@
       </c>
       <c r="O121" s="69"/>
       <c r="P121" s="69" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="Q121" s="69"/>
       <c r="R121" s="69"/>
@@ -26861,10 +27299,10 @@
     </row>
     <row r="122" spans="1:246" ht="15" customHeight="1">
       <c r="A122" s="66" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B122" s="66" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C122" s="66" t="s">
         <v>96</v>
@@ -26898,7 +27336,7 @@
         <v>4700</v>
       </c>
       <c r="L122" s="66" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="M122" s="66"/>
       <c r="N122" s="66" t="s">
@@ -26913,10 +27351,10 @@
     </row>
     <row r="123" spans="1:246" s="72" customFormat="1" ht="75" customHeight="1">
       <c r="A123" s="78" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B123" s="78" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C123" s="78" t="s">
         <v>95</v>
@@ -26928,10 +27366,10 @@
         <v>1380</v>
       </c>
       <c r="F123" s="79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G123" s="79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H123" s="78">
         <f t="shared" si="9"/>
@@ -26943,14 +27381,14 @@
       </c>
       <c r="J123" s="78">
         <f t="shared" si="10"/>
-        <v>4457.2000000000007</v>
+        <v>5348.64</v>
       </c>
       <c r="K123" s="78">
         <f t="shared" si="11"/>
-        <v>891.44</v>
+        <v>0</v>
       </c>
       <c r="L123" s="78" t="s">
-        <v>716</v>
+        <v>960</v>
       </c>
       <c r="M123" s="78"/>
       <c r="N123" s="78" t="s">
@@ -27191,10 +27629,10 @@
     </row>
     <row r="124" spans="1:246" s="83" customFormat="1" ht="30" customHeight="1">
       <c r="A124" s="80" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B124" s="80" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C124" s="80" t="s">
         <v>95</v>
@@ -27228,7 +27666,7 @@
         <v>0</v>
       </c>
       <c r="L124" s="80" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="M124" s="80"/>
       <c r="N124" s="80" t="s">
@@ -27471,10 +27909,10 @@
     </row>
     <row r="125" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A125" s="78" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B125" s="78" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C125" s="78" t="s">
         <v>95</v>
@@ -27508,7 +27946,7 @@
         <v>0</v>
       </c>
       <c r="L125" s="78" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="M125" s="78"/>
       <c r="N125" s="78" t="s">
@@ -27516,7 +27954,7 @@
       </c>
       <c r="O125" s="78"/>
       <c r="P125" s="78" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="Q125" s="78"/>
       <c r="R125" s="78"/>
@@ -27751,10 +28189,10 @@
     </row>
     <row r="126" spans="1:246" ht="15" customHeight="1">
       <c r="A126" s="80" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B126" s="66" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C126" s="66" t="s">
         <v>96</v>
@@ -27788,14 +28226,14 @@
         <v>0</v>
       </c>
       <c r="L126" s="66" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="M126" s="66"/>
       <c r="N126" s="66" t="s">
         <v>425</v>
       </c>
       <c r="O126" s="66" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="P126" s="66"/>
       <c r="Q126" s="66"/>
@@ -27805,10 +28243,10 @@
     </row>
     <row r="127" spans="1:246" ht="15" customHeight="1">
       <c r="A127" s="78" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B127" s="69" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C127" s="69" t="s">
         <v>96</v>
@@ -27859,10 +28297,10 @@
     </row>
     <row r="128" spans="1:246" ht="15" customHeight="1">
       <c r="A128" s="80" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B128" s="66" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C128" s="66" t="s">
         <v>95</v>
@@ -27898,7 +28336,7 @@
       <c r="L128" s="66"/>
       <c r="M128" s="66"/>
       <c r="N128" s="66" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O128" s="66"/>
       <c r="P128" s="66"/>
@@ -27909,10 +28347,10 @@
     </row>
     <row r="129" spans="1:20" ht="15" customHeight="1">
       <c r="A129" s="78" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B129" s="69" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C129" s="69" t="s">
         <v>95</v>
@@ -27946,7 +28384,7 @@
         <v>0</v>
       </c>
       <c r="L129" s="69" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="M129" s="69"/>
       <c r="N129" s="69" t="s">
@@ -27961,10 +28399,10 @@
     </row>
     <row r="130" spans="1:20" ht="15" customHeight="1">
       <c r="A130" s="80" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="B130" s="66" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="C130" s="66" t="s">
         <v>95</v>
@@ -27998,7 +28436,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="66" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="M130" s="66"/>
       <c r="N130" s="66" t="s">
@@ -28013,10 +28451,10 @@
     </row>
     <row r="131" spans="1:20" ht="15" customHeight="1">
       <c r="A131" s="78" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B131" s="69" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C131" s="69" t="s">
         <v>95</v>
@@ -28052,7 +28490,7 @@
       <c r="L131" s="69"/>
       <c r="M131" s="69"/>
       <c r="N131" s="69" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O131" s="69"/>
       <c r="P131" s="69"/>
@@ -28063,10 +28501,10 @@
     </row>
     <row r="132" spans="1:20" ht="15" customHeight="1">
       <c r="A132" s="80" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="B132" s="66" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C132" s="66" t="s">
         <v>95</v>
@@ -28100,7 +28538,7 @@
         <v>0</v>
       </c>
       <c r="L132" s="66" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="M132" s="66"/>
       <c r="N132" s="66" t="s">
@@ -28115,10 +28553,10 @@
     </row>
     <row r="133" spans="1:20" ht="15" customHeight="1">
       <c r="A133" s="78" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B133" s="69" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="C133" s="69" t="s">
         <v>95</v>
@@ -28154,7 +28592,7 @@
       <c r="L133" s="69"/>
       <c r="M133" s="69"/>
       <c r="N133" s="69" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O133" s="69"/>
       <c r="P133" s="69"/>
@@ -28165,10 +28603,10 @@
     </row>
     <row r="134" spans="1:20" ht="15" customHeight="1">
       <c r="A134" s="80" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B134" s="66" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C134" s="66" t="s">
         <v>95</v>
@@ -28204,7 +28642,7 @@
       <c r="L134" s="66"/>
       <c r="M134" s="66"/>
       <c r="N134" s="66" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O134" s="66"/>
       <c r="P134" s="66"/>
@@ -28215,10 +28653,10 @@
     </row>
     <row r="135" spans="1:20" ht="15" customHeight="1">
       <c r="A135" s="78" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="B135" s="69" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C135" s="69" t="s">
         <v>95</v>
@@ -28252,7 +28690,7 @@
         <v>0</v>
       </c>
       <c r="L135" s="69" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="M135" s="69"/>
       <c r="N135" s="69" t="s">
@@ -28267,10 +28705,10 @@
     </row>
     <row r="136" spans="1:20" ht="15" customHeight="1">
       <c r="A136" s="80" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B136" s="66" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C136" s="66" t="s">
         <v>95</v>
@@ -28304,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="L136" s="66" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="M136" s="66"/>
       <c r="N136" s="66" t="s">
@@ -28312,7 +28750,7 @@
       </c>
       <c r="O136" s="66"/>
       <c r="P136" s="66" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="Q136" s="66"/>
       <c r="R136" s="66"/>
@@ -28321,10 +28759,10 @@
     </row>
     <row r="137" spans="1:20" ht="15" customHeight="1">
       <c r="A137" s="78" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B137" s="69" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="C137" s="69" t="s">
         <v>95</v>
@@ -28373,10 +28811,10 @@
     </row>
     <row r="138" spans="1:20" ht="15" customHeight="1">
       <c r="A138" s="80" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B138" s="66" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C138" s="66" t="s">
         <v>95</v>
@@ -28410,7 +28848,7 @@
         <v>0</v>
       </c>
       <c r="L138" s="66" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="M138" s="66"/>
       <c r="N138" s="66" t="s">
@@ -28425,10 +28863,10 @@
     </row>
     <row r="139" spans="1:20" ht="15" customHeight="1">
       <c r="A139" s="78" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B139" s="69" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C139" s="69" t="s">
         <v>95</v>
@@ -28477,10 +28915,10 @@
     </row>
     <row r="140" spans="1:20" ht="15" customHeight="1">
       <c r="A140" s="80" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B140" s="66" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="C140" s="66" t="s">
         <v>95</v>
@@ -28514,7 +28952,7 @@
         <v>699</v>
       </c>
       <c r="L140" s="66" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="M140" s="66"/>
       <c r="N140" s="66" t="s">
@@ -28529,10 +28967,10 @@
     </row>
     <row r="141" spans="1:20" ht="15" customHeight="1">
       <c r="A141" s="78" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="B141" s="69" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C141" s="69" t="s">
         <v>95</v>
@@ -28566,7 +29004,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="69" t="s">
-        <v>965</v>
+        <v>954</v>
       </c>
       <c r="M141" s="69"/>
       <c r="N141" s="69" t="s">
@@ -28581,10 +29019,10 @@
     </row>
     <row r="142" spans="1:20" ht="15" customHeight="1">
       <c r="A142" s="66" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B142" s="66" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="C142" s="66" t="s">
         <v>95</v>
@@ -28618,7 +29056,7 @@
         <v>600</v>
       </c>
       <c r="L142" s="66" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="M142" s="66"/>
       <c r="N142" s="66" t="s">
@@ -28635,10 +29073,10 @@
     </row>
     <row r="143" spans="1:20" ht="15" customHeight="1">
       <c r="A143" s="69" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B143" s="69" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C143" s="69" t="s">
         <v>95</v>
@@ -28674,7 +29112,7 @@
       <c r="L143" s="69"/>
       <c r="M143" s="69"/>
       <c r="N143" s="69" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O143" s="69"/>
       <c r="P143" s="69"/>
@@ -28685,10 +29123,10 @@
     </row>
     <row r="144" spans="1:20" ht="15" customHeight="1">
       <c r="A144" s="66" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B144" s="66" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C144" s="66" t="s">
         <v>95</v>
@@ -28724,7 +29162,7 @@
       <c r="L144" s="66"/>
       <c r="M144" s="66"/>
       <c r="N144" s="66" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O144" s="66"/>
       <c r="P144" s="66"/>
@@ -28735,7 +29173,7 @@
     </row>
     <row r="145" spans="1:20" ht="15" customHeight="1">
       <c r="A145" s="69" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B145" s="69" t="s">
         <v>296</v>
@@ -28787,10 +29225,10 @@
     </row>
     <row r="146" spans="1:20" ht="15" customHeight="1">
       <c r="A146" s="66" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B146" s="66" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="C146" s="66" t="s">
         <v>95</v>
@@ -28824,7 +29262,7 @@
         <v>761</v>
       </c>
       <c r="L146" s="66" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="M146" s="66"/>
       <c r="N146" s="66" t="s">
@@ -28832,7 +29270,7 @@
       </c>
       <c r="O146" s="66"/>
       <c r="P146" s="66" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="Q146" s="66"/>
       <c r="R146" s="66"/>
@@ -28841,10 +29279,10 @@
     </row>
     <row r="147" spans="1:20" ht="63.75" customHeight="1">
       <c r="A147" s="69" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B147" s="69" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C147" s="69" t="s">
         <v>95</v>
@@ -28878,7 +29316,7 @@
         <v>2157</v>
       </c>
       <c r="L147" s="69" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="M147" s="69"/>
       <c r="N147" s="69" t="s">
@@ -28886,7 +29324,7 @@
       </c>
       <c r="O147" s="69"/>
       <c r="P147" s="69" t="s">
-        <v>953</v>
+        <v>944</v>
       </c>
       <c r="Q147" s="69"/>
       <c r="R147" s="69"/>
@@ -28895,10 +29333,10 @@
     </row>
     <row r="148" spans="1:20" ht="15" customHeight="1">
       <c r="A148" s="66" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B148" s="66" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C148" s="66" t="s">
         <v>95</v>
@@ -28932,7 +29370,7 @@
         <v>502</v>
       </c>
       <c r="L148" s="66" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="M148" s="66"/>
       <c r="N148" s="66" t="s">
@@ -28947,10 +29385,10 @@
     </row>
     <row r="149" spans="1:20" ht="15" customHeight="1">
       <c r="A149" s="69" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B149" s="69" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C149" s="69" t="s">
         <v>95</v>
@@ -28984,7 +29422,7 @@
         <v>1024</v>
       </c>
       <c r="L149" s="69" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="M149" s="69"/>
       <c r="N149" s="69" t="s">
@@ -28999,10 +29437,10 @@
     </row>
     <row r="150" spans="1:20" ht="15" customHeight="1">
       <c r="A150" s="66" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B150" s="66" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="C150" s="66" t="s">
         <v>95</v>
@@ -29038,7 +29476,7 @@
       <c r="L150" s="66"/>
       <c r="M150" s="66"/>
       <c r="N150" s="66" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O150" s="66"/>
       <c r="P150" s="66"/>
@@ -29049,10 +29487,10 @@
     </row>
     <row r="151" spans="1:20" ht="15" customHeight="1">
       <c r="A151" s="69" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B151" s="69" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C151" s="69" t="s">
         <v>96</v>
@@ -29086,7 +29524,7 @@
         <v>645</v>
       </c>
       <c r="L151" s="69" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="M151" s="69"/>
       <c r="N151" s="69" t="s">
@@ -29096,7 +29534,7 @@
         <v>210</v>
       </c>
       <c r="P151" s="69" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="Q151" s="69"/>
       <c r="R151" s="69"/>
@@ -29105,10 +29543,10 @@
     </row>
     <row r="152" spans="1:20" ht="15" customHeight="1">
       <c r="A152" s="66" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B152" s="66" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="C152" s="66" t="s">
         <v>97</v>
@@ -29120,10 +29558,10 @@
         <v>580</v>
       </c>
       <c r="F152" s="81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G152" s="81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H152" s="80">
         <f t="shared" si="12"/>
@@ -29135,24 +29573,24 @@
       </c>
       <c r="J152" s="80">
         <f t="shared" si="13"/>
-        <v>295</v>
+        <v>590</v>
       </c>
       <c r="K152" s="80">
         <f t="shared" si="14"/>
-        <v>885</v>
+        <v>590</v>
       </c>
       <c r="L152" s="66" t="s">
-        <v>795</v>
+        <v>967</v>
       </c>
       <c r="M152" s="66"/>
       <c r="N152" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O152" s="66" t="s">
-        <v>796</v>
+        <v>968</v>
       </c>
       <c r="P152" s="66" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="Q152" s="66"/>
       <c r="R152" s="66"/>
@@ -29161,10 +29599,10 @@
     </row>
     <row r="153" spans="1:20" ht="15" customHeight="1">
       <c r="A153" s="69" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="B153" s="69" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="C153" s="69" t="s">
         <v>95</v>
@@ -29198,7 +29636,7 @@
         <v>891.5</v>
       </c>
       <c r="L153" s="69" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="M153" s="69"/>
       <c r="N153" s="69" t="s">
@@ -29206,7 +29644,7 @@
       </c>
       <c r="O153" s="69"/>
       <c r="P153" s="69" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="Q153" s="69"/>
       <c r="R153" s="69"/>
@@ -29215,10 +29653,10 @@
     </row>
     <row r="154" spans="1:20" ht="15" customHeight="1">
       <c r="A154" s="66" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="B154" s="66" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C154" s="66" t="s">
         <v>96</v>
@@ -29252,14 +29690,14 @@
         <v>1898</v>
       </c>
       <c r="L154" s="66" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="M154" s="66"/>
       <c r="N154" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O154" s="66" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="P154" s="66"/>
       <c r="Q154" s="66"/>
@@ -29269,10 +29707,10 @@
     </row>
     <row r="155" spans="1:20" ht="15" customHeight="1">
       <c r="A155" s="69" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="B155" s="69" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="C155" s="69" t="s">
         <v>96</v>
@@ -29308,10 +29746,10 @@
       <c r="L155" s="69"/>
       <c r="M155" s="69"/>
       <c r="N155" s="69" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O155" s="69" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="P155" s="69"/>
       <c r="Q155" s="69"/>
@@ -29321,10 +29759,10 @@
     </row>
     <row r="156" spans="1:20" ht="15" customHeight="1">
       <c r="A156" s="66" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="B156" s="66" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="C156" s="66" t="s">
         <v>96</v>
@@ -29358,14 +29796,14 @@
         <v>2850</v>
       </c>
       <c r="L156" s="66" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="M156" s="66"/>
       <c r="N156" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O156" s="66" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="P156" s="66"/>
       <c r="Q156" s="66"/>
@@ -29375,10 +29813,10 @@
     </row>
     <row r="157" spans="1:20" ht="15" customHeight="1">
       <c r="A157" s="69" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="B157" s="69" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="C157" s="69" t="s">
         <v>96</v>
@@ -29390,10 +29828,10 @@
         <v>850</v>
       </c>
       <c r="F157" s="79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G157" s="79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H157" s="78">
         <f t="shared" si="12"/>
@@ -29405,21 +29843,21 @@
       </c>
       <c r="J157" s="78">
         <f t="shared" si="13"/>
-        <v>525</v>
+        <v>1050</v>
       </c>
       <c r="K157" s="78">
         <f t="shared" si="14"/>
-        <v>1575</v>
+        <v>1050</v>
       </c>
       <c r="L157" s="69" t="s">
-        <v>814</v>
+        <v>969</v>
       </c>
       <c r="M157" s="69"/>
       <c r="N157" s="69" t="s">
         <v>510</v>
       </c>
       <c r="O157" s="69" t="s">
-        <v>815</v>
+        <v>540</v>
       </c>
       <c r="P157" s="69"/>
       <c r="Q157" s="69"/>
@@ -29429,10 +29867,10 @@
     </row>
     <row r="158" spans="1:20" ht="15" customHeight="1">
       <c r="A158" s="66" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="B158" s="66" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="C158" s="66" t="s">
         <v>96</v>
@@ -29466,14 +29904,14 @@
         <v>3356</v>
       </c>
       <c r="L158" s="66" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="M158" s="66"/>
       <c r="N158" s="66" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O158" s="66" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="P158" s="66"/>
       <c r="Q158" s="66"/>
@@ -29483,10 +29921,10 @@
     </row>
     <row r="159" spans="1:20" ht="15" customHeight="1">
       <c r="A159" s="69" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="B159" s="69" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="C159" s="69" t="s">
         <v>96</v>
@@ -29520,14 +29958,14 @@
         <v>2517</v>
       </c>
       <c r="L159" s="69" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="M159" s="69"/>
       <c r="N159" s="69" t="s">
         <v>510</v>
       </c>
       <c r="O159" s="69" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="P159" s="69"/>
       <c r="Q159" s="69"/>
@@ -29537,10 +29975,10 @@
     </row>
     <row r="160" spans="1:20" ht="15" customHeight="1">
       <c r="A160" s="66" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="B160" s="66" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="C160" s="66" t="s">
         <v>95</v>
@@ -29589,10 +30027,10 @@
     </row>
     <row r="161" spans="1:20" ht="15" customHeight="1">
       <c r="A161" s="69" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="B161" s="69" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="C161" s="69" t="s">
         <v>95</v>
@@ -29641,10 +30079,10 @@
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1">
       <c r="A162" s="66" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="B162" s="66" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="C162" s="66" t="s">
         <v>95</v>
@@ -29693,10 +30131,10 @@
     </row>
     <row r="163" spans="1:20" ht="15" customHeight="1">
       <c r="A163" s="69" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="B163" s="69" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="C163" s="69" t="s">
         <v>95</v>
@@ -29732,7 +30170,7 @@
       <c r="L163" s="69"/>
       <c r="M163" s="69"/>
       <c r="N163" s="69" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O163" s="69"/>
       <c r="P163" s="69"/>
@@ -29743,10 +30181,10 @@
     </row>
     <row r="164" spans="1:20" ht="60" customHeight="1">
       <c r="A164" s="66" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="B164" s="66" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="C164" s="66" t="s">
         <v>95</v>
@@ -29780,7 +30218,7 @@
         <v>1013</v>
       </c>
       <c r="L164" s="66" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="M164" s="66"/>
       <c r="N164" s="66" t="s">
@@ -29788,7 +30226,7 @@
       </c>
       <c r="O164" s="66"/>
       <c r="P164" s="66" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="Q164" s="66"/>
       <c r="R164" s="66"/>
@@ -29797,10 +30235,10 @@
     </row>
     <row r="165" spans="1:20" ht="15" customHeight="1">
       <c r="A165" s="69" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="B165" s="69" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="C165" s="69" t="s">
         <v>95</v>
@@ -29842,7 +30280,7 @@
       </c>
       <c r="O165" s="69"/>
       <c r="P165" s="69" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="Q165" s="69"/>
       <c r="R165" s="69"/>
@@ -29851,10 +30289,10 @@
     </row>
     <row r="166" spans="1:20" ht="15" customHeight="1">
       <c r="A166" s="66" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="B166" s="66" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="C166" s="66" t="s">
         <v>95</v>
@@ -29890,11 +30328,11 @@
       <c r="L166" s="66"/>
       <c r="M166" s="66"/>
       <c r="N166" s="66" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O166" s="66"/>
       <c r="P166" s="66" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="Q166" s="66"/>
       <c r="R166" s="66"/>
@@ -29903,10 +30341,10 @@
     </row>
     <row r="167" spans="1:20" ht="15" customHeight="1">
       <c r="A167" s="69" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B167" s="69" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="C167" s="69" t="s">
         <v>95</v>
@@ -29940,7 +30378,7 @@
         <v>2220</v>
       </c>
       <c r="L167" s="69" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="M167" s="69"/>
       <c r="N167" s="69" t="s">
@@ -29948,7 +30386,7 @@
       </c>
       <c r="O167" s="69"/>
       <c r="P167" s="69" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="Q167" s="69"/>
       <c r="R167" s="69"/>
@@ -29957,10 +30395,10 @@
     </row>
     <row r="168" spans="1:20" ht="15" customHeight="1">
       <c r="A168" s="66" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="B168" s="66" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="C168" s="66" t="s">
         <v>95</v>
@@ -29994,7 +30432,7 @@
         <v>1216</v>
       </c>
       <c r="L168" s="66" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="M168" s="66"/>
       <c r="N168" s="66" t="s">
@@ -30002,7 +30440,7 @@
       </c>
       <c r="O168" s="66"/>
       <c r="P168" s="66" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="Q168" s="66"/>
       <c r="R168" s="66"/>
@@ -30011,10 +30449,10 @@
     </row>
     <row r="169" spans="1:20" ht="15" customHeight="1">
       <c r="A169" s="69" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="B169" s="69" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="C169" s="69" t="s">
         <v>95</v>
@@ -30050,11 +30488,11 @@
       <c r="L169" s="69"/>
       <c r="M169" s="69"/>
       <c r="N169" s="69" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O169" s="69"/>
       <c r="P169" s="69" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="Q169" s="69"/>
       <c r="R169" s="69"/>
@@ -30063,10 +30501,10 @@
     </row>
     <row r="170" spans="1:20" ht="30" customHeight="1">
       <c r="A170" s="66" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="B170" s="66" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="C170" s="66" t="s">
         <v>95</v>
@@ -30100,7 +30538,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="66" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="M170" s="66"/>
       <c r="N170" s="66" t="s">
@@ -30108,7 +30546,7 @@
       </c>
       <c r="O170" s="66"/>
       <c r="P170" s="66" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="Q170" s="66"/>
       <c r="R170" s="66"/>
@@ -30117,10 +30555,10 @@
     </row>
     <row r="171" spans="1:20" ht="31.5" customHeight="1">
       <c r="A171" s="69" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="B171" s="66" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="C171" s="69" t="s">
         <v>95</v>
@@ -30154,7 +30592,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="69" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="M171" s="69"/>
       <c r="N171" s="69" t="s">
@@ -30169,10 +30607,10 @@
     </row>
     <row r="172" spans="1:20" ht="15" customHeight="1">
       <c r="A172" s="66" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="B172" s="66" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="C172" s="66" t="s">
         <v>95</v>
@@ -30187,11 +30625,11 @@
         <v>2</v>
       </c>
       <c r="G172" s="81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H172" s="80">
         <f t="shared" si="15"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I172" s="80">
         <f>IF(D172&lt;&gt;"",D172,IFERROR(E172/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -30203,10 +30641,10 @@
       </c>
       <c r="K172" s="80">
         <f t="shared" si="17"/>
-        <v>2094</v>
+        <v>0</v>
       </c>
       <c r="L172" s="66" t="s">
-        <v>947</v>
+        <v>938</v>
       </c>
       <c r="M172" s="66"/>
       <c r="N172" s="66" t="s">
@@ -30221,10 +30659,10 @@
     </row>
     <row r="173" spans="1:20" ht="15" customHeight="1">
       <c r="A173" s="69" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="B173" s="69" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="C173" s="69" t="s">
         <v>95</v>
@@ -30273,10 +30711,10 @@
     </row>
     <row r="174" spans="1:20" ht="15" customHeight="1">
       <c r="A174" s="66" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="B174" s="66" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="C174" s="66" t="s">
         <v>95</v>
@@ -30310,7 +30748,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="66" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="M174" s="66"/>
       <c r="N174" s="66" t="s">
@@ -30325,10 +30763,10 @@
     </row>
     <row r="175" spans="1:20" ht="90" customHeight="1">
       <c r="A175" s="69" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="B175" s="69" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="C175" s="69" t="s">
         <v>95</v>
@@ -30340,10 +30778,10 @@
         <v>1250</v>
       </c>
       <c r="F175" s="79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G175" s="79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H175" s="78">
         <f t="shared" si="15"/>
@@ -30355,14 +30793,14 @@
       </c>
       <c r="J175" s="78">
         <f t="shared" si="16"/>
-        <v>2094.75</v>
+        <v>3491.25</v>
       </c>
       <c r="K175" s="78">
         <f t="shared" si="17"/>
-        <v>4887.75</v>
+        <v>3491.25</v>
       </c>
       <c r="L175" s="69" t="s">
-        <v>931</v>
+        <v>963</v>
       </c>
       <c r="M175" s="69"/>
       <c r="N175" s="69" t="s">
@@ -30370,7 +30808,7 @@
       </c>
       <c r="O175" s="69"/>
       <c r="P175" s="69" t="s">
-        <v>934</v>
+        <v>964</v>
       </c>
       <c r="Q175" s="69"/>
       <c r="R175" s="69"/>
@@ -30379,10 +30817,10 @@
     </row>
     <row r="176" spans="1:20" ht="24" customHeight="1">
       <c r="A176" s="66" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="B176" s="66" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="C176" s="66" t="s">
         <v>95</v>
@@ -30416,7 +30854,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="66" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="M176" s="66"/>
       <c r="N176" s="66" t="s">
@@ -30431,10 +30869,10 @@
     </row>
     <row r="177" spans="1:20" ht="34" customHeight="1">
       <c r="A177" s="69" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="B177" s="69" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="C177" s="69" t="s">
         <v>95</v>
@@ -30468,7 +30906,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="69" t="s">
-        <v>924</v>
+        <v>917</v>
       </c>
       <c r="M177" s="69"/>
       <c r="N177" s="69" t="s">
@@ -30476,7 +30914,7 @@
       </c>
       <c r="O177" s="69"/>
       <c r="P177" s="69" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="Q177" s="69"/>
       <c r="R177" s="69"/>
@@ -30485,10 +30923,10 @@
     </row>
     <row r="178" spans="1:20" ht="15" customHeight="1">
       <c r="A178" s="66" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="B178" s="66" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="C178" s="66" t="s">
         <v>95</v>
@@ -30522,7 +30960,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="66" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
       <c r="M178" s="66"/>
       <c r="N178" s="66" t="s">
@@ -30530,7 +30968,7 @@
       </c>
       <c r="O178" s="66"/>
       <c r="P178" s="66" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="Q178" s="66"/>
       <c r="R178" s="66"/>
@@ -30539,10 +30977,10 @@
     </row>
     <row r="179" spans="1:20" ht="30" customHeight="1">
       <c r="A179" s="69" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="B179" s="69" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="C179" s="69" t="s">
         <v>95</v>
@@ -30576,7 +31014,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="69" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="M179" s="69"/>
       <c r="N179" s="69" t="s">
@@ -30584,7 +31022,7 @@
       </c>
       <c r="O179" s="69"/>
       <c r="P179" s="69" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="Q179" s="69"/>
       <c r="R179" s="69"/>
@@ -30593,10 +31031,10 @@
     </row>
     <row r="180" spans="1:20" ht="34" customHeight="1">
       <c r="A180" s="66" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="B180" s="66" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="C180" s="66" t="s">
         <v>95</v>
@@ -30630,7 +31068,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="66" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="M180" s="66"/>
       <c r="N180" s="66" t="s">
@@ -30645,10 +31083,10 @@
     </row>
     <row r="181" spans="1:20" ht="15" customHeight="1">
       <c r="A181" s="69" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="B181" s="69" t="s">
-        <v>967</v>
+        <v>956</v>
       </c>
       <c r="C181" s="69" t="s">
         <v>96</v>
@@ -30684,13 +31122,13 @@
       <c r="L181" s="69"/>
       <c r="M181" s="69"/>
       <c r="N181" s="69" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O181" s="69" t="s">
-        <v>966</v>
+        <v>955</v>
       </c>
       <c r="P181" s="69" t="s">
-        <v>970</v>
+        <v>959</v>
       </c>
       <c r="Q181" s="69"/>
       <c r="R181" s="69"/>
@@ -30699,10 +31137,10 @@
     </row>
     <row r="182" spans="1:20" ht="15" customHeight="1">
       <c r="A182" s="66" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="B182" s="66" t="s">
-        <v>968</v>
+        <v>957</v>
       </c>
       <c r="C182" s="66" t="s">
         <v>95</v>
@@ -30738,11 +31176,11 @@
       <c r="L182" s="66"/>
       <c r="M182" s="66"/>
       <c r="N182" s="66" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O182" s="66"/>
       <c r="P182" s="66" t="s">
-        <v>969</v>
+        <v>958</v>
       </c>
       <c r="Q182" s="66"/>
       <c r="R182" s="66"/>
@@ -30751,21 +31189,46 @@
     </row>
     <row r="183" spans="1:20" ht="15" customHeight="1">
       <c r="A183" s="69" t="s">
-        <v>883</v>
-      </c>
-      <c r="B183" s="69"/>
-      <c r="C183" s="69"/>
-      <c r="D183" s="70"/>
-      <c r="E183" s="70"/>
-      <c r="F183" s="79"/>
-      <c r="G183" s="79"/>
-      <c r="H183" s="78"/>
-      <c r="I183" s="78"/>
-      <c r="J183" s="78"/>
-      <c r="K183" s="78"/>
+        <v>876</v>
+      </c>
+      <c r="B183" s="69" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C183" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="D183" s="70">
+        <v>419</v>
+      </c>
+      <c r="E183" s="70">
+        <v>699</v>
+      </c>
+      <c r="F183" s="79">
+        <v>0</v>
+      </c>
+      <c r="G183" s="79">
+        <v>8</v>
+      </c>
+      <c r="H183" s="78">
+        <v>0</v>
+      </c>
+      <c r="I183" s="78">
+        <f>IF(D183&lt;&gt;"",D183,IFERROR(E183/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>419</v>
+      </c>
+      <c r="J183" s="78">
+        <f t="shared" ref="J183:J226" si="21">F183*I183</f>
+        <v>0</v>
+      </c>
+      <c r="K183" s="78">
+        <f t="shared" ref="K183:K226" si="22">IF(LEN(G183)=0,0,G183)*I183</f>
+        <v>3352</v>
+      </c>
       <c r="L183" s="69"/>
       <c r="M183" s="69"/>
-      <c r="N183" s="69"/>
+      <c r="N183" s="69" t="s">
+        <v>598</v>
+      </c>
       <c r="O183" s="69"/>
       <c r="P183" s="69"/>
       <c r="Q183" s="69"/>
@@ -30775,21 +31238,49 @@
     </row>
     <row r="184" spans="1:20" ht="15" customHeight="1">
       <c r="A184" s="66" t="s">
-        <v>884</v>
-      </c>
-      <c r="B184" s="66"/>
-      <c r="C184" s="66"/>
-      <c r="D184" s="67"/>
-      <c r="E184" s="67"/>
-      <c r="F184" s="81"/>
-      <c r="G184" s="81"/>
-      <c r="H184" s="80"/>
-      <c r="I184" s="80"/>
-      <c r="J184" s="80"/>
-      <c r="K184" s="80"/>
-      <c r="L184" s="66"/>
+        <v>877</v>
+      </c>
+      <c r="B184" s="66" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C184" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D184" s="67">
+        <v>891</v>
+      </c>
+      <c r="E184" s="67">
+        <v>1380</v>
+      </c>
+      <c r="F184" s="81">
+        <v>6</v>
+      </c>
+      <c r="G184" s="81">
+        <v>14</v>
+      </c>
+      <c r="H184" s="80">
+        <f t="shared" ref="H184:H226" si="23">F184+IF(LEN(G184)=0,0,G184)</f>
+        <v>20</v>
+      </c>
+      <c r="I184" s="80">
+        <f>IF(D184&lt;&gt;"",D184,IFERROR(E184/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>891</v>
+      </c>
+      <c r="J184" s="80">
+        <f t="shared" si="21"/>
+        <v>5346</v>
+      </c>
+      <c r="K184" s="80">
+        <f t="shared" si="22"/>
+        <v>12474</v>
+      </c>
+      <c r="L184" s="66" t="s">
+        <v>1024</v>
+      </c>
       <c r="M184" s="66"/>
-      <c r="N184" s="66"/>
+      <c r="N184" s="66" t="s">
+        <v>510</v>
+      </c>
       <c r="O184" s="66"/>
       <c r="P184" s="66"/>
       <c r="Q184" s="66"/>
@@ -30799,21 +31290,49 @@
     </row>
     <row r="185" spans="1:20" ht="15" customHeight="1">
       <c r="A185" s="69" t="s">
-        <v>885</v>
-      </c>
-      <c r="B185" s="69"/>
-      <c r="C185" s="69"/>
-      <c r="D185" s="70"/>
-      <c r="E185" s="70"/>
-      <c r="F185" s="79"/>
-      <c r="G185" s="79"/>
-      <c r="H185" s="78"/>
-      <c r="I185" s="78"/>
-      <c r="J185" s="78"/>
-      <c r="K185" s="78"/>
-      <c r="L185" s="69"/>
+        <v>878</v>
+      </c>
+      <c r="B185" s="69" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C185" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="D185" s="70">
+        <v>891</v>
+      </c>
+      <c r="E185" s="70">
+        <v>1380</v>
+      </c>
+      <c r="F185" s="79">
+        <v>4</v>
+      </c>
+      <c r="G185" s="79">
+        <v>1</v>
+      </c>
+      <c r="H185" s="78">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="I185" s="78">
+        <f>IF(D185&lt;&gt;"",D185,IFERROR(E185/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>891</v>
+      </c>
+      <c r="J185" s="78">
+        <f t="shared" si="21"/>
+        <v>3564</v>
+      </c>
+      <c r="K185" s="78">
+        <f t="shared" si="22"/>
+        <v>891</v>
+      </c>
+      <c r="L185" s="69" t="s">
+        <v>1023</v>
+      </c>
       <c r="M185" s="69"/>
-      <c r="N185" s="69"/>
+      <c r="N185" s="69" t="s">
+        <v>510</v>
+      </c>
       <c r="O185" s="69"/>
       <c r="P185" s="69"/>
       <c r="Q185" s="69"/>
@@ -30823,21 +31342,47 @@
     </row>
     <row r="186" spans="1:20" ht="15" customHeight="1">
       <c r="A186" s="66" t="s">
-        <v>886</v>
-      </c>
-      <c r="B186" s="66"/>
-      <c r="C186" s="66"/>
-      <c r="D186" s="67"/>
-      <c r="E186" s="67"/>
-      <c r="F186" s="81"/>
-      <c r="G186" s="81"/>
-      <c r="H186" s="80"/>
-      <c r="I186" s="80"/>
-      <c r="J186" s="80"/>
-      <c r="K186" s="80"/>
+        <v>879</v>
+      </c>
+      <c r="B186" s="66" t="s">
+        <v>713</v>
+      </c>
+      <c r="C186" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D186" s="67">
+        <v>891</v>
+      </c>
+      <c r="E186" s="67">
+        <v>1380</v>
+      </c>
+      <c r="F186" s="81">
+        <v>0</v>
+      </c>
+      <c r="G186" s="81">
+        <v>2</v>
+      </c>
+      <c r="H186" s="80">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="I186" s="80">
+        <f>IF(D186&lt;&gt;"",D186,IFERROR(E186/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>891</v>
+      </c>
+      <c r="J186" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K186" s="80">
+        <f t="shared" si="22"/>
+        <v>1782</v>
+      </c>
       <c r="L186" s="66"/>
       <c r="M186" s="66"/>
-      <c r="N186" s="66"/>
+      <c r="N186" s="66" t="s">
+        <v>598</v>
+      </c>
       <c r="O186" s="66"/>
       <c r="P186" s="66"/>
       <c r="Q186" s="66"/>
@@ -30847,21 +31392,47 @@
     </row>
     <row r="187" spans="1:20" ht="15" customHeight="1">
       <c r="A187" s="69" t="s">
-        <v>887</v>
-      </c>
-      <c r="B187" s="69"/>
-      <c r="C187" s="69"/>
-      <c r="D187" s="70"/>
-      <c r="E187" s="70"/>
-      <c r="F187" s="79"/>
-      <c r="G187" s="79"/>
-      <c r="H187" s="78"/>
-      <c r="I187" s="78"/>
-      <c r="J187" s="78"/>
-      <c r="K187" s="78"/>
+        <v>880</v>
+      </c>
+      <c r="B187" s="69" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C187" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="D187" s="70">
+        <v>891</v>
+      </c>
+      <c r="E187" s="70">
+        <v>1380</v>
+      </c>
+      <c r="F187" s="79">
+        <v>0</v>
+      </c>
+      <c r="G187" s="79">
+        <v>2</v>
+      </c>
+      <c r="H187" s="78">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="I187" s="78">
+        <f>IF(D187&lt;&gt;"",D187,IFERROR(E187/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>891</v>
+      </c>
+      <c r="J187" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K187" s="78">
+        <f t="shared" si="22"/>
+        <v>1782</v>
+      </c>
       <c r="L187" s="69"/>
       <c r="M187" s="69"/>
-      <c r="N187" s="69"/>
+      <c r="N187" s="69" t="s">
+        <v>598</v>
+      </c>
       <c r="O187" s="69"/>
       <c r="P187" s="69"/>
       <c r="Q187" s="69"/>
@@ -30871,21 +31442,47 @@
     </row>
     <row r="188" spans="1:20" ht="15" customHeight="1">
       <c r="A188" s="66" t="s">
-        <v>888</v>
-      </c>
-      <c r="B188" s="66"/>
-      <c r="C188" s="66"/>
-      <c r="D188" s="67"/>
-      <c r="E188" s="67"/>
-      <c r="F188" s="81"/>
-      <c r="G188" s="81"/>
-      <c r="H188" s="80"/>
-      <c r="I188" s="80"/>
-      <c r="J188" s="80"/>
-      <c r="K188" s="80"/>
+        <v>881</v>
+      </c>
+      <c r="B188" s="66" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C188" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D188" s="67">
+        <v>891</v>
+      </c>
+      <c r="E188" s="67">
+        <v>1380</v>
+      </c>
+      <c r="F188" s="81">
+        <v>0</v>
+      </c>
+      <c r="G188" s="81">
+        <v>2</v>
+      </c>
+      <c r="H188" s="80">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="I188" s="80">
+        <f>IF(D188&lt;&gt;"",D188,IFERROR(E188/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>891</v>
+      </c>
+      <c r="J188" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K188" s="80">
+        <f t="shared" si="22"/>
+        <v>1782</v>
+      </c>
       <c r="L188" s="66"/>
       <c r="M188" s="66"/>
-      <c r="N188" s="66"/>
+      <c r="N188" s="66" t="s">
+        <v>598</v>
+      </c>
       <c r="O188" s="66"/>
       <c r="P188" s="66"/>
       <c r="Q188" s="66"/>
@@ -30893,229 +31490,1463 @@
       <c r="S188" s="66"/>
       <c r="T188" s="66"/>
     </row>
-    <row r="189" spans="1:20">
-      <c r="A189" s="69"/>
-      <c r="B189" s="69"/>
-      <c r="C189" s="69"/>
-      <c r="D189" s="70"/>
-      <c r="E189" s="70"/>
-      <c r="F189" s="79"/>
-      <c r="G189" s="79"/>
-      <c r="H189" s="78"/>
-      <c r="I189" s="78"/>
-      <c r="J189" s="78"/>
-      <c r="K189" s="78"/>
-      <c r="L189" s="69"/>
+    <row r="189" spans="1:20" ht="45">
+      <c r="A189" s="69" t="s">
+        <v>972</v>
+      </c>
+      <c r="B189" s="66" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C189" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D189" s="67">
+        <v>891</v>
+      </c>
+      <c r="E189" s="67">
+        <v>1380</v>
+      </c>
+      <c r="F189" s="79">
+        <v>1</v>
+      </c>
+      <c r="G189" s="79">
+        <v>7</v>
+      </c>
+      <c r="H189" s="78">
+        <f t="shared" si="23"/>
+        <v>8</v>
+      </c>
+      <c r="I189" s="78">
+        <f>IF(D189&lt;&gt;"",D189,IFERROR(E189/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>891</v>
+      </c>
+      <c r="J189" s="78">
+        <f t="shared" si="21"/>
+        <v>891</v>
+      </c>
+      <c r="K189" s="78">
+        <f t="shared" si="22"/>
+        <v>6237</v>
+      </c>
+      <c r="L189" s="69" t="s">
+        <v>1022</v>
+      </c>
       <c r="M189" s="69"/>
-      <c r="N189" s="69"/>
+      <c r="N189" s="69" t="s">
+        <v>510</v>
+      </c>
       <c r="O189" s="69"/>
-      <c r="P189" s="69"/>
+      <c r="P189" s="69" t="s">
+        <v>1021</v>
+      </c>
       <c r="Q189" s="69"/>
       <c r="R189" s="69"/>
       <c r="S189" s="69"/>
       <c r="T189" s="69"/>
     </row>
-    <row r="190" spans="1:20">
+    <row r="190" spans="1:20" ht="15">
+      <c r="A190" s="66" t="s">
+        <v>973</v>
+      </c>
+      <c r="B190" s="69" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C190" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="D190" s="70">
+        <v>891</v>
+      </c>
+      <c r="E190" s="70">
+        <v>1380</v>
+      </c>
+      <c r="F190" s="81">
+        <v>0</v>
+      </c>
+      <c r="G190" s="81">
+        <v>3</v>
+      </c>
+      <c r="H190" s="80">
+        <f t="shared" si="23"/>
+        <v>3</v>
+      </c>
+      <c r="I190" s="80">
+        <f>IF(D190&lt;&gt;"",D190,IFERROR(E190/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>891</v>
+      </c>
+      <c r="J190" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K190" s="80">
+        <f t="shared" si="22"/>
+        <v>2673</v>
+      </c>
+      <c r="L190" s="66"/>
+      <c r="M190" s="66"/>
+      <c r="N190" s="61" t="s">
+        <v>1019</v>
+      </c>
+      <c r="P190" s="61" t="s">
+        <v>1020</v>
+      </c>
       <c r="S190" s="61"/>
       <c r="T190" s="61"/>
     </row>
-    <row r="191" spans="1:20">
+    <row r="191" spans="1:20" ht="30">
+      <c r="A191" s="69" t="s">
+        <v>974</v>
+      </c>
+      <c r="B191" s="66" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C191" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D191" s="67">
+        <v>773</v>
+      </c>
+      <c r="E191" s="67">
+        <v>1100</v>
+      </c>
+      <c r="F191" s="79">
+        <v>0</v>
+      </c>
+      <c r="G191" s="79">
+        <v>4</v>
+      </c>
+      <c r="H191" s="78">
+        <f t="shared" si="23"/>
+        <v>4</v>
+      </c>
+      <c r="I191" s="78">
+        <f>IF(D191&lt;&gt;"",D191,IFERROR(E191/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>773</v>
+      </c>
+      <c r="J191" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K191" s="78">
+        <f t="shared" si="22"/>
+        <v>3092</v>
+      </c>
+      <c r="L191" s="69"/>
+      <c r="M191" s="69"/>
+      <c r="N191" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="P191" s="61" t="s">
+        <v>1037</v>
+      </c>
       <c r="S191" s="61"/>
       <c r="T191" s="61"/>
     </row>
-    <row r="192" spans="1:20">
+    <row r="192" spans="1:20" ht="15">
+      <c r="A192" s="66" t="s">
+        <v>975</v>
+      </c>
+      <c r="B192" s="69" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C192" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="D192" s="70">
+        <v>808</v>
+      </c>
+      <c r="E192" s="70">
+        <v>1250</v>
+      </c>
+      <c r="F192" s="81">
+        <v>0</v>
+      </c>
+      <c r="G192" s="81">
+        <v>3</v>
+      </c>
+      <c r="H192" s="80">
+        <f t="shared" si="23"/>
+        <v>3</v>
+      </c>
+      <c r="I192" s="80">
+        <f>IF(D192&lt;&gt;"",D192,IFERROR(E192/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>808</v>
+      </c>
+      <c r="J192" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K192" s="80">
+        <f t="shared" si="22"/>
+        <v>2424</v>
+      </c>
+      <c r="L192" s="66"/>
+      <c r="M192" s="66"/>
+      <c r="N192" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="P192" s="61" t="s">
+        <v>1038</v>
+      </c>
       <c r="S192" s="61"/>
       <c r="T192" s="61"/>
     </row>
-    <row r="193" spans="19:20">
+    <row r="193" spans="1:20" ht="15">
+      <c r="A193" s="69" t="s">
+        <v>976</v>
+      </c>
+      <c r="B193" s="66" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C193" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D193" s="67">
+        <v>1024</v>
+      </c>
+      <c r="E193" s="67">
+        <v>1550</v>
+      </c>
+      <c r="F193" s="79">
+        <v>0</v>
+      </c>
+      <c r="G193" s="79">
+        <v>1</v>
+      </c>
+      <c r="H193" s="78">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="I193" s="78">
+        <f>IF(D193&lt;&gt;"",D193,IFERROR(E193/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>1024</v>
+      </c>
+      <c r="J193" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K193" s="78">
+        <f t="shared" si="22"/>
+        <v>1024</v>
+      </c>
+      <c r="L193" s="69"/>
+      <c r="M193" s="69"/>
+      <c r="N193" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="P193" s="61" t="s">
+        <v>1041</v>
+      </c>
       <c r="S193" s="61"/>
       <c r="T193" s="61"/>
     </row>
-    <row r="194" spans="19:20">
+    <row r="194" spans="1:20" ht="15">
+      <c r="A194" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="B194" s="66"/>
+      <c r="C194" s="66"/>
+      <c r="D194" s="67"/>
+      <c r="E194" s="67"/>
+      <c r="F194" s="81">
+        <v>0</v>
+      </c>
+      <c r="G194" s="81">
+        <v>-9</v>
+      </c>
+      <c r="H194" s="80">
+        <f t="shared" si="23"/>
+        <v>-9</v>
+      </c>
+      <c r="I194" s="80">
+        <f>IF(D194&lt;&gt;"",D194,IFERROR(E194/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J194" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K194" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L194" s="66"/>
+      <c r="M194" s="66"/>
       <c r="S194" s="61"/>
       <c r="T194" s="61"/>
     </row>
-    <row r="195" spans="19:20">
+    <row r="195" spans="1:20" ht="15">
+      <c r="A195" s="69" t="s">
+        <v>978</v>
+      </c>
+      <c r="B195" s="69"/>
+      <c r="C195" s="69"/>
+      <c r="D195" s="70"/>
+      <c r="E195" s="70"/>
+      <c r="F195" s="79">
+        <v>0</v>
+      </c>
+      <c r="G195" s="79">
+        <v>-10</v>
+      </c>
+      <c r="H195" s="78">
+        <f t="shared" si="23"/>
+        <v>-10</v>
+      </c>
+      <c r="I195" s="78">
+        <f>IF(D195&lt;&gt;"",D195,IFERROR(E195/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J195" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K195" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L195" s="69"/>
+      <c r="M195" s="69"/>
       <c r="S195" s="61"/>
       <c r="T195" s="61"/>
     </row>
-    <row r="196" spans="19:20">
+    <row r="196" spans="1:20" ht="15">
+      <c r="A196" s="66" t="s">
+        <v>979</v>
+      </c>
+      <c r="B196" s="66"/>
+      <c r="C196" s="66"/>
+      <c r="D196" s="67"/>
+      <c r="E196" s="67"/>
+      <c r="F196" s="81">
+        <v>0</v>
+      </c>
+      <c r="G196" s="81">
+        <v>-11</v>
+      </c>
+      <c r="H196" s="80">
+        <f t="shared" si="23"/>
+        <v>-11</v>
+      </c>
+      <c r="I196" s="80">
+        <f>IF(D196&lt;&gt;"",D196,IFERROR(E196/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J196" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K196" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L196" s="66"/>
+      <c r="M196" s="66"/>
       <c r="S196" s="61"/>
       <c r="T196" s="61"/>
     </row>
-    <row r="197" spans="19:20">
+    <row r="197" spans="1:20" ht="15">
+      <c r="A197" s="69" t="s">
+        <v>980</v>
+      </c>
+      <c r="B197" s="69"/>
+      <c r="C197" s="69"/>
+      <c r="D197" s="70"/>
+      <c r="E197" s="70"/>
+      <c r="F197" s="79">
+        <v>0</v>
+      </c>
+      <c r="G197" s="79">
+        <v>-12</v>
+      </c>
+      <c r="H197" s="78">
+        <f t="shared" si="23"/>
+        <v>-12</v>
+      </c>
+      <c r="I197" s="78">
+        <f>IF(D197&lt;&gt;"",D197,IFERROR(E197/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J197" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K197" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L197" s="69"/>
+      <c r="M197" s="69"/>
       <c r="S197" s="61"/>
       <c r="T197" s="61"/>
     </row>
-    <row r="198" spans="19:20">
+    <row r="198" spans="1:20" ht="15">
+      <c r="A198" s="66" t="s">
+        <v>981</v>
+      </c>
+      <c r="B198" s="66"/>
+      <c r="C198" s="66"/>
+      <c r="D198" s="67"/>
+      <c r="E198" s="67"/>
+      <c r="F198" s="81">
+        <v>0</v>
+      </c>
+      <c r="G198" s="81">
+        <v>-13</v>
+      </c>
+      <c r="H198" s="80">
+        <f t="shared" si="23"/>
+        <v>-13</v>
+      </c>
+      <c r="I198" s="80">
+        <f>IF(D198&lt;&gt;"",D198,IFERROR(E198/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J198" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K198" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L198" s="66"/>
+      <c r="M198" s="66"/>
       <c r="S198" s="61"/>
       <c r="T198" s="61"/>
     </row>
-    <row r="199" spans="19:20">
+    <row r="199" spans="1:20" ht="15">
+      <c r="A199" s="69" t="s">
+        <v>982</v>
+      </c>
+      <c r="B199" s="66"/>
+      <c r="C199" s="66"/>
+      <c r="D199" s="67"/>
+      <c r="E199" s="67"/>
+      <c r="F199" s="79">
+        <v>0</v>
+      </c>
+      <c r="G199" s="79">
+        <v>-14</v>
+      </c>
+      <c r="H199" s="78">
+        <f t="shared" si="23"/>
+        <v>-14</v>
+      </c>
+      <c r="I199" s="78">
+        <f>IF(D199&lt;&gt;"",D199,IFERROR(E199/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J199" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K199" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L199" s="69"/>
+      <c r="M199" s="69"/>
       <c r="S199" s="61"/>
       <c r="T199" s="61"/>
     </row>
-    <row r="200" spans="19:20">
+    <row r="200" spans="1:20" ht="15">
+      <c r="A200" s="66" t="s">
+        <v>983</v>
+      </c>
+      <c r="B200" s="69"/>
+      <c r="C200" s="69"/>
+      <c r="D200" s="70"/>
+      <c r="E200" s="70"/>
+      <c r="F200" s="81">
+        <v>0</v>
+      </c>
+      <c r="G200" s="81">
+        <v>-15</v>
+      </c>
+      <c r="H200" s="80">
+        <f t="shared" si="23"/>
+        <v>-15</v>
+      </c>
+      <c r="I200" s="80">
+        <f>IF(D200&lt;&gt;"",D200,IFERROR(E200/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J200" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K200" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L200" s="66"/>
+      <c r="M200" s="66"/>
       <c r="S200" s="61"/>
       <c r="T200" s="61"/>
     </row>
-    <row r="201" spans="19:20">
+    <row r="201" spans="1:20" ht="15">
+      <c r="A201" s="69" t="s">
+        <v>984</v>
+      </c>
+      <c r="B201" s="66"/>
+      <c r="C201" s="66"/>
+      <c r="D201" s="67"/>
+      <c r="E201" s="67"/>
+      <c r="F201" s="79">
+        <v>0</v>
+      </c>
+      <c r="G201" s="79">
+        <v>-16</v>
+      </c>
+      <c r="H201" s="78">
+        <f t="shared" si="23"/>
+        <v>-16</v>
+      </c>
+      <c r="I201" s="78">
+        <f>IF(D201&lt;&gt;"",D201,IFERROR(E201/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J201" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K201" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L201" s="69"/>
+      <c r="M201" s="69"/>
       <c r="S201" s="61"/>
       <c r="T201" s="61"/>
     </row>
-    <row r="202" spans="19:20">
+    <row r="202" spans="1:20" ht="15">
+      <c r="A202" s="66" t="s">
+        <v>985</v>
+      </c>
+      <c r="B202" s="69"/>
+      <c r="C202" s="69"/>
+      <c r="D202" s="70"/>
+      <c r="E202" s="70"/>
+      <c r="F202" s="81">
+        <v>0</v>
+      </c>
+      <c r="G202" s="81">
+        <v>-17</v>
+      </c>
+      <c r="H202" s="80">
+        <f t="shared" si="23"/>
+        <v>-17</v>
+      </c>
+      <c r="I202" s="80">
+        <f>IF(D202&lt;&gt;"",D202,IFERROR(E202/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J202" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K202" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L202" s="66"/>
+      <c r="M202" s="66"/>
       <c r="S202" s="61"/>
       <c r="T202" s="61"/>
     </row>
-    <row r="203" spans="19:20">
+    <row r="203" spans="1:20" ht="15">
+      <c r="A203" s="69" t="s">
+        <v>986</v>
+      </c>
+      <c r="B203" s="66"/>
+      <c r="C203" s="66"/>
+      <c r="D203" s="67"/>
+      <c r="E203" s="67"/>
+      <c r="F203" s="79">
+        <v>0</v>
+      </c>
+      <c r="G203" s="79">
+        <v>-18</v>
+      </c>
+      <c r="H203" s="78">
+        <f t="shared" si="23"/>
+        <v>-18</v>
+      </c>
+      <c r="I203" s="78">
+        <f>IF(D203&lt;&gt;"",D203,IFERROR(E203/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J203" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K203" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L203" s="69"/>
+      <c r="M203" s="69"/>
       <c r="S203" s="61"/>
       <c r="T203" s="61"/>
     </row>
-    <row r="204" spans="19:20">
+    <row r="204" spans="1:20" ht="15">
+      <c r="A204" s="66" t="s">
+        <v>987</v>
+      </c>
+      <c r="B204" s="66"/>
+      <c r="C204" s="66"/>
+      <c r="D204" s="67"/>
+      <c r="E204" s="67"/>
+      <c r="F204" s="81">
+        <v>0</v>
+      </c>
+      <c r="G204" s="81">
+        <v>-19</v>
+      </c>
+      <c r="H204" s="80">
+        <f t="shared" si="23"/>
+        <v>-19</v>
+      </c>
+      <c r="I204" s="80">
+        <f>IF(D204&lt;&gt;"",D204,IFERROR(E204/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J204" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K204" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L204" s="66"/>
+      <c r="M204" s="66"/>
       <c r="S204" s="61"/>
       <c r="T204" s="61"/>
     </row>
-    <row r="205" spans="19:20">
+    <row r="205" spans="1:20" ht="15">
+      <c r="A205" s="69" t="s">
+        <v>988</v>
+      </c>
+      <c r="B205" s="69"/>
+      <c r="C205" s="69"/>
+      <c r="D205" s="70"/>
+      <c r="E205" s="70"/>
+      <c r="F205" s="79">
+        <v>0</v>
+      </c>
+      <c r="G205" s="79">
+        <v>-20</v>
+      </c>
+      <c r="H205" s="78">
+        <f t="shared" si="23"/>
+        <v>-20</v>
+      </c>
+      <c r="I205" s="78">
+        <f>IF(D205&lt;&gt;"",D205,IFERROR(E205/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J205" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K205" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L205" s="69"/>
+      <c r="M205" s="69"/>
       <c r="S205" s="61"/>
       <c r="T205" s="61"/>
     </row>
-    <row r="206" spans="19:20">
+    <row r="206" spans="1:20" ht="15">
+      <c r="A206" s="66" t="s">
+        <v>989</v>
+      </c>
+      <c r="B206" s="66"/>
+      <c r="C206" s="66"/>
+      <c r="D206" s="67"/>
+      <c r="E206" s="67"/>
+      <c r="F206" s="81">
+        <v>0</v>
+      </c>
+      <c r="G206" s="81">
+        <v>-21</v>
+      </c>
+      <c r="H206" s="80">
+        <f t="shared" si="23"/>
+        <v>-21</v>
+      </c>
+      <c r="I206" s="80">
+        <f>IF(D206&lt;&gt;"",D206,IFERROR(E206/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J206" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K206" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L206" s="66"/>
+      <c r="M206" s="66"/>
       <c r="S206" s="61"/>
       <c r="T206" s="61"/>
     </row>
-    <row r="207" spans="19:20">
+    <row r="207" spans="1:20" ht="15">
+      <c r="A207" s="69" t="s">
+        <v>990</v>
+      </c>
+      <c r="B207" s="69"/>
+      <c r="C207" s="69"/>
+      <c r="D207" s="70"/>
+      <c r="E207" s="70"/>
+      <c r="F207" s="79">
+        <v>0</v>
+      </c>
+      <c r="G207" s="79">
+        <v>-22</v>
+      </c>
+      <c r="H207" s="78">
+        <f t="shared" si="23"/>
+        <v>-22</v>
+      </c>
+      <c r="I207" s="78">
+        <f>IF(D207&lt;&gt;"",D207,IFERROR(E207/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J207" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K207" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L207" s="69"/>
+      <c r="M207" s="69"/>
       <c r="S207" s="61"/>
       <c r="T207" s="61"/>
     </row>
-    <row r="208" spans="19:20">
+    <row r="208" spans="1:20" ht="15">
+      <c r="A208" s="66" t="s">
+        <v>991</v>
+      </c>
+      <c r="B208" s="66"/>
+      <c r="C208" s="66"/>
+      <c r="D208" s="67"/>
+      <c r="E208" s="67"/>
+      <c r="F208" s="81">
+        <v>0</v>
+      </c>
+      <c r="G208" s="81">
+        <v>-23</v>
+      </c>
+      <c r="H208" s="80">
+        <f t="shared" si="23"/>
+        <v>-23</v>
+      </c>
+      <c r="I208" s="80">
+        <f>IF(D208&lt;&gt;"",D208,IFERROR(E208/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J208" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K208" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L208" s="66"/>
+      <c r="M208" s="66"/>
       <c r="S208" s="61"/>
       <c r="T208" s="61"/>
     </row>
-    <row r="209" spans="19:20">
+    <row r="209" spans="1:20" ht="15">
+      <c r="A209" s="69" t="s">
+        <v>992</v>
+      </c>
+      <c r="B209" s="66"/>
+      <c r="C209" s="66"/>
+      <c r="D209" s="67"/>
+      <c r="E209" s="67"/>
+      <c r="F209" s="79">
+        <v>0</v>
+      </c>
+      <c r="G209" s="79">
+        <v>-24</v>
+      </c>
+      <c r="H209" s="78">
+        <f t="shared" si="23"/>
+        <v>-24</v>
+      </c>
+      <c r="I209" s="78">
+        <f>IF(D209&lt;&gt;"",D209,IFERROR(E209/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J209" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K209" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L209" s="69"/>
+      <c r="M209" s="69"/>
       <c r="S209" s="61"/>
       <c r="T209" s="61"/>
     </row>
-    <row r="210" spans="19:20">
+    <row r="210" spans="1:20" ht="15">
+      <c r="A210" s="66" t="s">
+        <v>993</v>
+      </c>
+      <c r="B210" s="69"/>
+      <c r="C210" s="69"/>
+      <c r="D210" s="70"/>
+      <c r="E210" s="70"/>
+      <c r="F210" s="81">
+        <v>0</v>
+      </c>
+      <c r="G210" s="81">
+        <v>-25</v>
+      </c>
+      <c r="H210" s="80">
+        <f t="shared" si="23"/>
+        <v>-25</v>
+      </c>
+      <c r="I210" s="80">
+        <f>IF(D210&lt;&gt;"",D210,IFERROR(E210/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J210" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K210" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L210" s="66"/>
+      <c r="M210" s="66"/>
       <c r="S210" s="61"/>
       <c r="T210" s="61"/>
     </row>
-    <row r="211" spans="19:20">
+    <row r="211" spans="1:20" ht="15">
+      <c r="A211" s="69" t="s">
+        <v>994</v>
+      </c>
+      <c r="B211" s="66"/>
+      <c r="C211" s="66"/>
+      <c r="D211" s="67"/>
+      <c r="E211" s="67"/>
+      <c r="F211" s="79">
+        <v>0</v>
+      </c>
+      <c r="G211" s="79">
+        <v>-26</v>
+      </c>
+      <c r="H211" s="78">
+        <f t="shared" si="23"/>
+        <v>-26</v>
+      </c>
+      <c r="I211" s="78">
+        <f>IF(D211&lt;&gt;"",D211,IFERROR(E211/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J211" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K211" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L211" s="69"/>
+      <c r="M211" s="69"/>
       <c r="S211" s="61"/>
       <c r="T211" s="61"/>
     </row>
-    <row r="212" spans="19:20">
+    <row r="212" spans="1:20" ht="15">
+      <c r="A212" s="66" t="s">
+        <v>995</v>
+      </c>
+      <c r="B212" s="69"/>
+      <c r="C212" s="69"/>
+      <c r="D212" s="70"/>
+      <c r="E212" s="70"/>
+      <c r="F212" s="81">
+        <v>0</v>
+      </c>
+      <c r="G212" s="81">
+        <v>-27</v>
+      </c>
+      <c r="H212" s="80">
+        <f t="shared" si="23"/>
+        <v>-27</v>
+      </c>
+      <c r="I212" s="80">
+        <f>IF(D212&lt;&gt;"",D212,IFERROR(E212/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J212" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K212" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L212" s="66"/>
+      <c r="M212" s="66"/>
       <c r="S212" s="61"/>
       <c r="T212" s="61"/>
     </row>
-    <row r="213" spans="19:20">
+    <row r="213" spans="1:20" ht="15">
+      <c r="A213" s="69" t="s">
+        <v>996</v>
+      </c>
+      <c r="B213" s="66"/>
+      <c r="C213" s="66"/>
+      <c r="D213" s="67"/>
+      <c r="E213" s="67"/>
+      <c r="F213" s="79">
+        <v>0</v>
+      </c>
+      <c r="G213" s="79">
+        <v>-28</v>
+      </c>
+      <c r="H213" s="78">
+        <f t="shared" si="23"/>
+        <v>-28</v>
+      </c>
+      <c r="I213" s="78">
+        <f>IF(D213&lt;&gt;"",D213,IFERROR(E213/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J213" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K213" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L213" s="69"/>
+      <c r="M213" s="69"/>
       <c r="S213" s="61"/>
       <c r="T213" s="61"/>
     </row>
-    <row r="214" spans="19:20">
+    <row r="214" spans="1:20" ht="15">
+      <c r="A214" s="66" t="s">
+        <v>997</v>
+      </c>
+      <c r="B214" s="66"/>
+      <c r="C214" s="66"/>
+      <c r="D214" s="67"/>
+      <c r="E214" s="67"/>
+      <c r="F214" s="81">
+        <v>0</v>
+      </c>
+      <c r="G214" s="81">
+        <v>-29</v>
+      </c>
+      <c r="H214" s="80">
+        <f t="shared" si="23"/>
+        <v>-29</v>
+      </c>
+      <c r="I214" s="80">
+        <f>IF(D214&lt;&gt;"",D214,IFERROR(E214/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J214" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K214" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L214" s="66"/>
+      <c r="M214" s="66"/>
       <c r="S214" s="61"/>
       <c r="T214" s="61"/>
     </row>
-    <row r="215" spans="19:20">
+    <row r="215" spans="1:20" ht="15">
+      <c r="A215" s="69" t="s">
+        <v>998</v>
+      </c>
+      <c r="B215" s="69"/>
+      <c r="C215" s="69"/>
+      <c r="D215" s="70"/>
+      <c r="E215" s="70"/>
+      <c r="F215" s="79">
+        <v>0</v>
+      </c>
+      <c r="G215" s="79">
+        <v>-30</v>
+      </c>
+      <c r="H215" s="78">
+        <f t="shared" si="23"/>
+        <v>-30</v>
+      </c>
+      <c r="I215" s="78">
+        <f>IF(D215&lt;&gt;"",D215,IFERROR(E215/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J215" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K215" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L215" s="69"/>
+      <c r="M215" s="69"/>
       <c r="S215" s="61"/>
       <c r="T215" s="61"/>
     </row>
-    <row r="216" spans="19:20">
+    <row r="216" spans="1:20" ht="15">
+      <c r="A216" s="66" t="s">
+        <v>999</v>
+      </c>
+      <c r="B216" s="66"/>
+      <c r="C216" s="66"/>
+      <c r="D216" s="67"/>
+      <c r="E216" s="67"/>
+      <c r="F216" s="81">
+        <v>0</v>
+      </c>
+      <c r="G216" s="81">
+        <v>-31</v>
+      </c>
+      <c r="H216" s="80">
+        <f t="shared" si="23"/>
+        <v>-31</v>
+      </c>
+      <c r="I216" s="80">
+        <f>IF(D216&lt;&gt;"",D216,IFERROR(E216/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J216" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K216" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L216" s="66"/>
+      <c r="M216" s="66"/>
       <c r="S216" s="61"/>
       <c r="T216" s="61"/>
     </row>
-    <row r="217" spans="19:20">
+    <row r="217" spans="1:20" ht="15">
+      <c r="A217" s="69" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B217" s="69"/>
+      <c r="C217" s="69"/>
+      <c r="D217" s="70"/>
+      <c r="E217" s="70"/>
+      <c r="F217" s="79">
+        <v>0</v>
+      </c>
+      <c r="G217" s="79">
+        <v>-32</v>
+      </c>
+      <c r="H217" s="78">
+        <f t="shared" si="23"/>
+        <v>-32</v>
+      </c>
+      <c r="I217" s="78">
+        <f>IF(D217&lt;&gt;"",D217,IFERROR(E217/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J217" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K217" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L217" s="69"/>
+      <c r="M217" s="69"/>
       <c r="S217" s="61"/>
       <c r="T217" s="61"/>
     </row>
-    <row r="218" spans="19:20">
+    <row r="218" spans="1:20" ht="15">
+      <c r="A218" s="66" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B218" s="66"/>
+      <c r="C218" s="66"/>
+      <c r="D218" s="67"/>
+      <c r="E218" s="67"/>
+      <c r="F218" s="81">
+        <v>0</v>
+      </c>
+      <c r="G218" s="81">
+        <v>-33</v>
+      </c>
+      <c r="H218" s="80">
+        <f t="shared" si="23"/>
+        <v>-33</v>
+      </c>
+      <c r="I218" s="80">
+        <f>IF(D218&lt;&gt;"",D218,IFERROR(E218/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J218" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K218" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L218" s="66"/>
+      <c r="M218" s="66"/>
       <c r="S218" s="61"/>
       <c r="T218" s="61"/>
     </row>
-    <row r="219" spans="19:20">
+    <row r="219" spans="1:20" ht="15">
+      <c r="A219" s="69" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B219" s="66"/>
+      <c r="C219" s="66"/>
+      <c r="D219" s="67"/>
+      <c r="E219" s="67"/>
+      <c r="F219" s="79">
+        <v>0</v>
+      </c>
+      <c r="G219" s="79">
+        <v>-34</v>
+      </c>
+      <c r="H219" s="78">
+        <f t="shared" si="23"/>
+        <v>-34</v>
+      </c>
+      <c r="I219" s="78">
+        <f>IF(D219&lt;&gt;"",D219,IFERROR(E219/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J219" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K219" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L219" s="69"/>
+      <c r="M219" s="69"/>
       <c r="S219" s="61"/>
       <c r="T219" s="61"/>
     </row>
-    <row r="220" spans="19:20">
+    <row r="220" spans="1:20" ht="15">
+      <c r="A220" s="66" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B220" s="69"/>
+      <c r="C220" s="69"/>
+      <c r="D220" s="70"/>
+      <c r="E220" s="70"/>
+      <c r="F220" s="81">
+        <v>0</v>
+      </c>
+      <c r="G220" s="81">
+        <v>-35</v>
+      </c>
+      <c r="H220" s="80">
+        <f t="shared" si="23"/>
+        <v>-35</v>
+      </c>
+      <c r="I220" s="80">
+        <f>IF(D220&lt;&gt;"",D220,IFERROR(E220/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J220" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K220" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L220" s="66"/>
+      <c r="M220" s="66"/>
       <c r="S220" s="61"/>
       <c r="T220" s="61"/>
     </row>
-    <row r="221" spans="19:20">
+    <row r="221" spans="1:20" ht="15">
+      <c r="A221" s="69" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B221" s="66"/>
+      <c r="C221" s="66"/>
+      <c r="D221" s="67"/>
+      <c r="E221" s="67"/>
+      <c r="F221" s="79">
+        <v>0</v>
+      </c>
+      <c r="G221" s="79">
+        <v>-36</v>
+      </c>
+      <c r="H221" s="78">
+        <f t="shared" si="23"/>
+        <v>-36</v>
+      </c>
+      <c r="I221" s="78">
+        <f>IF(D221&lt;&gt;"",D221,IFERROR(E221/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J221" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K221" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L221" s="69"/>
+      <c r="M221" s="69"/>
       <c r="S221" s="61"/>
       <c r="T221" s="61"/>
     </row>
-    <row r="222" spans="19:20">
+    <row r="222" spans="1:20" ht="15">
+      <c r="A222" s="66" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B222" s="69"/>
+      <c r="C222" s="69"/>
+      <c r="D222" s="70"/>
+      <c r="E222" s="70"/>
+      <c r="F222" s="81">
+        <v>0</v>
+      </c>
+      <c r="G222" s="81">
+        <v>-37</v>
+      </c>
+      <c r="H222" s="80">
+        <f t="shared" si="23"/>
+        <v>-37</v>
+      </c>
+      <c r="I222" s="80">
+        <f>IF(D222&lt;&gt;"",D222,IFERROR(E222/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J222" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K222" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L222" s="66"/>
+      <c r="M222" s="66"/>
       <c r="S222" s="61"/>
       <c r="T222" s="61"/>
     </row>
-    <row r="223" spans="19:20">
+    <row r="223" spans="1:20" ht="15">
+      <c r="A223" s="69" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B223" s="66"/>
+      <c r="C223" s="66"/>
+      <c r="D223" s="67"/>
+      <c r="E223" s="67"/>
+      <c r="F223" s="79">
+        <v>0</v>
+      </c>
+      <c r="G223" s="79">
+        <v>-38</v>
+      </c>
+      <c r="H223" s="78">
+        <f t="shared" si="23"/>
+        <v>-38</v>
+      </c>
+      <c r="I223" s="78">
+        <f>IF(D223&lt;&gt;"",D223,IFERROR(E223/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J223" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K223" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L223" s="69"/>
+      <c r="M223" s="69"/>
       <c r="S223" s="61"/>
       <c r="T223" s="61"/>
     </row>
-    <row r="224" spans="19:20">
+    <row r="224" spans="1:20" ht="15">
+      <c r="A224" s="66" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B224" s="66"/>
+      <c r="C224" s="66"/>
+      <c r="D224" s="67"/>
+      <c r="E224" s="67"/>
+      <c r="F224" s="81">
+        <v>0</v>
+      </c>
+      <c r="G224" s="81">
+        <v>-39</v>
+      </c>
+      <c r="H224" s="80">
+        <f t="shared" si="23"/>
+        <v>-39</v>
+      </c>
+      <c r="I224" s="80">
+        <f>IF(D224&lt;&gt;"",D224,IFERROR(E224/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J224" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K224" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L224" s="66"/>
+      <c r="M224" s="66"/>
       <c r="S224" s="61"/>
       <c r="T224" s="61"/>
     </row>
-    <row r="225" spans="19:20">
+    <row r="225" spans="1:20" ht="15">
+      <c r="A225" s="69" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B225" s="69"/>
+      <c r="C225" s="69"/>
+      <c r="D225" s="70"/>
+      <c r="E225" s="70"/>
+      <c r="F225" s="79">
+        <v>0</v>
+      </c>
+      <c r="G225" s="79">
+        <v>-40</v>
+      </c>
+      <c r="H225" s="78">
+        <f t="shared" si="23"/>
+        <v>-40</v>
+      </c>
+      <c r="I225" s="78">
+        <f>IF(D225&lt;&gt;"",D225,IFERROR(E225/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J225" s="78">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K225" s="78">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L225" s="69"/>
+      <c r="M225" s="69"/>
       <c r="S225" s="61"/>
       <c r="T225" s="61"/>
     </row>
-    <row r="226" spans="19:20">
+    <row r="226" spans="1:20" ht="15">
+      <c r="A226" s="66" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B226" s="66"/>
+      <c r="C226" s="66"/>
+      <c r="D226" s="67"/>
+      <c r="E226" s="67"/>
+      <c r="F226" s="81">
+        <v>0</v>
+      </c>
+      <c r="G226" s="81">
+        <v>-41</v>
+      </c>
+      <c r="H226" s="80">
+        <f t="shared" si="23"/>
+        <v>-41</v>
+      </c>
+      <c r="I226" s="80">
+        <f>IF(D226&lt;&gt;"",D226,IFERROR(E226/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J226" s="80">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K226" s="80">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L226" s="66"/>
       <c r="S226" s="61"/>
       <c r="T226" s="61"/>
     </row>
-    <row r="227" spans="19:20">
+    <row r="227" spans="1:20">
       <c r="S227" s="61"/>
       <c r="T227" s="61"/>
     </row>
-    <row r="228" spans="19:20">
+    <row r="228" spans="1:20">
       <c r="S228" s="61"/>
       <c r="T228" s="61"/>
     </row>
-    <row r="229" spans="19:20">
+    <row r="229" spans="1:20">
       <c r="S229" s="61"/>
       <c r="T229" s="61"/>
     </row>
-    <row r="230" spans="19:20">
+    <row r="230" spans="1:20">
       <c r="S230" s="61"/>
       <c r="T230" s="61"/>
     </row>
-    <row r="231" spans="19:20">
+    <row r="231" spans="1:20">
       <c r="S231" s="61"/>
       <c r="T231" s="61"/>
     </row>
-    <row r="232" spans="19:20">
+    <row r="232" spans="1:20">
       <c r="S232" s="61"/>
       <c r="T232" s="61"/>
     </row>
-    <row r="233" spans="19:20">
+    <row r="233" spans="1:20">
       <c r="S233" s="61"/>
       <c r="T233" s="61"/>
     </row>
-    <row r="234" spans="19:20">
+    <row r="234" spans="1:20">
       <c r="S234" s="61"/>
       <c r="T234" s="61"/>
     </row>
-    <row r="235" spans="19:20">
+    <row r="235" spans="1:20">
       <c r="S235" s="61"/>
       <c r="T235" s="61"/>
     </row>
-    <row r="236" spans="19:20">
+    <row r="236" spans="1:20">
       <c r="S236" s="61"/>
       <c r="T236" s="61"/>
     </row>
-    <row r="237" spans="19:20">
+    <row r="237" spans="1:20">
       <c r="S237" s="61"/>
       <c r="T237" s="61"/>
     </row>
-    <row r="238" spans="19:20">
+    <row r="238" spans="1:20">
       <c r="S238" s="61"/>
       <c r="T238" s="61"/>
     </row>
-    <row r="239" spans="19:20">
+    <row r="239" spans="1:20">
       <c r="S239" s="61"/>
       <c r="T239" s="61"/>
     </row>
-    <row r="240" spans="19:20">
+    <row r="240" spans="1:20">
       <c r="S240" s="61"/>
       <c r="T240" s="61"/>
     </row>
@@ -34917,6 +36748,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:T188" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
+  <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N988" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Pending,Partially Sold,Sold Out,New,Reserved"</formula1>
@@ -34946,7 +36778,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1">
       <c r="A1" s="95" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="B1" s="95"/>
     </row>
@@ -34955,7 +36787,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1">
@@ -34987,25 +36819,25 @@
         <v>42</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="C7" s="86" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="D7" s="86" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="E7" s="86" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="F7" s="86" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
       <c r="G7" s="86" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="H7" s="86" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1">
@@ -35014,15 +36846,15 @@
       </c>
       <c r="B8" s="9">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A8,Purchases!$C:$C),0)</f>
-        <v>168535</v>
+        <v>212261</v>
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>123157.33333333333</v>
+        <v>151066</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>45377.666666666672</v>
+        <v>61195</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -35030,7 +36862,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>45377.666666666672</v>
+        <v>61195</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -35038,7 +36870,7 @@
       </c>
       <c r="H8" s="88">
         <f>F8-G8</f>
-        <v>27074.326666666671</v>
+        <v>42891.66</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -35047,15 +36879,15 @@
       </c>
       <c r="B9" s="11">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A9,Purchases!$C:$C),0)</f>
-        <v>168337</v>
+        <v>208337</v>
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>123157.33333333333</v>
+        <v>151066</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>45179.666666666672</v>
+        <v>57271</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -35063,7 +36895,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>45179.666666666672</v>
+        <v>57271</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -35071,7 +36903,7 @@
       </c>
       <c r="H9" s="89">
         <f>F9-G9</f>
-        <v>3540.3366666666698</v>
+        <v>15631.669999999998</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -35084,11 +36916,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>123157.33333333333</v>
+        <v>151066</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-90557.333333333328</v>
+        <v>-118466</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -35096,7 +36928,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-90557.333333333328</v>
+        <v>-118466</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -35104,12 +36936,12 @@
       </c>
       <c r="H10" s="88">
         <f>F10-G10</f>
-        <v>-30614.66333333333</v>
+        <v>-58523.33</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="90" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="96" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="B12" s="96"/>
       <c r="C12" s="96"/>
@@ -35122,13 +36954,13 @@
         <v>98</v>
       </c>
       <c r="B13" s="86" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
       <c r="C13" s="86" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="D13" s="86" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="E13" s="86" t="s">
         <v>99</v>
@@ -35142,7 +36974,7 @@
         <v>45952</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>51</v>
@@ -35160,7 +36992,7 @@
         <v>45952</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>51</v>
@@ -35214,7 +37046,7 @@
         <v>45970</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>50</v>
@@ -35232,7 +37064,7 @@
         <v>45970</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>50</v>
@@ -35250,7 +37082,7 @@
         <v>45973</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>50</v>
@@ -35268,7 +37100,7 @@
         <v>45973</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>49</v>
@@ -35286,7 +37118,7 @@
         <v>46058</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>51</v>
@@ -35322,7 +37154,7 @@
         <v>46059</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>49</v>
@@ -35358,7 +37190,7 @@
         <v>46093</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>50</v>
@@ -35376,7 +37208,7 @@
         <v>46093</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>51</v>
@@ -35459,7 +37291,7 @@
     </row>
     <row r="58" spans="2:2" ht="13.5" customHeight="1">
       <c r="B58" s="6" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
     </row>
   </sheetData>
@@ -35489,7 +37321,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13.5" customHeight="1">
       <c r="A1" s="93" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="87" customFormat="1" ht="13.5" customHeight="1">
@@ -35497,22 +37329,22 @@
         <v>42</v>
       </c>
       <c r="B3" s="86" t="s">
-        <v>905</v>
+        <v>898</v>
       </c>
       <c r="C3" s="86" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="D3" s="86" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="E3" s="86" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="F3" s="86" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="G3" s="86" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1">
@@ -35521,7 +37353,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>293292</v>
+        <v>316402</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -35529,11 +37361,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>120172.69639999999</v>
+        <v>127877.5704</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>173119.30360000001</v>
+        <v>188524.4296</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35541,7 +37373,7 @@
       </c>
       <c r="G4" s="88">
         <f>E4+F4</f>
-        <v>35809.277600000001</v>
+        <v>51214.403599999991</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -35558,11 +37390,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>120100.6072</v>
+        <v>127800.85919999999</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-65476.607199999999</v>
+        <v>-73176.859199999992</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35570,7 +37402,7 @@
       </c>
       <c r="G5" s="89">
         <f>E5+F5</f>
-        <v>6110.4348000000027</v>
+        <v>-1589.8171999999904</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -35587,11 +37419,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>120172.69639999999</v>
+        <v>127877.5704</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-107642.69639999999</v>
+        <v>-115347.5704</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35599,7 +37431,7 @@
       </c>
       <c r="G6" s="88">
         <f>E6+F6</f>
-        <v>-41919.712399999975</v>
+        <v>-49624.586399999986</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">
@@ -35609,27 +37441,27 @@
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Chiraath-Summary-Jun26.xlsx
+++ b/docs/Chiraath-Summary-Jun26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614187F4-154F-304F-895A-B1C1FB5AEF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3591599D-D810-B648-9807-8BA52475E30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2596" uniqueCount="1042">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2713" uniqueCount="1095">
   <si>
     <t>Notes:</t>
   </si>
@@ -2949,20 +2949,6 @@
     <t>Bhavana Meenakshi</t>
   </si>
   <si>
-    <t>Shinoob Cousin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sherin - Maroon/navy blue(1099), Lakshmi - Navy Blue &amp; Maroon, Jaimy - Peacok Blue/Maroon, Shinoob Cousin - Lavender/Violet and Purple/Green </t>
-  </si>
-  <si>
-    <t>Peacok Blue/Maroon - 2
-Navy Blue/Maroon - 2
-Grey/Blue - 1</t>
-  </si>
-  <si>
-    <t>Cotton 2-piece set with blue floral prints-M (CHR-156), Short Kurti(CHR-151)-L, Dusty Rose Salwar(CHR-77)-L, Chanderis Silk Saree(Yellow-CHR-119), Matka - Lavender/Violet &amp; Purple/Green (CHR-174)</t>
-  </si>
-  <si>
     <t>Saida (1400), Binija (1560), Shinoob Cousin(1000)</t>
   </si>
   <si>
@@ -2975,222 +2961,395 @@
     <t>Prema(XXL)- 550, Shinoob cousin(M)-850</t>
   </si>
   <si>
+    <t>CHR-188</t>
+  </si>
+  <si>
+    <t>CHR-189</t>
+  </si>
+  <si>
+    <t>CHR-190</t>
+  </si>
+  <si>
+    <t>CHR-191</t>
+  </si>
+  <si>
+    <t>CHR-192</t>
+  </si>
+  <si>
+    <t>CHR-193</t>
+  </si>
+  <si>
+    <t>CHR-194</t>
+  </si>
+  <si>
+    <t>CHR-195</t>
+  </si>
+  <si>
+    <t>CHR-196</t>
+  </si>
+  <si>
+    <t>CHR-197</t>
+  </si>
+  <si>
+    <t>CHR-198</t>
+  </si>
+  <si>
+    <t>CHR-199</t>
+  </si>
+  <si>
+    <t>CHR-200</t>
+  </si>
+  <si>
+    <t>CHR-201</t>
+  </si>
+  <si>
+    <t>CHR-202</t>
+  </si>
+  <si>
+    <t>CHR-203</t>
+  </si>
+  <si>
+    <t>CHR-204</t>
+  </si>
+  <si>
+    <t>CHR-205</t>
+  </si>
+  <si>
+    <t>CHR-206</t>
+  </si>
+  <si>
+    <t>CHR-207</t>
+  </si>
+  <si>
+    <t>CHR-208</t>
+  </si>
+  <si>
+    <t>CHR-209</t>
+  </si>
+  <si>
+    <t>CHR-210</t>
+  </si>
+  <si>
+    <t>CHR-211</t>
+  </si>
+  <si>
+    <t>CHR-212</t>
+  </si>
+  <si>
+    <t>CHR-213</t>
+  </si>
+  <si>
+    <t>CHR-214</t>
+  </si>
+  <si>
+    <t>CHR-215</t>
+  </si>
+  <si>
+    <t>CHR-216</t>
+  </si>
+  <si>
+    <t>CHR-217</t>
+  </si>
+  <si>
+    <t>CHR-218</t>
+  </si>
+  <si>
+    <t>CHR-219</t>
+  </si>
+  <si>
+    <t>CHR-220</t>
+  </si>
+  <si>
+    <t>CHR-221</t>
+  </si>
+  <si>
+    <t>CHR-222</t>
+  </si>
+  <si>
+    <t>CHR-223</t>
+  </si>
+  <si>
+    <t>CHR-224</t>
+  </si>
+  <si>
+    <t>CHR-225</t>
+  </si>
+  <si>
+    <t>Yellow Lotus Saree Line</t>
+  </si>
+  <si>
+    <t>Postal</t>
+  </si>
+  <si>
+    <t>Temple design preordered - Yet to share the item</t>
+  </si>
+  <si>
+    <t>Banarasil Silk (Chikku Maroon)</t>
+  </si>
+  <si>
+    <t>Banarasi Silk (Chikku Green)</t>
+  </si>
+  <si>
+    <t>Banarasi Silk (Golden Yellow Green)</t>
+  </si>
+  <si>
+    <t>Banarasi Silk (Golden Yellow Blue)</t>
+  </si>
+  <si>
+    <t>Banarasi Silk (New Design)</t>
+  </si>
+  <si>
+    <t>Banarasi Silk (Leaf design)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New </t>
+  </si>
+  <si>
+    <t>Light green/dark green, navy/light, violet/green (leaf designs)</t>
+  </si>
+  <si>
+    <t>rust orange/coffee brown, peacock blue/navy, red/green, mustard/blue, chikku maroon, chikku green, golden yellow &amp; green triangle</t>
+  </si>
+  <si>
+    <t>Green/maroon - Rajitha Teacher</t>
+  </si>
+  <si>
+    <t>Rajitha Teacher</t>
+  </si>
+  <si>
+    <t>Green/maroon banarasi new design</t>
+  </si>
+  <si>
+    <t>Sheeba George</t>
+  </si>
+  <si>
+    <t>Soji Thomas</t>
+  </si>
+  <si>
+    <t>Jessy Joseph</t>
+  </si>
+  <si>
+    <t>Preetha</t>
+  </si>
+  <si>
+    <t>Prasanna</t>
+  </si>
+  <si>
+    <t>Philomina Anto</t>
+  </si>
+  <si>
+    <t>Sanam</t>
+  </si>
+  <si>
+    <t>Geetha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silk Sarees </t>
+  </si>
+  <si>
+    <t>Green/maroon border, maroon peacock blue, light green &amp; bottle green, purple &amp; blue</t>
+  </si>
+  <si>
+    <t>Floral green, floral peach, floral lavender</t>
+  </si>
+  <si>
+    <t>Kerala Sarees with Floral design</t>
+  </si>
+  <si>
+    <t>Kerala Saree with small temple design</t>
+  </si>
+  <si>
+    <t>Small temple design</t>
+  </si>
+  <si>
+    <t>Cotton Saree Collections (Jari Check)</t>
+  </si>
+  <si>
+    <t>Light blue/onion peel, brown/dark maroon, black/light green</t>
+  </si>
+  <si>
+    <t>Cotton Saree Collections (Tower Check)</t>
+  </si>
+  <si>
+    <t>Cotton Saree Collections (Body Jergai)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mustard, navy, rani pink, olive green (×2), purple </t>
+  </si>
+  <si>
+    <t>Linen Saree Semi Party Wear Collections</t>
+  </si>
+  <si>
+    <t>Pink, grey, onion peel, blue</t>
+  </si>
+  <si>
+    <t>Kerala Saree Floral Embroidery</t>
+  </si>
+  <si>
+    <t>Floral Embroidery</t>
+  </si>
+  <si>
+    <t>Semi Silk Saree Collections</t>
+  </si>
+  <si>
+    <t>Peach, light blue, pink, light green</t>
+  </si>
+  <si>
+    <t>Tissue Fancy Saree with Butta</t>
+  </si>
+  <si>
+    <t>Navy/blue, green/navy, maroon/grey, red/maroon, dark green/navy</t>
+  </si>
+  <si>
+    <t>Tissue mulmul (soft cotton) blend sarees</t>
+  </si>
+  <si>
+    <t>Tusser Silk Saree Collection</t>
+  </si>
+  <si>
+    <t>Blue, pink, yellow, maroon, deep blue, green</t>
+  </si>
+  <si>
+    <t>Linen Saree</t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>Kalyani Cotton Sarees with check</t>
+  </si>
+  <si>
+    <t>Matka Saree Collections</t>
+  </si>
+  <si>
+    <t>Black/pink, black/orange, violet/bottle green</t>
+  </si>
+  <si>
+    <t>Matka Saree</t>
+  </si>
+  <si>
+    <t>Golden yellow/bottle green</t>
+  </si>
+  <si>
+    <t>Cotton Saree Collection</t>
+  </si>
+  <si>
+    <t>Cotton Saree Collection ( Kabhali Check)</t>
+  </si>
+  <si>
+    <t>Navy/blue, yellow/peacock blue, violet/mustard, turquoise/violet</t>
+  </si>
+  <si>
+    <t>Kerala Saree Collections Check/Floral</t>
+  </si>
+  <si>
+    <t>Checks/floral + leaf, checks/floral + kathakali</t>
+  </si>
+  <si>
+    <t>Cotton Saree with Small and big borders</t>
+  </si>
+  <si>
+    <t>Cotton Lines</t>
+  </si>
+  <si>
+    <t>Maroon/black, violet/red</t>
+  </si>
+  <si>
+    <t>Kerala Saree with lines</t>
+  </si>
+  <si>
+    <t>Jeeja Anil</t>
+  </si>
+  <si>
+    <t>Sumi Boben</t>
+  </si>
+  <si>
+    <t>Jet Black (CHR-119)</t>
+  </si>
+  <si>
+    <t>Jinu Varghese</t>
+  </si>
+  <si>
+    <t>Blue (CHR-119)</t>
+  </si>
+  <si>
+    <t>Smitha S</t>
+  </si>
+  <si>
+    <t>Jayalakshmi, Preetha, Prasanna, Philomina, Smitha S</t>
+  </si>
+  <si>
+    <t>Raji V T</t>
+  </si>
+  <si>
+    <t>Sushama Bhaskar</t>
+  </si>
+  <si>
+    <t>Sanam, Geetha, Unknown, Jessy Joseph, Soji Thomas, Sheeba George, Sushma Bhaskar</t>
+  </si>
+  <si>
+    <t>CHR-194-Light Blue cotton, CHR-206 - green temple/brown</t>
+  </si>
+  <si>
+    <t>Green, pink, navy blue, dark navy, dark maroon, red, orange</t>
+  </si>
+  <si>
+    <t>Denny - Light Blue</t>
+  </si>
+  <si>
+    <t>Grey/black, brown/navy, purple/blue, mustard/blue</t>
+  </si>
+  <si>
+    <t>Denny - green temple/brown</t>
+  </si>
+  <si>
+    <t>Light Majenta - Latha</t>
+  </si>
+  <si>
+    <t>Grey</t>
+  </si>
+  <si>
+    <t>CHR-202 - Yellow Linen(699), CHR-200 - Tissue Mulmul(1250), CHR-206 - Grey/Black &amp; purple/blue</t>
+  </si>
+  <si>
+    <t>Sherin - Maroon/navy blue(1099), Lakshmi - Navy Blue &amp; Maroon, Jaimy - Peacok Blue/Maroon, Shinoob Cousin - Lavender/Violet</t>
+  </si>
+  <si>
+    <t>Peacok Blue/Maroon - 2,
+Navy Blue/Maroon - 2,
+Grey/Blue - 1, Purple/Green - 1</t>
+  </si>
+  <si>
+    <t>red/maroon - Nishitha</t>
+  </si>
+  <si>
+    <t>Nishitha (Shinoob Cousin)</t>
+  </si>
+  <si>
+    <t>Cotton 2-piece set with blue floral prints-M (CHR-156), Short Kurti(CHR-151)-L, Dusty Rose Salwar(CHR-77)-L, Chanderis Silk Saree(Yellow-CHR-119), Matka - Lavender/Violet(CHR-174), red/maroon tissue fancy (CHR-199)</t>
+  </si>
+  <si>
+    <t>Nishitha Friend</t>
+  </si>
+  <si>
+    <t>Blue/maroon, light green/maroon</t>
+  </si>
+  <si>
+    <t>Nishitha Friend - brown/maroon (1100)</t>
+  </si>
+  <si>
+    <t>Orange (CHR-119)</t>
+  </si>
+  <si>
+    <t>First Set: Aruna - violet, Resmi - navy blue, Malini - Rani Pink
+Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black, Bindu Krisharaj - Black, Kavitha - off white, Jisha Suresh - Rani Pink(2), Sudharma - Navy Blue, SIndrella - Maroon, Shaino Benny - Navy blue, Simi Sudhir - Navy Blue, Supriya - Green, Mercy - Black, Kalisari - Green, Latha Suresh - Black, Shinoob cousin - mustard yellow, off white returned, Sumi Boben (Jet black), Jinu (Blue), Raji VT(Black), Nishitha friend (Orange)</t>
+  </si>
+  <si>
     <t xml:space="preserve">
-Blue (2), Maroon (1), Orange (1), Black(3), White(5)</t>
-  </si>
-  <si>
-    <t>First Set: Aruna - violet, Resmi - navy blue, Malini - Rani Pink
-Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black, Bindu Krisharaj - Black, Kavitha - off white, Jisha Suresh - Rani Pink(2), Sudharma - Navy Blue, SIndrella - Maroon, Shaino Benny - Navy blue, Simi Sudhir - Navy Blue, Supriya - Green, Mercy - Black, Kalisari - Green, Latha Suresh - Black, Shinoob cousin - mustard yellow, off white returned</t>
-  </si>
-  <si>
-    <t>CHR-188</t>
-  </si>
-  <si>
-    <t>CHR-189</t>
-  </si>
-  <si>
-    <t>CHR-190</t>
-  </si>
-  <si>
-    <t>CHR-191</t>
-  </si>
-  <si>
-    <t>CHR-192</t>
-  </si>
-  <si>
-    <t>CHR-193</t>
-  </si>
-  <si>
-    <t>CHR-194</t>
-  </si>
-  <si>
-    <t>CHR-195</t>
-  </si>
-  <si>
-    <t>CHR-196</t>
-  </si>
-  <si>
-    <t>CHR-197</t>
-  </si>
-  <si>
-    <t>CHR-198</t>
-  </si>
-  <si>
-    <t>CHR-199</t>
-  </si>
-  <si>
-    <t>CHR-200</t>
-  </si>
-  <si>
-    <t>CHR-201</t>
-  </si>
-  <si>
-    <t>CHR-202</t>
-  </si>
-  <si>
-    <t>CHR-203</t>
-  </si>
-  <si>
-    <t>CHR-204</t>
-  </si>
-  <si>
-    <t>CHR-205</t>
-  </si>
-  <si>
-    <t>CHR-206</t>
-  </si>
-  <si>
-    <t>CHR-207</t>
-  </si>
-  <si>
-    <t>CHR-208</t>
-  </si>
-  <si>
-    <t>CHR-209</t>
-  </si>
-  <si>
-    <t>CHR-210</t>
-  </si>
-  <si>
-    <t>CHR-211</t>
-  </si>
-  <si>
-    <t>CHR-212</t>
-  </si>
-  <si>
-    <t>CHR-213</t>
-  </si>
-  <si>
-    <t>CHR-214</t>
-  </si>
-  <si>
-    <t>CHR-215</t>
-  </si>
-  <si>
-    <t>CHR-216</t>
-  </si>
-  <si>
-    <t>CHR-217</t>
-  </si>
-  <si>
-    <t>CHR-218</t>
-  </si>
-  <si>
-    <t>CHR-219</t>
-  </si>
-  <si>
-    <t>CHR-220</t>
-  </si>
-  <si>
-    <t>CHR-221</t>
-  </si>
-  <si>
-    <t>CHR-222</t>
-  </si>
-  <si>
-    <t>CHR-223</t>
-  </si>
-  <si>
-    <t>CHR-224</t>
-  </si>
-  <si>
-    <t>CHR-225</t>
-  </si>
-  <si>
-    <t>Yellow Lotus Saree Line</t>
-  </si>
-  <si>
-    <t>Postal</t>
-  </si>
-  <si>
-    <t>Temple design preordered - Yet to share the item</t>
-  </si>
-  <si>
-    <t>Banarasil Silk (Chikku Maroon)</t>
-  </si>
-  <si>
-    <t>Banarasi Silk (Chikku Green)</t>
-  </si>
-  <si>
-    <t>Banarasi Silk (Golden Yellow Green)</t>
-  </si>
-  <si>
-    <t>Banarasi Silk (Golden Yellow Blue)</t>
-  </si>
-  <si>
-    <t>Banarasi Silk (New Design)</t>
-  </si>
-  <si>
-    <t>Banarasi Silk (Leaf design)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New </t>
-  </si>
-  <si>
-    <t>Light green/dark green, navy/light, violet/green (leaf designs)</t>
-  </si>
-  <si>
-    <t>rust orange/coffee brown, peacock blue/navy, red/green, mustard/blue, chikku maroon, chikku green, golden yellow &amp; green triangle</t>
-  </si>
-  <si>
-    <t>Green/maroon - Rajitha Teacher</t>
-  </si>
-  <si>
-    <t>Jayalakshmi, Preetha, Prasanna, Philomina</t>
-  </si>
-  <si>
-    <t>Sanam, Geetha, Unknown, Jessy Joseph, Soji Thomas, Sheeba George</t>
-  </si>
-  <si>
-    <t>Rajitha Teacher</t>
-  </si>
-  <si>
-    <t>Green/maroon banarasi new design</t>
-  </si>
-  <si>
-    <t>Sheeba George</t>
-  </si>
-  <si>
-    <t>Soji Thomas</t>
-  </si>
-  <si>
-    <t>Jessy Joseph</t>
-  </si>
-  <si>
-    <t>Preetha</t>
-  </si>
-  <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>Prasanna</t>
-  </si>
-  <si>
-    <t>Philomina Anto</t>
-  </si>
-  <si>
-    <t>Sanam</t>
-  </si>
-  <si>
-    <t>Geetha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silk Sarees </t>
-  </si>
-  <si>
-    <t>Green/maroon border, maroon peacock blue, light green &amp; bottle green, purple &amp; blue</t>
-  </si>
-  <si>
-    <t>Floral green, floral peach, floral lavender</t>
-  </si>
-  <si>
-    <t>Kerala Sarees with Floral design</t>
-  </si>
-  <si>
-    <t>Kerala Saree with small temple design</t>
-  </si>
-  <si>
-    <t>Small temple design</t>
+Maroon (1), Black(2), White(5)</t>
+  </si>
+  <si>
+    <t>brown/maroon (CHR-203: 1100), Rust Orange/Coffee Brown (CHR-188)</t>
   </si>
 </sst>
 </file>
@@ -4109,7 +4268,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>225</c:v>
+                  <c:v>234</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>88</c:v>
@@ -4212,7 +4371,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>106</c:v>
+                  <c:v>155</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>60</c:v>
@@ -4545,7 +4704,7 @@
                   <c:v>63190</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>76679.463333333319</c:v>
+                  <c:v>117167.19666666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1062</c:v>
@@ -5035,7 +5194,7 @@
                   <c:v>54524</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>32953</c:v>
+                  <c:v>47938</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5475,7 +5634,7 @@
                   <c:v>50075</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-65503</c:v>
+                  <c:v>-50518</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5942,10 +6101,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>317</c:v>
+                  <c:v>326</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-656</c:v>
+                  <c:v>-292</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7132,7 +7291,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>383556</v>
+        <v>390893</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -7149,7 +7308,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>388466</v>
+        <v>403451</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -7166,7 +7325,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-69642</v>
+        <v>-62305</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -7378,15 +7537,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>316402</v>
+        <v>323739</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>127877.5704</v>
+        <v>130323.72619999999</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>188524.4296</v>
+        <v>193415.27380000002</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -7394,11 +7553,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>51214.403599999991</v>
+        <v>56105.247800000012</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹51,214</v>
+        <v>Pay ₹56,105</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -7412,11 +7571,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>127800.85919999999</v>
+        <v>130245.54760000001</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-73176.859199999992</v>
+        <v>-75621.547600000005</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -7424,11 +7583,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-1589.8171999999904</v>
+        <v>-4034.5056000000041</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹1,590</v>
+        <v>Receive ₹4,035</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -7442,11 +7601,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>127877.5704</v>
+        <v>130323.72619999999</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-115347.5704</v>
+        <v>-117793.72619999999</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -7454,11 +7613,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-49624.586399999986</v>
+        <v>-52070.742199999979</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹49,625</v>
+        <v>Receive ₹52,071</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -7570,7 +7729,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46194</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -7586,7 +7745,7 @@
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>383556</v>
+        <v>390893</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7595,14 +7754,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-69642</v>
+        <v>-62305</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>132522.66333333333</v>
+        <v>173010.39666666667</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -7654,7 +7813,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>317</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7678,7 +7837,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>-656</v>
+        <v>-292</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7742,11 +7901,11 @@
       </c>
       <c r="C15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>32953</v>
+        <v>47938</v>
       </c>
       <c r="D15" s="27">
         <f t="shared" si="0"/>
-        <v>-65503</v>
+        <v>-50518</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
@@ -7874,11 +8033,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>106</v>
+        <v>155</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -7905,7 +8064,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>76679.463333333319</v>
+        <v>117167.19666666666</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -9180,7 +9339,7 @@
         <v>246</v>
       </c>
       <c r="D84" s="36" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15" customHeight="1">
@@ -16691,7 +16850,7 @@
         <v>46188</v>
       </c>
       <c r="B216" s="53" t="s">
-        <v>962</v>
+        <v>1086</v>
       </c>
       <c r="C216" s="54">
         <v>5000</v>
@@ -16705,7 +16864,7 @@
       <c r="F216" s="56"/>
       <c r="G216" s="56"/>
       <c r="H216" s="57" t="s">
-        <v>965</v>
+        <v>1087</v>
       </c>
       <c r="I216" s="53" t="s">
         <v>142</v>
@@ -16730,7 +16889,7 @@
       <c r="F217" s="49"/>
       <c r="G217" s="49"/>
       <c r="H217" s="51" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="I217" s="49" t="s">
         <v>142</v>
@@ -16741,7 +16900,7 @@
         <v>46191</v>
       </c>
       <c r="B218" s="53" t="s">
-        <v>1025</v>
+        <v>1017</v>
       </c>
       <c r="C218" s="54">
         <v>1380</v>
@@ -16755,7 +16914,7 @@
       <c r="F218" s="56"/>
       <c r="G218" s="56"/>
       <c r="H218" s="57" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="I218" s="53" t="s">
         <v>142</v>
@@ -16766,7 +16925,7 @@
         <v>46191</v>
       </c>
       <c r="B219" s="49" t="s">
-        <v>1027</v>
+        <v>1019</v>
       </c>
       <c r="C219" s="50">
         <v>1380</v>
@@ -16791,7 +16950,7 @@
         <v>46191</v>
       </c>
       <c r="B220" s="53" t="s">
-        <v>1028</v>
+        <v>1020</v>
       </c>
       <c r="C220" s="54">
         <v>1380</v>
@@ -16841,7 +17000,7 @@
         <v>46191</v>
       </c>
       <c r="B222" s="53" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
       <c r="C222" s="54">
         <v>1380</v>
@@ -16866,7 +17025,7 @@
         <v>46191</v>
       </c>
       <c r="B223" s="49" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="C223" s="50">
         <v>1380</v>
@@ -16891,7 +17050,7 @@
         <v>46191</v>
       </c>
       <c r="B224" s="53" t="s">
-        <v>1031</v>
+        <v>1065</v>
       </c>
       <c r="C224" s="54">
         <v>1380</v>
@@ -16916,7 +17075,7 @@
         <v>46192</v>
       </c>
       <c r="B225" s="49" t="s">
-        <v>1032</v>
+        <v>1023</v>
       </c>
       <c r="C225" s="50">
         <v>1380</v>
@@ -16941,7 +17100,7 @@
         <v>46192</v>
       </c>
       <c r="B226" s="53" t="s">
-        <v>1033</v>
+        <v>1024</v>
       </c>
       <c r="C226" s="54">
         <v>1380</v>
@@ -16966,7 +17125,7 @@
         <v>46192</v>
       </c>
       <c r="B227" s="49" t="s">
-        <v>1034</v>
+        <v>1025</v>
       </c>
       <c r="C227" s="50">
         <v>1380</v>
@@ -16991,7 +17150,7 @@
         <v>46192</v>
       </c>
       <c r="B228" s="53" t="s">
-        <v>1035</v>
+        <v>1026</v>
       </c>
       <c r="C228" s="54">
         <v>1380</v>
@@ -17011,104 +17170,218 @@
         <v>142</v>
       </c>
     </row>
-    <row r="229" spans="1:9">
-      <c r="A229" s="48"/>
-      <c r="B229" s="49"/>
-      <c r="C229" s="50"/>
-      <c r="D229" s="49"/>
-      <c r="E229" s="49"/>
+    <row r="229" spans="1:9" ht="14">
+      <c r="A229" s="48">
+        <v>46193</v>
+      </c>
+      <c r="B229" s="49" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C229" s="50">
+        <v>699</v>
+      </c>
+      <c r="D229" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E229" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F229" s="49"/>
       <c r="G229" s="49"/>
-      <c r="H229" s="51"/>
-      <c r="I229" s="49"/>
-    </row>
-    <row r="230" spans="1:9">
-      <c r="A230" s="52"/>
-      <c r="B230" s="53"/>
-      <c r="C230" s="54"/>
-      <c r="D230" s="53"/>
-      <c r="E230" s="53"/>
+      <c r="H229" s="51" t="s">
+        <v>1067</v>
+      </c>
+      <c r="I229" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" ht="14">
+      <c r="A230" s="52">
+        <v>46193</v>
+      </c>
+      <c r="B230" s="53" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C230" s="54">
+        <v>699</v>
+      </c>
+      <c r="D230" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E230" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F230" s="56"/>
       <c r="G230" s="56"/>
-      <c r="H230" s="57"/>
-      <c r="I230" s="53"/>
-    </row>
-    <row r="231" spans="1:9">
-      <c r="A231" s="48"/>
-      <c r="B231" s="49"/>
-      <c r="C231" s="50"/>
-      <c r="D231" s="49"/>
-      <c r="E231" s="49"/>
+      <c r="H230" s="57" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I230" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" ht="14">
+      <c r="A231" s="48">
+        <v>46193</v>
+      </c>
+      <c r="B231" s="49" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C231" s="50">
+        <v>1380</v>
+      </c>
+      <c r="D231" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E231" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F231" s="49"/>
       <c r="G231" s="49"/>
-      <c r="H231" s="51"/>
-      <c r="I231" s="49"/>
-    </row>
-    <row r="232" spans="1:9">
-      <c r="A232" s="52"/>
-      <c r="B232" s="53"/>
-      <c r="C232" s="54"/>
-      <c r="D232" s="53"/>
-      <c r="E232" s="53"/>
+      <c r="H231" s="51" t="s">
+        <v>359</v>
+      </c>
+      <c r="I231" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" ht="14">
+      <c r="A232" s="52">
+        <v>46193</v>
+      </c>
+      <c r="B232" s="53" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C232" s="54">
+        <v>699</v>
+      </c>
+      <c r="D232" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E232" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F232" s="56"/>
       <c r="G232" s="56"/>
-      <c r="H232" s="57"/>
-      <c r="I232" s="53"/>
-    </row>
-    <row r="233" spans="1:9">
-      <c r="A233" s="48"/>
-      <c r="B233" s="49"/>
-      <c r="C233" s="50"/>
-      <c r="D233" s="49"/>
-      <c r="E233" s="49"/>
+      <c r="H232" s="57" t="s">
+        <v>1067</v>
+      </c>
+      <c r="I232" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" ht="14">
+      <c r="A233" s="48">
+        <v>46193</v>
+      </c>
+      <c r="B233" s="49" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C233" s="50">
+        <v>1380</v>
+      </c>
+      <c r="D233" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E233" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F233" s="49"/>
       <c r="G233" s="49"/>
-      <c r="H233" s="51"/>
-      <c r="I233" s="49"/>
-    </row>
-    <row r="234" spans="1:9">
-      <c r="A234" s="52"/>
-      <c r="B234" s="53"/>
-      <c r="C234" s="54"/>
+      <c r="H233" s="51" t="s">
+        <v>358</v>
+      </c>
+      <c r="I233" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" ht="14">
+      <c r="A234" s="52">
+        <v>46193</v>
+      </c>
+      <c r="B234" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="C234" s="54">
+        <v>2500</v>
+      </c>
       <c r="D234" s="53"/>
       <c r="E234" s="53"/>
       <c r="F234" s="56"/>
       <c r="G234" s="56"/>
-      <c r="H234" s="57"/>
-      <c r="I234" s="53"/>
-    </row>
-    <row r="235" spans="1:9">
-      <c r="A235" s="48"/>
-      <c r="B235" s="49"/>
-      <c r="C235" s="50"/>
+      <c r="H234" s="57" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I234" s="53" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" ht="28">
+      <c r="A235" s="48">
+        <v>46193</v>
+      </c>
+      <c r="B235" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="C235" s="50">
+        <v>4449</v>
+      </c>
       <c r="D235" s="49"/>
       <c r="E235" s="49"/>
       <c r="F235" s="49"/>
       <c r="G235" s="49"/>
-      <c r="H235" s="51"/>
-      <c r="I235" s="49"/>
-    </row>
-    <row r="236" spans="1:9">
-      <c r="A236" s="52"/>
-      <c r="B236" s="53"/>
-      <c r="C236" s="54"/>
+      <c r="H235" s="51" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I235" s="49" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" ht="14">
+      <c r="A236" s="52">
+        <v>46194</v>
+      </c>
+      <c r="B236" s="53" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C236" s="54">
+        <v>699</v>
+      </c>
       <c r="D236" s="53"/>
       <c r="E236" s="53"/>
       <c r="F236" s="56"/>
       <c r="G236" s="56"/>
-      <c r="H236" s="57"/>
-      <c r="I236" s="53"/>
-    </row>
-    <row r="237" spans="1:9">
-      <c r="A237" s="48"/>
-      <c r="B237" s="49"/>
-      <c r="C237" s="50"/>
-      <c r="D237" s="49"/>
-      <c r="E237" s="49"/>
+      <c r="H236" s="57" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I236" s="53" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" ht="28">
+      <c r="A237" s="48">
+        <v>46194</v>
+      </c>
+      <c r="B237" s="49" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C237" s="50">
+        <v>2480</v>
+      </c>
+      <c r="D237" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E237" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F237" s="49"/>
       <c r="G237" s="49"/>
-      <c r="H237" s="51"/>
-      <c r="I237" s="49"/>
+      <c r="H237" s="51" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I237" s="49" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="238" spans="1:9">
       <c r="A238" s="52"/>
@@ -24996,7 +25269,7 @@
         <v>1075</v>
       </c>
       <c r="L78" s="66" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="M78" s="66"/>
       <c r="N78" s="66" t="s">
@@ -27187,7 +27460,7 @@
       <c r="S119" s="69"/>
       <c r="T119" s="69"/>
     </row>
-    <row r="120" spans="1:246" ht="158" customHeight="1">
+    <row r="120" spans="1:246" ht="175" customHeight="1">
       <c r="A120" s="66" t="s">
         <v>703</v>
       </c>
@@ -27204,14 +27477,14 @@
         <v>699</v>
       </c>
       <c r="F120" s="67">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G120" s="67">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H120" s="66">
         <f t="shared" si="9"/>
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I120" s="66">
         <f>IF(D120&lt;&gt;"",D120,IFERROR(E120/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -27219,14 +27492,14 @@
       </c>
       <c r="J120" s="66">
         <f t="shared" si="10"/>
-        <v>15082.319999999987</v>
+        <v>15920.226666666653</v>
       </c>
       <c r="K120" s="66">
         <f t="shared" si="11"/>
-        <v>5446.3933333333289</v>
+        <v>3351.6266666666638</v>
       </c>
       <c r="L120" s="66" t="s">
-        <v>971</v>
+        <v>1092</v>
       </c>
       <c r="M120" s="66" t="s">
         <v>49</v>
@@ -27236,7 +27509,7 @@
       </c>
       <c r="O120" s="66"/>
       <c r="P120" s="66" t="s">
-        <v>970</v>
+        <v>1093</v>
       </c>
       <c r="Q120" s="66"/>
       <c r="R120" s="66"/>
@@ -29580,14 +29853,14 @@
         <v>590</v>
       </c>
       <c r="L152" s="66" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="M152" s="66"/>
       <c r="N152" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O152" s="66" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="P152" s="66" t="s">
         <v>792</v>
@@ -29850,7 +30123,7 @@
         <v>1050</v>
       </c>
       <c r="L157" s="69" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="M157" s="69"/>
       <c r="N157" s="69" t="s">
@@ -30778,10 +31051,10 @@
         <v>1250</v>
       </c>
       <c r="F175" s="79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G175" s="79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H175" s="78">
         <f t="shared" si="15"/>
@@ -30793,14 +31066,14 @@
       </c>
       <c r="J175" s="78">
         <f t="shared" si="16"/>
-        <v>3491.25</v>
+        <v>2793</v>
       </c>
       <c r="K175" s="78">
         <f t="shared" si="17"/>
-        <v>3491.25</v>
+        <v>4189.5</v>
       </c>
       <c r="L175" s="69" t="s">
-        <v>963</v>
+        <v>1083</v>
       </c>
       <c r="M175" s="69"/>
       <c r="N175" s="69" t="s">
@@ -30808,7 +31081,7 @@
       </c>
       <c r="O175" s="69"/>
       <c r="P175" s="69" t="s">
-        <v>964</v>
+        <v>1084</v>
       </c>
       <c r="Q175" s="69"/>
       <c r="R175" s="69"/>
@@ -31192,7 +31465,7 @@
         <v>876</v>
       </c>
       <c r="B183" s="69" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="C183" s="69" t="s">
         <v>95</v>
@@ -31241,7 +31514,7 @@
         <v>877</v>
       </c>
       <c r="B184" s="66" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C184" s="66" t="s">
         <v>95</v>
@@ -31253,10 +31526,10 @@
         <v>1380</v>
       </c>
       <c r="F184" s="81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G184" s="81">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H184" s="80">
         <f t="shared" ref="H184:H226" si="23">F184+IF(LEN(G184)=0,0,G184)</f>
@@ -31268,14 +31541,14 @@
       </c>
       <c r="J184" s="80">
         <f t="shared" si="21"/>
-        <v>5346</v>
+        <v>6237</v>
       </c>
       <c r="K184" s="80">
         <f t="shared" si="22"/>
-        <v>12474</v>
+        <v>11583</v>
       </c>
       <c r="L184" s="66" t="s">
-        <v>1024</v>
+        <v>1074</v>
       </c>
       <c r="M184" s="66"/>
       <c r="N184" s="66" t="s">
@@ -31293,7 +31566,7 @@
         <v>878</v>
       </c>
       <c r="B185" s="69" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="C185" s="69" t="s">
         <v>95</v>
@@ -31305,10 +31578,10 @@
         <v>1380</v>
       </c>
       <c r="F185" s="79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G185" s="79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H185" s="78">
         <f t="shared" si="23"/>
@@ -31320,18 +31593,18 @@
       </c>
       <c r="J185" s="78">
         <f t="shared" si="21"/>
-        <v>3564</v>
+        <v>4455</v>
       </c>
       <c r="K185" s="78">
         <f t="shared" si="22"/>
-        <v>891</v>
+        <v>0</v>
       </c>
       <c r="L185" s="69" t="s">
-        <v>1023</v>
+        <v>1071</v>
       </c>
       <c r="M185" s="69"/>
       <c r="N185" s="69" t="s">
-        <v>510</v>
+        <v>425</v>
       </c>
       <c r="O185" s="69"/>
       <c r="P185" s="69"/>
@@ -31395,7 +31668,7 @@
         <v>880</v>
       </c>
       <c r="B187" s="69" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="C187" s="69" t="s">
         <v>95</v>
@@ -31445,7 +31718,7 @@
         <v>881</v>
       </c>
       <c r="B188" s="66" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="C188" s="66" t="s">
         <v>95</v>
@@ -31492,10 +31765,10 @@
     </row>
     <row r="189" spans="1:20" ht="45">
       <c r="A189" s="69" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="B189" s="66" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="C189" s="66" t="s">
         <v>95</v>
@@ -31529,7 +31802,7 @@
         <v>6237</v>
       </c>
       <c r="L189" s="69" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="M189" s="69"/>
       <c r="N189" s="69" t="s">
@@ -31537,7 +31810,7 @@
       </c>
       <c r="O189" s="69"/>
       <c r="P189" s="69" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="Q189" s="69"/>
       <c r="R189" s="69"/>
@@ -31546,10 +31819,10 @@
     </row>
     <row r="190" spans="1:20" ht="15">
       <c r="A190" s="66" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="B190" s="69" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="C190" s="69" t="s">
         <v>95</v>
@@ -31585,20 +31858,20 @@
       <c r="L190" s="66"/>
       <c r="M190" s="66"/>
       <c r="N190" s="61" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="P190" s="61" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="S190" s="61"/>
       <c r="T190" s="61"/>
     </row>
     <row r="191" spans="1:20" ht="30">
       <c r="A191" s="69" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="B191" s="66" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
       <c r="C191" s="66" t="s">
         <v>95</v>
@@ -31637,17 +31910,17 @@
         <v>598</v>
       </c>
       <c r="P191" s="61" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="S191" s="61"/>
       <c r="T191" s="61"/>
     </row>
     <row r="192" spans="1:20" ht="15">
       <c r="A192" s="66" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="B192" s="69" t="s">
-        <v>1039</v>
+        <v>1030</v>
       </c>
       <c r="C192" s="69" t="s">
         <v>95</v>
@@ -31686,17 +31959,17 @@
         <v>598</v>
       </c>
       <c r="P192" s="61" t="s">
-        <v>1038</v>
+        <v>1029</v>
       </c>
       <c r="S192" s="61"/>
       <c r="T192" s="61"/>
     </row>
     <row r="193" spans="1:20" ht="15">
       <c r="A193" s="69" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="B193" s="66" t="s">
-        <v>1040</v>
+        <v>1031</v>
       </c>
       <c r="C193" s="66" t="s">
         <v>95</v>
@@ -31735,32 +32008,40 @@
         <v>598</v>
       </c>
       <c r="P193" s="61" t="s">
-        <v>1041</v>
+        <v>1032</v>
       </c>
       <c r="S193" s="61"/>
       <c r="T193" s="61"/>
     </row>
     <row r="194" spans="1:20" ht="15">
       <c r="A194" s="66" t="s">
-        <v>977</v>
-      </c>
-      <c r="B194" s="66"/>
-      <c r="C194" s="66"/>
-      <c r="D194" s="67"/>
-      <c r="E194" s="67"/>
+        <v>971</v>
+      </c>
+      <c r="B194" s="66" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C194" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D194" s="67">
+        <v>790</v>
+      </c>
+      <c r="E194" s="67">
+        <v>1250</v>
+      </c>
       <c r="F194" s="81">
         <v>0</v>
       </c>
       <c r="G194" s="81">
-        <v>-9</v>
+        <v>3</v>
       </c>
       <c r="H194" s="80">
         <f t="shared" si="23"/>
-        <v>-9</v>
+        <v>3</v>
       </c>
       <c r="I194" s="80">
         <f>IF(D194&lt;&gt;"",D194,IFERROR(E194/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>790</v>
       </c>
       <c r="J194" s="80">
         <f t="shared" si="21"/>
@@ -31768,69 +32049,99 @@
       </c>
       <c r="K194" s="80">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>2370</v>
       </c>
       <c r="L194" s="66"/>
       <c r="M194" s="66"/>
+      <c r="N194" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="P194" s="61" t="s">
+        <v>1034</v>
+      </c>
       <c r="S194" s="61"/>
       <c r="T194" s="61"/>
     </row>
     <row r="195" spans="1:20" ht="15">
       <c r="A195" s="69" t="s">
-        <v>978</v>
-      </c>
-      <c r="B195" s="69"/>
-      <c r="C195" s="69"/>
-      <c r="D195" s="70"/>
-      <c r="E195" s="70"/>
+        <v>972</v>
+      </c>
+      <c r="B195" s="69" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C195" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="D195" s="70">
+        <v>781</v>
+      </c>
+      <c r="E195" s="70">
+        <v>1250</v>
+      </c>
       <c r="F195" s="79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G195" s="79">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="H195" s="78">
         <f t="shared" si="23"/>
-        <v>-10</v>
+        <v>8</v>
       </c>
       <c r="I195" s="78">
         <f>IF(D195&lt;&gt;"",D195,IFERROR(E195/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="J195" s="78">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="K195" s="78">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L195" s="69"/>
+        <v>5467</v>
+      </c>
+      <c r="L195" s="69" t="s">
+        <v>1077</v>
+      </c>
       <c r="M195" s="69"/>
+      <c r="N195" s="61" t="s">
+        <v>510</v>
+      </c>
+      <c r="P195" s="61" t="s">
+        <v>1076</v>
+      </c>
       <c r="S195" s="61"/>
       <c r="T195" s="61"/>
     </row>
     <row r="196" spans="1:20" ht="15">
       <c r="A196" s="66" t="s">
-        <v>979</v>
-      </c>
-      <c r="B196" s="66"/>
-      <c r="C196" s="66"/>
-      <c r="D196" s="67"/>
-      <c r="E196" s="67"/>
+        <v>973</v>
+      </c>
+      <c r="B196" s="66" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C196" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D196" s="67">
+        <v>797</v>
+      </c>
+      <c r="E196" s="67">
+        <v>1250</v>
+      </c>
       <c r="F196" s="81">
         <v>0</v>
       </c>
       <c r="G196" s="81">
-        <v>-11</v>
+        <v>6</v>
       </c>
       <c r="H196" s="80">
         <f t="shared" si="23"/>
-        <v>-11</v>
+        <v>6</v>
       </c>
       <c r="I196" s="80">
         <f>IF(D196&lt;&gt;"",D196,IFERROR(E196/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="J196" s="80">
         <f t="shared" si="21"/>
@@ -31838,34 +32149,48 @@
       </c>
       <c r="K196" s="80">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>4782</v>
       </c>
       <c r="L196" s="66"/>
       <c r="M196" s="66"/>
+      <c r="N196" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="P196" s="61" t="s">
+        <v>1037</v>
+      </c>
       <c r="S196" s="61"/>
       <c r="T196" s="61"/>
     </row>
     <row r="197" spans="1:20" ht="15">
       <c r="A197" s="69" t="s">
-        <v>980</v>
-      </c>
-      <c r="B197" s="69"/>
-      <c r="C197" s="69"/>
-      <c r="D197" s="70"/>
-      <c r="E197" s="70"/>
+        <v>974</v>
+      </c>
+      <c r="B197" s="69" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C197" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="D197" s="70">
+        <v>772</v>
+      </c>
+      <c r="E197" s="70">
+        <v>1250</v>
+      </c>
       <c r="F197" s="79">
         <v>0</v>
       </c>
       <c r="G197" s="79">
-        <v>-12</v>
+        <v>4</v>
       </c>
       <c r="H197" s="78">
         <f t="shared" si="23"/>
-        <v>-12</v>
+        <v>4</v>
       </c>
       <c r="I197" s="78">
         <f>IF(D197&lt;&gt;"",D197,IFERROR(E197/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>772</v>
       </c>
       <c r="J197" s="78">
         <f t="shared" si="21"/>
@@ -31873,34 +32198,48 @@
       </c>
       <c r="K197" s="78">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3088</v>
       </c>
       <c r="L197" s="69"/>
       <c r="M197" s="69"/>
+      <c r="N197" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="P197" s="61" t="s">
+        <v>1039</v>
+      </c>
       <c r="S197" s="61"/>
       <c r="T197" s="61"/>
     </row>
     <row r="198" spans="1:20" ht="15">
       <c r="A198" s="66" t="s">
-        <v>981</v>
-      </c>
-      <c r="B198" s="66"/>
-      <c r="C198" s="66"/>
-      <c r="D198" s="67"/>
-      <c r="E198" s="67"/>
+        <v>975</v>
+      </c>
+      <c r="B198" s="66" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C198" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D198" s="67">
+        <v>772</v>
+      </c>
+      <c r="E198" s="67">
+        <v>1250</v>
+      </c>
       <c r="F198" s="81">
         <v>0</v>
       </c>
       <c r="G198" s="81">
-        <v>-13</v>
+        <v>1</v>
       </c>
       <c r="H198" s="80">
         <f t="shared" si="23"/>
-        <v>-13</v>
+        <v>1</v>
       </c>
       <c r="I198" s="80">
         <f>IF(D198&lt;&gt;"",D198,IFERROR(E198/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>772</v>
       </c>
       <c r="J198" s="80">
         <f t="shared" si="21"/>
@@ -31908,34 +32247,48 @@
       </c>
       <c r="K198" s="80">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>772</v>
       </c>
       <c r="L198" s="66"/>
       <c r="M198" s="66"/>
+      <c r="N198" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="P198" s="61" t="s">
+        <v>1041</v>
+      </c>
       <c r="S198" s="61"/>
       <c r="T198" s="61"/>
     </row>
     <row r="199" spans="1:20" ht="15">
       <c r="A199" s="69" t="s">
-        <v>982</v>
-      </c>
-      <c r="B199" s="66"/>
-      <c r="C199" s="66"/>
-      <c r="D199" s="67"/>
-      <c r="E199" s="67"/>
+        <v>976</v>
+      </c>
+      <c r="B199" s="66" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C199" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D199" s="67">
+        <v>467</v>
+      </c>
+      <c r="E199" s="67">
+        <v>850</v>
+      </c>
       <c r="F199" s="79">
         <v>0</v>
       </c>
       <c r="G199" s="79">
-        <v>-14</v>
+        <v>4</v>
       </c>
       <c r="H199" s="78">
         <f t="shared" si="23"/>
-        <v>-14</v>
+        <v>4</v>
       </c>
       <c r="I199" s="78">
         <f>IF(D199&lt;&gt;"",D199,IFERROR(E199/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="J199" s="78">
         <f t="shared" si="21"/>
@@ -31943,104 +32296,150 @@
       </c>
       <c r="K199" s="78">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1868</v>
       </c>
       <c r="L199" s="69"/>
       <c r="M199" s="69"/>
+      <c r="N199" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="P199" s="61" t="s">
+        <v>1043</v>
+      </c>
       <c r="S199" s="61"/>
       <c r="T199" s="61"/>
     </row>
-    <row r="200" spans="1:20" ht="15">
+    <row r="200" spans="1:20" ht="30">
       <c r="A200" s="66" t="s">
-        <v>983</v>
-      </c>
-      <c r="B200" s="69"/>
-      <c r="C200" s="69"/>
-      <c r="D200" s="70"/>
-      <c r="E200" s="70"/>
+        <v>977</v>
+      </c>
+      <c r="B200" s="69" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C200" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="D200" s="70">
+        <v>866</v>
+      </c>
+      <c r="E200" s="70">
+        <v>1350</v>
+      </c>
       <c r="F200" s="81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G200" s="81">
-        <v>-15</v>
+        <v>4</v>
       </c>
       <c r="H200" s="80">
         <f t="shared" si="23"/>
-        <v>-15</v>
+        <v>5</v>
       </c>
       <c r="I200" s="80">
         <f>IF(D200&lt;&gt;"",D200,IFERROR(E200/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>866</v>
       </c>
       <c r="J200" s="80">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>866</v>
       </c>
       <c r="K200" s="80">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L200" s="66"/>
+        <v>3464</v>
+      </c>
+      <c r="L200" s="66" t="s">
+        <v>1085</v>
+      </c>
       <c r="M200" s="66"/>
+      <c r="N200" s="61" t="s">
+        <v>510</v>
+      </c>
+      <c r="P200" s="61" t="s">
+        <v>1045</v>
+      </c>
       <c r="S200" s="61"/>
       <c r="T200" s="61"/>
     </row>
     <row r="201" spans="1:20" ht="15">
       <c r="A201" s="69" t="s">
-        <v>984</v>
-      </c>
-      <c r="B201" s="66"/>
-      <c r="C201" s="66"/>
-      <c r="D201" s="67"/>
-      <c r="E201" s="67"/>
+        <v>978</v>
+      </c>
+      <c r="B201" s="66" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C201" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D201" s="67">
+        <v>724</v>
+      </c>
+      <c r="E201" s="67">
+        <v>1250</v>
+      </c>
       <c r="F201" s="79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G201" s="79">
-        <v>-16</v>
+        <v>1</v>
       </c>
       <c r="H201" s="78">
         <f t="shared" si="23"/>
-        <v>-16</v>
+        <v>2</v>
       </c>
       <c r="I201" s="78">
         <f>IF(D201&lt;&gt;"",D201,IFERROR(E201/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>724</v>
       </c>
       <c r="J201" s="78">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>724</v>
       </c>
       <c r="K201" s="78">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L201" s="69"/>
+        <v>724</v>
+      </c>
+      <c r="L201" s="69" t="s">
+        <v>1080</v>
+      </c>
       <c r="M201" s="69"/>
+      <c r="N201" s="61" t="s">
+        <v>510</v>
+      </c>
+      <c r="P201" s="61" t="s">
+        <v>1081</v>
+      </c>
       <c r="S201" s="61"/>
       <c r="T201" s="61"/>
     </row>
     <row r="202" spans="1:20" ht="15">
       <c r="A202" s="66" t="s">
-        <v>985</v>
-      </c>
-      <c r="B202" s="69"/>
-      <c r="C202" s="69"/>
-      <c r="D202" s="70"/>
-      <c r="E202" s="70"/>
+        <v>979</v>
+      </c>
+      <c r="B202" s="69" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C202" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="D202" s="70">
+        <v>940</v>
+      </c>
+      <c r="E202" s="70">
+        <v>1500</v>
+      </c>
       <c r="F202" s="81">
         <v>0</v>
       </c>
       <c r="G202" s="81">
-        <v>-17</v>
+        <v>5</v>
       </c>
       <c r="H202" s="80">
         <f t="shared" si="23"/>
-        <v>-17</v>
+        <v>5</v>
       </c>
       <c r="I202" s="80">
         <f>IF(D202&lt;&gt;"",D202,IFERROR(E202/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="J202" s="80">
         <f t="shared" si="21"/>
@@ -32048,104 +32447,150 @@
       </c>
       <c r="K202" s="80">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="L202" s="66"/>
       <c r="M202" s="66"/>
+      <c r="N202" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="P202" s="61" t="s">
+        <v>1048</v>
+      </c>
       <c r="S202" s="61"/>
       <c r="T202" s="61"/>
     </row>
     <row r="203" spans="1:20" ht="15">
       <c r="A203" s="69" t="s">
-        <v>986</v>
-      </c>
-      <c r="B203" s="66"/>
-      <c r="C203" s="66"/>
-      <c r="D203" s="67"/>
-      <c r="E203" s="67"/>
+        <v>980</v>
+      </c>
+      <c r="B203" s="66" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C203" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D203" s="67">
+        <v>488.25</v>
+      </c>
+      <c r="E203" s="67">
+        <v>699</v>
+      </c>
       <c r="F203" s="79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G203" s="79">
-        <v>-18</v>
+        <v>1</v>
       </c>
       <c r="H203" s="78">
         <f t="shared" si="23"/>
-        <v>-18</v>
+        <v>2</v>
       </c>
       <c r="I203" s="78">
         <f>IF(D203&lt;&gt;"",D203,IFERROR(E203/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>488.25</v>
       </c>
       <c r="J203" s="78">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>488.25</v>
       </c>
       <c r="K203" s="78">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L203" s="69"/>
+        <v>488.25</v>
+      </c>
+      <c r="L203" s="69" t="s">
+        <v>147</v>
+      </c>
       <c r="M203" s="69"/>
+      <c r="N203" s="61" t="s">
+        <v>510</v>
+      </c>
+      <c r="P203" s="61" t="s">
+        <v>1050</v>
+      </c>
       <c r="S203" s="61"/>
       <c r="T203" s="61"/>
     </row>
     <row r="204" spans="1:20" ht="15">
       <c r="A204" s="66" t="s">
-        <v>987</v>
-      </c>
-      <c r="B204" s="66"/>
-      <c r="C204" s="66"/>
-      <c r="D204" s="67"/>
-      <c r="E204" s="67"/>
+        <v>981</v>
+      </c>
+      <c r="B204" s="66" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C204" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D204" s="67">
+        <v>880</v>
+      </c>
+      <c r="E204" s="67">
+        <v>1350</v>
+      </c>
       <c r="F204" s="81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G204" s="81">
-        <v>-19</v>
+        <v>2</v>
       </c>
       <c r="H204" s="80">
         <f t="shared" si="23"/>
-        <v>-19</v>
+        <v>3</v>
       </c>
       <c r="I204" s="80">
         <f>IF(D204&lt;&gt;"",D204,IFERROR(E204/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="J204" s="80">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="K204" s="80">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L204" s="66"/>
+        <v>1760</v>
+      </c>
+      <c r="L204" s="66" t="s">
+        <v>1090</v>
+      </c>
       <c r="M204" s="66"/>
+      <c r="N204" s="61" t="s">
+        <v>510</v>
+      </c>
+      <c r="P204" s="61" t="s">
+        <v>1089</v>
+      </c>
       <c r="S204" s="61"/>
       <c r="T204" s="61"/>
     </row>
     <row r="205" spans="1:20" ht="15">
       <c r="A205" s="69" t="s">
-        <v>988</v>
-      </c>
-      <c r="B205" s="69"/>
-      <c r="C205" s="69"/>
-      <c r="D205" s="70"/>
-      <c r="E205" s="70"/>
+        <v>982</v>
+      </c>
+      <c r="B205" s="69" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C205" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="D205" s="70">
+        <v>761</v>
+      </c>
+      <c r="E205" s="70">
+        <v>1250</v>
+      </c>
       <c r="F205" s="79">
         <v>0</v>
       </c>
       <c r="G205" s="79">
-        <v>-20</v>
+        <v>3</v>
       </c>
       <c r="H205" s="78">
         <f t="shared" si="23"/>
-        <v>-20</v>
+        <v>3</v>
       </c>
       <c r="I205" s="78">
         <f>IF(D205&lt;&gt;"",D205,IFERROR(E205/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>761</v>
       </c>
       <c r="J205" s="78">
         <f t="shared" si="21"/>
@@ -32153,34 +32598,48 @@
       </c>
       <c r="K205" s="78">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>2283</v>
       </c>
       <c r="L205" s="69"/>
       <c r="M205" s="69"/>
+      <c r="N205" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="P205" s="61" t="s">
+        <v>1053</v>
+      </c>
       <c r="S205" s="61"/>
       <c r="T205" s="61"/>
     </row>
     <row r="206" spans="1:20" ht="15">
       <c r="A206" s="66" t="s">
-        <v>989</v>
-      </c>
-      <c r="B206" s="66"/>
-      <c r="C206" s="66"/>
-      <c r="D206" s="67"/>
-      <c r="E206" s="67"/>
+        <v>983</v>
+      </c>
+      <c r="B206" s="66" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C206" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D206" s="67">
+        <v>761</v>
+      </c>
+      <c r="E206" s="67">
+        <v>1250</v>
+      </c>
       <c r="F206" s="81">
         <v>0</v>
       </c>
       <c r="G206" s="81">
-        <v>-21</v>
+        <v>1</v>
       </c>
       <c r="H206" s="80">
         <f t="shared" si="23"/>
-        <v>-21</v>
+        <v>1</v>
       </c>
       <c r="I206" s="80">
         <f>IF(D206&lt;&gt;"",D206,IFERROR(E206/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>761</v>
       </c>
       <c r="J206" s="80">
         <f t="shared" si="21"/>
@@ -32188,69 +32647,99 @@
       </c>
       <c r="K206" s="80">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>761</v>
       </c>
       <c r="L206" s="66"/>
       <c r="M206" s="66"/>
+      <c r="N206" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="P206" s="61" t="s">
+        <v>1055</v>
+      </c>
       <c r="S206" s="61"/>
       <c r="T206" s="61"/>
     </row>
     <row r="207" spans="1:20" ht="15">
       <c r="A207" s="69" t="s">
-        <v>990</v>
-      </c>
-      <c r="B207" s="69"/>
-      <c r="C207" s="69"/>
-      <c r="D207" s="70"/>
-      <c r="E207" s="70"/>
+        <v>984</v>
+      </c>
+      <c r="B207" s="69" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C207" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="D207" s="70">
+        <v>828</v>
+      </c>
+      <c r="E207" s="70">
+        <v>1250</v>
+      </c>
       <c r="F207" s="79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G207" s="79">
-        <v>-22</v>
+        <v>4</v>
       </c>
       <c r="H207" s="78">
         <f t="shared" si="23"/>
-        <v>-22</v>
+        <v>5</v>
       </c>
       <c r="I207" s="78">
         <f>IF(D207&lt;&gt;"",D207,IFERROR(E207/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>828</v>
       </c>
       <c r="J207" s="78">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>828</v>
       </c>
       <c r="K207" s="78">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L207" s="69"/>
+        <v>3312</v>
+      </c>
+      <c r="L207" s="69" t="s">
+        <v>1079</v>
+      </c>
       <c r="M207" s="69"/>
+      <c r="N207" s="61" t="s">
+        <v>510</v>
+      </c>
+      <c r="P207" s="61" t="s">
+        <v>1078</v>
+      </c>
       <c r="S207" s="61"/>
       <c r="T207" s="61"/>
     </row>
-    <row r="208" spans="1:20" ht="15">
+    <row r="208" spans="1:20" ht="30">
       <c r="A208" s="66" t="s">
-        <v>991</v>
-      </c>
-      <c r="B208" s="66"/>
-      <c r="C208" s="66"/>
-      <c r="D208" s="67"/>
-      <c r="E208" s="67"/>
+        <v>985</v>
+      </c>
+      <c r="B208" s="66" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C208" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D208" s="67">
+        <v>782</v>
+      </c>
+      <c r="E208" s="67">
+        <v>1250</v>
+      </c>
       <c r="F208" s="81">
         <v>0</v>
       </c>
       <c r="G208" s="81">
-        <v>-23</v>
+        <v>4</v>
       </c>
       <c r="H208" s="80">
         <f t="shared" si="23"/>
-        <v>-23</v>
+        <v>4</v>
       </c>
       <c r="I208" s="80">
         <f>IF(D208&lt;&gt;"",D208,IFERROR(E208/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>782</v>
       </c>
       <c r="J208" s="80">
         <f t="shared" si="21"/>
@@ -32258,34 +32747,48 @@
       </c>
       <c r="K208" s="80">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3128</v>
       </c>
       <c r="L208" s="66"/>
       <c r="M208" s="66"/>
+      <c r="N208" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="P208" s="61" t="s">
+        <v>1058</v>
+      </c>
       <c r="S208" s="61"/>
       <c r="T208" s="61"/>
     </row>
     <row r="209" spans="1:20" ht="15">
       <c r="A209" s="69" t="s">
-        <v>992</v>
-      </c>
-      <c r="B209" s="66"/>
-      <c r="C209" s="66"/>
-      <c r="D209" s="67"/>
-      <c r="E209" s="67"/>
+        <v>986</v>
+      </c>
+      <c r="B209" s="66" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C209" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D209" s="67">
+        <v>982</v>
+      </c>
+      <c r="E209" s="67">
+        <v>1550</v>
+      </c>
       <c r="F209" s="79">
         <v>0</v>
       </c>
       <c r="G209" s="79">
-        <v>-24</v>
+        <v>2</v>
       </c>
       <c r="H209" s="78">
         <f t="shared" si="23"/>
-        <v>-24</v>
+        <v>2</v>
       </c>
       <c r="I209" s="78">
         <f>IF(D209&lt;&gt;"",D209,IFERROR(E209/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="J209" s="78">
         <f t="shared" si="21"/>
@@ -32293,34 +32796,48 @@
       </c>
       <c r="K209" s="78">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1964</v>
       </c>
       <c r="L209" s="69"/>
       <c r="M209" s="69"/>
+      <c r="N209" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="P209" s="61" t="s">
+        <v>1060</v>
+      </c>
       <c r="S209" s="61"/>
       <c r="T209" s="61"/>
     </row>
     <row r="210" spans="1:20" ht="15">
       <c r="A210" s="66" t="s">
-        <v>993</v>
-      </c>
-      <c r="B210" s="69"/>
-      <c r="C210" s="69"/>
-      <c r="D210" s="70"/>
-      <c r="E210" s="70"/>
+        <v>987</v>
+      </c>
+      <c r="B210" s="69" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C210" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="D210" s="70">
+        <v>891</v>
+      </c>
+      <c r="E210" s="70">
+        <v>1350</v>
+      </c>
       <c r="F210" s="81">
         <v>0</v>
       </c>
       <c r="G210" s="81">
-        <v>-25</v>
+        <v>1</v>
       </c>
       <c r="H210" s="80">
         <f t="shared" si="23"/>
-        <v>-25</v>
+        <v>1</v>
       </c>
       <c r="I210" s="80">
         <f>IF(D210&lt;&gt;"",D210,IFERROR(E210/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>891</v>
       </c>
       <c r="J210" s="80">
         <f t="shared" si="21"/>
@@ -32328,34 +32845,48 @@
       </c>
       <c r="K210" s="80">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>891</v>
       </c>
       <c r="L210" s="66"/>
       <c r="M210" s="66"/>
+      <c r="N210" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="P210" s="61" t="s">
+        <v>1062</v>
+      </c>
       <c r="S210" s="61"/>
       <c r="T210" s="61"/>
     </row>
     <row r="211" spans="1:20" ht="15">
       <c r="A211" s="69" t="s">
-        <v>994</v>
-      </c>
-      <c r="B211" s="66"/>
-      <c r="C211" s="66"/>
-      <c r="D211" s="67"/>
-      <c r="E211" s="67"/>
+        <v>988</v>
+      </c>
+      <c r="B211" s="66" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C211" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D211" s="67">
+        <v>922</v>
+      </c>
+      <c r="E211" s="67">
+        <v>1400</v>
+      </c>
       <c r="F211" s="79">
         <v>0</v>
       </c>
       <c r="G211" s="79">
-        <v>-26</v>
+        <v>2</v>
       </c>
       <c r="H211" s="78">
         <f t="shared" si="23"/>
-        <v>-26</v>
+        <v>2</v>
       </c>
       <c r="I211" s="78">
         <f>IF(D211&lt;&gt;"",D211,IFERROR(E211/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="J211" s="78">
         <f t="shared" si="21"/>
@@ -32363,16 +32894,22 @@
       </c>
       <c r="K211" s="78">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="L211" s="69"/>
       <c r="M211" s="69"/>
+      <c r="N211" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="P211" s="61" t="s">
+        <v>1063</v>
+      </c>
       <c r="S211" s="61"/>
       <c r="T211" s="61"/>
     </row>
     <row r="212" spans="1:20" ht="15">
       <c r="A212" s="66" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="B212" s="69"/>
       <c r="C212" s="69"/>
@@ -32407,7 +32944,7 @@
     </row>
     <row r="213" spans="1:20" ht="15">
       <c r="A213" s="69" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="B213" s="66"/>
       <c r="C213" s="66"/>
@@ -32442,7 +32979,7 @@
     </row>
     <row r="214" spans="1:20" ht="15">
       <c r="A214" s="66" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="B214" s="66"/>
       <c r="C214" s="66"/>
@@ -32477,7 +33014,7 @@
     </row>
     <row r="215" spans="1:20" ht="15">
       <c r="A215" s="69" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="B215" s="69"/>
       <c r="C215" s="69"/>
@@ -32512,7 +33049,7 @@
     </row>
     <row r="216" spans="1:20" ht="15">
       <c r="A216" s="66" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="B216" s="66"/>
       <c r="C216" s="66"/>
@@ -32547,7 +33084,7 @@
     </row>
     <row r="217" spans="1:20" ht="15">
       <c r="A217" s="69" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="B217" s="69"/>
       <c r="C217" s="69"/>
@@ -32582,7 +33119,7 @@
     </row>
     <row r="218" spans="1:20" ht="15">
       <c r="A218" s="66" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="B218" s="66"/>
       <c r="C218" s="66"/>
@@ -32617,7 +33154,7 @@
     </row>
     <row r="219" spans="1:20" ht="15">
       <c r="A219" s="69" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="B219" s="66"/>
       <c r="C219" s="66"/>
@@ -32652,7 +33189,7 @@
     </row>
     <row r="220" spans="1:20" ht="15">
       <c r="A220" s="66" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="B220" s="69"/>
       <c r="C220" s="69"/>
@@ -32687,7 +33224,7 @@
     </row>
     <row r="221" spans="1:20" ht="15">
       <c r="A221" s="69" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="B221" s="66"/>
       <c r="C221" s="66"/>
@@ -32722,7 +33259,7 @@
     </row>
     <row r="222" spans="1:20" ht="15">
       <c r="A222" s="66" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="B222" s="69"/>
       <c r="C222" s="69"/>
@@ -32757,7 +33294,7 @@
     </row>
     <row r="223" spans="1:20" ht="15">
       <c r="A223" s="69" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="B223" s="66"/>
       <c r="C223" s="66"/>
@@ -32792,7 +33329,7 @@
     </row>
     <row r="224" spans="1:20" ht="15">
       <c r="A224" s="66" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="B224" s="66"/>
       <c r="C224" s="66"/>
@@ -32827,7 +33364,7 @@
     </row>
     <row r="225" spans="1:20" ht="15">
       <c r="A225" s="69" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="B225" s="69"/>
       <c r="C225" s="69"/>
@@ -32862,7 +33399,7 @@
     </row>
     <row r="226" spans="1:20" ht="15">
       <c r="A226" s="66" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="B226" s="66"/>
       <c r="C226" s="66"/>
@@ -37353,7 +37890,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>316402</v>
+        <v>323739</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -37361,11 +37898,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>127877.5704</v>
+        <v>130323.72619999999</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>188524.4296</v>
+        <v>193415.27380000002</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -37373,7 +37910,7 @@
       </c>
       <c r="G4" s="88">
         <f>E4+F4</f>
-        <v>51214.403599999991</v>
+        <v>56105.247800000012</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -37390,11 +37927,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>127800.85919999999</v>
+        <v>130245.54760000001</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-73176.859199999992</v>
+        <v>-75621.547600000005</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -37402,7 +37939,7 @@
       </c>
       <c r="G5" s="89">
         <f>E5+F5</f>
-        <v>-1589.8171999999904</v>
+        <v>-4034.5056000000041</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -37419,11 +37956,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>127877.5704</v>
+        <v>130323.72619999999</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-115347.5704</v>
+        <v>-117793.72619999999</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -37431,7 +37968,7 @@
       </c>
       <c r="G6" s="88">
         <f>E6+F6</f>
-        <v>-49624.586399999986</v>
+        <v>-52070.742199999979</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">

--- a/docs/Chiraath-Summary-Jun26.xlsx
+++ b/docs/Chiraath-Summary-Jun26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3591599D-D810-B648-9807-8BA52475E30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE98F41-E936-CA46-8B2F-F9D6C20FB277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2713" uniqueCount="1095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2738" uniqueCount="1105">
   <si>
     <t>Notes:</t>
   </si>
@@ -2443,9 +2443,6 @@
     <t>Banarasi (Yellow/Green)</t>
   </si>
   <si>
-    <t>Shinoob (1200)</t>
-  </si>
-  <si>
     <t>Yellow Green</t>
   </si>
   <si>
@@ -3285,9 +3282,6 @@
     <t>Sushama Bhaskar</t>
   </si>
   <si>
-    <t>Sanam, Geetha, Unknown, Jessy Joseph, Soji Thomas, Sheeba George, Sushma Bhaskar</t>
-  </si>
-  <si>
     <t>CHR-194-Light Blue cotton, CHR-206 - green temple/brown</t>
   </si>
   <si>
@@ -3307,9 +3301,6 @@
   </si>
   <si>
     <t>Grey</t>
-  </si>
-  <si>
-    <t>CHR-202 - Yellow Linen(699), CHR-200 - Tissue Mulmul(1250), CHR-206 - Grey/Black &amp; purple/blue</t>
   </si>
   <si>
     <t>Sherin - Maroon/navy blue(1099), Lakshmi - Navy Blue &amp; Maroon, Jaimy - Peacok Blue/Maroon, Shinoob Cousin - Lavender/Violet</t>
@@ -3320,9 +3311,6 @@
 Grey/Blue - 1, Purple/Green - 1</t>
   </si>
   <si>
-    <t>red/maroon - Nishitha</t>
-  </si>
-  <si>
     <t>Nishitha (Shinoob Cousin)</t>
   </si>
   <si>
@@ -3341,15 +3329,57 @@
     <t>Orange (CHR-119)</t>
   </si>
   <si>
+    <t>brown/maroon (CHR-203: 1100), Rust Orange/Coffee Brown (CHR-188)</t>
+  </si>
+  <si>
+    <t>Parcel Charges</t>
+  </si>
+  <si>
+    <t>CHR-202 - Yellow Linen(699), CHR-200 - Tissue Mulmul(1250), CHR-206 - Grey/Black &amp; purple/blue (1000 advace)</t>
+  </si>
+  <si>
+    <t>Nishida Friend</t>
+  </si>
+  <si>
+    <t>CHR-202 Yellow</t>
+  </si>
+  <si>
+    <t>Latha, Nishida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shinoob (1200), Shirley </t>
+  </si>
+  <si>
+    <t>Shirley</t>
+  </si>
+  <si>
+    <t>Karthika</t>
+  </si>
+  <si>
+    <t>Banarasi Yello CHR-152</t>
+  </si>
+  <si>
+    <t>CHR-119 Chanderi Blue</t>
+  </si>
+  <si>
     <t>First Set: Aruna - violet, Resmi - navy blue, Malini - Rani Pink
-Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black, Bindu Krisharaj - Black, Kavitha - off white, Jisha Suresh - Rani Pink(2), Sudharma - Navy Blue, SIndrella - Maroon, Shaino Benny - Navy blue, Simi Sudhir - Navy Blue, Supriya - Green, Mercy - Black, Kalisari - Green, Latha Suresh - Black, Shinoob cousin - mustard yellow, off white returned, Sumi Boben (Jet black), Jinu (Blue), Raji VT(Black), Nishitha friend (Orange)</t>
+Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black, Bindu Krisharaj - Black, Kavitha - off white, Jisha Suresh - Rani Pink(2), Sudharma - Navy Blue, SIndrella - Maroon, Shaino Benny - Navy blue, Simi Sudhir - Navy Blue, Supriya - Green, Mercy - Black, Kalisari - Green, Latha Suresh - Black, Shinoob cousin - mustard yellow, off white returned, Sumi Boben (Jet black), Jinu (Blue), Raji VT(Black), Nishitha friend (Orange), Karthika (Blue)</t>
   </si>
   <si>
     <t xml:space="preserve">
-Maroon (1), Black(2), White(5)</t>
-  </si>
-  <si>
-    <t>brown/maroon (CHR-203: 1100), Rust Orange/Coffee Brown (CHR-188)</t>
+Maroon, Black, White(5)</t>
+  </si>
+  <si>
+    <t>Sanam, Geetha, Unknown, Jessy Joseph, Soji Thomas, Sheeba George, Sushma Bhaskar, Navya</t>
+  </si>
+  <si>
+    <t>Navya - Black Orange</t>
+  </si>
+  <si>
+    <t>Banarasi CM(CHR-183), Black Orange (CHR-204), CHR-199 - Navy/blue &amp; maroon/grey</t>
+  </si>
+  <si>
+    <t>red/maroon - Nishitha, Navy/blue &amp; maroon/grey - Navya</t>
   </si>
 </sst>
 </file>
@@ -4268,7 +4298,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>234</c:v>
+                  <c:v>241</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>88</c:v>
@@ -4371,7 +4401,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>155</c:v>
+                  <c:v>148</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>60</c:v>
@@ -4704,7 +4734,7 @@
                   <c:v>63190</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>117167.19666666666</c:v>
+                  <c:v>111984.49333333333</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1062</c:v>
@@ -5022,7 +5052,7 @@
                   <c:v>47311</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4790</c:v>
+                  <c:v>5152</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>22172</c:v>
@@ -5194,7 +5224,7 @@
                   <c:v>54524</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>47938</c:v>
+                  <c:v>55717</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5622,7 +5652,7 @@
                   <c:v>-1863</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14299</c:v>
+                  <c:v>13937</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>-5924</c:v>
@@ -5634,7 +5664,7 @@
                   <c:v>50075</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-50518</c:v>
+                  <c:v>-42739</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -6101,10 +6131,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>326</c:v>
+                  <c:v>333</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-292</c:v>
+                  <c:v>-299</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7276,7 +7306,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>453198</v>
+        <v>453560</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -7291,7 +7321,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>390893</v>
+        <v>398672</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -7308,7 +7338,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>403451</v>
+        <v>411230</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -7325,7 +7355,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-62305</v>
+        <v>-54888</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -7360,7 +7390,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>42891.66</v>
+        <v>43132.993333333347</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -7370,7 +7400,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>15631.669999999998</v>
+        <v>15511.003333333341</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -7380,7 +7410,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-58523.33</v>
+        <v>-58643.996666666659</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -7419,15 +7449,15 @@
       </c>
       <c r="B18" s="10">
         <f>PartnerShares!B8</f>
-        <v>212261</v>
+        <v>212623</v>
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>151066</v>
+        <v>151186.66666666666</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>61195</v>
+        <v>61436.333333333343</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7435,11 +7465,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>42891.66</v>
+        <v>43132.993333333347</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹42,892</v>
+        <v>Receive ₹43,133</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -7453,11 +7483,11 @@
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>151066</v>
+        <v>151186.66666666666</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>57271</v>
+        <v>57150.333333333343</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7465,11 +7495,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>15631.669999999998</v>
+        <v>15511.003333333341</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹15,632</v>
+        <v>Receive ₹15,511</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -7483,11 +7513,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>151066</v>
+        <v>151186.66666666666</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-118466</v>
+        <v>-118586.66666666666</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7495,11 +7525,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-58523.33</v>
+        <v>-58643.996666666659</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹58,523</v>
+        <v>Pay ₹58,644</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -7537,15 +7567,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>323739</v>
+        <v>331518</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>130323.72619999999</v>
+        <v>132917.24479999999</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>193415.27380000002</v>
+        <v>198600.75520000001</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -7553,11 +7583,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>56105.247800000012</v>
+        <v>61290.729200000002</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹56,105</v>
+        <v>Pay ₹61,291</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -7571,11 +7601,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>130245.54760000001</v>
+        <v>132837.5104</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-75621.547600000005</v>
+        <v>-78213.510399999999</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -7583,11 +7613,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-4034.5056000000041</v>
+        <v>-6626.4683999999979</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹4,035</v>
+        <v>Receive ₹6,626</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -7601,11 +7631,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>130323.72619999999</v>
+        <v>132917.24479999999</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-117793.72619999999</v>
+        <v>-120387.24479999999</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -7613,11 +7643,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-52070.742199999979</v>
+        <v>-54664.260799999975</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹52,071</v>
+        <v>Receive ₹54,664</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -7729,7 +7759,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46194</v>
+        <v>46196</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -7738,14 +7768,14 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>453198</v>
+        <v>453560</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>390893</v>
+        <v>398672</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7754,14 +7784,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-62305</v>
+        <v>-54888</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>173010.39666666667</v>
+        <v>167827.69333333333</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -7813,7 +7843,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7822,7 +7852,7 @@
       </c>
       <c r="B11" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A11)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>4790</v>
+        <v>5152</v>
       </c>
       <c r="C11" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A11)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
@@ -7830,14 +7860,14 @@
       </c>
       <c r="D11" s="27">
         <f t="shared" si="0"/>
-        <v>14299</v>
+        <v>13937</v>
       </c>
       <c r="F11" s="26" t="s">
         <v>82</v>
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>-292</v>
+        <v>-299</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7901,11 +7931,11 @@
       </c>
       <c r="C15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>47938</v>
+        <v>55717</v>
       </c>
       <c r="D15" s="27">
         <f t="shared" si="0"/>
-        <v>-50518</v>
+        <v>-42739</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
@@ -8033,11 +8063,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -8064,7 +8094,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>117167.19666666666</v>
+        <v>111984.49333333333</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -9199,7 +9229,7 @@
         <v>960</v>
       </c>
       <c r="D74" s="36" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15" customHeight="1">
@@ -9227,7 +9257,7 @@
         <v>2900</v>
       </c>
       <c r="D76" s="36" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15" customHeight="1">
@@ -9241,7 +9271,7 @@
         <v>180</v>
       </c>
       <c r="D77" s="39" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15" customHeight="1">
@@ -9255,7 +9285,7 @@
         <v>84</v>
       </c>
       <c r="D78" s="36" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15" customHeight="1">
@@ -9269,7 +9299,7 @@
         <v>208</v>
       </c>
       <c r="D79" s="39" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15" customHeight="1">
@@ -9339,7 +9369,7 @@
         <v>246</v>
       </c>
       <c r="D84" s="36" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15" customHeight="1">
@@ -9357,16 +9387,32 @@
       </c>
     </row>
     <row r="86" spans="1:4" ht="15" customHeight="1">
-      <c r="A86" s="35"/>
-      <c r="B86" s="36"/>
-      <c r="C86" s="37"/>
-      <c r="D86" s="36"/>
+      <c r="A86" s="35">
+        <v>46076</v>
+      </c>
+      <c r="B86" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C86" s="37">
+        <v>300</v>
+      </c>
+      <c r="D86" s="36" t="s">
+        <v>1089</v>
+      </c>
     </row>
     <row r="87" spans="1:4" ht="15" customHeight="1">
-      <c r="A87" s="38"/>
-      <c r="B87" s="39"/>
-      <c r="C87" s="40"/>
-      <c r="D87" s="39"/>
+      <c r="A87" s="38">
+        <v>46076</v>
+      </c>
+      <c r="B87" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C87" s="40">
+        <v>62</v>
+      </c>
+      <c r="D87" s="39" t="s">
+        <v>1089</v>
+      </c>
     </row>
     <row r="88" spans="1:4" ht="15" customHeight="1">
       <c r="A88" s="35"/>
@@ -15195,7 +15241,7 @@
       <c r="F149" s="49"/>
       <c r="G149" s="49"/>
       <c r="H149" s="51" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="I149" s="49" t="s">
         <v>142</v>
@@ -15468,7 +15514,7 @@
       <c r="F160" s="56"/>
       <c r="G160" s="56"/>
       <c r="H160" s="57" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="I160" s="53" t="s">
         <v>142</v>
@@ -15668,7 +15714,7 @@
       <c r="F168" s="49"/>
       <c r="G168" s="49"/>
       <c r="H168" s="51" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="I168" s="49" t="s">
         <v>142</v>
@@ -15968,7 +16014,7 @@
       <c r="F180" s="49"/>
       <c r="G180" s="49"/>
       <c r="H180" s="51" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="I180" s="49" t="s">
         <v>142</v>
@@ -16400,7 +16446,7 @@
         <v>46168</v>
       </c>
       <c r="B198" s="53" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C198" s="54">
         <v>5200</v>
@@ -16414,7 +16460,7 @@
       <c r="F198" s="56"/>
       <c r="G198" s="56"/>
       <c r="H198" s="57" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="I198" s="53" t="s">
         <v>142</v>
@@ -16425,7 +16471,7 @@
         <v>46172</v>
       </c>
       <c r="B199" s="49" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C199" s="50">
         <v>1425</v>
@@ -16439,7 +16485,7 @@
       <c r="F199" s="49"/>
       <c r="G199" s="49"/>
       <c r="H199" s="51" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="I199" s="49" t="s">
         <v>142</v>
@@ -16450,7 +16496,7 @@
         <v>46173</v>
       </c>
       <c r="B200" s="53" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C200" s="54">
         <v>2850</v>
@@ -16464,7 +16510,7 @@
       <c r="F200" s="56"/>
       <c r="G200" s="56"/>
       <c r="H200" s="57" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I200" s="53" t="s">
         <v>142</v>
@@ -16475,7 +16521,7 @@
         <v>46173</v>
       </c>
       <c r="B201" s="49" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C201" s="50">
         <v>3850</v>
@@ -16489,7 +16535,7 @@
       <c r="F201" s="49"/>
       <c r="G201" s="49"/>
       <c r="H201" s="51" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="I201" s="49" t="s">
         <v>142</v>
@@ -16500,7 +16546,7 @@
         <v>46173</v>
       </c>
       <c r="B202" s="53" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C202" s="54">
         <v>930</v>
@@ -16514,7 +16560,7 @@
       <c r="F202" s="56"/>
       <c r="G202" s="56"/>
       <c r="H202" s="57" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="I202" s="53" t="s">
         <v>142</v>
@@ -16525,7 +16571,7 @@
         <v>46173</v>
       </c>
       <c r="B203" s="49" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C203" s="50">
         <v>930</v>
@@ -16539,7 +16585,7 @@
       <c r="F203" s="49"/>
       <c r="G203" s="49"/>
       <c r="H203" s="51" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="I203" s="49" t="s">
         <v>341</v>
@@ -16550,7 +16596,7 @@
         <v>46175</v>
       </c>
       <c r="B204" s="53" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C204" s="54">
         <v>699</v>
@@ -16564,7 +16610,7 @@
       <c r="F204" s="56"/>
       <c r="G204" s="56"/>
       <c r="H204" s="57" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="I204" s="53" t="s">
         <v>142</v>
@@ -16575,7 +16621,7 @@
         <v>46175</v>
       </c>
       <c r="B205" s="49" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C205" s="50">
         <v>700</v>
@@ -16589,7 +16635,7 @@
       <c r="F205" s="49"/>
       <c r="G205" s="49"/>
       <c r="H205" s="51" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I205" s="49" t="s">
         <v>142</v>
@@ -16600,7 +16646,7 @@
         <v>46175</v>
       </c>
       <c r="B206" s="53" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C206" s="54">
         <v>1350</v>
@@ -16614,7 +16660,7 @@
       <c r="F206" s="56"/>
       <c r="G206" s="56"/>
       <c r="H206" s="51" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="I206" s="53" t="s">
         <v>142</v>
@@ -16625,7 +16671,7 @@
         <v>46175</v>
       </c>
       <c r="B207" s="49" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C207" s="50">
         <v>699</v>
@@ -16639,7 +16685,7 @@
       <c r="F207" s="49"/>
       <c r="G207" s="49"/>
       <c r="H207" s="51" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="I207" s="49" t="s">
         <v>142</v>
@@ -16650,7 +16696,7 @@
         <v>46175</v>
       </c>
       <c r="B208" s="53" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C208" s="54">
         <v>699</v>
@@ -16664,7 +16710,7 @@
       <c r="F208" s="56"/>
       <c r="G208" s="56"/>
       <c r="H208" s="57" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="I208" s="53" t="s">
         <v>142</v>
@@ -16675,7 +16721,7 @@
         <v>46176</v>
       </c>
       <c r="B209" s="49" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C209" s="50">
         <v>699</v>
@@ -16689,7 +16735,7 @@
       <c r="F209" s="49"/>
       <c r="G209" s="49"/>
       <c r="H209" s="51" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="I209" s="49" t="s">
         <v>142</v>
@@ -16700,7 +16746,7 @@
         <v>46176</v>
       </c>
       <c r="B210" s="53" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C210" s="54">
         <v>2200</v>
@@ -16714,7 +16760,7 @@
       <c r="F210" s="56"/>
       <c r="G210" s="56"/>
       <c r="H210" s="57" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="I210" s="53" t="s">
         <v>142</v>
@@ -16725,7 +16771,7 @@
         <v>46176</v>
       </c>
       <c r="B211" s="49" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C211" s="50">
         <v>699</v>
@@ -16739,7 +16785,7 @@
       <c r="F211" s="49"/>
       <c r="G211" s="49"/>
       <c r="H211" s="51" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="I211" s="49" t="s">
         <v>142</v>
@@ -16750,7 +16796,7 @@
         <v>46176</v>
       </c>
       <c r="B212" s="53" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C212" s="54">
         <v>699</v>
@@ -16764,7 +16810,7 @@
       <c r="F212" s="56"/>
       <c r="G212" s="56"/>
       <c r="H212" s="56" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="I212" s="53" t="s">
         <v>142</v>
@@ -16775,7 +16821,7 @@
         <v>46176</v>
       </c>
       <c r="B213" s="49" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C213" s="50">
         <v>700</v>
@@ -16789,7 +16835,7 @@
       <c r="F213" s="49"/>
       <c r="G213" s="49"/>
       <c r="H213" s="51" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="I213" s="49" t="s">
         <v>142</v>
@@ -16800,7 +16846,7 @@
         <v>46177</v>
       </c>
       <c r="B214" s="53" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C214" s="54">
         <v>699</v>
@@ -16814,7 +16860,7 @@
       <c r="F214" s="56"/>
       <c r="G214" s="56"/>
       <c r="H214" s="56" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="I214" s="53" t="s">
         <v>142</v>
@@ -16825,7 +16871,7 @@
         <v>46187</v>
       </c>
       <c r="B215" s="49" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C215" s="50">
         <v>1380</v>
@@ -16850,7 +16896,7 @@
         <v>46188</v>
       </c>
       <c r="B216" s="53" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="C216" s="54">
         <v>5000</v>
@@ -16864,7 +16910,7 @@
       <c r="F216" s="56"/>
       <c r="G216" s="56"/>
       <c r="H216" s="57" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="I216" s="53" t="s">
         <v>142</v>
@@ -16889,7 +16935,7 @@
       <c r="F217" s="49"/>
       <c r="G217" s="49"/>
       <c r="H217" s="51" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="I217" s="49" t="s">
         <v>142</v>
@@ -16900,7 +16946,7 @@
         <v>46191</v>
       </c>
       <c r="B218" s="53" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C218" s="54">
         <v>1380</v>
@@ -16914,7 +16960,7 @@
       <c r="F218" s="56"/>
       <c r="G218" s="56"/>
       <c r="H218" s="57" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="I218" s="53" t="s">
         <v>142</v>
@@ -16925,7 +16971,7 @@
         <v>46191</v>
       </c>
       <c r="B219" s="49" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C219" s="50">
         <v>1380</v>
@@ -16950,7 +16996,7 @@
         <v>46191</v>
       </c>
       <c r="B220" s="53" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C220" s="54">
         <v>1380</v>
@@ -17000,7 +17046,7 @@
         <v>46191</v>
       </c>
       <c r="B222" s="53" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C222" s="54">
         <v>1380</v>
@@ -17025,7 +17071,7 @@
         <v>46191</v>
       </c>
       <c r="B223" s="49" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C223" s="50">
         <v>1380</v>
@@ -17050,7 +17096,7 @@
         <v>46191</v>
       </c>
       <c r="B224" s="53" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C224" s="54">
         <v>1380</v>
@@ -17075,7 +17121,7 @@
         <v>46192</v>
       </c>
       <c r="B225" s="49" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C225" s="50">
         <v>1380</v>
@@ -17100,7 +17146,7 @@
         <v>46192</v>
       </c>
       <c r="B226" s="53" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C226" s="54">
         <v>1380</v>
@@ -17125,7 +17171,7 @@
         <v>46192</v>
       </c>
       <c r="B227" s="49" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C227" s="50">
         <v>1380</v>
@@ -17150,7 +17196,7 @@
         <v>46192</v>
       </c>
       <c r="B228" s="53" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C228" s="54">
         <v>1380</v>
@@ -17175,7 +17221,7 @@
         <v>46193</v>
       </c>
       <c r="B229" s="49" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C229" s="50">
         <v>699</v>
@@ -17189,7 +17235,7 @@
       <c r="F229" s="49"/>
       <c r="G229" s="49"/>
       <c r="H229" s="51" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="I229" s="49" t="s">
         <v>142</v>
@@ -17200,7 +17246,7 @@
         <v>46193</v>
       </c>
       <c r="B230" s="53" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C230" s="54">
         <v>699</v>
@@ -17214,7 +17260,7 @@
       <c r="F230" s="56"/>
       <c r="G230" s="56"/>
       <c r="H230" s="57" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="I230" s="53" t="s">
         <v>142</v>
@@ -17225,7 +17271,7 @@
         <v>46193</v>
       </c>
       <c r="B231" s="49" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C231" s="50">
         <v>1380</v>
@@ -17250,7 +17296,7 @@
         <v>46193</v>
       </c>
       <c r="B232" s="53" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C232" s="54">
         <v>699</v>
@@ -17264,7 +17310,7 @@
       <c r="F232" s="56"/>
       <c r="G232" s="56"/>
       <c r="H232" s="57" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="I232" s="53" t="s">
         <v>142</v>
@@ -17275,7 +17321,7 @@
         <v>46193</v>
       </c>
       <c r="B233" s="49" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C233" s="50">
         <v>1380</v>
@@ -17310,7 +17356,7 @@
       <c r="F234" s="56"/>
       <c r="G234" s="56"/>
       <c r="H234" s="57" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="I234" s="53" t="s">
         <v>341</v>
@@ -17331,7 +17377,7 @@
       <c r="F235" s="49"/>
       <c r="G235" s="49"/>
       <c r="H235" s="51" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="I235" s="49" t="s">
         <v>341</v>
@@ -17342,7 +17388,7 @@
         <v>46194</v>
       </c>
       <c r="B236" s="53" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="C236" s="54">
         <v>699</v>
@@ -17352,7 +17398,7 @@
       <c r="F236" s="56"/>
       <c r="G236" s="56"/>
       <c r="H236" s="57" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="I236" s="53" t="s">
         <v>341</v>
@@ -17363,7 +17409,7 @@
         <v>46194</v>
       </c>
       <c r="B237" s="49" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="C237" s="50">
         <v>2480</v>
@@ -17377,55 +17423,111 @@
       <c r="F237" s="49"/>
       <c r="G237" s="49"/>
       <c r="H237" s="51" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="I237" s="49" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="238" spans="1:9">
-      <c r="A238" s="52"/>
-      <c r="B238" s="53"/>
-      <c r="C238" s="54"/>
-      <c r="D238" s="53"/>
-      <c r="E238" s="53"/>
+    <row r="238" spans="1:9" ht="14">
+      <c r="A238" s="52">
+        <v>46196</v>
+      </c>
+      <c r="B238" s="53" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C238" s="54">
+        <v>700</v>
+      </c>
+      <c r="D238" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E238" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F238" s="56"/>
       <c r="G238" s="56"/>
-      <c r="H238" s="57"/>
-      <c r="I238" s="53"/>
-    </row>
-    <row r="239" spans="1:9">
-      <c r="A239" s="48"/>
-      <c r="B239" s="49"/>
-      <c r="C239" s="50"/>
-      <c r="D239" s="49"/>
-      <c r="E239" s="49"/>
+      <c r="H238" s="57" t="s">
+        <v>1092</v>
+      </c>
+      <c r="I238" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" ht="14">
+      <c r="A239" s="48">
+        <v>46196</v>
+      </c>
+      <c r="B239" s="49" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C239" s="50">
+        <v>1380</v>
+      </c>
+      <c r="D239" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E239" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F239" s="49"/>
       <c r="G239" s="49"/>
-      <c r="H239" s="51"/>
-      <c r="I239" s="49"/>
-    </row>
-    <row r="240" spans="1:9">
-      <c r="A240" s="52"/>
-      <c r="B240" s="53"/>
-      <c r="C240" s="54"/>
-      <c r="D240" s="53"/>
-      <c r="E240" s="53"/>
+      <c r="H239" s="51" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I239" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" ht="14">
+      <c r="A240" s="52">
+        <v>46196</v>
+      </c>
+      <c r="B240" s="53" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C240" s="54">
+        <v>699</v>
+      </c>
+      <c r="D240" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E240" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F240" s="56"/>
       <c r="G240" s="56"/>
-      <c r="H240" s="57"/>
-      <c r="I240" s="53"/>
-    </row>
-    <row r="241" spans="1:9">
-      <c r="A241" s="48"/>
-      <c r="B241" s="49"/>
-      <c r="C241" s="50"/>
-      <c r="D241" s="49"/>
-      <c r="E241" s="49"/>
+      <c r="H240" s="57" t="s">
+        <v>1098</v>
+      </c>
+      <c r="I240" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" ht="28">
+      <c r="A241" s="48">
+        <v>46196</v>
+      </c>
+      <c r="B241" s="49" t="s">
+        <v>298</v>
+      </c>
+      <c r="C241" s="50">
+        <v>5000</v>
+      </c>
+      <c r="D241" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E241" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F241" s="49"/>
       <c r="G241" s="49"/>
-      <c r="H241" s="51"/>
-      <c r="I241" s="49"/>
+      <c r="H241" s="51" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I241" s="49" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" s="52"/>
@@ -17662,7 +17764,7 @@
     <col min="9" max="9" width="15.1640625" style="61" customWidth="1"/>
     <col min="10" max="10" width="13.83203125" style="61" customWidth="1"/>
     <col min="11" max="11" width="13.6640625" style="61" customWidth="1"/>
-    <col min="12" max="12" width="59" style="61" customWidth="1"/>
+    <col min="12" max="12" width="70.5" style="61" customWidth="1"/>
     <col min="13" max="13" width="20.6640625" style="61" customWidth="1"/>
     <col min="14" max="14" width="13" style="61" customWidth="1"/>
     <col min="15" max="15" width="22.33203125" style="61" customWidth="1"/>
@@ -24425,7 +24527,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="66" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="M62" s="66"/>
       <c r="N62" s="66" t="s">
@@ -25269,7 +25371,7 @@
         <v>1075</v>
       </c>
       <c r="L78" s="66" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="M78" s="66"/>
       <c r="N78" s="66" t="s">
@@ -27460,7 +27562,7 @@
       <c r="S119" s="69"/>
       <c r="T119" s="69"/>
     </row>
-    <row r="120" spans="1:246" ht="175" customHeight="1">
+    <row r="120" spans="1:246" ht="182" customHeight="1">
       <c r="A120" s="66" t="s">
         <v>703</v>
       </c>
@@ -27477,10 +27579,10 @@
         <v>699</v>
       </c>
       <c r="F120" s="67">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G120" s="67">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H120" s="66">
         <f t="shared" si="9"/>
@@ -27492,14 +27594,14 @@
       </c>
       <c r="J120" s="66">
         <f t="shared" si="10"/>
-        <v>15920.226666666653</v>
+        <v>16339.179999999986</v>
       </c>
       <c r="K120" s="66">
         <f t="shared" si="11"/>
-        <v>3351.6266666666638</v>
+        <v>2932.6733333333309</v>
       </c>
       <c r="L120" s="66" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="M120" s="66" t="s">
         <v>49</v>
@@ -27509,7 +27611,7 @@
       </c>
       <c r="O120" s="66"/>
       <c r="P120" s="66" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="Q120" s="66"/>
       <c r="R120" s="66"/>
@@ -27661,7 +27763,7 @@
         <v>0</v>
       </c>
       <c r="L123" s="78" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="M123" s="78"/>
       <c r="N123" s="78" t="s">
@@ -29277,7 +29379,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="69" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="M141" s="69"/>
       <c r="N141" s="69" t="s">
@@ -29597,7 +29699,7 @@
       </c>
       <c r="O147" s="69"/>
       <c r="P147" s="69" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="Q147" s="69"/>
       <c r="R147" s="69"/>
@@ -29853,14 +29955,14 @@
         <v>590</v>
       </c>
       <c r="L152" s="66" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="M152" s="66"/>
       <c r="N152" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O152" s="66" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="P152" s="66" t="s">
         <v>792</v>
@@ -29887,10 +29989,10 @@
         <v>1380</v>
       </c>
       <c r="F153" s="79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G153" s="79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153" s="78">
         <f t="shared" si="12"/>
@@ -29902,22 +30004,22 @@
       </c>
       <c r="J153" s="78">
         <f t="shared" si="13"/>
-        <v>891.5</v>
+        <v>1783</v>
       </c>
       <c r="K153" s="78">
         <f t="shared" si="14"/>
-        <v>891.5</v>
+        <v>0</v>
       </c>
       <c r="L153" s="69" t="s">
-        <v>795</v>
+        <v>1094</v>
       </c>
       <c r="M153" s="69"/>
       <c r="N153" s="69" t="s">
-        <v>510</v>
+        <v>425</v>
       </c>
       <c r="O153" s="69"/>
       <c r="P153" s="69" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Q153" s="69"/>
       <c r="R153" s="69"/>
@@ -29926,10 +30028,10 @@
     </row>
     <row r="154" spans="1:20" ht="15" customHeight="1">
       <c r="A154" s="66" t="s">
+        <v>796</v>
+      </c>
+      <c r="B154" s="66" t="s">
         <v>797</v>
-      </c>
-      <c r="B154" s="66" t="s">
-        <v>798</v>
       </c>
       <c r="C154" s="66" t="s">
         <v>96</v>
@@ -29963,14 +30065,14 @@
         <v>1898</v>
       </c>
       <c r="L154" s="66" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="M154" s="66"/>
       <c r="N154" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O154" s="66" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="P154" s="66"/>
       <c r="Q154" s="66"/>
@@ -29980,10 +30082,10 @@
     </row>
     <row r="155" spans="1:20" ht="15" customHeight="1">
       <c r="A155" s="69" t="s">
+        <v>800</v>
+      </c>
+      <c r="B155" s="69" t="s">
         <v>801</v>
-      </c>
-      <c r="B155" s="69" t="s">
-        <v>802</v>
       </c>
       <c r="C155" s="69" t="s">
         <v>96</v>
@@ -30022,7 +30124,7 @@
         <v>598</v>
       </c>
       <c r="O155" s="69" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="P155" s="69"/>
       <c r="Q155" s="69"/>
@@ -30032,10 +30134,10 @@
     </row>
     <row r="156" spans="1:20" ht="15" customHeight="1">
       <c r="A156" s="66" t="s">
+        <v>803</v>
+      </c>
+      <c r="B156" s="66" t="s">
         <v>804</v>
-      </c>
-      <c r="B156" s="66" t="s">
-        <v>805</v>
       </c>
       <c r="C156" s="66" t="s">
         <v>96</v>
@@ -30069,14 +30171,14 @@
         <v>2850</v>
       </c>
       <c r="L156" s="66" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="M156" s="66"/>
       <c r="N156" s="66" t="s">
         <v>510</v>
       </c>
       <c r="O156" s="66" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="P156" s="66"/>
       <c r="Q156" s="66"/>
@@ -30086,10 +30188,10 @@
     </row>
     <row r="157" spans="1:20" ht="15" customHeight="1">
       <c r="A157" s="69" t="s">
+        <v>806</v>
+      </c>
+      <c r="B157" s="69" t="s">
         <v>807</v>
-      </c>
-      <c r="B157" s="69" t="s">
-        <v>808</v>
       </c>
       <c r="C157" s="69" t="s">
         <v>96</v>
@@ -30123,7 +30225,7 @@
         <v>1050</v>
       </c>
       <c r="L157" s="69" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="M157" s="69"/>
       <c r="N157" s="69" t="s">
@@ -30140,10 +30242,10 @@
     </row>
     <row r="158" spans="1:20" ht="15" customHeight="1">
       <c r="A158" s="66" t="s">
+        <v>808</v>
+      </c>
+      <c r="B158" s="66" t="s">
         <v>809</v>
-      </c>
-      <c r="B158" s="66" t="s">
-        <v>810</v>
       </c>
       <c r="C158" s="66" t="s">
         <v>96</v>
@@ -30177,14 +30279,14 @@
         <v>3356</v>
       </c>
       <c r="L158" s="66" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="M158" s="66"/>
       <c r="N158" s="66" t="s">
         <v>598</v>
       </c>
       <c r="O158" s="66" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="P158" s="66"/>
       <c r="Q158" s="66"/>
@@ -30194,10 +30296,10 @@
     </row>
     <row r="159" spans="1:20" ht="15" customHeight="1">
       <c r="A159" s="69" t="s">
+        <v>812</v>
+      </c>
+      <c r="B159" s="69" t="s">
         <v>813</v>
-      </c>
-      <c r="B159" s="69" t="s">
-        <v>814</v>
       </c>
       <c r="C159" s="69" t="s">
         <v>96</v>
@@ -30231,14 +30333,14 @@
         <v>2517</v>
       </c>
       <c r="L159" s="69" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="M159" s="69"/>
       <c r="N159" s="69" t="s">
         <v>510</v>
       </c>
       <c r="O159" s="69" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="P159" s="69"/>
       <c r="Q159" s="69"/>
@@ -30248,10 +30350,10 @@
     </row>
     <row r="160" spans="1:20" ht="15" customHeight="1">
       <c r="A160" s="66" t="s">
+        <v>816</v>
+      </c>
+      <c r="B160" s="66" t="s">
         <v>817</v>
-      </c>
-      <c r="B160" s="66" t="s">
-        <v>818</v>
       </c>
       <c r="C160" s="66" t="s">
         <v>95</v>
@@ -30300,10 +30402,10 @@
     </row>
     <row r="161" spans="1:20" ht="15" customHeight="1">
       <c r="A161" s="69" t="s">
+        <v>818</v>
+      </c>
+      <c r="B161" s="69" t="s">
         <v>819</v>
-      </c>
-      <c r="B161" s="69" t="s">
-        <v>820</v>
       </c>
       <c r="C161" s="69" t="s">
         <v>95</v>
@@ -30352,10 +30454,10 @@
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1">
       <c r="A162" s="66" t="s">
+        <v>820</v>
+      </c>
+      <c r="B162" s="66" t="s">
         <v>821</v>
-      </c>
-      <c r="B162" s="66" t="s">
-        <v>822</v>
       </c>
       <c r="C162" s="66" t="s">
         <v>95</v>
@@ -30404,10 +30506,10 @@
     </row>
     <row r="163" spans="1:20" ht="15" customHeight="1">
       <c r="A163" s="69" t="s">
+        <v>822</v>
+      </c>
+      <c r="B163" s="69" t="s">
         <v>823</v>
-      </c>
-      <c r="B163" s="69" t="s">
-        <v>824</v>
       </c>
       <c r="C163" s="69" t="s">
         <v>95</v>
@@ -30454,10 +30556,10 @@
     </row>
     <row r="164" spans="1:20" ht="60" customHeight="1">
       <c r="A164" s="66" t="s">
+        <v>824</v>
+      </c>
+      <c r="B164" s="66" t="s">
         <v>825</v>
-      </c>
-      <c r="B164" s="66" t="s">
-        <v>826</v>
       </c>
       <c r="C164" s="66" t="s">
         <v>95</v>
@@ -30491,7 +30593,7 @@
         <v>1013</v>
       </c>
       <c r="L164" s="66" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="M164" s="66"/>
       <c r="N164" s="66" t="s">
@@ -30499,7 +30601,7 @@
       </c>
       <c r="O164" s="66"/>
       <c r="P164" s="66" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="Q164" s="66"/>
       <c r="R164" s="66"/>
@@ -30508,10 +30610,10 @@
     </row>
     <row r="165" spans="1:20" ht="15" customHeight="1">
       <c r="A165" s="69" t="s">
+        <v>826</v>
+      </c>
+      <c r="B165" s="69" t="s">
         <v>827</v>
-      </c>
-      <c r="B165" s="69" t="s">
-        <v>828</v>
       </c>
       <c r="C165" s="69" t="s">
         <v>95</v>
@@ -30553,7 +30655,7 @@
       </c>
       <c r="O165" s="69"/>
       <c r="P165" s="69" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="Q165" s="69"/>
       <c r="R165" s="69"/>
@@ -30562,10 +30664,10 @@
     </row>
     <row r="166" spans="1:20" ht="15" customHeight="1">
       <c r="A166" s="66" t="s">
+        <v>829</v>
+      </c>
+      <c r="B166" s="66" t="s">
         <v>830</v>
-      </c>
-      <c r="B166" s="66" t="s">
-        <v>831</v>
       </c>
       <c r="C166" s="66" t="s">
         <v>95</v>
@@ -30605,7 +30707,7 @@
       </c>
       <c r="O166" s="66"/>
       <c r="P166" s="66" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="Q166" s="66"/>
       <c r="R166" s="66"/>
@@ -30614,10 +30716,10 @@
     </row>
     <row r="167" spans="1:20" ht="15" customHeight="1">
       <c r="A167" s="69" t="s">
+        <v>832</v>
+      </c>
+      <c r="B167" s="69" t="s">
         <v>833</v>
-      </c>
-      <c r="B167" s="69" t="s">
-        <v>834</v>
       </c>
       <c r="C167" s="69" t="s">
         <v>95</v>
@@ -30651,7 +30753,7 @@
         <v>2220</v>
       </c>
       <c r="L167" s="69" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="M167" s="69"/>
       <c r="N167" s="69" t="s">
@@ -30659,7 +30761,7 @@
       </c>
       <c r="O167" s="69"/>
       <c r="P167" s="69" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="Q167" s="69"/>
       <c r="R167" s="69"/>
@@ -30668,10 +30770,10 @@
     </row>
     <row r="168" spans="1:20" ht="15" customHeight="1">
       <c r="A168" s="66" t="s">
+        <v>836</v>
+      </c>
+      <c r="B168" s="66" t="s">
         <v>837</v>
-      </c>
-      <c r="B168" s="66" t="s">
-        <v>838</v>
       </c>
       <c r="C168" s="66" t="s">
         <v>95</v>
@@ -30705,7 +30807,7 @@
         <v>1216</v>
       </c>
       <c r="L168" s="66" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="M168" s="66"/>
       <c r="N168" s="66" t="s">
@@ -30713,7 +30815,7 @@
       </c>
       <c r="O168" s="66"/>
       <c r="P168" s="66" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q168" s="66"/>
       <c r="R168" s="66"/>
@@ -30722,10 +30824,10 @@
     </row>
     <row r="169" spans="1:20" ht="15" customHeight="1">
       <c r="A169" s="69" t="s">
+        <v>840</v>
+      </c>
+      <c r="B169" s="69" t="s">
         <v>841</v>
-      </c>
-      <c r="B169" s="69" t="s">
-        <v>842</v>
       </c>
       <c r="C169" s="69" t="s">
         <v>95</v>
@@ -30765,7 +30867,7 @@
       </c>
       <c r="O169" s="69"/>
       <c r="P169" s="69" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="Q169" s="69"/>
       <c r="R169" s="69"/>
@@ -30774,10 +30876,10 @@
     </row>
     <row r="170" spans="1:20" ht="30" customHeight="1">
       <c r="A170" s="66" t="s">
+        <v>843</v>
+      </c>
+      <c r="B170" s="66" t="s">
         <v>844</v>
-      </c>
-      <c r="B170" s="66" t="s">
-        <v>845</v>
       </c>
       <c r="C170" s="66" t="s">
         <v>95</v>
@@ -30811,7 +30913,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="66" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="M170" s="66"/>
       <c r="N170" s="66" t="s">
@@ -30819,7 +30921,7 @@
       </c>
       <c r="O170" s="66"/>
       <c r="P170" s="66" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="Q170" s="66"/>
       <c r="R170" s="66"/>
@@ -30828,10 +30930,10 @@
     </row>
     <row r="171" spans="1:20" ht="31.5" customHeight="1">
       <c r="A171" s="69" t="s">
+        <v>847</v>
+      </c>
+      <c r="B171" s="66" t="s">
         <v>848</v>
-      </c>
-      <c r="B171" s="66" t="s">
-        <v>849</v>
       </c>
       <c r="C171" s="69" t="s">
         <v>95</v>
@@ -30865,7 +30967,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="69" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="M171" s="69"/>
       <c r="N171" s="69" t="s">
@@ -30880,10 +30982,10 @@
     </row>
     <row r="172" spans="1:20" ht="15" customHeight="1">
       <c r="A172" s="66" t="s">
+        <v>850</v>
+      </c>
+      <c r="B172" s="66" t="s">
         <v>851</v>
-      </c>
-      <c r="B172" s="66" t="s">
-        <v>852</v>
       </c>
       <c r="C172" s="66" t="s">
         <v>95</v>
@@ -30917,7 +31019,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="66" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="M172" s="66"/>
       <c r="N172" s="66" t="s">
@@ -30932,10 +31034,10 @@
     </row>
     <row r="173" spans="1:20" ht="15" customHeight="1">
       <c r="A173" s="69" t="s">
+        <v>852</v>
+      </c>
+      <c r="B173" s="69" t="s">
         <v>853</v>
-      </c>
-      <c r="B173" s="69" t="s">
-        <v>854</v>
       </c>
       <c r="C173" s="69" t="s">
         <v>95</v>
@@ -30984,10 +31086,10 @@
     </row>
     <row r="174" spans="1:20" ht="15" customHeight="1">
       <c r="A174" s="66" t="s">
+        <v>854</v>
+      </c>
+      <c r="B174" s="66" t="s">
         <v>855</v>
-      </c>
-      <c r="B174" s="66" t="s">
-        <v>856</v>
       </c>
       <c r="C174" s="66" t="s">
         <v>95</v>
@@ -31021,7 +31123,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="66" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="M174" s="66"/>
       <c r="N174" s="66" t="s">
@@ -31036,10 +31138,10 @@
     </row>
     <row r="175" spans="1:20" ht="90" customHeight="1">
       <c r="A175" s="69" t="s">
+        <v>857</v>
+      </c>
+      <c r="B175" s="69" t="s">
         <v>858</v>
-      </c>
-      <c r="B175" s="69" t="s">
-        <v>859</v>
       </c>
       <c r="C175" s="69" t="s">
         <v>95</v>
@@ -31073,7 +31175,7 @@
         <v>4189.5</v>
       </c>
       <c r="L175" s="69" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="M175" s="69"/>
       <c r="N175" s="69" t="s">
@@ -31081,7 +31183,7 @@
       </c>
       <c r="O175" s="69"/>
       <c r="P175" s="69" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="Q175" s="69"/>
       <c r="R175" s="69"/>
@@ -31090,10 +31192,10 @@
     </row>
     <row r="176" spans="1:20" ht="24" customHeight="1">
       <c r="A176" s="66" t="s">
+        <v>859</v>
+      </c>
+      <c r="B176" s="66" t="s">
         <v>860</v>
-      </c>
-      <c r="B176" s="66" t="s">
-        <v>861</v>
       </c>
       <c r="C176" s="66" t="s">
         <v>95</v>
@@ -31127,7 +31229,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="66" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="M176" s="66"/>
       <c r="N176" s="66" t="s">
@@ -31142,10 +31244,10 @@
     </row>
     <row r="177" spans="1:20" ht="34" customHeight="1">
       <c r="A177" s="69" t="s">
+        <v>861</v>
+      </c>
+      <c r="B177" s="69" t="s">
         <v>862</v>
-      </c>
-      <c r="B177" s="69" t="s">
-        <v>863</v>
       </c>
       <c r="C177" s="69" t="s">
         <v>95</v>
@@ -31179,7 +31281,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="69" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="M177" s="69"/>
       <c r="N177" s="69" t="s">
@@ -31187,7 +31289,7 @@
       </c>
       <c r="O177" s="69"/>
       <c r="P177" s="69" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="Q177" s="69"/>
       <c r="R177" s="69"/>
@@ -31196,10 +31298,10 @@
     </row>
     <row r="178" spans="1:20" ht="15" customHeight="1">
       <c r="A178" s="66" t="s">
+        <v>864</v>
+      </c>
+      <c r="B178" s="66" t="s">
         <v>865</v>
-      </c>
-      <c r="B178" s="66" t="s">
-        <v>866</v>
       </c>
       <c r="C178" s="66" t="s">
         <v>95</v>
@@ -31233,7 +31335,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="66" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M178" s="66"/>
       <c r="N178" s="66" t="s">
@@ -31241,7 +31343,7 @@
       </c>
       <c r="O178" s="66"/>
       <c r="P178" s="66" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="Q178" s="66"/>
       <c r="R178" s="66"/>
@@ -31250,10 +31352,10 @@
     </row>
     <row r="179" spans="1:20" ht="30" customHeight="1">
       <c r="A179" s="69" t="s">
+        <v>867</v>
+      </c>
+      <c r="B179" s="69" t="s">
         <v>868</v>
-      </c>
-      <c r="B179" s="69" t="s">
-        <v>869</v>
       </c>
       <c r="C179" s="69" t="s">
         <v>95</v>
@@ -31287,7 +31389,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="69" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="M179" s="69"/>
       <c r="N179" s="69" t="s">
@@ -31295,7 +31397,7 @@
       </c>
       <c r="O179" s="69"/>
       <c r="P179" s="69" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="Q179" s="69"/>
       <c r="R179" s="69"/>
@@ -31304,10 +31406,10 @@
     </row>
     <row r="180" spans="1:20" ht="34" customHeight="1">
       <c r="A180" s="66" t="s">
+        <v>871</v>
+      </c>
+      <c r="B180" s="66" t="s">
         <v>872</v>
-      </c>
-      <c r="B180" s="66" t="s">
-        <v>873</v>
       </c>
       <c r="C180" s="66" t="s">
         <v>95</v>
@@ -31341,7 +31443,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="66" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="M180" s="66"/>
       <c r="N180" s="66" t="s">
@@ -31356,10 +31458,10 @@
     </row>
     <row r="181" spans="1:20" ht="15" customHeight="1">
       <c r="A181" s="69" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B181" s="69" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C181" s="69" t="s">
         <v>96</v>
@@ -31398,10 +31500,10 @@
         <v>598</v>
       </c>
       <c r="O181" s="69" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="P181" s="69" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Q181" s="69"/>
       <c r="R181" s="69"/>
@@ -31410,10 +31512,10 @@
     </row>
     <row r="182" spans="1:20" ht="15" customHeight="1">
       <c r="A182" s="66" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B182" s="66" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C182" s="66" t="s">
         <v>95</v>
@@ -31453,7 +31555,7 @@
       </c>
       <c r="O182" s="66"/>
       <c r="P182" s="66" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Q182" s="66"/>
       <c r="R182" s="66"/>
@@ -31462,10 +31564,10 @@
     </row>
     <row r="183" spans="1:20" ht="15" customHeight="1">
       <c r="A183" s="69" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B183" s="69" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C183" s="69" t="s">
         <v>95</v>
@@ -31509,12 +31611,12 @@
       <c r="S183" s="69"/>
       <c r="T183" s="69"/>
     </row>
-    <row r="184" spans="1:20" ht="15" customHeight="1">
+    <row r="184" spans="1:20" ht="40" customHeight="1">
       <c r="A184" s="66" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B184" s="66" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C184" s="66" t="s">
         <v>95</v>
@@ -31526,10 +31628,10 @@
         <v>1380</v>
       </c>
       <c r="F184" s="81">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G184" s="81">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H184" s="80">
         <f t="shared" ref="H184:H226" si="23">F184+IF(LEN(G184)=0,0,G184)</f>
@@ -31541,14 +31643,14 @@
       </c>
       <c r="J184" s="80">
         <f t="shared" si="21"/>
-        <v>6237</v>
+        <v>7128</v>
       </c>
       <c r="K184" s="80">
         <f t="shared" si="22"/>
-        <v>11583</v>
+        <v>10692</v>
       </c>
       <c r="L184" s="66" t="s">
-        <v>1074</v>
+        <v>1101</v>
       </c>
       <c r="M184" s="66"/>
       <c r="N184" s="66" t="s">
@@ -31563,10 +31665,10 @@
     </row>
     <row r="185" spans="1:20" ht="15" customHeight="1">
       <c r="A185" s="69" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B185" s="69" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C185" s="69" t="s">
         <v>95</v>
@@ -31600,7 +31702,7 @@
         <v>0</v>
       </c>
       <c r="L185" s="69" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="M185" s="69"/>
       <c r="N185" s="69" t="s">
@@ -31615,7 +31717,7 @@
     </row>
     <row r="186" spans="1:20" ht="15" customHeight="1">
       <c r="A186" s="66" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B186" s="66" t="s">
         <v>713</v>
@@ -31665,10 +31767,10 @@
     </row>
     <row r="187" spans="1:20" ht="15" customHeight="1">
       <c r="A187" s="69" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B187" s="69" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C187" s="69" t="s">
         <v>95</v>
@@ -31715,10 +31817,10 @@
     </row>
     <row r="188" spans="1:20" ht="15" customHeight="1">
       <c r="A188" s="66" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B188" s="66" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C188" s="66" t="s">
         <v>95</v>
@@ -31765,10 +31867,10 @@
     </row>
     <row r="189" spans="1:20" ht="45">
       <c r="A189" s="69" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B189" s="66" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C189" s="66" t="s">
         <v>95</v>
@@ -31802,7 +31904,7 @@
         <v>6237</v>
       </c>
       <c r="L189" s="69" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="M189" s="69"/>
       <c r="N189" s="69" t="s">
@@ -31810,7 +31912,7 @@
       </c>
       <c r="O189" s="69"/>
       <c r="P189" s="69" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Q189" s="69"/>
       <c r="R189" s="69"/>
@@ -31819,10 +31921,10 @@
     </row>
     <row r="190" spans="1:20" ht="15">
       <c r="A190" s="66" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B190" s="69" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C190" s="69" t="s">
         <v>95</v>
@@ -31858,20 +31960,20 @@
       <c r="L190" s="66"/>
       <c r="M190" s="66"/>
       <c r="N190" s="61" t="s">
+        <v>1012</v>
+      </c>
+      <c r="P190" s="61" t="s">
         <v>1013</v>
-      </c>
-      <c r="P190" s="61" t="s">
-        <v>1014</v>
       </c>
       <c r="S190" s="61"/>
       <c r="T190" s="61"/>
     </row>
     <row r="191" spans="1:20" ht="30">
       <c r="A191" s="69" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B191" s="66" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C191" s="66" t="s">
         <v>95</v>
@@ -31910,17 +32012,17 @@
         <v>598</v>
       </c>
       <c r="P191" s="61" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="S191" s="61"/>
       <c r="T191" s="61"/>
     </row>
     <row r="192" spans="1:20" ht="15">
       <c r="A192" s="66" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B192" s="69" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C192" s="69" t="s">
         <v>95</v>
@@ -31959,17 +32061,17 @@
         <v>598</v>
       </c>
       <c r="P192" s="61" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="S192" s="61"/>
       <c r="T192" s="61"/>
     </row>
     <row r="193" spans="1:20" ht="15">
       <c r="A193" s="69" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B193" s="66" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C193" s="66" t="s">
         <v>95</v>
@@ -32008,17 +32110,17 @@
         <v>598</v>
       </c>
       <c r="P193" s="61" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="S193" s="61"/>
       <c r="T193" s="61"/>
     </row>
     <row r="194" spans="1:20" ht="15">
       <c r="A194" s="66" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B194" s="66" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C194" s="66" t="s">
         <v>95</v>
@@ -32057,17 +32159,17 @@
         <v>598</v>
       </c>
       <c r="P194" s="61" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="S194" s="61"/>
       <c r="T194" s="61"/>
     </row>
     <row r="195" spans="1:20" ht="15">
       <c r="A195" s="69" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B195" s="69" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C195" s="69" t="s">
         <v>95</v>
@@ -32101,24 +32203,24 @@
         <v>5467</v>
       </c>
       <c r="L195" s="69" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="M195" s="69"/>
       <c r="N195" s="61" t="s">
         <v>510</v>
       </c>
       <c r="P195" s="61" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="S195" s="61"/>
       <c r="T195" s="61"/>
     </row>
     <row r="196" spans="1:20" ht="15">
       <c r="A196" s="66" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B196" s="66" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C196" s="66" t="s">
         <v>95</v>
@@ -32157,17 +32259,17 @@
         <v>598</v>
       </c>
       <c r="P196" s="61" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="S196" s="61"/>
       <c r="T196" s="61"/>
     </row>
     <row r="197" spans="1:20" ht="15">
       <c r="A197" s="69" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B197" s="69" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C197" s="69" t="s">
         <v>95</v>
@@ -32206,17 +32308,17 @@
         <v>598</v>
       </c>
       <c r="P197" s="61" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="S197" s="61"/>
       <c r="T197" s="61"/>
     </row>
     <row r="198" spans="1:20" ht="15">
       <c r="A198" s="66" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B198" s="66" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C198" s="66" t="s">
         <v>95</v>
@@ -32255,17 +32357,17 @@
         <v>598</v>
       </c>
       <c r="P198" s="61" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="S198" s="61"/>
       <c r="T198" s="61"/>
     </row>
     <row r="199" spans="1:20" ht="15">
       <c r="A199" s="69" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B199" s="66" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C199" s="66" t="s">
         <v>95</v>
@@ -32304,17 +32406,17 @@
         <v>598</v>
       </c>
       <c r="P199" s="61" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="S199" s="61"/>
       <c r="T199" s="61"/>
     </row>
     <row r="200" spans="1:20" ht="30">
       <c r="A200" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B200" s="69" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C200" s="69" t="s">
         <v>95</v>
@@ -32326,10 +32428,10 @@
         <v>1350</v>
       </c>
       <c r="F200" s="81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G200" s="81">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H200" s="80">
         <f t="shared" si="23"/>
@@ -32341,31 +32443,31 @@
       </c>
       <c r="J200" s="80">
         <f t="shared" si="21"/>
-        <v>866</v>
+        <v>2598</v>
       </c>
       <c r="K200" s="80">
         <f t="shared" si="22"/>
-        <v>3464</v>
+        <v>1732</v>
       </c>
       <c r="L200" s="66" t="s">
-        <v>1085</v>
+        <v>1104</v>
       </c>
       <c r="M200" s="66"/>
       <c r="N200" s="61" t="s">
         <v>510</v>
       </c>
       <c r="P200" s="61" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="S200" s="61"/>
       <c r="T200" s="61"/>
     </row>
     <row r="201" spans="1:20" ht="15">
       <c r="A201" s="69" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B201" s="66" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C201" s="66" t="s">
         <v>95</v>
@@ -32399,24 +32501,24 @@
         <v>724</v>
       </c>
       <c r="L201" s="69" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="M201" s="69"/>
       <c r="N201" s="61" t="s">
         <v>510</v>
       </c>
       <c r="P201" s="61" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="S201" s="61"/>
       <c r="T201" s="61"/>
     </row>
     <row r="202" spans="1:20" ht="15">
       <c r="A202" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B202" s="69" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C202" s="69" t="s">
         <v>95</v>
@@ -32455,17 +32557,17 @@
         <v>598</v>
       </c>
       <c r="P202" s="61" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="S202" s="61"/>
       <c r="T202" s="61"/>
     </row>
     <row r="203" spans="1:20" ht="15">
       <c r="A203" s="69" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B203" s="66" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C203" s="66" t="s">
         <v>95</v>
@@ -32477,10 +32579,10 @@
         <v>699</v>
       </c>
       <c r="F203" s="79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G203" s="79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H203" s="78">
         <f t="shared" si="23"/>
@@ -32492,31 +32594,31 @@
       </c>
       <c r="J203" s="78">
         <f t="shared" si="21"/>
-        <v>488.25</v>
+        <v>976.5</v>
       </c>
       <c r="K203" s="78">
         <f t="shared" si="22"/>
-        <v>488.25</v>
+        <v>0</v>
       </c>
       <c r="L203" s="69" t="s">
-        <v>147</v>
+        <v>1093</v>
       </c>
       <c r="M203" s="69"/>
       <c r="N203" s="61" t="s">
-        <v>510</v>
+        <v>425</v>
       </c>
       <c r="P203" s="61" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="S203" s="61"/>
       <c r="T203" s="61"/>
     </row>
     <row r="204" spans="1:20" ht="15">
       <c r="A204" s="66" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B204" s="66" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C204" s="66" t="s">
         <v>95</v>
@@ -32550,24 +32652,24 @@
         <v>1760</v>
       </c>
       <c r="L204" s="66" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="M204" s="66"/>
       <c r="N204" s="61" t="s">
         <v>510</v>
       </c>
       <c r="P204" s="61" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="S204" s="61"/>
       <c r="T204" s="61"/>
     </row>
     <row r="205" spans="1:20" ht="15">
       <c r="A205" s="69" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B205" s="69" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C205" s="69" t="s">
         <v>95</v>
@@ -32579,10 +32681,10 @@
         <v>1250</v>
       </c>
       <c r="F205" s="79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G205" s="79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H205" s="78">
         <f t="shared" si="23"/>
@@ -32594,29 +32696,31 @@
       </c>
       <c r="J205" s="78">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>761</v>
       </c>
       <c r="K205" s="78">
         <f t="shared" si="22"/>
-        <v>2283</v>
-      </c>
-      <c r="L205" s="69"/>
+        <v>1522</v>
+      </c>
+      <c r="L205" s="69" t="s">
+        <v>1102</v>
+      </c>
       <c r="M205" s="69"/>
       <c r="N205" s="61" t="s">
         <v>598</v>
       </c>
       <c r="P205" s="61" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="S205" s="61"/>
       <c r="T205" s="61"/>
     </row>
     <row r="206" spans="1:20" ht="15">
       <c r="A206" s="66" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B206" s="66" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C206" s="66" t="s">
         <v>95</v>
@@ -32655,17 +32759,17 @@
         <v>598</v>
       </c>
       <c r="P206" s="61" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="S206" s="61"/>
       <c r="T206" s="61"/>
     </row>
     <row r="207" spans="1:20" ht="15">
       <c r="A207" s="69" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B207" s="69" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C207" s="69" t="s">
         <v>95</v>
@@ -32699,24 +32803,24 @@
         <v>3312</v>
       </c>
       <c r="L207" s="69" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="M207" s="69"/>
       <c r="N207" s="61" t="s">
         <v>510</v>
       </c>
       <c r="P207" s="61" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="S207" s="61"/>
       <c r="T207" s="61"/>
     </row>
     <row r="208" spans="1:20" ht="30">
       <c r="A208" s="66" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B208" s="66" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C208" s="66" t="s">
         <v>95</v>
@@ -32755,17 +32859,17 @@
         <v>598</v>
       </c>
       <c r="P208" s="61" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="S208" s="61"/>
       <c r="T208" s="61"/>
     </row>
     <row r="209" spans="1:20" ht="15">
       <c r="A209" s="69" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B209" s="66" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C209" s="66" t="s">
         <v>95</v>
@@ -32804,17 +32908,17 @@
         <v>598</v>
       </c>
       <c r="P209" s="61" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="S209" s="61"/>
       <c r="T209" s="61"/>
     </row>
     <row r="210" spans="1:20" ht="15">
       <c r="A210" s="66" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B210" s="69" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C210" s="69" t="s">
         <v>95</v>
@@ -32853,17 +32957,17 @@
         <v>598</v>
       </c>
       <c r="P210" s="61" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="S210" s="61"/>
       <c r="T210" s="61"/>
     </row>
     <row r="211" spans="1:20" ht="15">
       <c r="A211" s="69" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B211" s="66" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C211" s="66" t="s">
         <v>95</v>
@@ -32902,14 +33006,14 @@
         <v>598</v>
       </c>
       <c r="P211" s="61" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="S211" s="61"/>
       <c r="T211" s="61"/>
     </row>
     <row r="212" spans="1:20" ht="15">
       <c r="A212" s="66" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B212" s="69"/>
       <c r="C212" s="69"/>
@@ -32944,7 +33048,7 @@
     </row>
     <row r="213" spans="1:20" ht="15">
       <c r="A213" s="69" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B213" s="66"/>
       <c r="C213" s="66"/>
@@ -32979,7 +33083,7 @@
     </row>
     <row r="214" spans="1:20" ht="15">
       <c r="A214" s="66" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B214" s="66"/>
       <c r="C214" s="66"/>
@@ -33014,7 +33118,7 @@
     </row>
     <row r="215" spans="1:20" ht="15">
       <c r="A215" s="69" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B215" s="69"/>
       <c r="C215" s="69"/>
@@ -33049,7 +33153,7 @@
     </row>
     <row r="216" spans="1:20" ht="15">
       <c r="A216" s="66" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B216" s="66"/>
       <c r="C216" s="66"/>
@@ -33084,7 +33188,7 @@
     </row>
     <row r="217" spans="1:20" ht="15">
       <c r="A217" s="69" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B217" s="69"/>
       <c r="C217" s="69"/>
@@ -33119,7 +33223,7 @@
     </row>
     <row r="218" spans="1:20" ht="15">
       <c r="A218" s="66" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B218" s="66"/>
       <c r="C218" s="66"/>
@@ -33154,7 +33258,7 @@
     </row>
     <row r="219" spans="1:20" ht="15">
       <c r="A219" s="69" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B219" s="66"/>
       <c r="C219" s="66"/>
@@ -33189,7 +33293,7 @@
     </row>
     <row r="220" spans="1:20" ht="15">
       <c r="A220" s="66" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B220" s="69"/>
       <c r="C220" s="69"/>
@@ -33224,7 +33328,7 @@
     </row>
     <row r="221" spans="1:20" ht="15">
       <c r="A221" s="69" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B221" s="66"/>
       <c r="C221" s="66"/>
@@ -33259,7 +33363,7 @@
     </row>
     <row r="222" spans="1:20" ht="15">
       <c r="A222" s="66" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B222" s="69"/>
       <c r="C222" s="69"/>
@@ -33294,7 +33398,7 @@
     </row>
     <row r="223" spans="1:20" ht="15">
       <c r="A223" s="69" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B223" s="66"/>
       <c r="C223" s="66"/>
@@ -33329,7 +33433,7 @@
     </row>
     <row r="224" spans="1:20" ht="15">
       <c r="A224" s="66" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B224" s="66"/>
       <c r="C224" s="66"/>
@@ -33364,7 +33468,7 @@
     </row>
     <row r="225" spans="1:20" ht="15">
       <c r="A225" s="69" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B225" s="69"/>
       <c r="C225" s="69"/>
@@ -33399,7 +33503,7 @@
     </row>
     <row r="226" spans="1:20" ht="15">
       <c r="A226" s="66" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B226" s="66"/>
       <c r="C226" s="66"/>
@@ -37315,7 +37419,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1">
       <c r="A1" s="95" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B1" s="95"/>
     </row>
@@ -37324,7 +37428,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1">
@@ -37356,25 +37460,25 @@
         <v>42</v>
       </c>
       <c r="B7" s="86" t="s">
+        <v>883</v>
+      </c>
+      <c r="C7" s="86" t="s">
         <v>884</v>
       </c>
-      <c r="C7" s="86" t="s">
+      <c r="D7" s="86" t="s">
         <v>885</v>
       </c>
-      <c r="D7" s="86" t="s">
+      <c r="E7" s="86" t="s">
         <v>886</v>
       </c>
-      <c r="E7" s="86" t="s">
+      <c r="F7" s="86" t="s">
         <v>887</v>
       </c>
-      <c r="F7" s="86" t="s">
+      <c r="G7" s="86" t="s">
         <v>888</v>
       </c>
-      <c r="G7" s="86" t="s">
+      <c r="H7" s="86" t="s">
         <v>889</v>
-      </c>
-      <c r="H7" s="86" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1">
@@ -37383,15 +37487,15 @@
       </c>
       <c r="B8" s="9">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A8,Purchases!$C:$C),0)</f>
-        <v>212261</v>
+        <v>212623</v>
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>151066</v>
+        <v>151186.66666666666</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>61195</v>
+        <v>61436.333333333343</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -37399,7 +37503,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>61195</v>
+        <v>61436.333333333343</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -37407,7 +37511,7 @@
       </c>
       <c r="H8" s="88">
         <f>F8-G8</f>
-        <v>42891.66</v>
+        <v>43132.993333333347</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -37420,11 +37524,11 @@
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>151066</v>
+        <v>151186.66666666666</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>57271</v>
+        <v>57150.333333333343</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -37432,7 +37536,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>57271</v>
+        <v>57150.333333333343</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -37440,7 +37544,7 @@
       </c>
       <c r="H9" s="89">
         <f>F9-G9</f>
-        <v>15631.669999999998</v>
+        <v>15511.003333333341</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -37453,11 +37557,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>151066</v>
+        <v>151186.66666666666</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-118466</v>
+        <v>-118586.66666666666</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -37465,7 +37569,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-118466</v>
+        <v>-118586.66666666666</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -37473,12 +37577,12 @@
       </c>
       <c r="H10" s="88">
         <f>F10-G10</f>
-        <v>-58523.33</v>
+        <v>-58643.996666666659</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="90" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="96" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B12" s="96"/>
       <c r="C12" s="96"/>
@@ -37491,13 +37595,13 @@
         <v>98</v>
       </c>
       <c r="B13" s="86" t="s">
+        <v>891</v>
+      </c>
+      <c r="C13" s="86" t="s">
         <v>892</v>
       </c>
-      <c r="C13" s="86" t="s">
+      <c r="D13" s="86" t="s">
         <v>893</v>
-      </c>
-      <c r="D13" s="86" t="s">
-        <v>894</v>
       </c>
       <c r="E13" s="86" t="s">
         <v>99</v>
@@ -37511,7 +37615,7 @@
         <v>45952</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>51</v>
@@ -37529,7 +37633,7 @@
         <v>45952</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>51</v>
@@ -37583,7 +37687,7 @@
         <v>45970</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>50</v>
@@ -37601,7 +37705,7 @@
         <v>45970</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>50</v>
@@ -37619,7 +37723,7 @@
         <v>45973</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>50</v>
@@ -37637,7 +37741,7 @@
         <v>45973</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>49</v>
@@ -37655,7 +37759,7 @@
         <v>46058</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>51</v>
@@ -37691,7 +37795,7 @@
         <v>46059</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>49</v>
@@ -37727,7 +37831,7 @@
         <v>46093</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>50</v>
@@ -37745,7 +37849,7 @@
         <v>46093</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>51</v>
@@ -37828,7 +37932,7 @@
     </row>
     <row r="58" spans="2:2" ht="13.5" customHeight="1">
       <c r="B58" s="6" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
   </sheetData>
@@ -37858,7 +37962,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13.5" customHeight="1">
       <c r="A1" s="93" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="87" customFormat="1" ht="13.5" customHeight="1">
@@ -37866,22 +37970,22 @@
         <v>42</v>
       </c>
       <c r="B3" s="86" t="s">
+        <v>897</v>
+      </c>
+      <c r="C3" s="86" t="s">
+        <v>882</v>
+      </c>
+      <c r="D3" s="86" t="s">
         <v>898</v>
       </c>
-      <c r="C3" s="86" t="s">
-        <v>883</v>
-      </c>
-      <c r="D3" s="86" t="s">
+      <c r="E3" s="86" t="s">
         <v>899</v>
       </c>
-      <c r="E3" s="86" t="s">
+      <c r="F3" s="86" t="s">
         <v>900</v>
       </c>
-      <c r="F3" s="86" t="s">
+      <c r="G3" s="86" t="s">
         <v>901</v>
-      </c>
-      <c r="G3" s="86" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1">
@@ -37890,7 +37994,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>323739</v>
+        <v>331518</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -37898,11 +38002,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>130323.72619999999</v>
+        <v>132917.24479999999</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>193415.27380000002</v>
+        <v>198600.75520000001</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -37910,7 +38014,7 @@
       </c>
       <c r="G4" s="88">
         <f>E4+F4</f>
-        <v>56105.247800000012</v>
+        <v>61290.729200000002</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -37927,11 +38031,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>130245.54760000001</v>
+        <v>132837.5104</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-75621.547600000005</v>
+        <v>-78213.510399999999</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -37939,7 +38043,7 @@
       </c>
       <c r="G5" s="89">
         <f>E5+F5</f>
-        <v>-4034.5056000000041</v>
+        <v>-6626.4683999999979</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -37956,11 +38060,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>130323.72619999999</v>
+        <v>132917.24479999999</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-117793.72619999999</v>
+        <v>-120387.24479999999</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -37968,7 +38072,7 @@
       </c>
       <c r="G6" s="88">
         <f>E6+F6</f>
-        <v>-52070.742199999979</v>
+        <v>-54664.260799999975</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">
@@ -37978,27 +38082,27 @@
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Chiraath-Summary-Jun26.xlsx
+++ b/docs/Chiraath-Summary-Jun26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE98F41-E936-CA46-8B2F-F9D6C20FB277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785E3F12-4497-1348-8408-FA40268A10B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2738" uniqueCount="1105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2768" uniqueCount="1111">
   <si>
     <t>Notes:</t>
   </si>
@@ -3105,12 +3105,6 @@
     <t>Light green/dark green, navy/light, violet/green (leaf designs)</t>
   </si>
   <si>
-    <t>rust orange/coffee brown, peacock blue/navy, red/green, mustard/blue, chikku maroon, chikku green, golden yellow &amp; green triangle</t>
-  </si>
-  <si>
-    <t>Green/maroon - Rajitha Teacher</t>
-  </si>
-  <si>
     <t>Rajitha Teacher</t>
   </si>
   <si>
@@ -3311,15 +3305,9 @@
 Grey/Blue - 1, Purple/Green - 1</t>
   </si>
   <si>
-    <t>Nishitha (Shinoob Cousin)</t>
-  </si>
-  <si>
     <t>Cotton 2-piece set with blue floral prints-M (CHR-156), Short Kurti(CHR-151)-L, Dusty Rose Salwar(CHR-77)-L, Chanderis Silk Saree(Yellow-CHR-119), Matka - Lavender/Violet(CHR-174), red/maroon tissue fancy (CHR-199)</t>
   </si>
   <si>
-    <t>Nishitha Friend</t>
-  </si>
-  <si>
     <t>Blue/maroon, light green/maroon</t>
   </si>
   <si>
@@ -3362,24 +3350,54 @@
     <t>CHR-119 Chanderi Blue</t>
   </si>
   <si>
+    <t>Navya - Black Orange</t>
+  </si>
+  <si>
+    <t>Banarasi CM(CHR-183), Black Orange (CHR-204), CHR-199 - Navy/blue &amp; maroon/grey</t>
+  </si>
+  <si>
+    <t>red/maroon - Nishitha, Navy/blue &amp; maroon/grey - Navya</t>
+  </si>
+  <si>
+    <t>Nishida</t>
+  </si>
+  <si>
+    <t>Divya Jacob</t>
+  </si>
+  <si>
+    <t>Razia Salim</t>
+  </si>
+  <si>
+    <t>Banarasi Silk (New Design) - Chikku Green (CHR-188)</t>
+  </si>
+  <si>
+    <t>rust orange/coffee brown, peacock blue/navy, red/green, mustard/blue, chikku maroon, golden yellow &amp; green triangle</t>
+  </si>
+  <si>
+    <t>Green/maroon - Rajitha Teacher,  chikku green - Razia Salim</t>
+  </si>
+  <si>
+    <t>Baby Johny</t>
+  </si>
+  <si>
+    <t>2026--06-24</t>
+  </si>
+  <si>
+    <t>Chanderi White (CHR-119)</t>
+  </si>
+  <si>
     <t>First Set: Aruna - violet, Resmi - navy blue, Malini - Rani Pink
-Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black, Bindu Krisharaj - Black, Kavitha - off white, Jisha Suresh - Rani Pink(2), Sudharma - Navy Blue, SIndrella - Maroon, Shaino Benny - Navy blue, Simi Sudhir - Navy Blue, Supriya - Green, Mercy - Black, Kalisari - Green, Latha Suresh - Black, Shinoob cousin - mustard yellow, off white returned, Sumi Boben (Jet black), Jinu (Blue), Raji VT(Black), Nishitha friend (Orange), Karthika (Blue)</t>
+Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black, Bindu Krisharaj - Black, Kavitha - off white, Jisha Suresh - Rani Pink(2), Sudharma - Navy Blue, SIndrella - Maroon, Shaino Benny - Navy blue, Simi Sudhir - Navy Blue, Supriya - Green, Mercy - Black, Kalisari - Green, Latha Suresh - Black, Shinoob cousin - mustard yellow, off white returned, Sumi Boben (Jet black), Jinu (Blue), Raji VT(Black), Nishitha friend (Orange), Karthika (Blue), SIndhu (White)</t>
   </si>
   <si>
     <t xml:space="preserve">
-Maroon, Black, White(5)</t>
-  </si>
-  <si>
-    <t>Sanam, Geetha, Unknown, Jessy Joseph, Soji Thomas, Sheeba George, Sushma Bhaskar, Navya</t>
-  </si>
-  <si>
-    <t>Navya - Black Orange</t>
-  </si>
-  <si>
-    <t>Banarasi CM(CHR-183), Black Orange (CHR-204), CHR-199 - Navy/blue &amp; maroon/grey</t>
-  </si>
-  <si>
-    <t>red/maroon - Nishitha, Navy/blue &amp; maroon/grey - Navya</t>
+Maroon, Black, White(4)</t>
+  </si>
+  <si>
+    <t>Jayasree</t>
+  </si>
+  <si>
+    <t>Sanam, Geetha, Unknown, Jessy Joseph, Soji Thomas, Sheeba George, Sushma Bhaskar, Navya, Divya Jacob, Baby Johny, Jayashree</t>
   </si>
 </sst>
 </file>
@@ -4298,7 +4316,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>241</c:v>
+                  <c:v>246</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>88</c:v>
@@ -4401,7 +4419,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>148</c:v>
+                  <c:v>143</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>60</c:v>
@@ -4734,7 +4752,7 @@
                   <c:v>63190</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>111984.49333333333</c:v>
+                  <c:v>108001.54</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1062</c:v>
@@ -5064,7 +5082,7 @@
                   <c:v>4449</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>98456</c:v>
+                  <c:v>98616</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5209,22 +5227,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>45448</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19089</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16248</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>54177</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>54524</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>55717</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5649,22 +5667,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>-1863</c:v>
+                  <c:v>-47311</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13937</c:v>
+                  <c:v>-5152</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-5924</c:v>
+                  <c:v>-22172</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-16825</c:v>
+                  <c:v>-71002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>50075</c:v>
+                  <c:v>-4449</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-42739</c:v>
+                  <c:v>-98616</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -6131,10 +6149,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>333</c:v>
+                  <c:v>338</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-299</c:v>
+                  <c:v>-304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7291,7 +7309,7 @@
     <col min="4" max="4" width="30.1640625" style="6" customWidth="1"/>
     <col min="5" max="5" width="22.1640625" style="6" customWidth="1"/>
     <col min="6" max="6" width="31.1640625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" style="6" customWidth="1"/>
     <col min="8" max="16384" width="8.83203125" style="6"/>
   </cols>
   <sheetData>
@@ -7306,7 +7324,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>453560</v>
+        <v>453720</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -7321,7 +7339,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>398672</v>
+        <v>408891</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -7338,7 +7356,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>411230</v>
+        <v>417000</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -7355,7 +7373,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-54888</v>
+        <v>-44829</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -7390,7 +7408,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>43132.993333333347</v>
+        <v>43239.66</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -7400,7 +7418,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>15511.003333333341</v>
+        <v>15457.669999999998</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -7410,7 +7428,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-58643.996666666659</v>
+        <v>-58697.33</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -7449,15 +7467,15 @@
       </c>
       <c r="B18" s="10">
         <f>PartnerShares!B8</f>
-        <v>212623</v>
+        <v>212783</v>
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>151186.66666666666</v>
+        <v>151240</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>61436.333333333343</v>
+        <v>61543</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7465,11 +7483,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>43132.993333333347</v>
+        <v>43239.66</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹43,133</v>
+        <v>Receive ₹43,240</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -7483,11 +7501,11 @@
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>151186.66666666666</v>
+        <v>151240</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>57150.333333333343</v>
+        <v>57097</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7495,11 +7513,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>15511.003333333341</v>
+        <v>15457.669999999998</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹15,511</v>
+        <v>Receive ₹15,458</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -7513,11 +7531,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>151186.66666666666</v>
+        <v>151240</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-118586.66666666666</v>
+        <v>-118640</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7525,11 +7543,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-58643.996666666659</v>
+        <v>-58697.33</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹58,644</v>
+        <v>Pay ₹58,697</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -7567,15 +7585,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>331518</v>
+        <v>341737</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>132917.24479999999</v>
+        <v>136324.25939999998</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>198600.75520000001</v>
+        <v>205412.74060000002</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -7583,11 +7601,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>61290.729200000002</v>
+        <v>68102.714600000007</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹61,291</v>
+        <v>Pay ₹68,103</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -7601,11 +7619,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>132837.5104</v>
+        <v>136242.48120000001</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-78213.510399999999</v>
+        <v>-81618.481200000009</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -7613,11 +7631,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-6626.4683999999979</v>
+        <v>-10031.439200000008</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹6,626</v>
+        <v>Receive ₹10,031</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -7631,11 +7649,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>132917.24479999999</v>
+        <v>136324.25939999998</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-120387.24479999999</v>
+        <v>-123794.25939999998</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -7643,11 +7661,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-54664.260799999975</v>
+        <v>-58071.27539999997</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹54,664</v>
+        <v>Receive ₹58,071</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -7759,7 +7777,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46198</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -7768,14 +7786,14 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>453560</v>
+        <v>453720</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>398672</v>
+        <v>408891</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7784,14 +7802,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-54888</v>
+        <v>-44829</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>167827.69333333333</v>
+        <v>163844.74</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -7832,18 +7850,18 @@
       </c>
       <c r="C10" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A10)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>45448</v>
+        <v>0</v>
       </c>
       <c r="D10" s="21">
         <f t="shared" ref="D10:D21" si="0">C10-B10</f>
-        <v>-1863</v>
+        <v>-47311</v>
       </c>
       <c r="F10" s="25" t="s">
         <v>80</v>
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7856,18 +7874,18 @@
       </c>
       <c r="C11" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A11)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>19089</v>
+        <v>0</v>
       </c>
       <c r="D11" s="27">
         <f t="shared" si="0"/>
-        <v>13937</v>
+        <v>-5152</v>
       </c>
       <c r="F11" s="26" t="s">
         <v>82</v>
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>-299</v>
+        <v>-304</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7880,11 +7898,11 @@
       </c>
       <c r="C12" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A12)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>16248</v>
+        <v>0</v>
       </c>
       <c r="D12" s="21">
         <f t="shared" si="0"/>
-        <v>-5924</v>
+        <v>-22172</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
@@ -7897,11 +7915,11 @@
       </c>
       <c r="C13" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A13)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>54177</v>
+        <v>0</v>
       </c>
       <c r="D13" s="27">
         <f t="shared" si="0"/>
-        <v>-16825</v>
+        <v>-71002</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
@@ -7914,11 +7932,11 @@
       </c>
       <c r="C14" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A14)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>54524</v>
+        <v>0</v>
       </c>
       <c r="D14" s="21">
         <f t="shared" si="0"/>
-        <v>50075</v>
+        <v>-4449</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
@@ -7927,15 +7945,15 @@
       </c>
       <c r="B15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A15)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>98456</v>
+        <v>98616</v>
       </c>
       <c r="C15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>55717</v>
+        <v>0</v>
       </c>
       <c r="D15" s="27">
         <f t="shared" si="0"/>
-        <v>-42739</v>
+        <v>-98616</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
@@ -8063,11 +8081,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -8094,7 +8112,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>111984.49333333333</v>
+        <v>108001.54</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -9397,7 +9415,7 @@
         <v>300</v>
       </c>
       <c r="D86" s="36" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15" customHeight="1">
@@ -9411,14 +9429,22 @@
         <v>62</v>
       </c>
       <c r="D87" s="39" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15" customHeight="1">
-      <c r="A88" s="35"/>
-      <c r="B88" s="36"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="36"/>
+      <c r="A88" s="35">
+        <v>46197</v>
+      </c>
+      <c r="B88" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C88" s="37">
+        <v>160</v>
+      </c>
+      <c r="D88" s="36" t="s">
+        <v>1085</v>
+      </c>
     </row>
     <row r="89" spans="1:4" ht="15" customHeight="1">
       <c r="A89" s="38"/>
@@ -16896,7 +16922,7 @@
         <v>46188</v>
       </c>
       <c r="B216" s="53" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="C216" s="54">
         <v>5000</v>
@@ -16910,7 +16936,7 @@
       <c r="F216" s="56"/>
       <c r="G216" s="56"/>
       <c r="H216" s="57" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="I216" s="53" t="s">
         <v>142</v>
@@ -16946,7 +16972,7 @@
         <v>46191</v>
       </c>
       <c r="B218" s="53" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C218" s="54">
         <v>1380</v>
@@ -16960,7 +16986,7 @@
       <c r="F218" s="56"/>
       <c r="G218" s="56"/>
       <c r="H218" s="57" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="I218" s="53" t="s">
         <v>142</v>
@@ -16971,7 +16997,7 @@
         <v>46191</v>
       </c>
       <c r="B219" s="49" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C219" s="50">
         <v>1380</v>
@@ -16996,7 +17022,7 @@
         <v>46191</v>
       </c>
       <c r="B220" s="53" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="C220" s="54">
         <v>1380</v>
@@ -17046,7 +17072,7 @@
         <v>46191</v>
       </c>
       <c r="B222" s="53" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C222" s="54">
         <v>1380</v>
@@ -17071,7 +17097,7 @@
         <v>46191</v>
       </c>
       <c r="B223" s="49" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="C223" s="50">
         <v>1380</v>
@@ -17096,7 +17122,7 @@
         <v>46191</v>
       </c>
       <c r="B224" s="53" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C224" s="54">
         <v>1380</v>
@@ -17121,7 +17147,7 @@
         <v>46192</v>
       </c>
       <c r="B225" s="49" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C225" s="50">
         <v>1380</v>
@@ -17146,7 +17172,7 @@
         <v>46192</v>
       </c>
       <c r="B226" s="53" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C226" s="54">
         <v>1380</v>
@@ -17171,7 +17197,7 @@
         <v>46192</v>
       </c>
       <c r="B227" s="49" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C227" s="50">
         <v>1380</v>
@@ -17196,7 +17222,7 @@
         <v>46192</v>
       </c>
       <c r="B228" s="53" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C228" s="54">
         <v>1380</v>
@@ -17221,7 +17247,7 @@
         <v>46193</v>
       </c>
       <c r="B229" s="49" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C229" s="50">
         <v>699</v>
@@ -17235,7 +17261,7 @@
       <c r="F229" s="49"/>
       <c r="G229" s="49"/>
       <c r="H229" s="51" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="I229" s="49" t="s">
         <v>142</v>
@@ -17246,7 +17272,7 @@
         <v>46193</v>
       </c>
       <c r="B230" s="53" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C230" s="54">
         <v>699</v>
@@ -17260,7 +17286,7 @@
       <c r="F230" s="56"/>
       <c r="G230" s="56"/>
       <c r="H230" s="57" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="I230" s="53" t="s">
         <v>142</v>
@@ -17271,7 +17297,7 @@
         <v>46193</v>
       </c>
       <c r="B231" s="49" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C231" s="50">
         <v>1380</v>
@@ -17296,7 +17322,7 @@
         <v>46193</v>
       </c>
       <c r="B232" s="53" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C232" s="54">
         <v>699</v>
@@ -17310,7 +17336,7 @@
       <c r="F232" s="56"/>
       <c r="G232" s="56"/>
       <c r="H232" s="57" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="I232" s="53" t="s">
         <v>142</v>
@@ -17321,7 +17347,7 @@
         <v>46193</v>
       </c>
       <c r="B233" s="49" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="C233" s="50">
         <v>1380</v>
@@ -17356,7 +17382,7 @@
       <c r="F234" s="56"/>
       <c r="G234" s="56"/>
       <c r="H234" s="57" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="I234" s="53" t="s">
         <v>341</v>
@@ -17370,17 +17396,21 @@
         <v>147</v>
       </c>
       <c r="C235" s="50">
-        <v>4449</v>
-      </c>
-      <c r="D235" s="49"/>
-      <c r="E235" s="49"/>
+        <v>4000</v>
+      </c>
+      <c r="D235" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E235" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F235" s="49"/>
       <c r="G235" s="49"/>
       <c r="H235" s="51" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="I235" s="49" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
     </row>
     <row r="236" spans="1:9" ht="14">
@@ -17388,7 +17418,7 @@
         <v>46194</v>
       </c>
       <c r="B236" s="53" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="C236" s="54">
         <v>699</v>
@@ -17398,7 +17428,7 @@
       <c r="F236" s="56"/>
       <c r="G236" s="56"/>
       <c r="H236" s="57" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="I236" s="53" t="s">
         <v>341</v>
@@ -17409,7 +17439,7 @@
         <v>46194</v>
       </c>
       <c r="B237" s="49" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="C237" s="50">
         <v>2480</v>
@@ -17423,7 +17453,7 @@
       <c r="F237" s="49"/>
       <c r="G237" s="49"/>
       <c r="H237" s="51" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="I237" s="49" t="s">
         <v>142</v>
@@ -17434,7 +17464,7 @@
         <v>46196</v>
       </c>
       <c r="B238" s="53" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="C238" s="54">
         <v>700</v>
@@ -17448,7 +17478,7 @@
       <c r="F238" s="56"/>
       <c r="G238" s="56"/>
       <c r="H238" s="57" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="I238" s="53" t="s">
         <v>142</v>
@@ -17459,7 +17489,7 @@
         <v>46196</v>
       </c>
       <c r="B239" s="49" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="C239" s="50">
         <v>1380</v>
@@ -17473,7 +17503,7 @@
       <c r="F239" s="49"/>
       <c r="G239" s="49"/>
       <c r="H239" s="51" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="I239" s="49" t="s">
         <v>142</v>
@@ -17484,7 +17514,7 @@
         <v>46196</v>
       </c>
       <c r="B240" s="53" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="C240" s="54">
         <v>699</v>
@@ -17498,7 +17528,7 @@
       <c r="F240" s="56"/>
       <c r="G240" s="56"/>
       <c r="H240" s="57" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="I240" s="53" t="s">
         <v>142</v>
@@ -17523,66 +17553,136 @@
       <c r="F241" s="49"/>
       <c r="G241" s="49"/>
       <c r="H241" s="51" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="I241" s="49" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="242" spans="1:9">
-      <c r="A242" s="52"/>
-      <c r="B242" s="53"/>
-      <c r="C242" s="54"/>
-      <c r="D242" s="53"/>
-      <c r="E242" s="53"/>
+    <row r="242" spans="1:9" ht="14">
+      <c r="A242" s="52">
+        <v>46197</v>
+      </c>
+      <c r="B242" s="53" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C242" s="54">
+        <v>1380</v>
+      </c>
+      <c r="D242" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E242" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F242" s="56"/>
       <c r="G242" s="56"/>
-      <c r="H242" s="57"/>
-      <c r="I242" s="53"/>
-    </row>
-    <row r="243" spans="1:9">
-      <c r="A243" s="48"/>
-      <c r="B243" s="49"/>
-      <c r="C243" s="50"/>
-      <c r="D243" s="49"/>
-      <c r="E243" s="49"/>
+      <c r="H242" s="57" t="s">
+        <v>358</v>
+      </c>
+      <c r="I242" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" ht="14">
+      <c r="A243" s="48">
+        <v>46197</v>
+      </c>
+      <c r="B243" s="49" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C243" s="50">
+        <v>1380</v>
+      </c>
+      <c r="D243" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E243" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F243" s="49"/>
       <c r="G243" s="49"/>
-      <c r="H243" s="51"/>
-      <c r="I243" s="49"/>
-    </row>
-    <row r="244" spans="1:9">
-      <c r="A244" s="52"/>
-      <c r="B244" s="53"/>
-      <c r="C244" s="54"/>
-      <c r="D244" s="53"/>
-      <c r="E244" s="53"/>
+      <c r="H243" s="51" t="s">
+        <v>1101</v>
+      </c>
+      <c r="I243" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" ht="14">
+      <c r="A244" s="52">
+        <v>46197</v>
+      </c>
+      <c r="B244" s="53" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C244" s="54">
+        <v>1380</v>
+      </c>
+      <c r="D244" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E244" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F244" s="56"/>
       <c r="G244" s="56"/>
-      <c r="H244" s="57"/>
-      <c r="I244" s="53"/>
-    </row>
-    <row r="245" spans="1:9">
-      <c r="A245" s="48"/>
-      <c r="B245" s="49"/>
-      <c r="C245" s="50"/>
-      <c r="D245" s="49"/>
-      <c r="E245" s="49"/>
+      <c r="H244" s="57" t="s">
+        <v>358</v>
+      </c>
+      <c r="I244" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" ht="14">
+      <c r="A245" s="48" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B245" s="49" t="s">
+        <v>159</v>
+      </c>
+      <c r="C245" s="50">
+        <v>699</v>
+      </c>
+      <c r="D245" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E245" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F245" s="49"/>
       <c r="G245" s="49"/>
-      <c r="H245" s="51"/>
-      <c r="I245" s="49"/>
-    </row>
-    <row r="246" spans="1:9">
-      <c r="A246" s="52"/>
-      <c r="B246" s="53"/>
-      <c r="C246" s="54"/>
-      <c r="D246" s="53"/>
-      <c r="E246" s="53"/>
+      <c r="H245" s="51" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I245" s="49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" ht="14">
+      <c r="A246" s="52">
+        <v>46198</v>
+      </c>
+      <c r="B246" s="53" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C246" s="54">
+        <v>1380</v>
+      </c>
+      <c r="D246" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E246" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F246" s="56"/>
       <c r="G246" s="56"/>
-      <c r="H246" s="57"/>
-      <c r="I246" s="53"/>
+      <c r="H246" s="57" t="s">
+        <v>358</v>
+      </c>
+      <c r="I246" s="53" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="247" spans="1:9">
       <c r="A247" s="48"/>
@@ -27579,10 +27679,10 @@
         <v>699</v>
       </c>
       <c r="F120" s="67">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G120" s="67">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H120" s="66">
         <f t="shared" si="9"/>
@@ -27594,14 +27694,14 @@
       </c>
       <c r="J120" s="66">
         <f t="shared" si="10"/>
-        <v>16339.179999999986</v>
+        <v>16758.13333333332</v>
       </c>
       <c r="K120" s="66">
         <f t="shared" si="11"/>
-        <v>2932.6733333333309</v>
+        <v>2513.719999999998</v>
       </c>
       <c r="L120" s="66" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="M120" s="66" t="s">
         <v>49</v>
@@ -27611,7 +27711,7 @@
       </c>
       <c r="O120" s="66"/>
       <c r="P120" s="66" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="Q120" s="66"/>
       <c r="R120" s="66"/>
@@ -30011,7 +30111,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="69" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="M153" s="69"/>
       <c r="N153" s="69" t="s">
@@ -31175,7 +31275,7 @@
         <v>4189.5</v>
       </c>
       <c r="L175" s="69" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="M175" s="69"/>
       <c r="N175" s="69" t="s">
@@ -31183,7 +31283,7 @@
       </c>
       <c r="O175" s="69"/>
       <c r="P175" s="69" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="Q175" s="69"/>
       <c r="R175" s="69"/>
@@ -31628,10 +31728,10 @@
         <v>1380</v>
       </c>
       <c r="F184" s="81">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G184" s="81">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H184" s="80">
         <f t="shared" ref="H184:H226" si="23">F184+IF(LEN(G184)=0,0,G184)</f>
@@ -31643,14 +31743,14 @@
       </c>
       <c r="J184" s="80">
         <f t="shared" si="21"/>
-        <v>7128</v>
+        <v>9801</v>
       </c>
       <c r="K184" s="80">
         <f t="shared" si="22"/>
-        <v>10692</v>
+        <v>8019</v>
       </c>
       <c r="L184" s="66" t="s">
-        <v>1101</v>
+        <v>1110</v>
       </c>
       <c r="M184" s="66"/>
       <c r="N184" s="66" t="s">
@@ -31702,7 +31802,7 @@
         <v>0</v>
       </c>
       <c r="L185" s="69" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="M185" s="69"/>
       <c r="N185" s="69" t="s">
@@ -31865,7 +31965,7 @@
       <c r="S188" s="66"/>
       <c r="T188" s="66"/>
     </row>
-    <row r="189" spans="1:20" ht="45">
+    <row r="189" spans="1:20" ht="30">
       <c r="A189" s="69" t="s">
         <v>965</v>
       </c>
@@ -31882,10 +31982,10 @@
         <v>1380</v>
       </c>
       <c r="F189" s="79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G189" s="79">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H189" s="78">
         <f t="shared" si="23"/>
@@ -31897,14 +31997,14 @@
       </c>
       <c r="J189" s="78">
         <f t="shared" si="21"/>
-        <v>891</v>
+        <v>1782</v>
       </c>
       <c r="K189" s="78">
         <f t="shared" si="22"/>
-        <v>6237</v>
+        <v>5346</v>
       </c>
       <c r="L189" s="69" t="s">
-        <v>1015</v>
+        <v>1103</v>
       </c>
       <c r="M189" s="69"/>
       <c r="N189" s="69" t="s">
@@ -31912,7 +32012,7 @@
       </c>
       <c r="O189" s="69"/>
       <c r="P189" s="69" t="s">
-        <v>1014</v>
+        <v>1102</v>
       </c>
       <c r="Q189" s="69"/>
       <c r="R189" s="69"/>
@@ -31973,7 +32073,7 @@
         <v>967</v>
       </c>
       <c r="B191" s="66" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C191" s="66" t="s">
         <v>95</v>
@@ -32012,7 +32112,7 @@
         <v>598</v>
       </c>
       <c r="P191" s="61" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="S191" s="61"/>
       <c r="T191" s="61"/>
@@ -32022,7 +32122,7 @@
         <v>968</v>
       </c>
       <c r="B192" s="69" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C192" s="69" t="s">
         <v>95</v>
@@ -32061,7 +32161,7 @@
         <v>598</v>
       </c>
       <c r="P192" s="61" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="S192" s="61"/>
       <c r="T192" s="61"/>
@@ -32071,7 +32171,7 @@
         <v>969</v>
       </c>
       <c r="B193" s="66" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C193" s="66" t="s">
         <v>95</v>
@@ -32110,7 +32210,7 @@
         <v>598</v>
       </c>
       <c r="P193" s="61" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="S193" s="61"/>
       <c r="T193" s="61"/>
@@ -32120,7 +32220,7 @@
         <v>970</v>
       </c>
       <c r="B194" s="66" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C194" s="66" t="s">
         <v>95</v>
@@ -32159,7 +32259,7 @@
         <v>598</v>
       </c>
       <c r="P194" s="61" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="S194" s="61"/>
       <c r="T194" s="61"/>
@@ -32169,7 +32269,7 @@
         <v>971</v>
       </c>
       <c r="B195" s="69" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C195" s="69" t="s">
         <v>95</v>
@@ -32203,14 +32303,14 @@
         <v>5467</v>
       </c>
       <c r="L195" s="69" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="M195" s="69"/>
       <c r="N195" s="61" t="s">
         <v>510</v>
       </c>
       <c r="P195" s="61" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="S195" s="61"/>
       <c r="T195" s="61"/>
@@ -32220,7 +32320,7 @@
         <v>972</v>
       </c>
       <c r="B196" s="66" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C196" s="66" t="s">
         <v>95</v>
@@ -32259,7 +32359,7 @@
         <v>598</v>
       </c>
       <c r="P196" s="61" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="S196" s="61"/>
       <c r="T196" s="61"/>
@@ -32269,7 +32369,7 @@
         <v>973</v>
       </c>
       <c r="B197" s="69" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C197" s="69" t="s">
         <v>95</v>
@@ -32308,7 +32408,7 @@
         <v>598</v>
       </c>
       <c r="P197" s="61" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="S197" s="61"/>
       <c r="T197" s="61"/>
@@ -32318,7 +32418,7 @@
         <v>974</v>
       </c>
       <c r="B198" s="66" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C198" s="66" t="s">
         <v>95</v>
@@ -32357,7 +32457,7 @@
         <v>598</v>
       </c>
       <c r="P198" s="61" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="S198" s="61"/>
       <c r="T198" s="61"/>
@@ -32367,7 +32467,7 @@
         <v>975</v>
       </c>
       <c r="B199" s="66" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C199" s="66" t="s">
         <v>95</v>
@@ -32406,7 +32506,7 @@
         <v>598</v>
       </c>
       <c r="P199" s="61" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="S199" s="61"/>
       <c r="T199" s="61"/>
@@ -32416,7 +32516,7 @@
         <v>976</v>
       </c>
       <c r="B200" s="69" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C200" s="69" t="s">
         <v>95</v>
@@ -32450,14 +32550,14 @@
         <v>1732</v>
       </c>
       <c r="L200" s="66" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
       <c r="M200" s="66"/>
       <c r="N200" s="61" t="s">
         <v>510</v>
       </c>
       <c r="P200" s="61" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="S200" s="61"/>
       <c r="T200" s="61"/>
@@ -32467,7 +32567,7 @@
         <v>977</v>
       </c>
       <c r="B201" s="66" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C201" s="66" t="s">
         <v>95</v>
@@ -32501,14 +32601,14 @@
         <v>724</v>
       </c>
       <c r="L201" s="69" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="M201" s="69"/>
       <c r="N201" s="61" t="s">
         <v>510</v>
       </c>
       <c r="P201" s="61" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="S201" s="61"/>
       <c r="T201" s="61"/>
@@ -32518,7 +32618,7 @@
         <v>978</v>
       </c>
       <c r="B202" s="69" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C202" s="69" t="s">
         <v>95</v>
@@ -32557,7 +32657,7 @@
         <v>598</v>
       </c>
       <c r="P202" s="61" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="S202" s="61"/>
       <c r="T202" s="61"/>
@@ -32567,7 +32667,7 @@
         <v>979</v>
       </c>
       <c r="B203" s="66" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C203" s="66" t="s">
         <v>95</v>
@@ -32601,14 +32701,14 @@
         <v>0</v>
       </c>
       <c r="L203" s="69" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="M203" s="69"/>
       <c r="N203" s="61" t="s">
         <v>425</v>
       </c>
       <c r="P203" s="61" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="S203" s="61"/>
       <c r="T203" s="61"/>
@@ -32618,7 +32718,7 @@
         <v>980</v>
       </c>
       <c r="B204" s="66" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C204" s="66" t="s">
         <v>95</v>
@@ -32652,14 +32752,14 @@
         <v>1760</v>
       </c>
       <c r="L204" s="66" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="M204" s="66"/>
       <c r="N204" s="61" t="s">
         <v>510</v>
       </c>
       <c r="P204" s="61" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="S204" s="61"/>
       <c r="T204" s="61"/>
@@ -32669,7 +32769,7 @@
         <v>981</v>
       </c>
       <c r="B205" s="69" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C205" s="69" t="s">
         <v>95</v>
@@ -32703,14 +32803,14 @@
         <v>1522</v>
       </c>
       <c r="L205" s="69" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
       <c r="M205" s="69"/>
       <c r="N205" s="61" t="s">
         <v>598</v>
       </c>
       <c r="P205" s="61" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="S205" s="61"/>
       <c r="T205" s="61"/>
@@ -32720,7 +32820,7 @@
         <v>982</v>
       </c>
       <c r="B206" s="66" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C206" s="66" t="s">
         <v>95</v>
@@ -32759,7 +32859,7 @@
         <v>598</v>
       </c>
       <c r="P206" s="61" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="S206" s="61"/>
       <c r="T206" s="61"/>
@@ -32769,7 +32869,7 @@
         <v>983</v>
       </c>
       <c r="B207" s="69" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C207" s="69" t="s">
         <v>95</v>
@@ -32803,14 +32903,14 @@
         <v>3312</v>
       </c>
       <c r="L207" s="69" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="M207" s="69"/>
       <c r="N207" s="61" t="s">
         <v>510</v>
       </c>
       <c r="P207" s="61" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="S207" s="61"/>
       <c r="T207" s="61"/>
@@ -32820,7 +32920,7 @@
         <v>984</v>
       </c>
       <c r="B208" s="66" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C208" s="66" t="s">
         <v>95</v>
@@ -32859,7 +32959,7 @@
         <v>598</v>
       </c>
       <c r="P208" s="61" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="S208" s="61"/>
       <c r="T208" s="61"/>
@@ -32869,7 +32969,7 @@
         <v>985</v>
       </c>
       <c r="B209" s="66" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C209" s="66" t="s">
         <v>95</v>
@@ -32908,7 +33008,7 @@
         <v>598</v>
       </c>
       <c r="P209" s="61" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="S209" s="61"/>
       <c r="T209" s="61"/>
@@ -32918,7 +33018,7 @@
         <v>986</v>
       </c>
       <c r="B210" s="69" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="C210" s="69" t="s">
         <v>95</v>
@@ -32957,7 +33057,7 @@
         <v>598</v>
       </c>
       <c r="P210" s="61" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="S210" s="61"/>
       <c r="T210" s="61"/>
@@ -32967,7 +33067,7 @@
         <v>987</v>
       </c>
       <c r="B211" s="66" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="C211" s="66" t="s">
         <v>95</v>
@@ -33006,7 +33106,7 @@
         <v>598</v>
       </c>
       <c r="P211" s="61" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="S211" s="61"/>
       <c r="T211" s="61"/>
@@ -37487,15 +37587,15 @@
       </c>
       <c r="B8" s="9">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A8,Purchases!$C:$C),0)</f>
-        <v>212623</v>
+        <v>212783</v>
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>151186.66666666666</v>
+        <v>151240</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>61436.333333333343</v>
+        <v>61543</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -37503,7 +37603,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>61436.333333333343</v>
+        <v>61543</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -37511,7 +37611,7 @@
       </c>
       <c r="H8" s="88">
         <f>F8-G8</f>
-        <v>43132.993333333347</v>
+        <v>43239.66</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -37524,11 +37624,11 @@
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>151186.66666666666</v>
+        <v>151240</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>57150.333333333343</v>
+        <v>57097</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -37536,7 +37636,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>57150.333333333343</v>
+        <v>57097</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -37544,7 +37644,7 @@
       </c>
       <c r="H9" s="89">
         <f>F9-G9</f>
-        <v>15511.003333333341</v>
+        <v>15457.669999999998</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -37557,11 +37657,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>151186.66666666666</v>
+        <v>151240</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-118586.66666666666</v>
+        <v>-118640</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -37569,7 +37669,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-118586.66666666666</v>
+        <v>-118640</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -37577,7 +37677,7 @@
       </c>
       <c r="H10" s="88">
         <f>F10-G10</f>
-        <v>-58643.996666666659</v>
+        <v>-58697.33</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="90" customFormat="1" ht="15.75" customHeight="1">
@@ -37994,7 +38094,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>331518</v>
+        <v>341737</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -38002,11 +38102,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>132917.24479999999</v>
+        <v>136324.25939999998</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>198600.75520000001</v>
+        <v>205412.74060000002</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -38014,7 +38114,7 @@
       </c>
       <c r="G4" s="88">
         <f>E4+F4</f>
-        <v>61290.729200000002</v>
+        <v>68102.714600000007</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -38031,11 +38131,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>132837.5104</v>
+        <v>136242.48120000001</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-78213.510399999999</v>
+        <v>-81618.481200000009</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -38043,7 +38143,7 @@
       </c>
       <c r="G5" s="89">
         <f>E5+F5</f>
-        <v>-6626.4683999999979</v>
+        <v>-10031.439200000008</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -38060,11 +38160,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>132917.24479999999</v>
+        <v>136324.25939999998</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-120387.24479999999</v>
+        <v>-123794.25939999998</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -38072,7 +38172,7 @@
       </c>
       <c r="G6" s="88">
         <f>E6+F6</f>
-        <v>-54664.260799999975</v>
+        <v>-58071.27539999997</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">

--- a/docs/Chiraath-Summary-Jun26.xlsx
+++ b/docs/Chiraath-Summary-Jun26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28503694-F265-C041-8B38-BFBDB47A882E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F50DF1-8180-E740-A481-E7CA8F64093F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2776" uniqueCount="1111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2813" uniqueCount="1125">
   <si>
     <t>Notes:</t>
   </si>
@@ -1403,9 +1403,6 @@
   </si>
   <si>
     <t>Nishida</t>
-  </si>
-  <si>
-    <t>Cotton 2-piece set with blue floral prints-M (CHR-156), Short Kurti(CHR-151)-L, Dusty Rose Salwar(CHR-77)-L, Chanderis Silk Saree(Yellow-CHR-119), Matka - Lavender/Violet(CHR-174), red/maroon tissue fancy (CHR-199)</t>
   </si>
   <si>
     <t>Rajitha Teacher</t>
@@ -2419,14 +2416,6 @@
     <t>Chanderi Printed Silk Saree</t>
   </si>
   <si>
-    <t>First Set: Aruna - violet, Resmi - navy blue, Malini - Rani Pink
-Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black, Bindu Krisharaj - Black, Kavitha - off white, Jisha Suresh - Rani Pink(2), Sudharma - Navy Blue, SIndrella - Maroon, Shaino Benny - Navy blue, Simi Sudhir - Navy Blue, Supriya - Green, Mercy - Black, Kalisari - Green, Latha Suresh - Black, Shinoob cousin - mustard yellow, off white returned, Sumi Boben (Jet black), Jinu (Blue), Raji VT(Black), Nishitha friend (Orange), Karthika (Blue), SIndhu (White)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Maroon, Black, White(4)</t>
-  </si>
-  <si>
     <t>CHR-120</t>
   </si>
   <si>
@@ -2653,13 +2642,6 @@
     <t>Matka Silk Saree collections - old design</t>
   </si>
   <si>
-    <t>Blue/bottle green - Saranya Hyd, Blue/red - Jothika, Mustard - Vineetha, Bottle Green/Golden Yellow - Swapna (Thrissur)-1200, Black/Golden yellow - Kavya(Kasargod) - 1200, Back/Yellow - Subha - 1200</t>
-  </si>
-  <si>
-    <t>Bottle Green/Golden Yellow - 1
-Navy Blue/Bottle Green - 2</t>
-  </si>
-  <si>
     <t>CHR-147</t>
   </si>
   <si>
@@ -3019,9 +3001,6 @@
     <t>Banarasil Silk (Chikku Maroon)</t>
   </si>
   <si>
-    <t>Sheeba George, Soji Thomas, Jessy Joseph, Jeeja Anil ,Sanam, Geetha, Sushama Bhaskar, Divya Jacob, Baby Johny, Jayasree, Navya, Bindu Saji, Vanajakshi</t>
-  </si>
-  <si>
     <t>CHR-184</t>
   </si>
   <si>
@@ -3052,12 +3031,6 @@
     <t>Banarasi Silk (New Design)</t>
   </si>
   <si>
-    <t>Green/maroon - Rajitha Teacher,  chikku green - Razia Salim, Rust Orange/Coffee Brown - Nishida</t>
-  </si>
-  <si>
-    <t>peacock blue/navy, red/green, mustard/blue, chikku maroon, golden yellow &amp; green triangle</t>
-  </si>
-  <si>
     <t>CHR-189</t>
   </si>
   <si>
@@ -3085,9 +3058,6 @@
     <t>Kerala Sarees with Floral design</t>
   </si>
   <si>
-    <t>Floral green, floral peach, floral lavender</t>
-  </si>
-  <si>
     <t>CHR-192</t>
   </si>
   <si>
@@ -3124,9 +3094,6 @@
     <t>Cotton Saree Collections (Body Jergai)</t>
   </si>
   <si>
-    <t xml:space="preserve">Mustard, navy, rani pink, olive green (×2), purple </t>
-  </si>
-  <si>
     <t>CHR-196</t>
   </si>
   <si>
@@ -3160,12 +3127,6 @@
     <t>Tissue Fancy Saree with Butta</t>
   </si>
   <si>
-    <t>red/maroon - Nishitha, Navy/blue &amp; maroon/grey - Navya</t>
-  </si>
-  <si>
-    <t>Navy/blue, green/navy, maroon/grey, red/maroon, dark green/navy</t>
-  </si>
-  <si>
     <t>CHR-200</t>
   </si>
   <si>
@@ -3259,9 +3220,6 @@
     <t>Kerala Saree Collections Check/Floral</t>
   </si>
   <si>
-    <t>Checks/floral + leaf, checks/floral + kathakali</t>
-  </si>
-  <si>
     <t>CHR-209</t>
   </si>
   <si>
@@ -3398,6 +3356,90 @@
   </si>
   <si>
     <t>5. Cash Position After Settlements = Over/(Under) + Net Cash Settlements.</t>
+  </si>
+  <si>
+    <t>Blue/bottle green - Saranya Hyd, Blue/red - Jothika, Mustard - Vineetha, Bottle Green/Golden Yellow - Swapna (Thrissur)-1200, Black/Golden yellow - Kavya(Kasargod) - 1200, Back/Yellow - Subha - 1200, Navy Blue/Bottle Green - Latha</t>
+  </si>
+  <si>
+    <t>Bottle Green/Golden Yellow - 1
+Navy Blue/Bottle Green - 1</t>
+  </si>
+  <si>
+    <t>Matka old design - Navy Blue/Bottle Green</t>
+  </si>
+  <si>
+    <t>Leena - 950</t>
+  </si>
+  <si>
+    <t>Net Kota Stairs</t>
+  </si>
+  <si>
+    <t>Mustard, navy, rani pink, olive green (×2)</t>
+  </si>
+  <si>
+    <t>purple - Malini</t>
+  </si>
+  <si>
+    <t>Sheeba George, Soji Thomas, Jessy Joseph, Jeeja Anil ,Sanam, Geetha, Sushama Bhaskar, Divya Jacob, Baby Johny, Jayasree, Navya, Bindu Saji, Vanajakshi, Abudhabi Customer</t>
+  </si>
+  <si>
+    <t>Abudabi Customer</t>
+  </si>
+  <si>
+    <t>Linu Goerge</t>
+  </si>
+  <si>
+    <t>CHR-119 Black</t>
+  </si>
+  <si>
+    <t>Sheeja S</t>
+  </si>
+  <si>
+    <t>CHR-119 White</t>
+  </si>
+  <si>
+    <t>SARANYA S</t>
+  </si>
+  <si>
+    <t>CHR-119 Maroon</t>
+  </si>
+  <si>
+    <t>First Set: Aruna - violet, Resmi - navy blue, Malini - Rani Pink
+Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange, Saritha - Rani Pink, Rose - Black, Bindu Krisharaj - Black, Kavitha - off white, Jisha Suresh - Rani Pink(2), Sudharma - Navy Blue, SIndrella - Maroon, Shaino Benny - Navy blue, Simi Sudhir - Navy Blue, Supriya - Green, Mercy - Black, Kalisari - Green, Latha Suresh - Black, Shinoob cousin - mustard yellow, off white returned, Sumi Boben (Jet black), Jinu (Blue), Raji VT(Black), Nishitha friend (Orange), Karthika (Blue), SIndhu (White), Linu George (Black), Sheeja S(White), Sarnya (Maroon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+White(3)</t>
+  </si>
+  <si>
+    <t>CHR-191 (Floral Green) &amp; CHR-208 (Kathakali)</t>
+  </si>
+  <si>
+    <t>Nishida friend - 1250</t>
+  </si>
+  <si>
+    <t>floral peach, floral lavender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checks/floral + leaf, </t>
+  </si>
+  <si>
+    <t>Nishida friend - 1400 - checks/floral + kathakali</t>
+  </si>
+  <si>
+    <t>Navy/blue &amp; maroon/grey - Navya</t>
+  </si>
+  <si>
+    <t>Green/Navy, Red/maroon, Dark green/Navy</t>
+  </si>
+  <si>
+    <t>Cotton 2-piece set with blue floral prints-M (CHR-156), Short Kurti(CHR-151)-L, Dusty Rose Salwar(CHR-77)-L, Chanderis Silk Saree(Yellow-CHR-119), Matka - Lavender/Violet(CHR-174), Chikku Maroon new design(CHR-188)</t>
+  </si>
+  <si>
+    <t>peacock blue/navy, red/green, mustard/blue, golden yellow &amp; green triangle</t>
+  </si>
+  <si>
+    <t>Green/maroon - Rajitha Teacher,  chikku green - Razia Salim, Rust Orange/Coffee Brown - Nishida, Chikku Maroon(1200) - Nishida</t>
   </si>
 </sst>
 </file>
@@ -4310,7 +4352,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>250</c:v>
+                  <c:v>259</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>88</c:v>
@@ -4413,7 +4455,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>139</c:v>
+                  <c:v>130</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>60</c:v>
@@ -4746,7 +4788,7 @@
                   <c:v>63190</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>104728.54</c:v>
+                  <c:v>98094.68</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1062</c:v>
@@ -5076,7 +5118,7 @@
                   <c:v>4449</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>98616</c:v>
+                  <c:v>98803</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5236,7 +5278,7 @@
                   <c:v>54524</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>63757</c:v>
+                  <c:v>72035</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5676,7 +5718,7 @@
                   <c:v>50075</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-34859</c:v>
+                  <c:v>-26768</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -6143,10 +6185,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>342</c:v>
+                  <c:v>351</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-308</c:v>
+                  <c:v>-317</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7318,7 +7360,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>453720</v>
+        <v>453907</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -7333,7 +7375,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>411161</v>
+        <v>417988</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -7350,7 +7392,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>419270</v>
+        <v>427548</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -7367,7 +7409,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-42559</v>
+        <v>-35919</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -7402,7 +7444,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>43239.66</v>
+        <v>43364.32666666666</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -7412,7 +7454,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>15457.669999999998</v>
+        <v>15395.336666666655</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -7422,7 +7464,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-58697.33</v>
+        <v>-58759.663333333345</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -7461,15 +7503,15 @@
       </c>
       <c r="B18" s="10">
         <f>PartnerShares!B8</f>
-        <v>212783</v>
+        <v>212970</v>
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>151240</v>
+        <v>151302.33333333334</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>61543</v>
+        <v>61667.666666666657</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7477,11 +7519,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>43239.66</v>
+        <v>43364.32666666666</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹43,240</v>
+        <v>Receive ₹43,364</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -7495,11 +7537,11 @@
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>151240</v>
+        <v>151302.33333333334</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>57097</v>
+        <v>57034.666666666657</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7507,11 +7549,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>15457.669999999998</v>
+        <v>15395.336666666655</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹15,458</v>
+        <v>Receive ₹15,395</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -7525,11 +7567,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>151240</v>
+        <v>151302.33333333334</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-118640</v>
+        <v>-118702.33333333334</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7537,11 +7579,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-58697.33</v>
+        <v>-58759.663333333345</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹58,697</v>
+        <v>Pay ₹58,760</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -7579,15 +7621,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>344007</v>
+        <v>350834</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>137081.07739999998</v>
+        <v>139357.1992</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>206925.92260000002</v>
+        <v>211476.8008</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -7595,11 +7637,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>69615.896600000007</v>
+        <v>74166.774799999985</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹69,616</v>
+        <v>Pay ₹74,167</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -7613,11 +7655,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>136998.84520000001</v>
+        <v>139273.60159999999</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-82374.845200000011</v>
+        <v>-84649.601599999995</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -7625,11 +7667,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-10787.803200000009</v>
+        <v>-13062.559599999993</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹10,788</v>
+        <v>Receive ₹13,063</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -7643,11 +7685,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>137081.07739999998</v>
+        <v>139357.1992</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-124551.07739999998</v>
+        <v>-126827.1992</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -7655,11 +7697,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-58828.093399999969</v>
+        <v>-61104.215199999991</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹58,828</v>
+        <v>Receive ₹61,104</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -7771,7 +7813,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46201</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -7780,14 +7822,14 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>453720</v>
+        <v>453907</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>411161</v>
+        <v>417988</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7796,14 +7838,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-42559</v>
+        <v>-35919</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>160571.74</v>
+        <v>153937.88</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -7855,7 +7897,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>342</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7879,7 +7921,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>-308</v>
+        <v>-317</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7939,15 +7981,15 @@
       </c>
       <c r="B15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A15)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>98616</v>
+        <v>98803</v>
       </c>
       <c r="C15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$995,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$995)=$B$7)*Sales!$C$2:$C$995),0)</f>
-        <v>63757</v>
+        <v>72035</v>
       </c>
       <c r="D15" s="27">
         <f t="shared" si="0"/>
-        <v>-34859</v>
+        <v>-26768</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
@@ -8075,11 +8117,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -8106,7 +8148,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>104728.54</v>
+        <v>98094.68</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -9392,7 +9434,7 @@
         <v>49</v>
       </c>
       <c r="C85" s="40">
-        <v>18720</v>
+        <v>18907</v>
       </c>
       <c r="D85" s="39" t="s">
         <v>118</v>
@@ -16930,7 +16972,7 @@
       <c r="F216" s="56"/>
       <c r="G216" s="56"/>
       <c r="H216" s="57" t="s">
-        <v>452</v>
+        <v>1122</v>
       </c>
       <c r="I216" s="53" t="s">
         <v>148</v>
@@ -16941,7 +16983,7 @@
         <v>46191</v>
       </c>
       <c r="B217" s="53" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C217" s="54">
         <v>1380</v>
@@ -16955,7 +16997,7 @@
       <c r="F217" s="56"/>
       <c r="G217" s="56"/>
       <c r="H217" s="57" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I217" s="53" t="s">
         <v>148</v>
@@ -16966,7 +17008,7 @@
         <v>46191</v>
       </c>
       <c r="B218" s="49" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C218" s="50">
         <v>1380</v>
@@ -16991,7 +17033,7 @@
         <v>46191</v>
       </c>
       <c r="B219" s="53" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C219" s="54">
         <v>1380</v>
@@ -17041,7 +17083,7 @@
         <v>46191</v>
       </c>
       <c r="B221" s="53" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C221" s="54">
         <v>1380</v>
@@ -17066,7 +17108,7 @@
         <v>46191</v>
       </c>
       <c r="B222" s="49" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C222" s="50">
         <v>1380</v>
@@ -17091,7 +17133,7 @@
         <v>46191</v>
       </c>
       <c r="B223" s="53" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C223" s="54">
         <v>1380</v>
@@ -17116,7 +17158,7 @@
         <v>46192</v>
       </c>
       <c r="B224" s="49" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C224" s="50">
         <v>1380</v>
@@ -17141,7 +17183,7 @@
         <v>46192</v>
       </c>
       <c r="B225" s="53" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C225" s="54">
         <v>1440</v>
@@ -17166,7 +17208,7 @@
         <v>46192</v>
       </c>
       <c r="B226" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C226" s="50">
         <v>1380</v>
@@ -17191,7 +17233,7 @@
         <v>46192</v>
       </c>
       <c r="B227" s="53" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C227" s="54">
         <v>1380</v>
@@ -17216,7 +17258,7 @@
         <v>46193</v>
       </c>
       <c r="B228" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C228" s="50">
         <v>699</v>
@@ -17230,7 +17272,7 @@
       <c r="F228" s="49"/>
       <c r="G228" s="49"/>
       <c r="H228" s="51" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I228" s="49" t="s">
         <v>148</v>
@@ -17241,7 +17283,7 @@
         <v>46193</v>
       </c>
       <c r="B229" s="53" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C229" s="54">
         <v>699</v>
@@ -17255,7 +17297,7 @@
       <c r="F229" s="56"/>
       <c r="G229" s="56"/>
       <c r="H229" s="57" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I229" s="53" t="s">
         <v>148</v>
@@ -17266,7 +17308,7 @@
         <v>46193</v>
       </c>
       <c r="B230" s="49" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C230" s="50">
         <v>1380</v>
@@ -17291,7 +17333,7 @@
         <v>46193</v>
       </c>
       <c r="B231" s="53" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C231" s="54">
         <v>699</v>
@@ -17305,7 +17347,7 @@
       <c r="F231" s="56"/>
       <c r="G231" s="56"/>
       <c r="H231" s="57" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I231" s="53" t="s">
         <v>148</v>
@@ -17316,7 +17358,7 @@
         <v>46193</v>
       </c>
       <c r="B232" s="49" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C232" s="50">
         <v>1380</v>
@@ -17351,7 +17393,7 @@
       <c r="F233" s="56"/>
       <c r="G233" s="56"/>
       <c r="H233" s="57" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I233" s="53" t="s">
         <v>356</v>
@@ -17376,7 +17418,7 @@
       <c r="F234" s="49"/>
       <c r="G234" s="49"/>
       <c r="H234" s="51" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I234" s="49" t="s">
         <v>148</v>
@@ -17387,20 +17429,24 @@
         <v>46194</v>
       </c>
       <c r="B235" s="53" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C235" s="54">
-        <v>699</v>
-      </c>
-      <c r="D235" s="53"/>
-      <c r="E235" s="53"/>
+        <v>700</v>
+      </c>
+      <c r="D235" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="E235" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F235" s="56"/>
       <c r="G235" s="56"/>
       <c r="H235" s="57" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I235" s="53" t="s">
-        <v>356</v>
+        <v>148</v>
       </c>
     </row>
     <row r="236" spans="1:9" ht="27.75" customHeight="1">
@@ -17408,7 +17454,7 @@
         <v>46194</v>
       </c>
       <c r="B236" s="49" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C236" s="50">
         <v>2480</v>
@@ -17422,7 +17468,7 @@
       <c r="F236" s="49"/>
       <c r="G236" s="49"/>
       <c r="H236" s="51" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I236" s="49" t="s">
         <v>148</v>
@@ -17433,7 +17479,7 @@
         <v>46196</v>
       </c>
       <c r="B237" s="53" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C237" s="54">
         <v>700</v>
@@ -17447,7 +17493,7 @@
       <c r="F237" s="56"/>
       <c r="G237" s="56"/>
       <c r="H237" s="57" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I237" s="53" t="s">
         <v>148</v>
@@ -17458,7 +17504,7 @@
         <v>46196</v>
       </c>
       <c r="B238" s="49" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C238" s="50">
         <v>1380</v>
@@ -17472,7 +17518,7 @@
       <c r="F238" s="49"/>
       <c r="G238" s="49"/>
       <c r="H238" s="51" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I238" s="49" t="s">
         <v>148</v>
@@ -17483,7 +17529,7 @@
         <v>46196</v>
       </c>
       <c r="B239" s="53" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C239" s="54">
         <v>699</v>
@@ -17497,7 +17543,7 @@
       <c r="F239" s="56"/>
       <c r="G239" s="56"/>
       <c r="H239" s="57" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I239" s="53" t="s">
         <v>148</v>
@@ -17522,7 +17568,7 @@
       <c r="F240" s="49"/>
       <c r="G240" s="49"/>
       <c r="H240" s="51" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I240" s="49" t="s">
         <v>148</v>
@@ -17533,7 +17579,7 @@
         <v>46197</v>
       </c>
       <c r="B241" s="53" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C241" s="54">
         <v>1380</v>
@@ -17558,7 +17604,7 @@
         <v>46197</v>
       </c>
       <c r="B242" s="49" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C242" s="50">
         <v>1380</v>
@@ -17572,7 +17618,7 @@
       <c r="F242" s="49"/>
       <c r="G242" s="49"/>
       <c r="H242" s="51" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I242" s="49" t="s">
         <v>148</v>
@@ -17583,7 +17629,7 @@
         <v>46197</v>
       </c>
       <c r="B243" s="53" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C243" s="54">
         <v>1380</v>
@@ -17622,7 +17668,7 @@
       <c r="F244" s="49"/>
       <c r="G244" s="49"/>
       <c r="H244" s="51" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I244" s="49" t="s">
         <v>148</v>
@@ -17633,7 +17679,7 @@
         <v>46198</v>
       </c>
       <c r="B245" s="53" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C245" s="54">
         <v>1380</v>
@@ -17658,7 +17704,7 @@
         <v>46199</v>
       </c>
       <c r="B246" s="49" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C246" s="50">
         <v>1380</v>
@@ -17683,7 +17729,7 @@
         <v>46199</v>
       </c>
       <c r="B247" s="53" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C247" s="54">
         <v>1380</v>
@@ -17722,88 +17768,178 @@
       <c r="F248" s="49"/>
       <c r="G248" s="49"/>
       <c r="H248" s="51" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I248" s="49" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="249" spans="1:9">
-      <c r="A249" s="52"/>
-      <c r="B249" s="53"/>
-      <c r="C249" s="54"/>
+    <row r="249" spans="1:9" ht="14">
+      <c r="A249" s="52">
+        <v>46200</v>
+      </c>
+      <c r="B249" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="C249" s="54">
+        <v>1200</v>
+      </c>
       <c r="D249" s="53"/>
       <c r="E249" s="53"/>
       <c r="F249" s="56"/>
       <c r="G249" s="56"/>
-      <c r="H249" s="57"/>
-      <c r="I249" s="53"/>
-    </row>
-    <row r="250" spans="1:9">
-      <c r="A250" s="48"/>
-      <c r="B250" s="49"/>
-      <c r="C250" s="50"/>
+      <c r="H249" s="57" t="s">
+        <v>1100</v>
+      </c>
+      <c r="I249" s="53" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" ht="14">
+      <c r="A250" s="48">
+        <v>46200</v>
+      </c>
+      <c r="B250" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="C250" s="50">
+        <v>950</v>
+      </c>
       <c r="D250" s="49"/>
       <c r="E250" s="49"/>
       <c r="F250" s="49"/>
       <c r="G250" s="49"/>
-      <c r="H250" s="51"/>
-      <c r="I250" s="49"/>
-    </row>
-    <row r="251" spans="1:9">
-      <c r="A251" s="52"/>
-      <c r="B251" s="53"/>
-      <c r="C251" s="54"/>
-      <c r="D251" s="53"/>
-      <c r="E251" s="53"/>
+      <c r="H250" s="51" t="s">
+        <v>1102</v>
+      </c>
+      <c r="I250" s="49" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" ht="14">
+      <c r="A251" s="52">
+        <v>46201</v>
+      </c>
+      <c r="B251" s="53" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C251" s="54">
+        <v>1380</v>
+      </c>
+      <c r="D251" s="53" t="s">
+        <v>205</v>
+      </c>
+      <c r="E251" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F251" s="56"/>
       <c r="G251" s="56"/>
-      <c r="H251" s="57"/>
-      <c r="I251" s="53"/>
-    </row>
-    <row r="252" spans="1:9">
-      <c r="A252" s="48"/>
-      <c r="B252" s="49"/>
-      <c r="C252" s="50"/>
-      <c r="D252" s="49"/>
-      <c r="E252" s="49"/>
+      <c r="H251" s="57" t="s">
+        <v>366</v>
+      </c>
+      <c r="I251" s="53" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" ht="14">
+      <c r="A252" s="48">
+        <v>46201</v>
+      </c>
+      <c r="B252" s="49" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C252" s="50">
+        <v>699</v>
+      </c>
+      <c r="D252" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="E252" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F252" s="49"/>
       <c r="G252" s="49"/>
-      <c r="H252" s="51"/>
-      <c r="I252" s="49"/>
-    </row>
-    <row r="253" spans="1:9">
-      <c r="A253" s="52"/>
-      <c r="B253" s="53"/>
-      <c r="C253" s="54"/>
-      <c r="D253" s="53"/>
-      <c r="E253" s="53"/>
+      <c r="H252" s="51" t="s">
+        <v>1108</v>
+      </c>
+      <c r="I252" s="49" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" ht="14">
+      <c r="A253" s="52">
+        <v>46201</v>
+      </c>
+      <c r="B253" s="53" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C253" s="54">
+        <v>699</v>
+      </c>
+      <c r="D253" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="E253" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F253" s="56"/>
       <c r="G253" s="56"/>
-      <c r="H253" s="57"/>
-      <c r="I253" s="53"/>
-    </row>
-    <row r="254" spans="1:9">
-      <c r="A254" s="48"/>
-      <c r="B254" s="49"/>
-      <c r="C254" s="50"/>
-      <c r="D254" s="49"/>
-      <c r="E254" s="49"/>
+      <c r="H253" s="57" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I253" s="53" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" ht="14">
+      <c r="A254" s="48">
+        <v>46201</v>
+      </c>
+      <c r="B254" s="49" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C254" s="50">
+        <v>699</v>
+      </c>
+      <c r="D254" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="E254" s="49" t="s">
+        <v>49</v>
+      </c>
       <c r="F254" s="49"/>
       <c r="G254" s="49"/>
-      <c r="H254" s="51"/>
-      <c r="I254" s="49"/>
-    </row>
-    <row r="255" spans="1:9">
-      <c r="A255" s="52"/>
-      <c r="B255" s="53"/>
-      <c r="C255" s="54"/>
-      <c r="D255" s="53"/>
-      <c r="E255" s="53"/>
+      <c r="H254" s="51" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I254" s="49" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" ht="14">
+      <c r="A255" s="52">
+        <v>46201</v>
+      </c>
+      <c r="B255" s="53" t="s">
+        <v>472</v>
+      </c>
+      <c r="C255" s="54">
+        <v>2650</v>
+      </c>
+      <c r="D255" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="E255" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="F255" s="56"/>
       <c r="G255" s="56"/>
-      <c r="H255" s="57"/>
-      <c r="I255" s="53"/>
+      <c r="H255" s="57" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I255" s="53" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" s="48"/>
@@ -17889,19 +18025,19 @@
   <sheetData>
     <row r="1" spans="1:246" s="65" customFormat="1" ht="33.75" customHeight="1">
       <c r="A1" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="B1" s="63" t="s">
         <v>491</v>
-      </c>
-      <c r="B1" s="63" t="s">
-        <v>492</v>
       </c>
       <c r="C1" s="63" t="s">
         <v>93</v>
       </c>
       <c r="D1" s="63" t="s">
+        <v>492</v>
+      </c>
+      <c r="E1" s="63" t="s">
         <v>493</v>
-      </c>
-      <c r="E1" s="63" t="s">
-        <v>494</v>
       </c>
       <c r="F1" s="63" t="s">
         <v>80</v>
@@ -17910,19 +18046,19 @@
         <v>82</v>
       </c>
       <c r="H1" s="63" t="s">
+        <v>494</v>
+      </c>
+      <c r="I1" s="63" t="s">
         <v>495</v>
       </c>
-      <c r="I1" s="63" t="s">
+      <c r="J1" s="63" t="s">
         <v>496</v>
       </c>
-      <c r="J1" s="63" t="s">
+      <c r="K1" s="63" t="s">
         <v>497</v>
       </c>
-      <c r="K1" s="63" t="s">
+      <c r="L1" s="63" t="s">
         <v>498</v>
-      </c>
-      <c r="L1" s="63" t="s">
-        <v>499</v>
       </c>
       <c r="M1" s="63" t="s">
         <v>141</v>
@@ -17940,13 +18076,13 @@
         <v>144</v>
       </c>
       <c r="R1" s="63" t="s">
+        <v>499</v>
+      </c>
+      <c r="S1" s="63" t="s">
         <v>500</v>
       </c>
-      <c r="S1" s="63" t="s">
+      <c r="T1" s="63" t="s">
         <v>501</v>
-      </c>
-      <c r="T1" s="63" t="s">
-        <v>502</v>
       </c>
       <c r="U1" s="64"/>
       <c r="V1" s="64"/>
@@ -18177,10 +18313,10 @@
     </row>
     <row r="2" spans="1:246" s="68" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="66" t="s">
+        <v>502</v>
+      </c>
+      <c r="B2" s="66" t="s">
         <v>503</v>
-      </c>
-      <c r="B2" s="66" t="s">
-        <v>504</v>
       </c>
       <c r="C2" s="66" t="s">
         <v>95</v>
@@ -18220,7 +18356,7 @@
         <v>49</v>
       </c>
       <c r="N2" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O2" s="66"/>
       <c r="P2" s="66"/>
@@ -18457,10 +18593,10 @@
     </row>
     <row r="3" spans="1:246" ht="15" customHeight="1">
       <c r="A3" s="69" t="s">
+        <v>505</v>
+      </c>
+      <c r="B3" s="69" t="s">
         <v>506</v>
-      </c>
-      <c r="B3" s="69" t="s">
-        <v>507</v>
       </c>
       <c r="C3" s="69" t="s">
         <v>95</v>
@@ -18500,7 +18636,7 @@
         <v>49</v>
       </c>
       <c r="N3" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O3" s="69"/>
       <c r="P3" s="69"/>
@@ -18511,10 +18647,10 @@
     </row>
     <row r="4" spans="1:246" ht="15" customHeight="1">
       <c r="A4" s="66" t="s">
+        <v>507</v>
+      </c>
+      <c r="B4" s="66" t="s">
         <v>508</v>
-      </c>
-      <c r="B4" s="66" t="s">
-        <v>509</v>
       </c>
       <c r="C4" s="66" t="s">
         <v>95</v>
@@ -18554,7 +18690,7 @@
         <v>49</v>
       </c>
       <c r="N4" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O4" s="66"/>
       <c r="P4" s="66"/>
@@ -18565,10 +18701,10 @@
     </row>
     <row r="5" spans="1:246" ht="15" customHeight="1">
       <c r="A5" s="69" t="s">
+        <v>509</v>
+      </c>
+      <c r="B5" s="69" t="s">
         <v>510</v>
-      </c>
-      <c r="B5" s="69" t="s">
-        <v>511</v>
       </c>
       <c r="C5" s="69" t="s">
         <v>95</v>
@@ -18608,7 +18744,7 @@
         <v>49</v>
       </c>
       <c r="N5" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O5" s="69"/>
       <c r="P5" s="69"/>
@@ -18619,10 +18755,10 @@
     </row>
     <row r="6" spans="1:246" ht="15" customHeight="1">
       <c r="A6" s="66" t="s">
+        <v>511</v>
+      </c>
+      <c r="B6" s="66" t="s">
         <v>512</v>
-      </c>
-      <c r="B6" s="66" t="s">
-        <v>513</v>
       </c>
       <c r="C6" s="66" t="s">
         <v>95</v>
@@ -18656,13 +18792,13 @@
         <v>0</v>
       </c>
       <c r="L6" s="66" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="M6" s="66" t="s">
         <v>49</v>
       </c>
       <c r="N6" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O6" s="66"/>
       <c r="P6" s="66"/>
@@ -18673,10 +18809,10 @@
     </row>
     <row r="7" spans="1:246" ht="15" customHeight="1">
       <c r="A7" s="69" t="s">
+        <v>514</v>
+      </c>
+      <c r="B7" s="69" t="s">
         <v>515</v>
-      </c>
-      <c r="B7" s="69" t="s">
-        <v>516</v>
       </c>
       <c r="C7" s="69" t="s">
         <v>95</v>
@@ -18716,7 +18852,7 @@
         <v>49</v>
       </c>
       <c r="N7" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="69"/>
       <c r="P7" s="69"/>
@@ -18727,10 +18863,10 @@
     </row>
     <row r="8" spans="1:246" ht="15" customHeight="1">
       <c r="A8" s="66" t="s">
+        <v>516</v>
+      </c>
+      <c r="B8" s="66" t="s">
         <v>517</v>
-      </c>
-      <c r="B8" s="66" t="s">
-        <v>518</v>
       </c>
       <c r="C8" s="66" t="s">
         <v>95</v>
@@ -18770,7 +18906,7 @@
         <v>49</v>
       </c>
       <c r="N8" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="66"/>
       <c r="P8" s="66"/>
@@ -18781,10 +18917,10 @@
     </row>
     <row r="9" spans="1:246" ht="15" customHeight="1">
       <c r="A9" s="69" t="s">
+        <v>518</v>
+      </c>
+      <c r="B9" s="69" t="s">
         <v>519</v>
-      </c>
-      <c r="B9" s="69" t="s">
-        <v>520</v>
       </c>
       <c r="C9" s="69" t="s">
         <v>96</v>
@@ -18824,7 +18960,7 @@
         <v>49</v>
       </c>
       <c r="N9" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O9" s="69"/>
       <c r="P9" s="69"/>
@@ -18835,10 +18971,10 @@
     </row>
     <row r="10" spans="1:246" ht="15" customHeight="1">
       <c r="A10" s="66" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C10" s="66" t="s">
         <v>95</v>
@@ -18878,7 +19014,7 @@
         <v>49</v>
       </c>
       <c r="N10" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O10" s="66"/>
       <c r="P10" s="66"/>
@@ -18889,10 +19025,10 @@
     </row>
     <row r="11" spans="1:246" ht="15" customHeight="1">
       <c r="A11" s="69" t="s">
+        <v>521</v>
+      </c>
+      <c r="B11" s="69" t="s">
         <v>522</v>
-      </c>
-      <c r="B11" s="69" t="s">
-        <v>523</v>
       </c>
       <c r="C11" s="69" t="s">
         <v>95</v>
@@ -18926,13 +19062,13 @@
         <v>0</v>
       </c>
       <c r="L11" s="69" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="M11" s="69" t="s">
         <v>49</v>
       </c>
       <c r="N11" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O11" s="69"/>
       <c r="P11" s="69"/>
@@ -18943,10 +19079,10 @@
     </row>
     <row r="12" spans="1:246" ht="15" customHeight="1">
       <c r="A12" s="66" t="s">
+        <v>524</v>
+      </c>
+      <c r="B12" s="66" t="s">
         <v>525</v>
-      </c>
-      <c r="B12" s="66" t="s">
-        <v>526</v>
       </c>
       <c r="C12" s="66" t="s">
         <v>96</v>
@@ -18986,7 +19122,7 @@
         <v>49</v>
       </c>
       <c r="N12" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O12" s="66"/>
       <c r="P12" s="66"/>
@@ -18997,10 +19133,10 @@
     </row>
     <row r="13" spans="1:246" ht="15" customHeight="1">
       <c r="A13" s="69" t="s">
+        <v>526</v>
+      </c>
+      <c r="B13" s="69" t="s">
         <v>527</v>
-      </c>
-      <c r="B13" s="69" t="s">
-        <v>528</v>
       </c>
       <c r="C13" s="69" t="s">
         <v>96</v>
@@ -19040,7 +19176,7 @@
         <v>49</v>
       </c>
       <c r="N13" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O13" s="69"/>
       <c r="P13" s="69"/>
@@ -19051,10 +19187,10 @@
     </row>
     <row r="14" spans="1:246" ht="15" customHeight="1">
       <c r="A14" s="66" t="s">
+        <v>528</v>
+      </c>
+      <c r="B14" s="66" t="s">
         <v>529</v>
-      </c>
-      <c r="B14" s="66" t="s">
-        <v>530</v>
       </c>
       <c r="C14" s="66" t="s">
         <v>96</v>
@@ -19094,7 +19230,7 @@
         <v>49</v>
       </c>
       <c r="N14" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O14" s="66"/>
       <c r="P14" s="66"/>
@@ -19105,10 +19241,10 @@
     </row>
     <row r="15" spans="1:246" ht="15" customHeight="1">
       <c r="A15" s="69" t="s">
+        <v>530</v>
+      </c>
+      <c r="B15" s="69" t="s">
         <v>531</v>
-      </c>
-      <c r="B15" s="69" t="s">
-        <v>532</v>
       </c>
       <c r="C15" s="69" t="s">
         <v>96</v>
@@ -19148,7 +19284,7 @@
         <v>49</v>
       </c>
       <c r="N15" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O15" s="69"/>
       <c r="P15" s="69"/>
@@ -19159,10 +19295,10 @@
     </row>
     <row r="16" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="66" t="s">
+        <v>532</v>
+      </c>
+      <c r="B16" s="66" t="s">
         <v>533</v>
-      </c>
-      <c r="B16" s="66" t="s">
-        <v>534</v>
       </c>
       <c r="C16" s="66" t="s">
         <v>96</v>
@@ -19202,7 +19338,7 @@
         <v>49</v>
       </c>
       <c r="N16" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O16" s="66"/>
       <c r="P16" s="66"/>
@@ -19439,10 +19575,10 @@
     </row>
     <row r="17" spans="1:246" ht="15" customHeight="1">
       <c r="A17" s="69" t="s">
+        <v>534</v>
+      </c>
+      <c r="B17" s="69" t="s">
         <v>535</v>
-      </c>
-      <c r="B17" s="69" t="s">
-        <v>536</v>
       </c>
       <c r="C17" s="69" t="s">
         <v>95</v>
@@ -19482,7 +19618,7 @@
         <v>49</v>
       </c>
       <c r="N17" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O17" s="69"/>
       <c r="P17" s="69"/>
@@ -19493,10 +19629,10 @@
     </row>
     <row r="18" spans="1:246" ht="15" customHeight="1">
       <c r="A18" s="66" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B18" s="66" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C18" s="66" t="s">
         <v>95</v>
@@ -19536,7 +19672,7 @@
         <v>49</v>
       </c>
       <c r="N18" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O18" s="66"/>
       <c r="P18" s="66"/>
@@ -19547,10 +19683,10 @@
     </row>
     <row r="19" spans="1:246" ht="15" customHeight="1">
       <c r="A19" s="69" t="s">
+        <v>537</v>
+      </c>
+      <c r="B19" s="69" t="s">
         <v>538</v>
-      </c>
-      <c r="B19" s="69" t="s">
-        <v>539</v>
       </c>
       <c r="C19" s="69" t="s">
         <v>96</v>
@@ -19590,7 +19726,7 @@
         <v>49</v>
       </c>
       <c r="N19" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O19" s="69"/>
       <c r="P19" s="69"/>
@@ -19601,10 +19737,10 @@
     </row>
     <row r="20" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="66" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B20" s="66" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C20" s="66" t="s">
         <v>96</v>
@@ -19644,7 +19780,7 @@
         <v>49</v>
       </c>
       <c r="N20" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O20" s="66"/>
       <c r="P20" s="66"/>
@@ -19881,10 +20017,10 @@
     </row>
     <row r="21" spans="1:246" ht="15" customHeight="1">
       <c r="A21" s="69" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B21" s="69" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C21" s="69" t="s">
         <v>96</v>
@@ -19924,7 +20060,7 @@
         <v>49</v>
       </c>
       <c r="N21" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O21" s="69"/>
       <c r="P21" s="69"/>
@@ -19935,10 +20071,10 @@
     </row>
     <row r="22" spans="1:246" ht="15" customHeight="1">
       <c r="A22" s="66" t="s">
+        <v>541</v>
+      </c>
+      <c r="B22" s="66" t="s">
         <v>542</v>
-      </c>
-      <c r="B22" s="66" t="s">
-        <v>543</v>
       </c>
       <c r="C22" s="66" t="s">
         <v>95</v>
@@ -19978,7 +20114,7 @@
         <v>49</v>
       </c>
       <c r="N22" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O22" s="66"/>
       <c r="P22" s="66"/>
@@ -19989,7 +20125,7 @@
     </row>
     <row r="23" spans="1:246" ht="15" customHeight="1">
       <c r="A23" s="69" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B23" s="69" t="s">
         <v>109</v>
@@ -20026,13 +20162,13 @@
         <v>0</v>
       </c>
       <c r="L23" s="69" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="M23" s="69" t="s">
         <v>49</v>
       </c>
       <c r="N23" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O23" s="69"/>
       <c r="P23" s="69"/>
@@ -20043,10 +20179,10 @@
     </row>
     <row r="24" spans="1:246" ht="15" customHeight="1">
       <c r="A24" s="66" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B24" s="66" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C24" s="66" t="s">
         <v>95</v>
@@ -20086,7 +20222,7 @@
         <v>49</v>
       </c>
       <c r="N24" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O24" s="66"/>
       <c r="P24" s="66"/>
@@ -20097,10 +20233,10 @@
     </row>
     <row r="25" spans="1:246" ht="15" customHeight="1">
       <c r="A25" s="69" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B25" s="69" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C25" s="69" t="s">
         <v>95</v>
@@ -20140,7 +20276,7 @@
         <v>49</v>
       </c>
       <c r="N25" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O25" s="69"/>
       <c r="P25" s="69"/>
@@ -20151,10 +20287,10 @@
     </row>
     <row r="26" spans="1:246" ht="15" customHeight="1">
       <c r="A26" s="66" t="s">
+        <v>547</v>
+      </c>
+      <c r="B26" s="66" t="s">
         <v>548</v>
-      </c>
-      <c r="B26" s="66" t="s">
-        <v>549</v>
       </c>
       <c r="C26" s="66" t="s">
         <v>95</v>
@@ -20194,7 +20330,7 @@
         <v>49</v>
       </c>
       <c r="N26" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O26" s="66"/>
       <c r="P26" s="66"/>
@@ -20205,10 +20341,10 @@
     </row>
     <row r="27" spans="1:246" ht="15" customHeight="1">
       <c r="A27" s="69" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B27" s="69" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C27" s="69" t="s">
         <v>95</v>
@@ -20248,7 +20384,7 @@
         <v>49</v>
       </c>
       <c r="N27" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O27" s="69"/>
       <c r="P27" s="69"/>
@@ -20259,10 +20395,10 @@
     </row>
     <row r="28" spans="1:246" ht="15" customHeight="1">
       <c r="A28" s="66" t="s">
+        <v>550</v>
+      </c>
+      <c r="B28" s="66" t="s">
         <v>551</v>
-      </c>
-      <c r="B28" s="66" t="s">
-        <v>552</v>
       </c>
       <c r="C28" s="66" t="s">
         <v>95</v>
@@ -20302,7 +20438,7 @@
         <v>49</v>
       </c>
       <c r="N28" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O28" s="66"/>
       <c r="P28" s="66"/>
@@ -20313,10 +20449,10 @@
     </row>
     <row r="29" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="69" t="s">
+        <v>552</v>
+      </c>
+      <c r="B29" s="69" t="s">
         <v>553</v>
-      </c>
-      <c r="B29" s="69" t="s">
-        <v>554</v>
       </c>
       <c r="C29" s="69" t="s">
         <v>96</v>
@@ -20356,7 +20492,7 @@
         <v>49</v>
       </c>
       <c r="N29" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O29" s="69"/>
       <c r="P29" s="69"/>
@@ -20593,10 +20729,10 @@
     </row>
     <row r="30" spans="1:246" ht="15" customHeight="1">
       <c r="A30" s="66" t="s">
+        <v>554</v>
+      </c>
+      <c r="B30" s="66" t="s">
         <v>555</v>
-      </c>
-      <c r="B30" s="66" t="s">
-        <v>556</v>
       </c>
       <c r="C30" s="66" t="s">
         <v>95</v>
@@ -20636,7 +20772,7 @@
         <v>49</v>
       </c>
       <c r="N30" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O30" s="66"/>
       <c r="P30" s="66"/>
@@ -20647,10 +20783,10 @@
     </row>
     <row r="31" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="69" t="s">
+        <v>556</v>
+      </c>
+      <c r="B31" s="69" t="s">
         <v>557</v>
-      </c>
-      <c r="B31" s="69" t="s">
-        <v>558</v>
       </c>
       <c r="C31" s="69" t="s">
         <v>96</v>
@@ -20690,7 +20826,7 @@
         <v>49</v>
       </c>
       <c r="N31" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O31" s="69"/>
       <c r="P31" s="69"/>
@@ -20927,10 +21063,10 @@
     </row>
     <row r="32" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="66" t="s">
+        <v>558</v>
+      </c>
+      <c r="B32" s="66" t="s">
         <v>559</v>
-      </c>
-      <c r="B32" s="66" t="s">
-        <v>560</v>
       </c>
       <c r="C32" s="66" t="s">
         <v>96</v>
@@ -20970,7 +21106,7 @@
         <v>49</v>
       </c>
       <c r="N32" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O32" s="66"/>
       <c r="P32" s="66"/>
@@ -21207,10 +21343,10 @@
     </row>
     <row r="33" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="69" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B33" s="69" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C33" s="69" t="s">
         <v>96</v>
@@ -21250,7 +21386,7 @@
         <v>49</v>
       </c>
       <c r="N33" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O33" s="69"/>
       <c r="P33" s="69"/>
@@ -21487,10 +21623,10 @@
     </row>
     <row r="34" spans="1:246" ht="15" customHeight="1">
       <c r="A34" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B34" s="66" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C34" s="66" t="s">
         <v>95</v>
@@ -21530,7 +21666,7 @@
         <v>49</v>
       </c>
       <c r="N34" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O34" s="66"/>
       <c r="P34" s="66"/>
@@ -21541,10 +21677,10 @@
     </row>
     <row r="35" spans="1:246" ht="15" customHeight="1">
       <c r="A35" s="69" t="s">
+        <v>562</v>
+      </c>
+      <c r="B35" s="69" t="s">
         <v>563</v>
-      </c>
-      <c r="B35" s="69" t="s">
-        <v>564</v>
       </c>
       <c r="C35" s="69" t="s">
         <v>95</v>
@@ -21584,7 +21720,7 @@
         <v>49</v>
       </c>
       <c r="N35" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O35" s="69"/>
       <c r="P35" s="69"/>
@@ -21595,10 +21731,10 @@
     </row>
     <row r="36" spans="1:246" ht="15" customHeight="1">
       <c r="A36" s="66" t="s">
+        <v>564</v>
+      </c>
+      <c r="B36" s="66" t="s">
         <v>565</v>
-      </c>
-      <c r="B36" s="66" t="s">
-        <v>566</v>
       </c>
       <c r="C36" s="66" t="s">
         <v>95</v>
@@ -21638,7 +21774,7 @@
         <v>49</v>
       </c>
       <c r="N36" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O36" s="66"/>
       <c r="P36" s="66"/>
@@ -21649,10 +21785,10 @@
     </row>
     <row r="37" spans="1:246" ht="15" customHeight="1">
       <c r="A37" s="69" t="s">
+        <v>566</v>
+      </c>
+      <c r="B37" s="69" t="s">
         <v>567</v>
-      </c>
-      <c r="B37" s="69" t="s">
-        <v>568</v>
       </c>
       <c r="C37" s="69" t="s">
         <v>96</v>
@@ -21692,7 +21828,7 @@
         <v>49</v>
       </c>
       <c r="N37" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O37" s="69"/>
       <c r="P37" s="69"/>
@@ -21703,10 +21839,10 @@
     </row>
     <row r="38" spans="1:246" ht="15" customHeight="1">
       <c r="A38" s="66" t="s">
+        <v>568</v>
+      </c>
+      <c r="B38" s="66" t="s">
         <v>569</v>
-      </c>
-      <c r="B38" s="66" t="s">
-        <v>570</v>
       </c>
       <c r="C38" s="66" t="s">
         <v>95</v>
@@ -21746,7 +21882,7 @@
         <v>49</v>
       </c>
       <c r="N38" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O38" s="66"/>
       <c r="P38" s="66"/>
@@ -21757,10 +21893,10 @@
     </row>
     <row r="39" spans="1:246" ht="15" customHeight="1">
       <c r="A39" s="69" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B39" s="69" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C39" s="69" t="s">
         <v>96</v>
@@ -21800,7 +21936,7 @@
         <v>49</v>
       </c>
       <c r="N39" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O39" s="69"/>
       <c r="P39" s="69"/>
@@ -21811,10 +21947,10 @@
     </row>
     <row r="40" spans="1:246" ht="15" customHeight="1">
       <c r="A40" s="66" t="s">
+        <v>571</v>
+      </c>
+      <c r="B40" s="66" t="s">
         <v>572</v>
-      </c>
-      <c r="B40" s="66" t="s">
-        <v>573</v>
       </c>
       <c r="C40" s="66" t="s">
         <v>96</v>
@@ -21854,7 +21990,7 @@
         <v>49</v>
       </c>
       <c r="N40" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O40" s="66"/>
       <c r="P40" s="66"/>
@@ -21865,10 +22001,10 @@
     </row>
     <row r="41" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A41" s="69" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B41" s="69" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C41" s="69" t="s">
         <v>95</v>
@@ -21908,7 +22044,7 @@
         <v>49</v>
       </c>
       <c r="N41" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O41" s="69"/>
       <c r="P41" s="69"/>
@@ -22145,10 +22281,10 @@
     </row>
     <row r="42" spans="1:246" ht="15" customHeight="1">
       <c r="A42" s="66" t="s">
+        <v>574</v>
+      </c>
+      <c r="B42" s="66" t="s">
         <v>575</v>
-      </c>
-      <c r="B42" s="66" t="s">
-        <v>576</v>
       </c>
       <c r="C42" s="66" t="s">
         <v>96</v>
@@ -22188,7 +22324,7 @@
         <v>49</v>
       </c>
       <c r="N42" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O42" s="66"/>
       <c r="P42" s="66"/>
@@ -22199,10 +22335,10 @@
     </row>
     <row r="43" spans="1:246" ht="15" customHeight="1">
       <c r="A43" s="69" t="s">
+        <v>576</v>
+      </c>
+      <c r="B43" s="69" t="s">
         <v>577</v>
-      </c>
-      <c r="B43" s="69" t="s">
-        <v>578</v>
       </c>
       <c r="C43" s="69" t="s">
         <v>96</v>
@@ -22242,7 +22378,7 @@
         <v>49</v>
       </c>
       <c r="N43" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O43" s="69"/>
       <c r="P43" s="69"/>
@@ -22253,10 +22389,10 @@
     </row>
     <row r="44" spans="1:246" ht="15" customHeight="1">
       <c r="A44" s="66" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B44" s="66" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C44" s="66" t="s">
         <v>96</v>
@@ -22290,20 +22426,20 @@
         <v>0</v>
       </c>
       <c r="L44" s="66" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="M44" s="66" t="s">
         <v>49</v>
       </c>
       <c r="N44" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O44" s="66" t="s">
         <v>216</v>
       </c>
       <c r="P44" s="66"/>
       <c r="Q44" s="66" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="R44" s="66"/>
       <c r="S44" s="66"/>
@@ -22311,10 +22447,10 @@
     </row>
     <row r="45" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A45" s="69" t="s">
+        <v>581</v>
+      </c>
+      <c r="B45" s="69" t="s">
         <v>582</v>
-      </c>
-      <c r="B45" s="69" t="s">
-        <v>583</v>
       </c>
       <c r="C45" s="69" t="s">
         <v>95</v>
@@ -22354,7 +22490,7 @@
         <v>49</v>
       </c>
       <c r="N45" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O45" s="69"/>
       <c r="P45" s="69"/>
@@ -22591,10 +22727,10 @@
     </row>
     <row r="46" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A46" s="66" t="s">
+        <v>583</v>
+      </c>
+      <c r="B46" s="66" t="s">
         <v>584</v>
-      </c>
-      <c r="B46" s="66" t="s">
-        <v>585</v>
       </c>
       <c r="C46" s="66" t="s">
         <v>95</v>
@@ -22634,7 +22770,7 @@
         <v>49</v>
       </c>
       <c r="N46" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O46" s="66"/>
       <c r="P46" s="66"/>
@@ -22871,10 +23007,10 @@
     </row>
     <row r="47" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A47" s="69" t="s">
+        <v>585</v>
+      </c>
+      <c r="B47" s="69" t="s">
         <v>586</v>
-      </c>
-      <c r="B47" s="69" t="s">
-        <v>587</v>
       </c>
       <c r="C47" s="69" t="s">
         <v>95</v>
@@ -22908,13 +23044,13 @@
         <v>1094</v>
       </c>
       <c r="L47" s="69" t="s">
+        <v>587</v>
+      </c>
+      <c r="M47" s="69" t="s">
         <v>588</v>
       </c>
-      <c r="M47" s="69" t="s">
+      <c r="N47" s="69" t="s">
         <v>589</v>
-      </c>
-      <c r="N47" s="69" t="s">
-        <v>590</v>
       </c>
       <c r="O47" s="69"/>
       <c r="P47" s="69"/>
@@ -23151,10 +23287,10 @@
     </row>
     <row r="48" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A48" s="66" t="s">
+        <v>590</v>
+      </c>
+      <c r="B48" s="66" t="s">
         <v>591</v>
-      </c>
-      <c r="B48" s="66" t="s">
-        <v>592</v>
       </c>
       <c r="C48" s="66" t="s">
         <v>95</v>
@@ -23194,7 +23330,7 @@
         <v>49</v>
       </c>
       <c r="N48" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O48" s="66"/>
       <c r="P48" s="66"/>
@@ -23431,10 +23567,10 @@
     </row>
     <row r="49" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A49" s="69" t="s">
+        <v>592</v>
+      </c>
+      <c r="B49" s="69" t="s">
         <v>593</v>
-      </c>
-      <c r="B49" s="69" t="s">
-        <v>594</v>
       </c>
       <c r="C49" s="69" t="s">
         <v>95</v>
@@ -23474,11 +23610,11 @@
         <v>49</v>
       </c>
       <c r="N49" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O49" s="69"/>
       <c r="P49" s="69" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="Q49" s="69"/>
       <c r="R49" s="69"/>
@@ -23713,10 +23849,10 @@
     </row>
     <row r="50" spans="1:246" ht="15" customHeight="1">
       <c r="A50" s="66" t="s">
+        <v>595</v>
+      </c>
+      <c r="B50" s="66" t="s">
         <v>596</v>
-      </c>
-      <c r="B50" s="66" t="s">
-        <v>597</v>
       </c>
       <c r="C50" s="66" t="s">
         <v>96</v>
@@ -23756,7 +23892,7 @@
         <v>49</v>
       </c>
       <c r="N50" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O50" s="66"/>
       <c r="P50" s="66"/>
@@ -23767,10 +23903,10 @@
     </row>
     <row r="51" spans="1:246" ht="15" customHeight="1">
       <c r="A51" s="69" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B51" s="69" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C51" s="69" t="s">
         <v>96</v>
@@ -23810,7 +23946,7 @@
         <v>49</v>
       </c>
       <c r="N51" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O51" s="69"/>
       <c r="P51" s="69"/>
@@ -23821,7 +23957,7 @@
     </row>
     <row r="52" spans="1:246" ht="15" customHeight="1">
       <c r="A52" s="66" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B52" s="66" t="s">
         <v>298</v>
@@ -23858,17 +23994,17 @@
         <v>2400</v>
       </c>
       <c r="L52" s="66" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="M52" s="66"/>
       <c r="N52" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O52" s="66" t="s">
+        <v>600</v>
+      </c>
+      <c r="P52" s="66" t="s">
         <v>601</v>
-      </c>
-      <c r="P52" s="66" t="s">
-        <v>602</v>
       </c>
       <c r="Q52" s="66"/>
       <c r="R52" s="66"/>
@@ -23877,7 +24013,7 @@
     </row>
     <row r="53" spans="1:246" ht="15" customHeight="1">
       <c r="A53" s="69" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B53" s="69" t="s">
         <v>296</v>
@@ -23914,7 +24050,7 @@
         <v>1941</v>
       </c>
       <c r="L53" s="69" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="M53" s="69"/>
       <c r="N53" s="69" t="s">
@@ -23924,7 +24060,7 @@
         <v>229</v>
       </c>
       <c r="P53" s="69" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="Q53" s="69"/>
       <c r="R53" s="69"/>
@@ -23933,10 +24069,10 @@
     </row>
     <row r="54" spans="1:246" s="76" customFormat="1" ht="15" customHeight="1">
       <c r="A54" s="66" t="s">
+        <v>605</v>
+      </c>
+      <c r="B54" s="73" t="s">
         <v>606</v>
-      </c>
-      <c r="B54" s="73" t="s">
-        <v>607</v>
       </c>
       <c r="C54" s="73" t="s">
         <v>96</v>
@@ -23978,10 +24114,10 @@
         <v>207</v>
       </c>
       <c r="P54" s="73" t="s">
+        <v>607</v>
+      </c>
+      <c r="Q54" s="66" t="s">
         <v>608</v>
-      </c>
-      <c r="Q54" s="66" t="s">
-        <v>609</v>
       </c>
       <c r="R54" s="73"/>
       <c r="S54" s="73"/>
@@ -24215,10 +24351,10 @@
     </row>
     <row r="55" spans="1:246" ht="15" customHeight="1">
       <c r="A55" s="69" t="s">
+        <v>609</v>
+      </c>
+      <c r="B55" s="69" t="s">
         <v>610</v>
-      </c>
-      <c r="B55" s="69" t="s">
-        <v>611</v>
       </c>
       <c r="C55" s="69" t="s">
         <v>96</v>
@@ -24252,13 +24388,13 @@
         <v>995</v>
       </c>
       <c r="L55" s="69" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="M55" s="69" t="s">
         <v>49</v>
       </c>
       <c r="N55" s="69" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O55" s="69" t="s">
         <v>207</v>
@@ -24271,10 +24407,10 @@
     </row>
     <row r="56" spans="1:246" ht="15" customHeight="1">
       <c r="A56" s="66" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B56" s="66" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C56" s="66" t="s">
         <v>96</v>
@@ -24314,10 +24450,10 @@
         <v>49</v>
       </c>
       <c r="N56" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O56" s="66" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="P56" s="66"/>
       <c r="Q56" s="66"/>
@@ -24327,10 +24463,10 @@
     </row>
     <row r="57" spans="1:246" ht="15" customHeight="1">
       <c r="A57" s="69" t="s">
+        <v>614</v>
+      </c>
+      <c r="B57" s="69" t="s">
         <v>615</v>
-      </c>
-      <c r="B57" s="69" t="s">
-        <v>616</v>
       </c>
       <c r="C57" s="69" t="s">
         <v>96</v>
@@ -24369,7 +24505,7 @@
         <v>356</v>
       </c>
       <c r="O57" s="69" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="P57" s="69"/>
       <c r="Q57" s="69"/>
@@ -24379,10 +24515,10 @@
     </row>
     <row r="58" spans="1:246" ht="15" customHeight="1">
       <c r="A58" s="66" t="s">
+        <v>617</v>
+      </c>
+      <c r="B58" s="66" t="s">
         <v>618</v>
-      </c>
-      <c r="B58" s="66" t="s">
-        <v>619</v>
       </c>
       <c r="C58" s="66" t="s">
         <v>96</v>
@@ -24421,7 +24557,7 @@
         <v>356</v>
       </c>
       <c r="O58" s="66" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="P58" s="66"/>
       <c r="Q58" s="66"/>
@@ -24431,10 +24567,10 @@
     </row>
     <row r="59" spans="1:246" ht="15" customHeight="1">
       <c r="A59" s="69" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B59" s="69" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C59" s="69" t="s">
         <v>96</v>
@@ -24468,17 +24604,17 @@
         <v>2290</v>
       </c>
       <c r="L59" s="69" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="M59" s="69"/>
       <c r="N59" s="69" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O59" s="69" t="s">
+        <v>622</v>
+      </c>
+      <c r="P59" s="69" t="s">
         <v>623</v>
-      </c>
-      <c r="P59" s="69" t="s">
-        <v>624</v>
       </c>
       <c r="Q59" s="69"/>
       <c r="R59" s="69"/>
@@ -24487,10 +24623,10 @@
     </row>
     <row r="60" spans="1:246" ht="15" customHeight="1">
       <c r="A60" s="66" t="s">
+        <v>624</v>
+      </c>
+      <c r="B60" s="66" t="s">
         <v>625</v>
-      </c>
-      <c r="B60" s="66" t="s">
-        <v>626</v>
       </c>
       <c r="C60" s="66" t="s">
         <v>96</v>
@@ -24524,17 +24660,17 @@
         <v>1080</v>
       </c>
       <c r="L60" s="66" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="M60" s="66" t="s">
         <v>49</v>
       </c>
       <c r="N60" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O60" s="66"/>
       <c r="P60" s="66" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="Q60" s="66"/>
       <c r="R60" s="66"/>
@@ -24543,10 +24679,10 @@
     </row>
     <row r="61" spans="1:246" ht="45" customHeight="1">
       <c r="A61" s="69" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B61" s="69" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C61" s="69" t="s">
         <v>96</v>
@@ -24580,20 +24716,20 @@
         <v>4384</v>
       </c>
       <c r="L61" s="69" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="M61" s="69"/>
       <c r="N61" s="69" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O61" s="69" t="s">
+        <v>630</v>
+      </c>
+      <c r="P61" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="P61" s="69" t="s">
+      <c r="Q61" s="69" t="s">
         <v>632</v>
-      </c>
-      <c r="Q61" s="69" t="s">
-        <v>633</v>
       </c>
       <c r="R61" s="69"/>
       <c r="S61" s="69"/>
@@ -24601,7 +24737,7 @@
     </row>
     <row r="62" spans="1:246" ht="15" customHeight="1">
       <c r="A62" s="66" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B62" s="66" t="s">
         <v>109</v>
@@ -24638,11 +24774,11 @@
         <v>0</v>
       </c>
       <c r="L62" s="66" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="M62" s="66"/>
       <c r="N62" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O62" s="66"/>
       <c r="P62" s="66"/>
@@ -24653,10 +24789,10 @@
     </row>
     <row r="63" spans="1:246" ht="15" customHeight="1">
       <c r="A63" s="69" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B63" s="69" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C63" s="69" t="s">
         <v>95</v>
@@ -24694,7 +24830,7 @@
       </c>
       <c r="M63" s="69"/>
       <c r="N63" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O63" s="69"/>
       <c r="P63" s="69"/>
@@ -24705,10 +24841,10 @@
     </row>
     <row r="64" spans="1:246" ht="15" customHeight="1">
       <c r="A64" s="66" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B64" s="66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C64" s="66" t="s">
         <v>95</v>
@@ -24746,7 +24882,7 @@
       </c>
       <c r="M64" s="66"/>
       <c r="N64" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O64" s="66"/>
       <c r="P64" s="66"/>
@@ -24757,10 +24893,10 @@
     </row>
     <row r="65" spans="1:20" ht="15" customHeight="1">
       <c r="A65" s="69" t="s">
+        <v>637</v>
+      </c>
+      <c r="B65" s="69" t="s">
         <v>638</v>
-      </c>
-      <c r="B65" s="69" t="s">
-        <v>639</v>
       </c>
       <c r="C65" s="69" t="s">
         <v>95</v>
@@ -24794,11 +24930,11 @@
         <v>0</v>
       </c>
       <c r="L65" s="69" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="M65" s="69"/>
       <c r="N65" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O65" s="69"/>
       <c r="P65" s="69"/>
@@ -24809,10 +24945,10 @@
     </row>
     <row r="66" spans="1:20" ht="15" customHeight="1">
       <c r="A66" s="66" t="s">
+        <v>640</v>
+      </c>
+      <c r="B66" s="66" t="s">
         <v>641</v>
-      </c>
-      <c r="B66" s="66" t="s">
-        <v>642</v>
       </c>
       <c r="C66" s="66" t="s">
         <v>95</v>
@@ -24846,11 +24982,11 @@
         <v>1558</v>
       </c>
       <c r="L66" s="66" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M66" s="66"/>
       <c r="N66" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O66" s="66"/>
       <c r="P66" s="66"/>
@@ -24861,10 +24997,10 @@
     </row>
     <row r="67" spans="1:20" ht="15" customHeight="1">
       <c r="A67" s="69" t="s">
+        <v>643</v>
+      </c>
+      <c r="B67" s="69" t="s">
         <v>644</v>
-      </c>
-      <c r="B67" s="69" t="s">
-        <v>645</v>
       </c>
       <c r="C67" s="69" t="s">
         <v>95</v>
@@ -24900,7 +25036,7 @@
       <c r="L67" s="69"/>
       <c r="M67" s="69"/>
       <c r="N67" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O67" s="69"/>
       <c r="P67" s="69"/>
@@ -24911,10 +25047,10 @@
     </row>
     <row r="68" spans="1:20" ht="15" customHeight="1">
       <c r="A68" s="66" t="s">
+        <v>645</v>
+      </c>
+      <c r="B68" s="66" t="s">
         <v>646</v>
-      </c>
-      <c r="B68" s="66" t="s">
-        <v>647</v>
       </c>
       <c r="C68" s="66" t="s">
         <v>95</v>
@@ -24948,15 +25084,15 @@
         <v>685</v>
       </c>
       <c r="L68" s="66" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="M68" s="66"/>
       <c r="N68" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O68" s="66"/>
       <c r="P68" s="66" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="Q68" s="66"/>
       <c r="R68" s="66"/>
@@ -24965,10 +25101,10 @@
     </row>
     <row r="69" spans="1:20" ht="15" customHeight="1">
       <c r="A69" s="69" t="s">
+        <v>649</v>
+      </c>
+      <c r="B69" s="69" t="s">
         <v>650</v>
-      </c>
-      <c r="B69" s="69" t="s">
-        <v>651</v>
       </c>
       <c r="C69" s="69" t="s">
         <v>96</v>
@@ -25007,7 +25143,7 @@
         <v>356</v>
       </c>
       <c r="O69" s="69" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="P69" s="69"/>
       <c r="Q69" s="69"/>
@@ -25017,10 +25153,10 @@
     </row>
     <row r="70" spans="1:20" ht="15" customHeight="1">
       <c r="A70" s="66" t="s">
+        <v>652</v>
+      </c>
+      <c r="B70" s="66" t="s">
         <v>653</v>
-      </c>
-      <c r="B70" s="66" t="s">
-        <v>654</v>
       </c>
       <c r="C70" s="66" t="s">
         <v>95</v>
@@ -25054,11 +25190,11 @@
         <v>0</v>
       </c>
       <c r="L70" s="66" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="M70" s="66"/>
       <c r="N70" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O70" s="66"/>
       <c r="P70" s="66"/>
@@ -25069,10 +25205,10 @@
     </row>
     <row r="71" spans="1:20" ht="15" customHeight="1">
       <c r="A71" s="69" t="s">
+        <v>655</v>
+      </c>
+      <c r="B71" s="69" t="s">
         <v>656</v>
-      </c>
-      <c r="B71" s="69" t="s">
-        <v>657</v>
       </c>
       <c r="C71" s="69" t="s">
         <v>95</v>
@@ -25106,17 +25242,17 @@
         <v>0</v>
       </c>
       <c r="L71" s="69" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="M71" s="69" t="s">
         <v>49</v>
       </c>
       <c r="N71" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O71" s="69"/>
       <c r="P71" s="69" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="Q71" s="69"/>
       <c r="R71" s="69"/>
@@ -25125,10 +25261,10 @@
     </row>
     <row r="72" spans="1:20" ht="15" customHeight="1">
       <c r="A72" s="66" t="s">
+        <v>659</v>
+      </c>
+      <c r="B72" s="66" t="s">
         <v>660</v>
-      </c>
-      <c r="B72" s="66" t="s">
-        <v>661</v>
       </c>
       <c r="C72" s="66" t="s">
         <v>95</v>
@@ -25166,7 +25302,7 @@
       </c>
       <c r="M72" s="66"/>
       <c r="N72" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O72" s="66"/>
       <c r="P72" s="66"/>
@@ -25177,10 +25313,10 @@
     </row>
     <row r="73" spans="1:20" ht="15" customHeight="1">
       <c r="A73" s="69" t="s">
+        <v>661</v>
+      </c>
+      <c r="B73" s="69" t="s">
         <v>662</v>
-      </c>
-      <c r="B73" s="69" t="s">
-        <v>663</v>
       </c>
       <c r="C73" s="69" t="s">
         <v>96</v>
@@ -25218,7 +25354,7 @@
       </c>
       <c r="M73" s="69"/>
       <c r="N73" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O73" s="69"/>
       <c r="P73" s="69"/>
@@ -25229,10 +25365,10 @@
     </row>
     <row r="74" spans="1:20" ht="15" customHeight="1">
       <c r="A74" s="66" t="s">
+        <v>663</v>
+      </c>
+      <c r="B74" s="66" t="s">
         <v>664</v>
-      </c>
-      <c r="B74" s="66" t="s">
-        <v>665</v>
       </c>
       <c r="C74" s="66" t="s">
         <v>95</v>
@@ -25272,7 +25408,7 @@
         <v>49</v>
       </c>
       <c r="N74" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O74" s="66"/>
       <c r="P74" s="66"/>
@@ -25283,10 +25419,10 @@
     </row>
     <row r="75" spans="1:20" ht="15" customHeight="1">
       <c r="A75" s="69" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B75" s="69" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C75" s="69" t="s">
         <v>96</v>
@@ -25326,7 +25462,7 @@
         <v>49</v>
       </c>
       <c r="N75" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O75" s="69"/>
       <c r="P75" s="69"/>
@@ -25337,10 +25473,10 @@
     </row>
     <row r="76" spans="1:20" ht="15" customHeight="1">
       <c r="A76" s="66" t="s">
+        <v>666</v>
+      </c>
+      <c r="B76" s="66" t="s">
         <v>667</v>
-      </c>
-      <c r="B76" s="66" t="s">
-        <v>668</v>
       </c>
       <c r="C76" s="66" t="s">
         <v>95</v>
@@ -25380,7 +25516,7 @@
         <v>49</v>
       </c>
       <c r="N76" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O76" s="66"/>
       <c r="P76" s="66"/>
@@ -25391,10 +25527,10 @@
     </row>
     <row r="77" spans="1:20" ht="15" customHeight="1">
       <c r="A77" s="69" t="s">
+        <v>668</v>
+      </c>
+      <c r="B77" s="69" t="s">
         <v>669</v>
-      </c>
-      <c r="B77" s="69" t="s">
-        <v>670</v>
       </c>
       <c r="C77" s="69" t="s">
         <v>96</v>
@@ -25428,14 +25564,14 @@
         <v>1990</v>
       </c>
       <c r="L77" s="69" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="M77" s="69"/>
       <c r="N77" s="69" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O77" s="69" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="P77" s="69"/>
       <c r="Q77" s="69"/>
@@ -25445,10 +25581,10 @@
     </row>
     <row r="78" spans="1:20" ht="15" customHeight="1">
       <c r="A78" s="66" t="s">
+        <v>672</v>
+      </c>
+      <c r="B78" s="66" t="s">
         <v>673</v>
-      </c>
-      <c r="B78" s="66" t="s">
-        <v>674</v>
       </c>
       <c r="C78" s="66" t="s">
         <v>96</v>
@@ -25482,14 +25618,14 @@
         <v>1075</v>
       </c>
       <c r="L78" s="66" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="M78" s="66"/>
       <c r="N78" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O78" s="66" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="P78" s="66"/>
       <c r="Q78" s="66"/>
@@ -25499,10 +25635,10 @@
     </row>
     <row r="79" spans="1:20" ht="15" customHeight="1">
       <c r="A79" s="69" t="s">
+        <v>676</v>
+      </c>
+      <c r="B79" s="69" t="s">
         <v>677</v>
-      </c>
-      <c r="B79" s="69" t="s">
-        <v>678</v>
       </c>
       <c r="C79" s="69" t="s">
         <v>96</v>
@@ -25536,14 +25672,14 @@
         <v>0</v>
       </c>
       <c r="L79" s="69" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="M79" s="69"/>
       <c r="N79" s="69" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O79" s="69" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="P79" s="69"/>
       <c r="Q79" s="69"/>
@@ -25553,10 +25689,10 @@
     </row>
     <row r="80" spans="1:20" ht="15" customHeight="1">
       <c r="A80" s="66" t="s">
+        <v>680</v>
+      </c>
+      <c r="B80" s="66" t="s">
         <v>681</v>
-      </c>
-      <c r="B80" s="66" t="s">
-        <v>682</v>
       </c>
       <c r="C80" s="66" t="s">
         <v>96</v>
@@ -25590,14 +25726,14 @@
         <v>1230</v>
       </c>
       <c r="L80" s="66" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="M80" s="66"/>
       <c r="N80" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O80" s="66" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="P80" s="66"/>
       <c r="Q80" s="66"/>
@@ -25607,10 +25743,10 @@
     </row>
     <row r="81" spans="1:20" ht="30" customHeight="1">
       <c r="A81" s="69" t="s">
+        <v>684</v>
+      </c>
+      <c r="B81" s="69" t="s">
         <v>685</v>
-      </c>
-      <c r="B81" s="69" t="s">
-        <v>686</v>
       </c>
       <c r="C81" s="69" t="s">
         <v>96</v>
@@ -25644,11 +25780,11 @@
         <v>0</v>
       </c>
       <c r="L81" s="69" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="M81" s="69"/>
       <c r="N81" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O81" s="69"/>
       <c r="P81" s="69"/>
@@ -25659,10 +25795,10 @@
     </row>
     <row r="82" spans="1:20" ht="15" customHeight="1">
       <c r="A82" s="66" t="s">
+        <v>687</v>
+      </c>
+      <c r="B82" s="66" t="s">
         <v>688</v>
-      </c>
-      <c r="B82" s="66" t="s">
-        <v>689</v>
       </c>
       <c r="C82" s="66" t="s">
         <v>96</v>
@@ -25696,11 +25832,11 @@
         <v>0</v>
       </c>
       <c r="L82" s="66" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="M82" s="66"/>
       <c r="N82" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O82" s="66"/>
       <c r="P82" s="66"/>
@@ -25711,10 +25847,10 @@
     </row>
     <row r="83" spans="1:20" ht="30" customHeight="1">
       <c r="A83" s="69" t="s">
+        <v>690</v>
+      </c>
+      <c r="B83" s="69" t="s">
         <v>691</v>
-      </c>
-      <c r="B83" s="69" t="s">
-        <v>692</v>
       </c>
       <c r="C83" s="69" t="s">
         <v>96</v>
@@ -25748,14 +25884,14 @@
         <v>0</v>
       </c>
       <c r="L83" s="69" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="M83" s="69"/>
       <c r="N83" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O83" s="69" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="P83" s="69"/>
       <c r="Q83" s="69"/>
@@ -25765,10 +25901,10 @@
     </row>
     <row r="84" spans="1:20" ht="15" customHeight="1">
       <c r="A84" s="66" t="s">
+        <v>694</v>
+      </c>
+      <c r="B84" s="66" t="s">
         <v>695</v>
-      </c>
-      <c r="B84" s="66" t="s">
-        <v>696</v>
       </c>
       <c r="C84" s="66" t="s">
         <v>96</v>
@@ -25802,14 +25938,14 @@
         <v>900</v>
       </c>
       <c r="L84" s="66" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="M84" s="66"/>
       <c r="N84" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O84" s="66" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="P84" s="66"/>
       <c r="Q84" s="66"/>
@@ -25819,10 +25955,10 @@
     </row>
     <row r="85" spans="1:20" ht="15" customHeight="1">
       <c r="A85" s="69" t="s">
+        <v>698</v>
+      </c>
+      <c r="B85" s="69" t="s">
         <v>699</v>
-      </c>
-      <c r="B85" s="69" t="s">
-        <v>700</v>
       </c>
       <c r="C85" s="69" t="s">
         <v>96</v>
@@ -25856,11 +25992,11 @@
         <v>0</v>
       </c>
       <c r="L85" s="69" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M85" s="69"/>
       <c r="N85" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O85" s="69"/>
       <c r="P85" s="69"/>
@@ -25871,10 +26007,10 @@
     </row>
     <row r="86" spans="1:20" ht="15" customHeight="1">
       <c r="A86" s="66" t="s">
+        <v>701</v>
+      </c>
+      <c r="B86" s="66" t="s">
         <v>702</v>
-      </c>
-      <c r="B86" s="66" t="s">
-        <v>703</v>
       </c>
       <c r="C86" s="66" t="s">
         <v>96</v>
@@ -25908,14 +26044,14 @@
         <v>2090</v>
       </c>
       <c r="L86" s="66" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="M86" s="66"/>
       <c r="N86" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O86" s="66" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="P86" s="66"/>
       <c r="Q86" s="66"/>
@@ -25925,10 +26061,10 @@
     </row>
     <row r="87" spans="1:20" ht="15" customHeight="1">
       <c r="A87" s="69" t="s">
+        <v>705</v>
+      </c>
+      <c r="B87" s="69" t="s">
         <v>706</v>
-      </c>
-      <c r="B87" s="69" t="s">
-        <v>707</v>
       </c>
       <c r="C87" s="69" t="s">
         <v>96</v>
@@ -25964,10 +26100,10 @@
       <c r="L87" s="69"/>
       <c r="M87" s="69"/>
       <c r="N87" s="69" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O87" s="69" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="P87" s="69"/>
       <c r="Q87" s="69"/>
@@ -25977,10 +26113,10 @@
     </row>
     <row r="88" spans="1:20" ht="30" customHeight="1">
       <c r="A88" s="66" t="s">
+        <v>708</v>
+      </c>
+      <c r="B88" s="66" t="s">
         <v>709</v>
-      </c>
-      <c r="B88" s="66" t="s">
-        <v>710</v>
       </c>
       <c r="C88" s="66" t="s">
         <v>96</v>
@@ -26014,14 +26150,14 @@
         <v>795</v>
       </c>
       <c r="L88" s="66" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="M88" s="66"/>
       <c r="N88" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O88" s="66" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="P88" s="66"/>
       <c r="Q88" s="66"/>
@@ -26031,10 +26167,10 @@
     </row>
     <row r="89" spans="1:20" ht="15" customHeight="1">
       <c r="A89" s="69" t="s">
+        <v>712</v>
+      </c>
+      <c r="B89" s="69" t="s">
         <v>713</v>
-      </c>
-      <c r="B89" s="69" t="s">
-        <v>714</v>
       </c>
       <c r="C89" s="69" t="s">
         <v>95</v>
@@ -26068,11 +26204,11 @@
         <v>0</v>
       </c>
       <c r="L89" s="69" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M89" s="69"/>
       <c r="N89" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O89" s="69"/>
       <c r="P89" s="69"/>
@@ -26083,10 +26219,10 @@
     </row>
     <row r="90" spans="1:20" ht="15" customHeight="1">
       <c r="A90" s="66" t="s">
+        <v>715</v>
+      </c>
+      <c r="B90" s="66" t="s">
         <v>716</v>
-      </c>
-      <c r="B90" s="66" t="s">
-        <v>717</v>
       </c>
       <c r="C90" s="66" t="s">
         <v>95</v>
@@ -26124,7 +26260,7 @@
       </c>
       <c r="M90" s="66"/>
       <c r="N90" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O90" s="66"/>
       <c r="P90" s="66"/>
@@ -26135,13 +26271,13 @@
     </row>
     <row r="91" spans="1:20" ht="15" customHeight="1">
       <c r="A91" s="69" t="s">
+        <v>717</v>
+      </c>
+      <c r="B91" s="69" t="s">
         <v>718</v>
       </c>
-      <c r="B91" s="69" t="s">
+      <c r="C91" s="69" t="s">
         <v>719</v>
-      </c>
-      <c r="C91" s="69" t="s">
-        <v>720</v>
       </c>
       <c r="D91" s="70">
         <v>389</v>
@@ -26172,11 +26308,11 @@
         <v>0</v>
       </c>
       <c r="L91" s="69" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="M91" s="69"/>
       <c r="N91" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O91" s="69"/>
       <c r="P91" s="69"/>
@@ -26187,13 +26323,13 @@
     </row>
     <row r="92" spans="1:20" ht="15" customHeight="1">
       <c r="A92" s="66" t="s">
+        <v>721</v>
+      </c>
+      <c r="B92" s="66" t="s">
         <v>722</v>
       </c>
-      <c r="B92" s="66" t="s">
-        <v>723</v>
-      </c>
       <c r="C92" s="66" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D92" s="67">
         <v>489</v>
@@ -26224,11 +26360,11 @@
         <v>0</v>
       </c>
       <c r="L92" s="66" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="M92" s="66"/>
       <c r="N92" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O92" s="66"/>
       <c r="P92" s="66"/>
@@ -26239,10 +26375,10 @@
     </row>
     <row r="93" spans="1:20" ht="15" customHeight="1">
       <c r="A93" s="69" t="s">
+        <v>724</v>
+      </c>
+      <c r="B93" s="69" t="s">
         <v>725</v>
-      </c>
-      <c r="B93" s="69" t="s">
-        <v>726</v>
       </c>
       <c r="C93" s="69" t="s">
         <v>97</v>
@@ -26276,11 +26412,11 @@
         <v>472</v>
       </c>
       <c r="L93" s="69" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="M93" s="69"/>
       <c r="N93" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O93" s="69" t="s">
         <v>216</v>
@@ -26293,10 +26429,10 @@
     </row>
     <row r="94" spans="1:20" ht="15" customHeight="1">
       <c r="A94" s="66" t="s">
+        <v>727</v>
+      </c>
+      <c r="B94" s="66" t="s">
         <v>728</v>
-      </c>
-      <c r="B94" s="66" t="s">
-        <v>729</v>
       </c>
       <c r="C94" s="66" t="s">
         <v>95</v>
@@ -26334,7 +26470,7 @@
       </c>
       <c r="M94" s="66"/>
       <c r="N94" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O94" s="66"/>
       <c r="P94" s="66"/>
@@ -26345,10 +26481,10 @@
     </row>
     <row r="95" spans="1:20" ht="15" customHeight="1">
       <c r="A95" s="69" t="s">
+        <v>729</v>
+      </c>
+      <c r="B95" s="69" t="s">
         <v>730</v>
-      </c>
-      <c r="B95" s="69" t="s">
-        <v>731</v>
       </c>
       <c r="C95" s="69" t="s">
         <v>95</v>
@@ -26382,11 +26518,11 @@
         <v>0</v>
       </c>
       <c r="L95" s="69" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="M95" s="69"/>
       <c r="N95" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O95" s="69"/>
       <c r="P95" s="69"/>
@@ -26397,10 +26533,10 @@
     </row>
     <row r="96" spans="1:20" ht="15" customHeight="1">
       <c r="A96" s="66" t="s">
+        <v>732</v>
+      </c>
+      <c r="B96" s="66" t="s">
         <v>733</v>
-      </c>
-      <c r="B96" s="66" t="s">
-        <v>734</v>
       </c>
       <c r="C96" s="66" t="s">
         <v>95</v>
@@ -26436,7 +26572,7 @@
       <c r="L96" s="66"/>
       <c r="M96" s="66"/>
       <c r="N96" s="66" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O96" s="66"/>
       <c r="P96" s="66"/>
@@ -26447,10 +26583,10 @@
     </row>
     <row r="97" spans="1:20" ht="15" customHeight="1">
       <c r="A97" s="69" t="s">
+        <v>734</v>
+      </c>
+      <c r="B97" s="69" t="s">
         <v>735</v>
-      </c>
-      <c r="B97" s="69" t="s">
-        <v>736</v>
       </c>
       <c r="C97" s="69" t="s">
         <v>95</v>
@@ -26488,7 +26624,7 @@
       </c>
       <c r="M97" s="69"/>
       <c r="N97" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O97" s="69"/>
       <c r="P97" s="69"/>
@@ -26499,10 +26635,10 @@
     </row>
     <row r="98" spans="1:20" ht="15" customHeight="1">
       <c r="A98" s="66" t="s">
+        <v>736</v>
+      </c>
+      <c r="B98" s="66" t="s">
         <v>737</v>
-      </c>
-      <c r="B98" s="66" t="s">
-        <v>738</v>
       </c>
       <c r="C98" s="66" t="s">
         <v>96</v>
@@ -26540,7 +26676,7 @@
       </c>
       <c r="M98" s="66"/>
       <c r="N98" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O98" s="66" t="s">
         <v>207</v>
@@ -26553,10 +26689,10 @@
     </row>
     <row r="99" spans="1:20" ht="15" customHeight="1">
       <c r="A99" s="69" t="s">
+        <v>738</v>
+      </c>
+      <c r="B99" s="69" t="s">
         <v>739</v>
-      </c>
-      <c r="B99" s="69" t="s">
-        <v>740</v>
       </c>
       <c r="C99" s="69" t="s">
         <v>96</v>
@@ -26594,7 +26730,7 @@
       </c>
       <c r="M99" s="69"/>
       <c r="N99" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O99" s="69" t="s">
         <v>207</v>
@@ -26607,10 +26743,10 @@
     </row>
     <row r="100" spans="1:20" ht="15" customHeight="1">
       <c r="A100" s="66" t="s">
+        <v>740</v>
+      </c>
+      <c r="B100" s="66" t="s">
         <v>741</v>
-      </c>
-      <c r="B100" s="66" t="s">
-        <v>742</v>
       </c>
       <c r="C100" s="66" t="s">
         <v>96</v>
@@ -26648,7 +26784,7 @@
       </c>
       <c r="M100" s="66"/>
       <c r="N100" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O100" s="66" t="s">
         <v>207</v>
@@ -26661,10 +26797,10 @@
     </row>
     <row r="101" spans="1:20" ht="15" customHeight="1">
       <c r="A101" s="69" t="s">
+        <v>742</v>
+      </c>
+      <c r="B101" s="69" t="s">
         <v>743</v>
-      </c>
-      <c r="B101" s="69" t="s">
-        <v>744</v>
       </c>
       <c r="C101" s="69" t="s">
         <v>96</v>
@@ -26702,7 +26838,7 @@
       </c>
       <c r="M101" s="69"/>
       <c r="N101" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O101" s="69" t="s">
         <v>207</v>
@@ -26715,10 +26851,10 @@
     </row>
     <row r="102" spans="1:20" ht="15" customHeight="1">
       <c r="A102" s="66" t="s">
+        <v>744</v>
+      </c>
+      <c r="B102" s="66" t="s">
         <v>745</v>
-      </c>
-      <c r="B102" s="66" t="s">
-        <v>746</v>
       </c>
       <c r="C102" s="66" t="s">
         <v>96</v>
@@ -26756,7 +26892,7 @@
       </c>
       <c r="M102" s="66"/>
       <c r="N102" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O102" s="66" t="s">
         <v>207</v>
@@ -26769,10 +26905,10 @@
     </row>
     <row r="103" spans="1:20" ht="15" customHeight="1">
       <c r="A103" s="69" t="s">
+        <v>746</v>
+      </c>
+      <c r="B103" s="69" t="s">
         <v>747</v>
-      </c>
-      <c r="B103" s="69" t="s">
-        <v>748</v>
       </c>
       <c r="C103" s="69" t="s">
         <v>96</v>
@@ -26810,7 +26946,7 @@
       </c>
       <c r="M103" s="69"/>
       <c r="N103" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O103" s="69" t="s">
         <v>207</v>
@@ -26823,10 +26959,10 @@
     </row>
     <row r="104" spans="1:20" ht="15" customHeight="1">
       <c r="A104" s="66" t="s">
+        <v>748</v>
+      </c>
+      <c r="B104" s="66" t="s">
         <v>749</v>
-      </c>
-      <c r="B104" s="66" t="s">
-        <v>750</v>
       </c>
       <c r="C104" s="66" t="s">
         <v>96</v>
@@ -26864,7 +27000,7 @@
       </c>
       <c r="M104" s="66"/>
       <c r="N104" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O104" s="66" t="s">
         <v>207</v>
@@ -26877,10 +27013,10 @@
     </row>
     <row r="105" spans="1:20" ht="15" customHeight="1">
       <c r="A105" s="69" t="s">
+        <v>750</v>
+      </c>
+      <c r="B105" s="69" t="s">
         <v>751</v>
-      </c>
-      <c r="B105" s="69" t="s">
-        <v>752</v>
       </c>
       <c r="C105" s="69" t="s">
         <v>96</v>
@@ -26918,7 +27054,7 @@
       </c>
       <c r="M105" s="69"/>
       <c r="N105" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O105" s="69" t="s">
         <v>207</v>
@@ -26931,10 +27067,10 @@
     </row>
     <row r="106" spans="1:20" ht="15" customHeight="1">
       <c r="A106" s="66" t="s">
+        <v>752</v>
+      </c>
+      <c r="B106" s="66" t="s">
         <v>753</v>
-      </c>
-      <c r="B106" s="66" t="s">
-        <v>754</v>
       </c>
       <c r="C106" s="66" t="s">
         <v>96</v>
@@ -26972,7 +27108,7 @@
       </c>
       <c r="M106" s="66"/>
       <c r="N106" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O106" s="66" t="s">
         <v>207</v>
@@ -26985,10 +27121,10 @@
     </row>
     <row r="107" spans="1:20" ht="15" customHeight="1">
       <c r="A107" s="69" t="s">
+        <v>754</v>
+      </c>
+      <c r="B107" s="69" t="s">
         <v>755</v>
-      </c>
-      <c r="B107" s="69" t="s">
-        <v>756</v>
       </c>
       <c r="C107" s="69" t="s">
         <v>96</v>
@@ -27026,7 +27162,7 @@
       </c>
       <c r="M107" s="69"/>
       <c r="N107" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O107" s="69" t="s">
         <v>207</v>
@@ -27039,10 +27175,10 @@
     </row>
     <row r="108" spans="1:20" ht="15" customHeight="1">
       <c r="A108" s="66" t="s">
+        <v>756</v>
+      </c>
+      <c r="B108" s="66" t="s">
         <v>757</v>
-      </c>
-      <c r="B108" s="66" t="s">
-        <v>758</v>
       </c>
       <c r="C108" s="66" t="s">
         <v>96</v>
@@ -27080,7 +27216,7 @@
       </c>
       <c r="M108" s="66"/>
       <c r="N108" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O108" s="66" t="s">
         <v>207</v>
@@ -27093,10 +27229,10 @@
     </row>
     <row r="109" spans="1:20" ht="15" customHeight="1">
       <c r="A109" s="69" t="s">
+        <v>758</v>
+      </c>
+      <c r="B109" s="69" t="s">
         <v>759</v>
-      </c>
-      <c r="B109" s="69" t="s">
-        <v>760</v>
       </c>
       <c r="C109" s="69" t="s">
         <v>96</v>
@@ -27134,7 +27270,7 @@
       </c>
       <c r="M109" s="69"/>
       <c r="N109" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O109" s="69" t="s">
         <v>207</v>
@@ -27147,10 +27283,10 @@
     </row>
     <row r="110" spans="1:20" ht="15" customHeight="1">
       <c r="A110" s="66" t="s">
+        <v>760</v>
+      </c>
+      <c r="B110" s="66" t="s">
         <v>761</v>
-      </c>
-      <c r="B110" s="66" t="s">
-        <v>762</v>
       </c>
       <c r="C110" s="66" t="s">
         <v>96</v>
@@ -27188,7 +27324,7 @@
       </c>
       <c r="M110" s="66"/>
       <c r="N110" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O110" s="66" t="s">
         <v>207</v>
@@ -27201,10 +27337,10 @@
     </row>
     <row r="111" spans="1:20" ht="15" customHeight="1">
       <c r="A111" s="69" t="s">
+        <v>762</v>
+      </c>
+      <c r="B111" s="69" t="s">
         <v>763</v>
-      </c>
-      <c r="B111" s="69" t="s">
-        <v>764</v>
       </c>
       <c r="C111" s="69" t="s">
         <v>96</v>
@@ -27242,7 +27378,7 @@
       </c>
       <c r="M111" s="69"/>
       <c r="N111" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O111" s="69" t="s">
         <v>207</v>
@@ -27255,10 +27391,10 @@
     </row>
     <row r="112" spans="1:20" ht="15" customHeight="1">
       <c r="A112" s="66" t="s">
+        <v>764</v>
+      </c>
+      <c r="B112" s="66" t="s">
         <v>765</v>
-      </c>
-      <c r="B112" s="66" t="s">
-        <v>766</v>
       </c>
       <c r="C112" s="66" t="s">
         <v>96</v>
@@ -27294,7 +27430,7 @@
       <c r="L112" s="66"/>
       <c r="M112" s="66"/>
       <c r="N112" s="66" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O112" s="66" t="s">
         <v>207</v>
@@ -27307,10 +27443,10 @@
     </row>
     <row r="113" spans="1:246" ht="15" customHeight="1">
       <c r="A113" s="69" t="s">
+        <v>766</v>
+      </c>
+      <c r="B113" s="69" t="s">
         <v>767</v>
-      </c>
-      <c r="B113" s="69" t="s">
-        <v>768</v>
       </c>
       <c r="C113" s="69" t="s">
         <v>96</v>
@@ -27348,7 +27484,7 @@
       </c>
       <c r="M113" s="69"/>
       <c r="N113" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O113" s="69" t="s">
         <v>207</v>
@@ -27361,10 +27497,10 @@
     </row>
     <row r="114" spans="1:246" ht="15" customHeight="1">
       <c r="A114" s="66" t="s">
+        <v>768</v>
+      </c>
+      <c r="B114" s="66" t="s">
         <v>769</v>
-      </c>
-      <c r="B114" s="66" t="s">
-        <v>770</v>
       </c>
       <c r="C114" s="66" t="s">
         <v>95</v>
@@ -27402,7 +27538,7 @@
       </c>
       <c r="M114" s="66"/>
       <c r="N114" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O114" s="66"/>
       <c r="P114" s="66"/>
@@ -27413,10 +27549,10 @@
     </row>
     <row r="115" spans="1:246" ht="30" customHeight="1">
       <c r="A115" s="69" t="s">
+        <v>770</v>
+      </c>
+      <c r="B115" s="69" t="s">
         <v>771</v>
-      </c>
-      <c r="B115" s="69" t="s">
-        <v>772</v>
       </c>
       <c r="C115" s="69" t="s">
         <v>95</v>
@@ -27450,11 +27586,11 @@
         <v>0</v>
       </c>
       <c r="L115" s="69" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="M115" s="69"/>
       <c r="N115" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O115" s="69"/>
       <c r="P115" s="77"/>
@@ -27465,10 +27601,10 @@
     </row>
     <row r="116" spans="1:246" ht="150" customHeight="1">
       <c r="A116" s="66" t="s">
+        <v>773</v>
+      </c>
+      <c r="B116" s="66" t="s">
         <v>774</v>
-      </c>
-      <c r="B116" s="66" t="s">
-        <v>775</v>
       </c>
       <c r="C116" s="66" t="s">
         <v>95</v>
@@ -27502,11 +27638,11 @@
         <v>0</v>
       </c>
       <c r="L116" s="66" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="M116" s="66"/>
       <c r="N116" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O116" s="66"/>
       <c r="P116" s="66"/>
@@ -27517,10 +27653,10 @@
     </row>
     <row r="117" spans="1:246" ht="15" customHeight="1">
       <c r="A117" s="69" t="s">
+        <v>776</v>
+      </c>
+      <c r="B117" s="69" t="s">
         <v>777</v>
-      </c>
-      <c r="B117" s="69" t="s">
-        <v>778</v>
       </c>
       <c r="C117" s="69" t="s">
         <v>95</v>
@@ -27558,7 +27694,7 @@
       </c>
       <c r="M117" s="69"/>
       <c r="N117" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O117" s="69"/>
       <c r="P117" s="69"/>
@@ -27569,10 +27705,10 @@
     </row>
     <row r="118" spans="1:246" ht="15" customHeight="1">
       <c r="A118" s="66" t="s">
+        <v>778</v>
+      </c>
+      <c r="B118" s="66" t="s">
         <v>779</v>
-      </c>
-      <c r="B118" s="66" t="s">
-        <v>780</v>
       </c>
       <c r="C118" s="66" t="s">
         <v>95</v>
@@ -27606,15 +27742,15 @@
         <v>2095.8000000000002</v>
       </c>
       <c r="L118" s="66" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="M118" s="66"/>
       <c r="N118" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O118" s="66"/>
       <c r="P118" s="66" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="Q118" s="66"/>
       <c r="R118" s="66"/>
@@ -27623,10 +27759,10 @@
     </row>
     <row r="119" spans="1:246" ht="15" customHeight="1">
       <c r="A119" s="69" t="s">
+        <v>782</v>
+      </c>
+      <c r="B119" s="69" t="s">
         <v>783</v>
-      </c>
-      <c r="B119" s="69" t="s">
-        <v>784</v>
       </c>
       <c r="C119" s="69" t="s">
         <v>95</v>
@@ -27664,7 +27800,7 @@
       </c>
       <c r="M119" s="69"/>
       <c r="N119" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O119" s="69"/>
       <c r="P119" s="69"/>
@@ -27675,10 +27811,10 @@
     </row>
     <row r="120" spans="1:246" ht="181.5" customHeight="1">
       <c r="A120" s="66" t="s">
+        <v>784</v>
+      </c>
+      <c r="B120" s="66" t="s">
         <v>785</v>
-      </c>
-      <c r="B120" s="66" t="s">
-        <v>786</v>
       </c>
       <c r="C120" s="66" t="s">
         <v>95</v>
@@ -27690,10 +27826,10 @@
         <v>699</v>
       </c>
       <c r="F120" s="67">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G120" s="67">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H120" s="66">
         <f t="shared" si="7"/>
@@ -27705,24 +27841,24 @@
       </c>
       <c r="J120" s="66">
         <f t="shared" si="5"/>
-        <v>16758.13333333332</v>
+        <v>18014.993333333317</v>
       </c>
       <c r="K120" s="66">
         <f t="shared" si="6"/>
-        <v>2513.719999999998</v>
+        <v>1256.859999999999</v>
       </c>
       <c r="L120" s="66" t="s">
-        <v>787</v>
+        <v>1113</v>
       </c>
       <c r="M120" s="66" t="s">
         <v>49</v>
       </c>
       <c r="N120" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O120" s="66"/>
       <c r="P120" s="66" t="s">
-        <v>788</v>
+        <v>1114</v>
       </c>
       <c r="Q120" s="66"/>
       <c r="R120" s="66"/>
@@ -27731,10 +27867,10 @@
     </row>
     <row r="121" spans="1:246" ht="15" customHeight="1">
       <c r="A121" s="69" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B121" s="69" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C121" s="69" t="s">
         <v>95</v>
@@ -27768,15 +27904,15 @@
         <v>0</v>
       </c>
       <c r="L121" s="69" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="M121" s="69"/>
       <c r="N121" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O121" s="69"/>
       <c r="P121" s="69" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="Q121" s="69"/>
       <c r="R121" s="69"/>
@@ -27785,10 +27921,10 @@
     </row>
     <row r="122" spans="1:246" ht="15" customHeight="1">
       <c r="A122" s="66" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B122" s="66" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="C122" s="66" t="s">
         <v>96</v>
@@ -27822,11 +27958,11 @@
         <v>4700</v>
       </c>
       <c r="L122" s="66" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="M122" s="66"/>
       <c r="N122" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O122" s="66"/>
       <c r="P122" s="66"/>
@@ -27837,10 +27973,10 @@
     </row>
     <row r="123" spans="1:246" s="72" customFormat="1" ht="75" customHeight="1">
       <c r="A123" s="78" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B123" s="78" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C123" s="78" t="s">
         <v>95</v>
@@ -27874,11 +28010,11 @@
         <v>0</v>
       </c>
       <c r="L123" s="78" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="M123" s="78"/>
       <c r="N123" s="78" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O123" s="78"/>
       <c r="P123" s="78"/>
@@ -28115,10 +28251,10 @@
     </row>
     <row r="124" spans="1:246" s="83" customFormat="1" ht="30" customHeight="1">
       <c r="A124" s="80" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="B124" s="80" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C124" s="80" t="s">
         <v>95</v>
@@ -28152,15 +28288,15 @@
         <v>0</v>
       </c>
       <c r="L124" s="80" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="M124" s="80"/>
       <c r="N124" s="80" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O124" s="80"/>
       <c r="P124" s="80" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="Q124" s="80"/>
       <c r="R124" s="80"/>
@@ -28395,10 +28531,10 @@
     </row>
     <row r="125" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A125" s="78" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B125" s="78" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="C125" s="78" t="s">
         <v>95</v>
@@ -28432,15 +28568,15 @@
         <v>0</v>
       </c>
       <c r="L125" s="78" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="M125" s="78"/>
       <c r="N125" s="78" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O125" s="78"/>
       <c r="P125" s="78" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="Q125" s="78"/>
       <c r="R125" s="78"/>
@@ -28675,10 +28811,10 @@
     </row>
     <row r="126" spans="1:246" ht="15" customHeight="1">
       <c r="A126" s="80" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B126" s="66" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C126" s="66" t="s">
         <v>96</v>
@@ -28712,14 +28848,14 @@
         <v>0</v>
       </c>
       <c r="L126" s="66" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="M126" s="66"/>
       <c r="N126" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O126" s="66" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="P126" s="66"/>
       <c r="Q126" s="66"/>
@@ -28729,10 +28865,10 @@
     </row>
     <row r="127" spans="1:246" ht="15" customHeight="1">
       <c r="A127" s="78" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="B127" s="69" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C127" s="69" t="s">
         <v>96</v>
@@ -28770,7 +28906,7 @@
       </c>
       <c r="M127" s="69"/>
       <c r="N127" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O127" s="69" t="s">
         <v>207</v>
@@ -28783,10 +28919,10 @@
     </row>
     <row r="128" spans="1:246" ht="15" customHeight="1">
       <c r="A128" s="80" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="B128" s="66" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C128" s="66" t="s">
         <v>95</v>
@@ -28798,10 +28934,10 @@
         <v>1650</v>
       </c>
       <c r="F128" s="81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" s="81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H128" s="80">
         <f t="shared" si="7"/>
@@ -28813,16 +28949,18 @@
       </c>
       <c r="J128" s="80">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="K128" s="80">
         <f t="shared" si="6"/>
-        <v>1155</v>
-      </c>
-      <c r="L128" s="66"/>
+        <v>0</v>
+      </c>
+      <c r="L128" s="66" t="s">
+        <v>1101</v>
+      </c>
       <c r="M128" s="66"/>
       <c r="N128" s="66" t="s">
-        <v>680</v>
+        <v>504</v>
       </c>
       <c r="O128" s="66"/>
       <c r="P128" s="66"/>
@@ -28833,10 +28971,10 @@
     </row>
     <row r="129" spans="1:20" ht="15" customHeight="1">
       <c r="A129" s="78" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B129" s="69" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C129" s="69" t="s">
         <v>95</v>
@@ -28870,11 +29008,11 @@
         <v>0</v>
       </c>
       <c r="L129" s="69" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="M129" s="69"/>
       <c r="N129" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O129" s="69"/>
       <c r="P129" s="69"/>
@@ -28885,10 +29023,10 @@
     </row>
     <row r="130" spans="1:20" ht="15" customHeight="1">
       <c r="A130" s="80" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="B130" s="66" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C130" s="66" t="s">
         <v>95</v>
@@ -28922,11 +29060,11 @@
         <v>0</v>
       </c>
       <c r="L130" s="66" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="M130" s="66"/>
       <c r="N130" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O130" s="66"/>
       <c r="P130" s="66"/>
@@ -28937,10 +29075,10 @@
     </row>
     <row r="131" spans="1:20" ht="15" customHeight="1">
       <c r="A131" s="78" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="B131" s="69" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="C131" s="69" t="s">
         <v>95</v>
@@ -28976,7 +29114,7 @@
       <c r="L131" s="69"/>
       <c r="M131" s="69"/>
       <c r="N131" s="69" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O131" s="69"/>
       <c r="P131" s="69"/>
@@ -28987,10 +29125,10 @@
     </row>
     <row r="132" spans="1:20" ht="15" customHeight="1">
       <c r="A132" s="80" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="B132" s="66" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="C132" s="66" t="s">
         <v>95</v>
@@ -29024,11 +29162,11 @@
         <v>0</v>
       </c>
       <c r="L132" s="66" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="M132" s="66"/>
       <c r="N132" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O132" s="66"/>
       <c r="P132" s="66"/>
@@ -29039,10 +29177,10 @@
     </row>
     <row r="133" spans="1:20" ht="15" customHeight="1">
       <c r="A133" s="78" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="B133" s="69" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="C133" s="69" t="s">
         <v>95</v>
@@ -29078,7 +29216,7 @@
       <c r="L133" s="69"/>
       <c r="M133" s="69"/>
       <c r="N133" s="69" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O133" s="69"/>
       <c r="P133" s="69"/>
@@ -29089,10 +29227,10 @@
     </row>
     <row r="134" spans="1:20" ht="15" customHeight="1">
       <c r="A134" s="80" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="B134" s="66" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="C134" s="66" t="s">
         <v>95</v>
@@ -29128,7 +29266,7 @@
       <c r="L134" s="66"/>
       <c r="M134" s="66"/>
       <c r="N134" s="66" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O134" s="66"/>
       <c r="P134" s="66"/>
@@ -29139,10 +29277,10 @@
     </row>
     <row r="135" spans="1:20" ht="15" customHeight="1">
       <c r="A135" s="78" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="B135" s="69" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C135" s="69" t="s">
         <v>95</v>
@@ -29176,11 +29314,11 @@
         <v>0</v>
       </c>
       <c r="L135" s="69" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="M135" s="69"/>
       <c r="N135" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O135" s="69"/>
       <c r="P135" s="69"/>
@@ -29191,10 +29329,10 @@
     </row>
     <row r="136" spans="1:20" ht="15" customHeight="1">
       <c r="A136" s="80" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="B136" s="66" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="C136" s="66" t="s">
         <v>95</v>
@@ -29228,15 +29366,15 @@
         <v>0</v>
       </c>
       <c r="L136" s="66" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="M136" s="66"/>
       <c r="N136" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O136" s="66"/>
       <c r="P136" s="66" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="Q136" s="66"/>
       <c r="R136" s="66"/>
@@ -29245,10 +29383,10 @@
     </row>
     <row r="137" spans="1:20" ht="15" customHeight="1">
       <c r="A137" s="78" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="B137" s="69" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="C137" s="69" t="s">
         <v>95</v>
@@ -29286,7 +29424,7 @@
       </c>
       <c r="M137" s="69"/>
       <c r="N137" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O137" s="69"/>
       <c r="P137" s="69"/>
@@ -29297,10 +29435,10 @@
     </row>
     <row r="138" spans="1:20" ht="15" customHeight="1">
       <c r="A138" s="80" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="B138" s="66" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="C138" s="66" t="s">
         <v>95</v>
@@ -29334,11 +29472,11 @@
         <v>0</v>
       </c>
       <c r="L138" s="66" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="M138" s="66"/>
       <c r="N138" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O138" s="66"/>
       <c r="P138" s="66"/>
@@ -29349,10 +29487,10 @@
     </row>
     <row r="139" spans="1:20" ht="15" customHeight="1">
       <c r="A139" s="78" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="B139" s="69" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C139" s="69" t="s">
         <v>95</v>
@@ -29390,7 +29528,7 @@
       </c>
       <c r="M139" s="69"/>
       <c r="N139" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O139" s="69"/>
       <c r="P139" s="69"/>
@@ -29401,10 +29539,10 @@
     </row>
     <row r="140" spans="1:20" ht="15" customHeight="1">
       <c r="A140" s="80" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="B140" s="66" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="C140" s="66" t="s">
         <v>95</v>
@@ -29438,11 +29576,11 @@
         <v>699</v>
       </c>
       <c r="L140" s="66" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="M140" s="66"/>
       <c r="N140" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O140" s="66"/>
       <c r="P140" s="66"/>
@@ -29453,10 +29591,10 @@
     </row>
     <row r="141" spans="1:20" ht="15" customHeight="1">
       <c r="A141" s="78" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B141" s="69" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="C141" s="69" t="s">
         <v>95</v>
@@ -29490,11 +29628,11 @@
         <v>0</v>
       </c>
       <c r="L141" s="69" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="M141" s="69"/>
       <c r="N141" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O141" s="69"/>
       <c r="P141" s="69"/>
@@ -29505,10 +29643,10 @@
     </row>
     <row r="142" spans="1:20" ht="15" customHeight="1">
       <c r="A142" s="66" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B142" s="66" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C142" s="66" t="s">
         <v>95</v>
@@ -29542,11 +29680,11 @@
         <v>0</v>
       </c>
       <c r="L142" s="66" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="M142" s="66"/>
       <c r="N142" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O142" s="66"/>
       <c r="P142" s="66"/>
@@ -29557,10 +29695,10 @@
     </row>
     <row r="143" spans="1:20" ht="15" customHeight="1">
       <c r="A143" s="69" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="B143" s="69" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="C143" s="69" t="s">
         <v>95</v>
@@ -29596,7 +29734,7 @@
       <c r="L143" s="69"/>
       <c r="M143" s="69"/>
       <c r="N143" s="69" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O143" s="69"/>
       <c r="P143" s="69"/>
@@ -29607,10 +29745,10 @@
     </row>
     <row r="144" spans="1:20" ht="15" customHeight="1">
       <c r="A144" s="66" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="B144" s="66" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="C144" s="66" t="s">
         <v>95</v>
@@ -29646,7 +29784,7 @@
       <c r="L144" s="66"/>
       <c r="M144" s="66"/>
       <c r="N144" s="66" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O144" s="66"/>
       <c r="P144" s="66"/>
@@ -29657,7 +29795,7 @@
     </row>
     <row r="145" spans="1:20" ht="15" customHeight="1">
       <c r="A145" s="69" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="B145" s="69" t="s">
         <v>302</v>
@@ -29698,7 +29836,7 @@
       </c>
       <c r="M145" s="69"/>
       <c r="N145" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O145" s="69"/>
       <c r="P145" s="69"/>
@@ -29709,10 +29847,10 @@
     </row>
     <row r="146" spans="1:20" ht="15" customHeight="1">
       <c r="A146" s="66" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B146" s="66" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C146" s="66" t="s">
         <v>95</v>
@@ -29746,15 +29884,15 @@
         <v>761</v>
       </c>
       <c r="L146" s="66" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="M146" s="66"/>
       <c r="N146" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O146" s="66"/>
       <c r="P146" s="66" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="Q146" s="66"/>
       <c r="R146" s="66"/>
@@ -29763,10 +29901,10 @@
     </row>
     <row r="147" spans="1:20" ht="63.75" customHeight="1">
       <c r="A147" s="69" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B147" s="69" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="C147" s="69" t="s">
         <v>95</v>
@@ -29778,10 +29916,10 @@
         <v>1200</v>
       </c>
       <c r="F147" s="79">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G147" s="79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H147" s="78">
         <f t="shared" si="8"/>
@@ -29793,22 +29931,22 @@
       </c>
       <c r="J147" s="78">
         <f t="shared" si="9"/>
-        <v>5033</v>
+        <v>5752</v>
       </c>
       <c r="K147" s="78">
         <f t="shared" si="10"/>
-        <v>2157</v>
+        <v>1438</v>
       </c>
       <c r="L147" s="69" t="s">
-        <v>863</v>
+        <v>1098</v>
       </c>
       <c r="M147" s="69"/>
       <c r="N147" s="69" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O147" s="69"/>
       <c r="P147" s="69" t="s">
-        <v>864</v>
+        <v>1099</v>
       </c>
       <c r="Q147" s="69"/>
       <c r="R147" s="69"/>
@@ -29817,10 +29955,10 @@
     </row>
     <row r="148" spans="1:20" ht="15" customHeight="1">
       <c r="A148" s="66" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="B148" s="66" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="C148" s="66" t="s">
         <v>95</v>
@@ -29854,11 +29992,11 @@
         <v>502</v>
       </c>
       <c r="L148" s="66" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="M148" s="66"/>
       <c r="N148" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O148" s="66"/>
       <c r="P148" s="66"/>
@@ -29869,10 +30007,10 @@
     </row>
     <row r="149" spans="1:20" ht="15" customHeight="1">
       <c r="A149" s="69" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="B149" s="69" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="C149" s="69" t="s">
         <v>95</v>
@@ -29906,11 +30044,11 @@
         <v>1024</v>
       </c>
       <c r="L149" s="69" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="M149" s="69"/>
       <c r="N149" s="69" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O149" s="69"/>
       <c r="P149" s="69"/>
@@ -29921,10 +30059,10 @@
     </row>
     <row r="150" spans="1:20" ht="15" customHeight="1">
       <c r="A150" s="66" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="B150" s="66" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="C150" s="66" t="s">
         <v>95</v>
@@ -29960,7 +30098,7 @@
       <c r="L150" s="66"/>
       <c r="M150" s="66"/>
       <c r="N150" s="66" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O150" s="66"/>
       <c r="P150" s="66"/>
@@ -29971,10 +30109,10 @@
     </row>
     <row r="151" spans="1:20" ht="15" customHeight="1">
       <c r="A151" s="69" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="B151" s="69" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C151" s="69" t="s">
         <v>96</v>
@@ -30008,17 +30146,17 @@
         <v>645</v>
       </c>
       <c r="L151" s="69" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="M151" s="69"/>
       <c r="N151" s="69" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O151" s="69" t="s">
         <v>216</v>
       </c>
       <c r="P151" s="69" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="Q151" s="69"/>
       <c r="R151" s="69"/>
@@ -30027,10 +30165,10 @@
     </row>
     <row r="152" spans="1:20" ht="15" customHeight="1">
       <c r="A152" s="66" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="B152" s="66" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="C152" s="66" t="s">
         <v>97</v>
@@ -30064,17 +30202,17 @@
         <v>590</v>
       </c>
       <c r="L152" s="66" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="M152" s="66"/>
       <c r="N152" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O152" s="66" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="P152" s="66" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="Q152" s="66"/>
       <c r="R152" s="66"/>
@@ -30083,10 +30221,10 @@
     </row>
     <row r="153" spans="1:20" ht="15" customHeight="1">
       <c r="A153" s="69" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="B153" s="69" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="C153" s="69" t="s">
         <v>95</v>
@@ -30120,15 +30258,15 @@
         <v>0</v>
       </c>
       <c r="L153" s="69" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="M153" s="69"/>
       <c r="N153" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O153" s="69"/>
       <c r="P153" s="69" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="Q153" s="69"/>
       <c r="R153" s="69"/>
@@ -30137,10 +30275,10 @@
     </row>
     <row r="154" spans="1:20" ht="15" customHeight="1">
       <c r="A154" s="66" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="B154" s="66" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="C154" s="66" t="s">
         <v>96</v>
@@ -30174,14 +30312,14 @@
         <v>1898</v>
       </c>
       <c r="L154" s="66" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="M154" s="66"/>
       <c r="N154" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O154" s="66" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="P154" s="66"/>
       <c r="Q154" s="66"/>
@@ -30191,10 +30329,10 @@
     </row>
     <row r="155" spans="1:20" ht="15" customHeight="1">
       <c r="A155" s="69" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="B155" s="69" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="C155" s="69" t="s">
         <v>96</v>
@@ -30230,10 +30368,10 @@
       <c r="L155" s="69"/>
       <c r="M155" s="69"/>
       <c r="N155" s="69" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O155" s="69" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="P155" s="69"/>
       <c r="Q155" s="69"/>
@@ -30243,10 +30381,10 @@
     </row>
     <row r="156" spans="1:20" ht="15" customHeight="1">
       <c r="A156" s="66" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="B156" s="66" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="C156" s="66" t="s">
         <v>96</v>
@@ -30280,14 +30418,14 @@
         <v>2850</v>
       </c>
       <c r="L156" s="66" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="M156" s="66"/>
       <c r="N156" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O156" s="66" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="P156" s="66"/>
       <c r="Q156" s="66"/>
@@ -30297,10 +30435,10 @@
     </row>
     <row r="157" spans="1:20" ht="15" customHeight="1">
       <c r="A157" s="69" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="B157" s="69" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="C157" s="69" t="s">
         <v>96</v>
@@ -30334,14 +30472,14 @@
         <v>1050</v>
       </c>
       <c r="L157" s="69" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="M157" s="69"/>
       <c r="N157" s="69" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O157" s="69" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="P157" s="69"/>
       <c r="Q157" s="69"/>
@@ -30351,10 +30489,10 @@
     </row>
     <row r="158" spans="1:20" ht="15" customHeight="1">
       <c r="A158" s="66" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="B158" s="66" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="C158" s="66" t="s">
         <v>96</v>
@@ -30388,14 +30526,14 @@
         <v>3356</v>
       </c>
       <c r="L158" s="66" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="M158" s="66"/>
       <c r="N158" s="66" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O158" s="66" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="P158" s="66"/>
       <c r="Q158" s="66"/>
@@ -30405,10 +30543,10 @@
     </row>
     <row r="159" spans="1:20" ht="15" customHeight="1">
       <c r="A159" s="69" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="B159" s="69" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="C159" s="69" t="s">
         <v>96</v>
@@ -30442,14 +30580,14 @@
         <v>2517</v>
       </c>
       <c r="L159" s="69" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="M159" s="69"/>
       <c r="N159" s="69" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O159" s="69" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="P159" s="69"/>
       <c r="Q159" s="69"/>
@@ -30459,10 +30597,10 @@
     </row>
     <row r="160" spans="1:20" ht="15" customHeight="1">
       <c r="A160" s="66" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="B160" s="66" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="C160" s="66" t="s">
         <v>95</v>
@@ -30500,7 +30638,7 @@
       </c>
       <c r="M160" s="66"/>
       <c r="N160" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O160" s="66"/>
       <c r="P160" s="66"/>
@@ -30511,10 +30649,10 @@
     </row>
     <row r="161" spans="1:20" ht="15" customHeight="1">
       <c r="A161" s="69" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="B161" s="69" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="C161" s="69" t="s">
         <v>95</v>
@@ -30552,7 +30690,7 @@
       </c>
       <c r="M161" s="69"/>
       <c r="N161" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O161" s="69"/>
       <c r="P161" s="69"/>
@@ -30563,10 +30701,10 @@
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1">
       <c r="A162" s="66" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="B162" s="66" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="C162" s="66" t="s">
         <v>95</v>
@@ -30604,7 +30742,7 @@
       </c>
       <c r="M162" s="66"/>
       <c r="N162" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O162" s="66"/>
       <c r="P162" s="66"/>
@@ -30615,10 +30753,10 @@
     </row>
     <row r="163" spans="1:20" ht="15" customHeight="1">
       <c r="A163" s="69" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="B163" s="69" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="C163" s="69" t="s">
         <v>95</v>
@@ -30654,7 +30792,7 @@
       <c r="L163" s="69"/>
       <c r="M163" s="69"/>
       <c r="N163" s="69" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O163" s="69"/>
       <c r="P163" s="69"/>
@@ -30665,10 +30803,10 @@
     </row>
     <row r="164" spans="1:20" ht="60" customHeight="1">
       <c r="A164" s="66" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="B164" s="66" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="C164" s="66" t="s">
         <v>95</v>
@@ -30702,15 +30840,15 @@
         <v>1013</v>
       </c>
       <c r="L164" s="66" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="M164" s="66"/>
       <c r="N164" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O164" s="66"/>
       <c r="P164" s="66" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="Q164" s="66"/>
       <c r="R164" s="66"/>
@@ -30719,10 +30857,10 @@
     </row>
     <row r="165" spans="1:20" ht="15" customHeight="1">
       <c r="A165" s="69" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="B165" s="69" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="C165" s="69" t="s">
         <v>95</v>
@@ -30760,11 +30898,11 @@
       </c>
       <c r="M165" s="69"/>
       <c r="N165" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O165" s="69"/>
       <c r="P165" s="69" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="Q165" s="69"/>
       <c r="R165" s="69"/>
@@ -30773,10 +30911,10 @@
     </row>
     <row r="166" spans="1:20" ht="15" customHeight="1">
       <c r="A166" s="66" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="B166" s="66" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="C166" s="66" t="s">
         <v>95</v>
@@ -30812,11 +30950,11 @@
       <c r="L166" s="66"/>
       <c r="M166" s="66"/>
       <c r="N166" s="66" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O166" s="66"/>
       <c r="P166" s="66" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="Q166" s="66"/>
       <c r="R166" s="66"/>
@@ -30825,10 +30963,10 @@
     </row>
     <row r="167" spans="1:20" ht="15" customHeight="1">
       <c r="A167" s="69" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="B167" s="69" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C167" s="69" t="s">
         <v>95</v>
@@ -30862,15 +31000,15 @@
         <v>2220</v>
       </c>
       <c r="L167" s="69" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="M167" s="69"/>
       <c r="N167" s="69" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O167" s="69"/>
       <c r="P167" s="69" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="Q167" s="69"/>
       <c r="R167" s="69"/>
@@ -30879,10 +31017,10 @@
     </row>
     <row r="168" spans="1:20" ht="15" customHeight="1">
       <c r="A168" s="66" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="B168" s="66" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="C168" s="66" t="s">
         <v>95</v>
@@ -30916,15 +31054,15 @@
         <v>1216</v>
       </c>
       <c r="L168" s="66" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="M168" s="66"/>
       <c r="N168" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O168" s="66"/>
       <c r="P168" s="66" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="Q168" s="66"/>
       <c r="R168" s="66"/>
@@ -30933,10 +31071,10 @@
     </row>
     <row r="169" spans="1:20" ht="15" customHeight="1">
       <c r="A169" s="69" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="B169" s="69" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="C169" s="69" t="s">
         <v>95</v>
@@ -30972,11 +31110,11 @@
       <c r="L169" s="69"/>
       <c r="M169" s="69"/>
       <c r="N169" s="69" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O169" s="69"/>
       <c r="P169" s="69" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="Q169" s="69"/>
       <c r="R169" s="69"/>
@@ -30985,10 +31123,10 @@
     </row>
     <row r="170" spans="1:20" ht="30" customHeight="1">
       <c r="A170" s="66" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="B170" s="66" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="C170" s="66" t="s">
         <v>95</v>
@@ -31022,15 +31160,15 @@
         <v>0</v>
       </c>
       <c r="L170" s="66" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="M170" s="66"/>
       <c r="N170" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O170" s="66"/>
       <c r="P170" s="66" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="Q170" s="66"/>
       <c r="R170" s="66"/>
@@ -31039,10 +31177,10 @@
     </row>
     <row r="171" spans="1:20" ht="31.5" customHeight="1">
       <c r="A171" s="69" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="B171" s="66" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="C171" s="69" t="s">
         <v>95</v>
@@ -31076,11 +31214,11 @@
         <v>0</v>
       </c>
       <c r="L171" s="69" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="M171" s="69"/>
       <c r="N171" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O171" s="69"/>
       <c r="P171" s="69"/>
@@ -31091,10 +31229,10 @@
     </row>
     <row r="172" spans="1:20" ht="15" customHeight="1">
       <c r="A172" s="66" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B172" s="66" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="C172" s="66" t="s">
         <v>95</v>
@@ -31128,11 +31266,11 @@
         <v>0</v>
       </c>
       <c r="L172" s="66" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="M172" s="66"/>
       <c r="N172" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O172" s="66"/>
       <c r="P172" s="66"/>
@@ -31143,10 +31281,10 @@
     </row>
     <row r="173" spans="1:20" ht="15" customHeight="1">
       <c r="A173" s="69" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="B173" s="69" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="C173" s="69" t="s">
         <v>95</v>
@@ -31184,7 +31322,7 @@
       </c>
       <c r="M173" s="69"/>
       <c r="N173" s="69" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O173" s="69"/>
       <c r="P173" s="69"/>
@@ -31195,10 +31333,10 @@
     </row>
     <row r="174" spans="1:20" ht="15" customHeight="1">
       <c r="A174" s="66" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="B174" s="66" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="C174" s="66" t="s">
         <v>95</v>
@@ -31232,11 +31370,11 @@
         <v>0</v>
       </c>
       <c r="L174" s="66" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="M174" s="66"/>
       <c r="N174" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O174" s="66"/>
       <c r="P174" s="66"/>
@@ -31247,10 +31385,10 @@
     </row>
     <row r="175" spans="1:20" ht="90" customHeight="1">
       <c r="A175" s="69" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="B175" s="69" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="C175" s="69" t="s">
         <v>95</v>
@@ -31284,15 +31422,15 @@
         <v>4189.5</v>
       </c>
       <c r="L175" s="69" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="M175" s="69"/>
       <c r="N175" s="69" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O175" s="69"/>
       <c r="P175" s="69" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="Q175" s="69"/>
       <c r="R175" s="69"/>
@@ -31301,10 +31439,10 @@
     </row>
     <row r="176" spans="1:20" ht="24" customHeight="1">
       <c r="A176" s="66" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="B176" s="66" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="C176" s="66" t="s">
         <v>95</v>
@@ -31338,11 +31476,11 @@
         <v>0</v>
       </c>
       <c r="L176" s="66" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="M176" s="66"/>
       <c r="N176" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O176" s="66"/>
       <c r="P176" s="66"/>
@@ -31353,10 +31491,10 @@
     </row>
     <row r="177" spans="1:20" ht="33.75" customHeight="1">
       <c r="A177" s="69" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="B177" s="69" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="C177" s="69" t="s">
         <v>95</v>
@@ -31390,15 +31528,15 @@
         <v>0</v>
       </c>
       <c r="L177" s="69" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="M177" s="69"/>
       <c r="N177" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O177" s="69"/>
       <c r="P177" s="69" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="Q177" s="69"/>
       <c r="R177" s="69"/>
@@ -31407,10 +31545,10 @@
     </row>
     <row r="178" spans="1:20" ht="15" customHeight="1">
       <c r="A178" s="66" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="B178" s="66" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="C178" s="66" t="s">
         <v>95</v>
@@ -31444,15 +31582,15 @@
         <v>0</v>
       </c>
       <c r="L178" s="66" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="M178" s="66"/>
       <c r="N178" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O178" s="66"/>
       <c r="P178" s="66" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="Q178" s="66"/>
       <c r="R178" s="66"/>
@@ -31461,10 +31599,10 @@
     </row>
     <row r="179" spans="1:20" ht="30" customHeight="1">
       <c r="A179" s="69" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="B179" s="69" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="C179" s="69" t="s">
         <v>95</v>
@@ -31498,15 +31636,15 @@
         <v>0</v>
       </c>
       <c r="L179" s="69" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="M179" s="69"/>
       <c r="N179" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O179" s="69"/>
       <c r="P179" s="69" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="Q179" s="69"/>
       <c r="R179" s="69"/>
@@ -31515,10 +31653,10 @@
     </row>
     <row r="180" spans="1:20" ht="33.75" customHeight="1">
       <c r="A180" s="66" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="B180" s="66" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="C180" s="66" t="s">
         <v>95</v>
@@ -31552,11 +31690,11 @@
         <v>0</v>
       </c>
       <c r="L180" s="66" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="M180" s="66"/>
       <c r="N180" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O180" s="66"/>
       <c r="P180" s="66"/>
@@ -31567,10 +31705,10 @@
     </row>
     <row r="181" spans="1:20" ht="15" customHeight="1">
       <c r="A181" s="69" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="B181" s="69" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="C181" s="69" t="s">
         <v>96</v>
@@ -31606,13 +31744,13 @@
       <c r="L181" s="69"/>
       <c r="M181" s="69"/>
       <c r="N181" s="69" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O181" s="69" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="P181" s="69" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Q181" s="69"/>
       <c r="R181" s="69"/>
@@ -31621,10 +31759,10 @@
     </row>
     <row r="182" spans="1:20" ht="15" customHeight="1">
       <c r="A182" s="66" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="B182" s="66" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="C182" s="66" t="s">
         <v>95</v>
@@ -31660,11 +31798,11 @@
       <c r="L182" s="66"/>
       <c r="M182" s="66"/>
       <c r="N182" s="66" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O182" s="66"/>
       <c r="P182" s="66" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="Q182" s="66"/>
       <c r="R182" s="66"/>
@@ -31673,10 +31811,10 @@
     </row>
     <row r="183" spans="1:20" ht="15" customHeight="1">
       <c r="A183" s="69" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="B183" s="69" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="C183" s="69" t="s">
         <v>95</v>
@@ -31711,7 +31849,7 @@
       <c r="L183" s="69"/>
       <c r="M183" s="69"/>
       <c r="N183" s="69" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O183" s="69"/>
       <c r="P183" s="69"/>
@@ -31722,10 +31860,10 @@
     </row>
     <row r="184" spans="1:20" ht="39.75" customHeight="1">
       <c r="A184" s="66" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="B184" s="66" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="C184" s="66" t="s">
         <v>95</v>
@@ -31737,10 +31875,10 @@
         <v>1380</v>
       </c>
       <c r="F184" s="81">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G184" s="81">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H184" s="80">
         <f t="shared" ref="H184:H226" si="12">F184+IF(LEN(G184)=0,0,G184)</f>
@@ -31752,18 +31890,18 @@
       </c>
       <c r="J184" s="80">
         <f t="shared" si="9"/>
-        <v>11583</v>
+        <v>12474</v>
       </c>
       <c r="K184" s="80">
         <f t="shared" si="10"/>
-        <v>6237</v>
+        <v>5346</v>
       </c>
       <c r="L184" s="66" t="s">
-        <v>984</v>
+        <v>1105</v>
       </c>
       <c r="M184" s="66"/>
       <c r="N184" s="66" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O184" s="66"/>
       <c r="P184" s="66"/>
@@ -31774,10 +31912,10 @@
     </row>
     <row r="185" spans="1:20" ht="15" customHeight="1">
       <c r="A185" s="69" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="B185" s="69" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="C185" s="69" t="s">
         <v>95</v>
@@ -31811,11 +31949,11 @@
         <v>0</v>
       </c>
       <c r="L185" s="69" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="M185" s="69"/>
       <c r="N185" s="69" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O185" s="69"/>
       <c r="P185" s="69"/>
@@ -31826,10 +31964,10 @@
     </row>
     <row r="186" spans="1:20" ht="15" customHeight="1">
       <c r="A186" s="66" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="B186" s="66" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C186" s="66" t="s">
         <v>95</v>
@@ -31865,7 +32003,7 @@
       <c r="L186" s="66"/>
       <c r="M186" s="66"/>
       <c r="N186" s="66" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O186" s="66"/>
       <c r="P186" s="66"/>
@@ -31876,10 +32014,10 @@
     </row>
     <row r="187" spans="1:20" ht="15" customHeight="1">
       <c r="A187" s="69" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="B187" s="69" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="C187" s="69" t="s">
         <v>95</v>
@@ -31915,7 +32053,7 @@
       <c r="L187" s="69"/>
       <c r="M187" s="69"/>
       <c r="N187" s="69" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O187" s="69"/>
       <c r="P187" s="69"/>
@@ -31926,10 +32064,10 @@
     </row>
     <row r="188" spans="1:20" ht="15" customHeight="1">
       <c r="A188" s="66" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="B188" s="66" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="C188" s="66" t="s">
         <v>95</v>
@@ -31965,7 +32103,7 @@
       <c r="L188" s="66"/>
       <c r="M188" s="66"/>
       <c r="N188" s="66" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O188" s="66"/>
       <c r="P188" s="66"/>
@@ -31976,10 +32114,10 @@
     </row>
     <row r="189" spans="1:20" ht="30" customHeight="1">
       <c r="A189" s="69" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="B189" s="66" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="C189" s="66" t="s">
         <v>95</v>
@@ -31991,10 +32129,10 @@
         <v>1380</v>
       </c>
       <c r="F189" s="79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G189" s="79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H189" s="78">
         <f t="shared" si="12"/>
@@ -32006,22 +32144,22 @@
       </c>
       <c r="J189" s="78">
         <f t="shared" si="9"/>
-        <v>2673</v>
+        <v>3564</v>
       </c>
       <c r="K189" s="78">
         <f t="shared" si="10"/>
-        <v>4455</v>
+        <v>3564</v>
       </c>
       <c r="L189" s="69" t="s">
-        <v>995</v>
+        <v>1124</v>
       </c>
       <c r="M189" s="69"/>
       <c r="N189" s="69" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O189" s="69"/>
       <c r="P189" s="69" t="s">
-        <v>996</v>
+        <v>1123</v>
       </c>
       <c r="Q189" s="69"/>
       <c r="R189" s="69"/>
@@ -32030,10 +32168,10 @@
     </row>
     <row r="190" spans="1:20" ht="15" customHeight="1">
       <c r="A190" s="66" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="B190" s="69" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="C190" s="69" t="s">
         <v>95</v>
@@ -32069,20 +32207,20 @@
       <c r="L190" s="66"/>
       <c r="M190" s="66"/>
       <c r="N190" s="61" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="P190" s="61" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="S190" s="61"/>
       <c r="T190" s="61"/>
     </row>
     <row r="191" spans="1:20" ht="30" customHeight="1">
       <c r="A191" s="69" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="B191" s="66" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="C191" s="66" t="s">
         <v>95</v>
@@ -32118,20 +32256,20 @@
       <c r="L191" s="69"/>
       <c r="M191" s="69"/>
       <c r="N191" s="61" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P191" s="61" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="S191" s="61"/>
       <c r="T191" s="61"/>
     </row>
     <row r="192" spans="1:20" ht="15" customHeight="1">
       <c r="A192" s="66" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="B192" s="69" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="C192" s="69" t="s">
         <v>95</v>
@@ -32143,10 +32281,10 @@
         <v>1250</v>
       </c>
       <c r="F192" s="81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G192" s="81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H192" s="80">
         <f t="shared" si="12"/>
@@ -32158,29 +32296,31 @@
       </c>
       <c r="J192" s="80">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>808</v>
       </c>
       <c r="K192" s="80">
         <f t="shared" si="10"/>
-        <v>2424</v>
-      </c>
-      <c r="L192" s="66"/>
+        <v>1616</v>
+      </c>
+      <c r="L192" s="66" t="s">
+        <v>1116</v>
+      </c>
       <c r="M192" s="66"/>
       <c r="N192" s="61" t="s">
-        <v>680</v>
+        <v>589</v>
       </c>
       <c r="P192" s="61" t="s">
-        <v>1006</v>
+        <v>1117</v>
       </c>
       <c r="S192" s="61"/>
       <c r="T192" s="61"/>
     </row>
     <row r="193" spans="1:20" ht="15" customHeight="1">
       <c r="A193" s="69" t="s">
-        <v>1007</v>
+        <v>998</v>
       </c>
       <c r="B193" s="66" t="s">
-        <v>1008</v>
+        <v>999</v>
       </c>
       <c r="C193" s="66" t="s">
         <v>95</v>
@@ -32216,20 +32356,20 @@
       <c r="L193" s="69"/>
       <c r="M193" s="69"/>
       <c r="N193" s="61" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P193" s="61" t="s">
-        <v>1009</v>
+        <v>1000</v>
       </c>
       <c r="S193" s="61"/>
       <c r="T193" s="61"/>
     </row>
     <row r="194" spans="1:20" ht="15" customHeight="1">
       <c r="A194" s="66" t="s">
-        <v>1010</v>
+        <v>1001</v>
       </c>
       <c r="B194" s="66" t="s">
-        <v>1011</v>
+        <v>1002</v>
       </c>
       <c r="C194" s="66" t="s">
         <v>95</v>
@@ -32265,20 +32405,20 @@
       <c r="L194" s="66"/>
       <c r="M194" s="66"/>
       <c r="N194" s="61" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P194" s="61" t="s">
-        <v>1012</v>
+        <v>1003</v>
       </c>
       <c r="S194" s="61"/>
       <c r="T194" s="61"/>
     </row>
     <row r="195" spans="1:20" ht="15" customHeight="1">
       <c r="A195" s="69" t="s">
-        <v>1013</v>
+        <v>1004</v>
       </c>
       <c r="B195" s="69" t="s">
-        <v>1014</v>
+        <v>1005</v>
       </c>
       <c r="C195" s="69" t="s">
         <v>95</v>
@@ -32312,24 +32452,24 @@
         <v>5467</v>
       </c>
       <c r="L195" s="69" t="s">
-        <v>1015</v>
+        <v>1006</v>
       </c>
       <c r="M195" s="69"/>
       <c r="N195" s="61" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P195" s="61" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
       <c r="S195" s="61"/>
       <c r="T195" s="61"/>
     </row>
     <row r="196" spans="1:20" ht="15" customHeight="1">
       <c r="A196" s="66" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
       <c r="B196" s="66" t="s">
-        <v>1018</v>
+        <v>1009</v>
       </c>
       <c r="C196" s="66" t="s">
         <v>95</v>
@@ -32341,10 +32481,10 @@
         <v>1250</v>
       </c>
       <c r="F196" s="81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G196" s="81">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H196" s="80">
         <f t="shared" si="12"/>
@@ -32356,29 +32496,31 @@
       </c>
       <c r="J196" s="80">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="K196" s="80">
         <f t="shared" si="14"/>
-        <v>4782</v>
-      </c>
-      <c r="L196" s="66"/>
+        <v>3985</v>
+      </c>
+      <c r="L196" s="66" t="s">
+        <v>1104</v>
+      </c>
       <c r="M196" s="66"/>
       <c r="N196" s="61" t="s">
-        <v>680</v>
+        <v>589</v>
       </c>
       <c r="P196" s="61" t="s">
-        <v>1019</v>
+        <v>1103</v>
       </c>
       <c r="S196" s="61"/>
       <c r="T196" s="61"/>
     </row>
     <row r="197" spans="1:20" ht="15" customHeight="1">
       <c r="A197" s="69" t="s">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B197" s="69" t="s">
-        <v>1021</v>
+        <v>1011</v>
       </c>
       <c r="C197" s="69" t="s">
         <v>95</v>
@@ -32414,20 +32556,20 @@
       <c r="L197" s="69"/>
       <c r="M197" s="69"/>
       <c r="N197" s="61" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P197" s="61" t="s">
-        <v>1022</v>
+        <v>1012</v>
       </c>
       <c r="S197" s="61"/>
       <c r="T197" s="61"/>
     </row>
     <row r="198" spans="1:20" ht="15" customHeight="1">
       <c r="A198" s="66" t="s">
-        <v>1023</v>
+        <v>1013</v>
       </c>
       <c r="B198" s="66" t="s">
-        <v>1024</v>
+        <v>1014</v>
       </c>
       <c r="C198" s="66" t="s">
         <v>95</v>
@@ -32463,20 +32605,20 @@
       <c r="L198" s="66"/>
       <c r="M198" s="66"/>
       <c r="N198" s="61" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P198" s="61" t="s">
-        <v>1025</v>
+        <v>1015</v>
       </c>
       <c r="S198" s="61"/>
       <c r="T198" s="61"/>
     </row>
     <row r="199" spans="1:20" ht="15" customHeight="1">
       <c r="A199" s="69" t="s">
-        <v>1026</v>
+        <v>1016</v>
       </c>
       <c r="B199" s="66" t="s">
-        <v>1027</v>
+        <v>1017</v>
       </c>
       <c r="C199" s="66" t="s">
         <v>95</v>
@@ -32512,20 +32654,20 @@
       <c r="L199" s="69"/>
       <c r="M199" s="69"/>
       <c r="N199" s="61" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P199" s="61" t="s">
-        <v>1028</v>
+        <v>1018</v>
       </c>
       <c r="S199" s="61"/>
       <c r="T199" s="61"/>
     </row>
     <row r="200" spans="1:20" ht="30" customHeight="1">
       <c r="A200" s="66" t="s">
-        <v>1029</v>
+        <v>1019</v>
       </c>
       <c r="B200" s="69" t="s">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="C200" s="69" t="s">
         <v>95</v>
@@ -32537,10 +32679,10 @@
         <v>1350</v>
       </c>
       <c r="F200" s="81">
+        <v>2</v>
+      </c>
+      <c r="G200" s="81">
         <v>3</v>
-      </c>
-      <c r="G200" s="81">
-        <v>2</v>
       </c>
       <c r="H200" s="80">
         <f t="shared" si="12"/>
@@ -32552,31 +32694,31 @@
       </c>
       <c r="J200" s="80">
         <f t="shared" si="13"/>
-        <v>2598</v>
+        <v>1732</v>
       </c>
       <c r="K200" s="80">
         <f t="shared" si="14"/>
-        <v>1732</v>
+        <v>2598</v>
       </c>
       <c r="L200" s="66" t="s">
-        <v>1031</v>
+        <v>1120</v>
       </c>
       <c r="M200" s="66"/>
       <c r="N200" s="61" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P200" s="61" t="s">
-        <v>1032</v>
+        <v>1121</v>
       </c>
       <c r="S200" s="61"/>
       <c r="T200" s="61"/>
     </row>
     <row r="201" spans="1:20" ht="15" customHeight="1">
       <c r="A201" s="69" t="s">
-        <v>1033</v>
+        <v>1021</v>
       </c>
       <c r="B201" s="66" t="s">
-        <v>1034</v>
+        <v>1022</v>
       </c>
       <c r="C201" s="66" t="s">
         <v>95</v>
@@ -32610,24 +32752,24 @@
         <v>724</v>
       </c>
       <c r="L201" s="69" t="s">
-        <v>1035</v>
+        <v>1023</v>
       </c>
       <c r="M201" s="69"/>
       <c r="N201" s="61" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P201" s="61" t="s">
-        <v>1036</v>
+        <v>1024</v>
       </c>
       <c r="S201" s="61"/>
       <c r="T201" s="61"/>
     </row>
     <row r="202" spans="1:20" ht="15" customHeight="1">
       <c r="A202" s="66" t="s">
-        <v>1037</v>
+        <v>1025</v>
       </c>
       <c r="B202" s="69" t="s">
-        <v>1038</v>
+        <v>1026</v>
       </c>
       <c r="C202" s="69" t="s">
         <v>95</v>
@@ -32663,20 +32805,20 @@
       <c r="L202" s="66"/>
       <c r="M202" s="66"/>
       <c r="N202" s="61" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P202" s="61" t="s">
-        <v>1039</v>
+        <v>1027</v>
       </c>
       <c r="S202" s="61"/>
       <c r="T202" s="61"/>
     </row>
     <row r="203" spans="1:20" ht="15" customHeight="1">
       <c r="A203" s="69" t="s">
-        <v>1040</v>
+        <v>1028</v>
       </c>
       <c r="B203" s="66" t="s">
-        <v>1041</v>
+        <v>1029</v>
       </c>
       <c r="C203" s="66" t="s">
         <v>95</v>
@@ -32710,24 +32852,24 @@
         <v>0</v>
       </c>
       <c r="L203" s="69" t="s">
-        <v>1042</v>
+        <v>1030</v>
       </c>
       <c r="M203" s="69"/>
       <c r="N203" s="61" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="P203" s="61" t="s">
-        <v>1043</v>
+        <v>1031</v>
       </c>
       <c r="S203" s="61"/>
       <c r="T203" s="61"/>
     </row>
     <row r="204" spans="1:20" ht="15" customHeight="1">
       <c r="A204" s="66" t="s">
-        <v>1044</v>
+        <v>1032</v>
       </c>
       <c r="B204" s="66" t="s">
-        <v>1045</v>
+        <v>1033</v>
       </c>
       <c r="C204" s="66" t="s">
         <v>95</v>
@@ -32761,24 +32903,24 @@
         <v>1760</v>
       </c>
       <c r="L204" s="66" t="s">
-        <v>1046</v>
+        <v>1034</v>
       </c>
       <c r="M204" s="66"/>
       <c r="N204" s="61" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P204" s="61" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
       <c r="S204" s="61"/>
       <c r="T204" s="61"/>
     </row>
     <row r="205" spans="1:20" ht="15" customHeight="1">
       <c r="A205" s="69" t="s">
-        <v>1048</v>
+        <v>1036</v>
       </c>
       <c r="B205" s="69" t="s">
-        <v>1049</v>
+        <v>1037</v>
       </c>
       <c r="C205" s="69" t="s">
         <v>95</v>
@@ -32812,24 +32954,24 @@
         <v>1522</v>
       </c>
       <c r="L205" s="69" t="s">
-        <v>1050</v>
+        <v>1038</v>
       </c>
       <c r="M205" s="69"/>
       <c r="N205" s="61" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P205" s="61" t="s">
-        <v>1051</v>
+        <v>1039</v>
       </c>
       <c r="S205" s="61"/>
       <c r="T205" s="61"/>
     </row>
     <row r="206" spans="1:20" ht="15" customHeight="1">
       <c r="A206" s="66" t="s">
-        <v>1052</v>
+        <v>1040</v>
       </c>
       <c r="B206" s="66" t="s">
-        <v>1053</v>
+        <v>1041</v>
       </c>
       <c r="C206" s="66" t="s">
         <v>95</v>
@@ -32865,20 +33007,20 @@
       <c r="L206" s="66"/>
       <c r="M206" s="66"/>
       <c r="N206" s="61" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P206" s="61" t="s">
-        <v>1054</v>
+        <v>1042</v>
       </c>
       <c r="S206" s="61"/>
       <c r="T206" s="61"/>
     </row>
     <row r="207" spans="1:20" ht="15" customHeight="1">
       <c r="A207" s="69" t="s">
-        <v>1055</v>
+        <v>1043</v>
       </c>
       <c r="B207" s="69" t="s">
-        <v>1056</v>
+        <v>1044</v>
       </c>
       <c r="C207" s="69" t="s">
         <v>95</v>
@@ -32912,24 +33054,24 @@
         <v>3312</v>
       </c>
       <c r="L207" s="69" t="s">
-        <v>1057</v>
+        <v>1045</v>
       </c>
       <c r="M207" s="69"/>
       <c r="N207" s="61" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P207" s="61" t="s">
-        <v>1058</v>
+        <v>1046</v>
       </c>
       <c r="S207" s="61"/>
       <c r="T207" s="61"/>
     </row>
     <row r="208" spans="1:20" ht="30" customHeight="1">
       <c r="A208" s="66" t="s">
-        <v>1059</v>
+        <v>1047</v>
       </c>
       <c r="B208" s="66" t="s">
-        <v>1060</v>
+        <v>1048</v>
       </c>
       <c r="C208" s="66" t="s">
         <v>95</v>
@@ -32965,20 +33107,20 @@
       <c r="L208" s="66"/>
       <c r="M208" s="66"/>
       <c r="N208" s="61" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P208" s="61" t="s">
-        <v>1061</v>
+        <v>1049</v>
       </c>
       <c r="S208" s="61"/>
       <c r="T208" s="61"/>
     </row>
     <row r="209" spans="1:20" ht="15" customHeight="1">
       <c r="A209" s="69" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="B209" s="66" t="s">
-        <v>1063</v>
+        <v>1051</v>
       </c>
       <c r="C209" s="66" t="s">
         <v>95</v>
@@ -32990,10 +33132,10 @@
         <v>1550</v>
       </c>
       <c r="F209" s="79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G209" s="79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H209" s="78">
         <f t="shared" si="12"/>
@@ -33005,29 +33147,31 @@
       </c>
       <c r="J209" s="78">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="K209" s="78">
         <f t="shared" si="14"/>
-        <v>1964</v>
-      </c>
-      <c r="L209" s="69"/>
+        <v>982</v>
+      </c>
+      <c r="L209" s="69" t="s">
+        <v>1119</v>
+      </c>
       <c r="M209" s="69"/>
       <c r="N209" s="61" t="s">
-        <v>680</v>
+        <v>589</v>
       </c>
       <c r="P209" s="61" t="s">
-        <v>1064</v>
+        <v>1118</v>
       </c>
       <c r="S209" s="61"/>
       <c r="T209" s="61"/>
     </row>
     <row r="210" spans="1:20" ht="15" customHeight="1">
       <c r="A210" s="66" t="s">
-        <v>1065</v>
+        <v>1052</v>
       </c>
       <c r="B210" s="69" t="s">
-        <v>1066</v>
+        <v>1053</v>
       </c>
       <c r="C210" s="69" t="s">
         <v>95</v>
@@ -33063,20 +33207,20 @@
       <c r="L210" s="66"/>
       <c r="M210" s="66"/>
       <c r="N210" s="61" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P210" s="61" t="s">
-        <v>1067</v>
+        <v>1054</v>
       </c>
       <c r="S210" s="61"/>
       <c r="T210" s="61"/>
     </row>
     <row r="211" spans="1:20" ht="15" customHeight="1">
       <c r="A211" s="69" t="s">
-        <v>1068</v>
+        <v>1055</v>
       </c>
       <c r="B211" s="66" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="C211" s="66" t="s">
         <v>95</v>
@@ -33112,17 +33256,17 @@
       <c r="L211" s="69"/>
       <c r="M211" s="69"/>
       <c r="N211" s="61" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P211" s="61" t="s">
-        <v>1069</v>
+        <v>1056</v>
       </c>
       <c r="S211" s="61"/>
       <c r="T211" s="61"/>
     </row>
     <row r="212" spans="1:20" ht="15" customHeight="1">
       <c r="A212" s="66" t="s">
-        <v>1070</v>
+        <v>1057</v>
       </c>
       <c r="B212" s="69"/>
       <c r="C212" s="69"/>
@@ -33157,7 +33301,7 @@
     </row>
     <row r="213" spans="1:20" ht="15" customHeight="1">
       <c r="A213" s="69" t="s">
-        <v>1071</v>
+        <v>1058</v>
       </c>
       <c r="B213" s="66"/>
       <c r="C213" s="66"/>
@@ -33192,7 +33336,7 @@
     </row>
     <row r="214" spans="1:20" ht="15" customHeight="1">
       <c r="A214" s="66" t="s">
-        <v>1072</v>
+        <v>1059</v>
       </c>
       <c r="B214" s="66"/>
       <c r="C214" s="66"/>
@@ -33227,7 +33371,7 @@
     </row>
     <row r="215" spans="1:20" ht="15" customHeight="1">
       <c r="A215" s="69" t="s">
-        <v>1073</v>
+        <v>1060</v>
       </c>
       <c r="B215" s="69"/>
       <c r="C215" s="69"/>
@@ -33262,7 +33406,7 @@
     </row>
     <row r="216" spans="1:20" ht="15" customHeight="1">
       <c r="A216" s="66" t="s">
-        <v>1074</v>
+        <v>1061</v>
       </c>
       <c r="B216" s="66"/>
       <c r="C216" s="66"/>
@@ -33297,7 +33441,7 @@
     </row>
     <row r="217" spans="1:20" ht="15" customHeight="1">
       <c r="A217" s="69" t="s">
-        <v>1075</v>
+        <v>1062</v>
       </c>
       <c r="B217" s="69"/>
       <c r="C217" s="69"/>
@@ -33332,7 +33476,7 @@
     </row>
     <row r="218" spans="1:20" ht="15" customHeight="1">
       <c r="A218" s="66" t="s">
-        <v>1076</v>
+        <v>1063</v>
       </c>
       <c r="B218" s="66"/>
       <c r="C218" s="66"/>
@@ -33367,7 +33511,7 @@
     </row>
     <row r="219" spans="1:20" ht="15" customHeight="1">
       <c r="A219" s="69" t="s">
-        <v>1077</v>
+        <v>1064</v>
       </c>
       <c r="B219" s="66"/>
       <c r="C219" s="66"/>
@@ -33402,7 +33546,7 @@
     </row>
     <row r="220" spans="1:20" ht="15" customHeight="1">
       <c r="A220" s="66" t="s">
-        <v>1078</v>
+        <v>1065</v>
       </c>
       <c r="B220" s="69"/>
       <c r="C220" s="69"/>
@@ -33437,7 +33581,7 @@
     </row>
     <row r="221" spans="1:20" ht="15" customHeight="1">
       <c r="A221" s="69" t="s">
-        <v>1079</v>
+        <v>1066</v>
       </c>
       <c r="B221" s="66"/>
       <c r="C221" s="66"/>
@@ -33472,7 +33616,7 @@
     </row>
     <row r="222" spans="1:20" ht="15" customHeight="1">
       <c r="A222" s="66" t="s">
-        <v>1080</v>
+        <v>1067</v>
       </c>
       <c r="B222" s="69"/>
       <c r="C222" s="69"/>
@@ -33507,7 +33651,7 @@
     </row>
     <row r="223" spans="1:20" ht="15" customHeight="1">
       <c r="A223" s="69" t="s">
-        <v>1081</v>
+        <v>1068</v>
       </c>
       <c r="B223" s="66"/>
       <c r="C223" s="66"/>
@@ -33542,7 +33686,7 @@
     </row>
     <row r="224" spans="1:20" ht="15" customHeight="1">
       <c r="A224" s="66" t="s">
-        <v>1082</v>
+        <v>1069</v>
       </c>
       <c r="B224" s="66"/>
       <c r="C224" s="66"/>
@@ -33577,7 +33721,7 @@
     </row>
     <row r="225" spans="1:20" ht="15" customHeight="1">
       <c r="A225" s="69" t="s">
-        <v>1083</v>
+        <v>1070</v>
       </c>
       <c r="B225" s="69"/>
       <c r="C225" s="69"/>
@@ -33612,7 +33756,7 @@
     </row>
     <row r="226" spans="1:20" ht="15" customHeight="1">
       <c r="A226" s="66" t="s">
-        <v>1084</v>
+        <v>1071</v>
       </c>
       <c r="B226" s="66"/>
       <c r="C226" s="66"/>
@@ -37527,7 +37671,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1">
       <c r="A1" s="95" t="s">
-        <v>1085</v>
+        <v>1072</v>
       </c>
       <c r="B1" s="95"/>
     </row>
@@ -37536,7 +37680,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1086</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1">
@@ -37568,25 +37712,25 @@
         <v>42</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>1087</v>
+        <v>1074</v>
       </c>
       <c r="C7" s="86" t="s">
-        <v>1088</v>
+        <v>1075</v>
       </c>
       <c r="D7" s="86" t="s">
-        <v>1089</v>
+        <v>1076</v>
       </c>
       <c r="E7" s="86" t="s">
-        <v>1090</v>
+        <v>1077</v>
       </c>
       <c r="F7" s="86" t="s">
-        <v>1091</v>
+        <v>1078</v>
       </c>
       <c r="G7" s="86" t="s">
-        <v>1092</v>
+        <v>1079</v>
       </c>
       <c r="H7" s="86" t="s">
-        <v>1093</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1">
@@ -37595,15 +37739,15 @@
       </c>
       <c r="B8" s="9">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A8,Purchases!$C:$C),0)</f>
-        <v>212783</v>
+        <v>212970</v>
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>151240</v>
+        <v>151302.33333333334</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>61543</v>
+        <v>61667.666666666657</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -37611,7 +37755,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>61543</v>
+        <v>61667.666666666657</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -37619,7 +37763,7 @@
       </c>
       <c r="H8" s="88">
         <f>F8-G8</f>
-        <v>43239.66</v>
+        <v>43364.32666666666</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -37632,11 +37776,11 @@
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>151240</v>
+        <v>151302.33333333334</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>57097</v>
+        <v>57034.666666666657</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -37644,7 +37788,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>57097</v>
+        <v>57034.666666666657</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -37652,7 +37796,7 @@
       </c>
       <c r="H9" s="89">
         <f>F9-G9</f>
-        <v>15457.669999999998</v>
+        <v>15395.336666666655</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -37665,11 +37809,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>151240</v>
+        <v>151302.33333333334</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-118640</v>
+        <v>-118702.33333333334</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -37677,7 +37821,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-118640</v>
+        <v>-118702.33333333334</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -37685,12 +37829,12 @@
       </c>
       <c r="H10" s="88">
         <f>F10-G10</f>
-        <v>-58697.33</v>
+        <v>-58759.663333333345</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="90" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="96" t="s">
-        <v>1094</v>
+        <v>1081</v>
       </c>
       <c r="B12" s="96"/>
       <c r="C12" s="96"/>
@@ -37703,13 +37847,13 @@
         <v>98</v>
       </c>
       <c r="B13" s="86" t="s">
-        <v>1095</v>
+        <v>1082</v>
       </c>
       <c r="C13" s="86" t="s">
-        <v>1096</v>
+        <v>1083</v>
       </c>
       <c r="D13" s="86" t="s">
-        <v>1097</v>
+        <v>1084</v>
       </c>
       <c r="E13" s="86" t="s">
         <v>99</v>
@@ -37723,7 +37867,7 @@
         <v>45952</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>51</v>
@@ -37741,7 +37885,7 @@
         <v>45952</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>51</v>
@@ -37795,7 +37939,7 @@
         <v>45970</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>50</v>
@@ -37813,7 +37957,7 @@
         <v>45970</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>50</v>
@@ -37831,7 +37975,7 @@
         <v>45973</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>50</v>
@@ -37849,7 +37993,7 @@
         <v>45973</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>49</v>
@@ -37867,7 +38011,7 @@
         <v>46058</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>51</v>
@@ -37903,7 +38047,7 @@
         <v>46059</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>49</v>
@@ -37939,7 +38083,7 @@
         <v>46093</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>50</v>
@@ -37957,7 +38101,7 @@
         <v>46093</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>51</v>
@@ -38040,7 +38184,7 @@
     </row>
     <row r="58" spans="2:2" ht="13.5" customHeight="1">
       <c r="B58" s="6" t="s">
-        <v>1099</v>
+        <v>1086</v>
       </c>
     </row>
   </sheetData>
@@ -38070,7 +38214,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13.5" customHeight="1">
       <c r="A1" s="93" t="s">
-        <v>1100</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="87" customFormat="1" ht="13.5" customHeight="1">
@@ -38078,22 +38222,22 @@
         <v>42</v>
       </c>
       <c r="B3" s="86" t="s">
-        <v>1101</v>
+        <v>1088</v>
       </c>
       <c r="C3" s="86" t="s">
-        <v>1086</v>
+        <v>1073</v>
       </c>
       <c r="D3" s="86" t="s">
-        <v>1102</v>
+        <v>1089</v>
       </c>
       <c r="E3" s="86" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
       <c r="F3" s="86" t="s">
-        <v>1104</v>
+        <v>1091</v>
       </c>
       <c r="G3" s="86" t="s">
-        <v>1105</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1">
@@ -38102,7 +38246,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>344007</v>
+        <v>350834</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -38110,11 +38254,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>137081.07739999998</v>
+        <v>139357.1992</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>206925.92260000002</v>
+        <v>211476.8008</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -38122,7 +38266,7 @@
       </c>
       <c r="G4" s="88">
         <f>E4+F4</f>
-        <v>69615.896600000007</v>
+        <v>74166.774799999985</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -38139,11 +38283,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>136998.84520000001</v>
+        <v>139273.60159999999</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-82374.845200000011</v>
+        <v>-84649.601599999995</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -38151,7 +38295,7 @@
       </c>
       <c r="G5" s="89">
         <f>E5+F5</f>
-        <v>-10787.803200000009</v>
+        <v>-13062.559599999993</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -38168,11 +38312,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>137081.07739999998</v>
+        <v>139357.1992</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-124551.07739999998</v>
+        <v>-126827.1992</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -38180,7 +38324,7 @@
       </c>
       <c r="G6" s="88">
         <f>E6+F6</f>
-        <v>-58828.093399999969</v>
+        <v>-61104.215199999991</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">
@@ -38190,27 +38334,27 @@
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>1106</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>1107</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>1108</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>1109</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>1110</v>
+        <v>1097</v>
       </c>
     </row>
   </sheetData>
